--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7697" uniqueCount="7580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7699" uniqueCount="7582">
   <si>
     <t>c</t>
   </si>
@@ -22767,6 +22767,12 @@
   </si>
   <si>
     <t>等级 {0}</t>
+  </si>
+  <si>
+    <t>任务</t>
+  </si>
+  <si>
+    <t>Task</t>
   </si>
 </sst>
 </file>
@@ -69500,10 +69506,16 @@
       </c>
     </row>
     <row r="3793" spans="3:6">
-      <c r="C3793"/>
-      <c r="D3793"/>
-      <c r="E3793"/>
-      <c r="F3793"/>
+      <c r="C3793" s="3">
+        <v>203753</v>
+      </c>
+      <c r="D3793" s="4"/>
+      <c r="E3793" s="1" t="s">
+        <v>7580</v>
+      </c>
+      <c r="F3793" s="6" t="s">
+        <v>7581</v>
+      </c>
     </row>
     <row r="3794" spans="3:6">
       <c r="C3794"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7681" uniqueCount="7565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7683" uniqueCount="7566">
   <si>
     <t>c</t>
   </si>
@@ -22722,6 +22722,9 @@
   </si>
   <si>
     <t>System Task</t>
+  </si>
+  <si>
+    <t>学习技能</t>
   </si>
 </sst>
 </file>
@@ -69359,10 +69362,16 @@
       </c>
     </row>
     <row r="3785" spans="3:6">
-      <c r="C3785"/>
+      <c r="C3785" s="3">
+        <v>203756</v>
+      </c>
       <c r="D3785"/>
-      <c r="E3785"/>
-      <c r="F3785"/>
+      <c r="E3785" s="1" t="s">
+        <v>7565</v>
+      </c>
+      <c r="F3785" s="6" t="s">
+        <v>3559</v>
+      </c>
     </row>
     <row r="3786" spans="3:6">
       <c r="C3786"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7683" uniqueCount="7566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7685" uniqueCount="7568">
   <si>
     <t>c</t>
   </si>
@@ -22725,6 +22725,12 @@
   </si>
   <si>
     <t>学习技能</t>
+  </si>
+  <si>
+    <t>任务描述</t>
+  </si>
+  <si>
+    <t>Task Description</t>
   </si>
 </sst>
 </file>
@@ -69374,10 +69380,16 @@
       </c>
     </row>
     <row r="3786" spans="3:6">
-      <c r="C3786"/>
+      <c r="C3786" s="3">
+        <v>203757</v>
+      </c>
       <c r="D3786"/>
-      <c r="E3786"/>
-      <c r="F3786"/>
+      <c r="E3786" s="1" t="s">
+        <v>7566</v>
+      </c>
+      <c r="F3786" s="6" t="s">
+        <v>7567</v>
+      </c>
     </row>
     <row r="3787" spans="3:6">
       <c r="C3787"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -3719,7 +3719,7 @@
     <t>成就点数：</t>
   </si>
   <si>
-    <t>Achievement Points:</t>
+    <t>Achievement Points：</t>
   </si>
   <si>
     <t>成就奖励</t>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15810" windowHeight="9810"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="MulLanguageProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7693" uniqueCount="7575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7697" uniqueCount="7579">
   <si>
     <t>c</t>
   </si>
@@ -22752,6 +22752,18 @@
   </si>
   <si>
     <t>Pet achievement</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>藏宝图</t>
+  </si>
+  <si>
+    <t>Treasure Map</t>
   </si>
 </sst>
 </file>
@@ -69461,16 +69473,28 @@
       </c>
     </row>
     <row r="3791" spans="3:6">
-      <c r="C3791"/>
-      <c r="D3791"/>
-      <c r="E3791"/>
-      <c r="F3791"/>
+      <c r="C3791" s="3">
+        <v>203768</v>
+      </c>
+      <c r="D3791" s="4"/>
+      <c r="E3791" s="1" t="s">
+        <v>7575</v>
+      </c>
+      <c r="F3791" s="6" t="s">
+        <v>7576</v>
+      </c>
     </row>
     <row r="3792" spans="3:6">
-      <c r="C3792"/>
-      <c r="D3792"/>
-      <c r="E3792"/>
-      <c r="F3792"/>
+      <c r="C3792" s="3">
+        <v>203769</v>
+      </c>
+      <c r="D3792" s="4"/>
+      <c r="E3792" s="1" t="s">
+        <v>7577</v>
+      </c>
+      <c r="F3792" s="6" t="s">
+        <v>7578</v>
+      </c>
     </row>
     <row r="3793" spans="3:6">
       <c r="C3793"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7795" uniqueCount="7670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7799" uniqueCount="7674">
   <si>
     <t>c</t>
   </si>
@@ -9983,6 +9983,12 @@
     <t>Memory footprint</t>
   </si>
   <si>
+    <t>无法移动</t>
+  </si>
+  <si>
+    <t>Unable to move</t>
+  </si>
+  <si>
     <t>自动一键出售</t>
   </si>
   <si>
@@ -17151,6 +17157,12 @@
   </si>
   <si>
     <t>{0} h</t>
+  </si>
+  <si>
+    <t>小时</t>
+  </si>
+  <si>
+    <t>h</t>
   </si>
   <si>
     <t>当前阶段: {0}</t>
@@ -24047,7 +24059,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:F3991"/>
+  <dimension ref="C2:F3993"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -44039,7 +44051,7 @@
         <v>3346</v>
       </c>
       <c r="F1647" s="6" t="s">
-        <v>1072</v>
+        <v>3347</v>
       </c>
     </row>
     <row r="1648" spans="3:6">
@@ -44048,10 +44060,10 @@
       </c>
       <c r="D1648" s="4"/>
       <c r="E1648" s="1" t="s">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="F1648" s="6" t="s">
-        <v>3348</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="1649" spans="3:6">
@@ -44987,7 +44999,7 @@
         <v>3503</v>
       </c>
       <c r="F1726" s="6" t="s">
-        <v>3478</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="1727" spans="3:6">
@@ -44996,10 +45008,10 @@
       </c>
       <c r="D1727" s="4"/>
       <c r="E1727" s="1" t="s">
-        <v>3504</v>
+        <v>3505</v>
       </c>
       <c r="F1727" s="6" t="s">
-        <v>3505</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="1728" spans="3:6">
@@ -45395,7 +45407,7 @@
         <v>3570</v>
       </c>
       <c r="F1760" s="6" t="s">
-        <v>1097</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="1761" spans="3:6">
@@ -45404,10 +45416,10 @@
       </c>
       <c r="D1761" s="4"/>
       <c r="E1761" s="1" t="s">
-        <v>3571</v>
+        <v>3572</v>
       </c>
       <c r="F1761" s="6" t="s">
-        <v>3572</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="1762" spans="3:6">
@@ -45419,7 +45431,7 @@
         <v>3573</v>
       </c>
       <c r="F1762" s="6" t="s">
-        <v>1748</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="1763" spans="3:6">
@@ -45428,10 +45440,10 @@
       </c>
       <c r="D1763" s="4"/>
       <c r="E1763" s="1" t="s">
-        <v>3574</v>
+        <v>3575</v>
       </c>
       <c r="F1763" s="6" t="s">
-        <v>2917</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1764" spans="3:6">
@@ -45440,10 +45452,10 @@
       </c>
       <c r="D1764" s="4"/>
       <c r="E1764" s="1" t="s">
-        <v>3575</v>
+        <v>3576</v>
       </c>
       <c r="F1764" s="6" t="s">
-        <v>807</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="1765" spans="3:6">
@@ -45452,10 +45464,10 @@
       </c>
       <c r="D1765" s="4"/>
       <c r="E1765" s="1" t="s">
-        <v>3576</v>
+        <v>3577</v>
       </c>
       <c r="F1765" s="6" t="s">
-        <v>3577</v>
+        <v>807</v>
       </c>
     </row>
     <row r="1766" spans="3:6">
@@ -46091,7 +46103,7 @@
         <v>3682</v>
       </c>
       <c r="F1818" s="6" t="s">
-        <v>3681</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="1819" spans="3:6">
@@ -46100,10 +46112,10 @@
       </c>
       <c r="D1819" s="4"/>
       <c r="E1819" s="1" t="s">
+        <v>3684</v>
+      </c>
+      <c r="F1819" s="6" t="s">
         <v>3683</v>
-      </c>
-      <c r="F1819" s="6" t="s">
-        <v>3684</v>
       </c>
     </row>
     <row r="1820" spans="3:6">
@@ -47471,7 +47483,7 @@
         <v>3911</v>
       </c>
       <c r="F1933" s="6" t="s">
-        <v>3688</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="1934" spans="3:6">
@@ -47480,10 +47492,10 @@
       </c>
       <c r="D1934" s="4"/>
       <c r="E1934" s="1" t="s">
-        <v>3912</v>
+        <v>3913</v>
       </c>
       <c r="F1934" s="6" t="s">
-        <v>3913</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="1935" spans="3:6">
@@ -48575,7 +48587,7 @@
         <v>4094</v>
       </c>
       <c r="F2025" s="6" t="s">
-        <v>3195</v>
+        <v>4095</v>
       </c>
     </row>
     <row r="2026" spans="3:6">
@@ -48584,10 +48596,10 @@
       </c>
       <c r="D2026" s="4"/>
       <c r="E2026" s="1" t="s">
-        <v>4095</v>
+        <v>4096</v>
       </c>
       <c r="F2026" s="6" t="s">
-        <v>4096</v>
+        <v>3195</v>
       </c>
     </row>
     <row r="2027" spans="3:6">
@@ -49703,7 +49715,7 @@
         <v>4281</v>
       </c>
       <c r="F2119" s="6" t="s">
-        <v>3432</v>
+        <v>4282</v>
       </c>
     </row>
     <row r="2120" spans="3:6">
@@ -49712,10 +49724,10 @@
       </c>
       <c r="D2120" s="4"/>
       <c r="E2120" s="1" t="s">
-        <v>4282</v>
+        <v>4283</v>
       </c>
       <c r="F2120" s="6" t="s">
-        <v>4283</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="2121" spans="3:6">
@@ -49907,7 +49919,7 @@
         <v>4314</v>
       </c>
       <c r="F2136" s="6" t="s">
-        <v>1218</v>
+        <v>4315</v>
       </c>
     </row>
     <row r="2137" spans="3:6">
@@ -49916,10 +49928,10 @@
       </c>
       <c r="D2137" s="4"/>
       <c r="E2137" s="1" t="s">
-        <v>4315</v>
+        <v>4316</v>
       </c>
       <c r="F2137" s="6" t="s">
-        <v>4316</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="2138" spans="3:6">
@@ -51947,7 +51959,7 @@
         <v>4653</v>
       </c>
       <c r="F2306" s="6" t="s">
-        <v>1036</v>
+        <v>4654</v>
       </c>
     </row>
     <row r="2307" spans="3:6">
@@ -51956,10 +51968,10 @@
       </c>
       <c r="D2307" s="4"/>
       <c r="E2307" s="1" t="s">
-        <v>4654</v>
+        <v>4655</v>
       </c>
       <c r="F2307" s="6" t="s">
-        <v>4655</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="2308" spans="3:6">
@@ -52187,7 +52199,7 @@
         <v>4692</v>
       </c>
       <c r="F2326" s="6" t="s">
-        <v>1887</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="2327" spans="3:6">
@@ -52196,10 +52208,10 @@
       </c>
       <c r="D2327" s="4"/>
       <c r="E2327" s="1" t="s">
-        <v>4693</v>
+        <v>4694</v>
       </c>
       <c r="F2327" s="6" t="s">
-        <v>4694</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="2328" spans="3:6">
@@ -52391,7 +52403,7 @@
         <v>4725</v>
       </c>
       <c r="F2343" s="6" t="s">
-        <v>4722</v>
+        <v>4726</v>
       </c>
     </row>
     <row r="2344" spans="3:6">
@@ -52400,10 +52412,10 @@
       </c>
       <c r="D2344" s="4"/>
       <c r="E2344" s="1" t="s">
-        <v>4726</v>
+        <v>4727</v>
       </c>
       <c r="F2344" s="6" t="s">
-        <v>4727</v>
+        <v>4724</v>
       </c>
     </row>
     <row r="2345" spans="3:6">
@@ -52811,7 +52823,7 @@
         <v>4794</v>
       </c>
       <c r="F2378" s="6" t="s">
-        <v>3175</v>
+        <v>4795</v>
       </c>
     </row>
     <row r="2379" spans="3:6">
@@ -52820,10 +52832,10 @@
       </c>
       <c r="D2379" s="4"/>
       <c r="E2379" s="1" t="s">
-        <v>4795</v>
+        <v>4796</v>
       </c>
       <c r="F2379" s="6" t="s">
-        <v>4796</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="2380" spans="3:6">
@@ -57779,7 +57791,7 @@
         <v>5621</v>
       </c>
       <c r="F2792" s="6" t="s">
-        <v>41</v>
+        <v>5622</v>
       </c>
     </row>
     <row r="2793" spans="3:6">
@@ -57788,10 +57800,10 @@
       </c>
       <c r="D2793" s="4"/>
       <c r="E2793" s="1" t="s">
-        <v>5622</v>
+        <v>5623</v>
       </c>
       <c r="F2793" s="6" t="s">
-        <v>5623</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2794" spans="3:6">
@@ -57827,7 +57839,7 @@
         <v>5628</v>
       </c>
       <c r="F2796" s="6" t="s">
-        <v>47</v>
+        <v>5629</v>
       </c>
     </row>
     <row r="2797" spans="3:6">
@@ -57836,10 +57848,10 @@
       </c>
       <c r="D2797" s="4"/>
       <c r="E2797" s="1" t="s">
-        <v>5629</v>
+        <v>5630</v>
       </c>
       <c r="F2797" s="6" t="s">
-        <v>5630</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2798" spans="3:6">
@@ -58019,7 +58031,7 @@
         <v>5659</v>
       </c>
       <c r="F2812" s="6" t="s">
-        <v>4988</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="2813" spans="3:6">
@@ -58028,10 +58040,10 @@
       </c>
       <c r="D2813" s="4"/>
       <c r="E2813" s="1" t="s">
-        <v>5660</v>
+        <v>5661</v>
       </c>
       <c r="F2813" s="6" t="s">
-        <v>5661</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="2814" spans="3:6">
@@ -58379,7 +58391,7 @@
         <v>5718</v>
       </c>
       <c r="F2842" s="6" t="s">
-        <v>5650</v>
+        <v>5719</v>
       </c>
     </row>
     <row r="2843" spans="3:6">
@@ -58388,10 +58400,10 @@
       </c>
       <c r="D2843" s="4"/>
       <c r="E2843" s="1" t="s">
-        <v>5719</v>
+        <v>5720</v>
       </c>
       <c r="F2843" s="6" t="s">
-        <v>5720</v>
+        <v>5721</v>
       </c>
     </row>
     <row r="2844" spans="3:6">
@@ -58400,10 +58412,10 @@
       </c>
       <c r="D2844" s="4"/>
       <c r="E2844" s="1" t="s">
-        <v>5721</v>
+        <v>5722</v>
       </c>
       <c r="F2844" s="6" t="s">
-        <v>5722</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="2845" spans="3:6">
@@ -58415,7 +58427,7 @@
         <v>5723</v>
       </c>
       <c r="F2845" s="6" t="s">
-        <v>4988</v>
+        <v>5724</v>
       </c>
     </row>
     <row r="2846" spans="3:6">
@@ -58424,10 +58436,10 @@
       </c>
       <c r="D2846" s="4"/>
       <c r="E2846" s="1" t="s">
-        <v>5724</v>
+        <v>5725</v>
       </c>
       <c r="F2846" s="6" t="s">
-        <v>5725</v>
+        <v>5726</v>
       </c>
     </row>
     <row r="2847" spans="3:6">
@@ -58436,10 +58448,10 @@
       </c>
       <c r="D2847" s="4"/>
       <c r="E2847" s="1" t="s">
-        <v>5726</v>
+        <v>5727</v>
       </c>
       <c r="F2847" s="6" t="s">
-        <v>2234</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="2848" spans="3:6">
@@ -58448,10 +58460,10 @@
       </c>
       <c r="D2848" s="4"/>
       <c r="E2848" s="1" t="s">
-        <v>5727</v>
+        <v>5728</v>
       </c>
       <c r="F2848" s="6" t="s">
-        <v>5728</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="2849" spans="3:6">
@@ -58460,10 +58472,10 @@
       </c>
       <c r="D2849" s="4"/>
       <c r="E2849" s="1" t="s">
-        <v>5729</v>
+        <v>5730</v>
       </c>
       <c r="F2849" s="6" t="s">
-        <v>5730</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="2850" spans="3:6">
@@ -58547,7 +58559,7 @@
         <v>5743</v>
       </c>
       <c r="F2856" s="6" t="s">
-        <v>4912</v>
+        <v>5744</v>
       </c>
     </row>
     <row r="2857" spans="3:6">
@@ -58556,10 +58568,10 @@
       </c>
       <c r="D2857" s="4"/>
       <c r="E2857" s="1" t="s">
-        <v>5744</v>
+        <v>5745</v>
       </c>
       <c r="F2857" s="6" t="s">
-        <v>5745</v>
+        <v>5746</v>
       </c>
     </row>
     <row r="2858" spans="3:6">
@@ -58568,10 +58580,10 @@
       </c>
       <c r="D2858" s="4"/>
       <c r="E2858" s="1" t="s">
-        <v>5746</v>
+        <v>5747</v>
       </c>
       <c r="F2858" s="6" t="s">
-        <v>5747</v>
+        <v>4914</v>
       </c>
     </row>
     <row r="2859" spans="3:6">
@@ -58679,7 +58691,7 @@
         <v>5764</v>
       </c>
       <c r="F2867" s="6" t="s">
-        <v>1558</v>
+        <v>5765</v>
       </c>
     </row>
     <row r="2868" spans="3:6">
@@ -58688,10 +58700,10 @@
       </c>
       <c r="D2868" s="4"/>
       <c r="E2868" s="1" t="s">
-        <v>5765</v>
+        <v>5766</v>
       </c>
       <c r="F2868" s="6" t="s">
-        <v>5766</v>
+        <v>5767</v>
       </c>
     </row>
     <row r="2869" spans="3:6">
@@ -58700,10 +58712,10 @@
       </c>
       <c r="D2869" s="4"/>
       <c r="E2869" s="1" t="s">
-        <v>5767</v>
+        <v>5768</v>
       </c>
       <c r="F2869" s="6" t="s">
-        <v>5768</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="2870" spans="3:6">
@@ -59219,7 +59231,7 @@
         <v>5853</v>
       </c>
       <c r="F2912" s="6" t="s">
-        <v>4765</v>
+        <v>5854</v>
       </c>
     </row>
     <row r="2913" spans="3:6">
@@ -59228,10 +59240,10 @@
       </c>
       <c r="D2913" s="4"/>
       <c r="E2913" s="1" t="s">
-        <v>5854</v>
+        <v>5855</v>
       </c>
       <c r="F2913" s="6" t="s">
-        <v>5855</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="2914" spans="3:6">
@@ -59240,10 +59252,10 @@
       </c>
       <c r="D2914" s="4"/>
       <c r="E2914" s="1" t="s">
-        <v>5856</v>
+        <v>5857</v>
       </c>
       <c r="F2914" s="6" t="s">
-        <v>5857</v>
+        <v>4767</v>
       </c>
     </row>
     <row r="2915" spans="3:6">
@@ -59675,7 +59687,7 @@
         <v>5928</v>
       </c>
       <c r="F2950" s="6" t="s">
-        <v>5044</v>
+        <v>5929</v>
       </c>
     </row>
     <row r="2951" spans="3:6">
@@ -59684,10 +59696,10 @@
       </c>
       <c r="D2951" s="4"/>
       <c r="E2951" s="1" t="s">
-        <v>5929</v>
+        <v>5930</v>
       </c>
       <c r="F2951" s="6" t="s">
-        <v>5930</v>
+        <v>5931</v>
       </c>
     </row>
     <row r="2952" spans="3:6">
@@ -59696,10 +59708,10 @@
       </c>
       <c r="D2952" s="4"/>
       <c r="E2952" s="1" t="s">
-        <v>5931</v>
+        <v>5932</v>
       </c>
       <c r="F2952" s="6" t="s">
-        <v>5932</v>
+        <v>5046</v>
       </c>
     </row>
     <row r="2953" spans="3:6">
@@ -59855,7 +59867,7 @@
         <v>5957</v>
       </c>
       <c r="F2965" s="6" t="s">
-        <v>5852</v>
+        <v>5958</v>
       </c>
     </row>
     <row r="2966" spans="3:6">
@@ -59864,10 +59876,10 @@
       </c>
       <c r="D2966" s="4"/>
       <c r="E2966" s="1" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="F2966" s="6" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="2967" spans="3:6">
@@ -59876,10 +59888,10 @@
       </c>
       <c r="D2967" s="4"/>
       <c r="E2967" s="1" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
       <c r="F2967" s="6" t="s">
-        <v>5961</v>
+        <v>5856</v>
       </c>
     </row>
     <row r="2968" spans="3:6">
@@ -60071,7 +60083,7 @@
         <v>5992</v>
       </c>
       <c r="F2983" s="6" t="s">
-        <v>5891</v>
+        <v>5993</v>
       </c>
     </row>
     <row r="2984" spans="3:6">
@@ -60080,10 +60092,10 @@
       </c>
       <c r="D2984" s="4"/>
       <c r="E2984" s="1" t="s">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="F2984" s="6" t="s">
-        <v>5994</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="2985" spans="3:6">
@@ -60092,10 +60104,10 @@
       </c>
       <c r="D2985" s="4"/>
       <c r="E2985" s="1" t="s">
-        <v>5995</v>
+        <v>5996</v>
       </c>
       <c r="F2985" s="6" t="s">
-        <v>5996</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="2986" spans="3:6">
@@ -60143,7 +60155,7 @@
         <v>6003</v>
       </c>
       <c r="F2989" s="6" t="s">
-        <v>5996</v>
+        <v>6004</v>
       </c>
     </row>
     <row r="2990" spans="3:6">
@@ -60152,10 +60164,10 @@
       </c>
       <c r="D2990" s="4"/>
       <c r="E2990" s="1" t="s">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="F2990" s="6" t="s">
-        <v>6005</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="2991" spans="3:6">
@@ -60164,10 +60176,10 @@
       </c>
       <c r="D2991" s="4"/>
       <c r="E2991" s="1" t="s">
-        <v>6006</v>
+        <v>6007</v>
       </c>
       <c r="F2991" s="6" t="s">
-        <v>6007</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="2992" spans="3:6">
@@ -60263,7 +60275,7 @@
         <v>6022</v>
       </c>
       <c r="F2999" s="6" t="s">
-        <v>4916</v>
+        <v>6023</v>
       </c>
     </row>
     <row r="3000" spans="3:6">
@@ -60272,10 +60284,10 @@
       </c>
       <c r="D3000" s="4"/>
       <c r="E3000" s="1" t="s">
-        <v>6023</v>
+        <v>6024</v>
       </c>
       <c r="F3000" s="6" t="s">
-        <v>6024</v>
+        <v>6025</v>
       </c>
     </row>
     <row r="3001" spans="3:6">
@@ -60284,10 +60296,10 @@
       </c>
       <c r="D3001" s="4"/>
       <c r="E3001" s="1" t="s">
-        <v>6025</v>
+        <v>6026</v>
       </c>
       <c r="F3001" s="6" t="s">
-        <v>6026</v>
+        <v>4918</v>
       </c>
     </row>
     <row r="3002" spans="3:6">
@@ -60431,7 +60443,7 @@
         <v>6049</v>
       </c>
       <c r="F3013" s="6" t="s">
-        <v>4986</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="3014" spans="3:6">
@@ -60440,10 +60452,10 @@
       </c>
       <c r="D3014" s="4"/>
       <c r="E3014" s="1" t="s">
-        <v>6050</v>
+        <v>6051</v>
       </c>
       <c r="F3014" s="6" t="s">
-        <v>6051</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="3015" spans="3:6">
@@ -60452,10 +60464,10 @@
       </c>
       <c r="D3015" s="4"/>
       <c r="E3015" s="1" t="s">
-        <v>6052</v>
+        <v>6053</v>
       </c>
       <c r="F3015" s="6" t="s">
-        <v>6053</v>
+        <v>4988</v>
       </c>
     </row>
     <row r="3016" spans="3:6">
@@ -60803,7 +60815,7 @@
         <v>6110</v>
       </c>
       <c r="F3044" s="6" t="s">
-        <v>5456</v>
+        <v>6111</v>
       </c>
     </row>
     <row r="3045" spans="3:6">
@@ -60812,10 +60824,10 @@
       </c>
       <c r="D3045" s="4"/>
       <c r="E3045" s="1" t="s">
-        <v>6111</v>
+        <v>6112</v>
       </c>
       <c r="F3045" s="6" t="s">
-        <v>6112</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="3046" spans="3:6">
@@ -60824,10 +60836,10 @@
       </c>
       <c r="D3046" s="4"/>
       <c r="E3046" s="1" t="s">
-        <v>6113</v>
+        <v>6114</v>
       </c>
       <c r="F3046" s="6" t="s">
-        <v>6114</v>
+        <v>5458</v>
       </c>
     </row>
     <row r="3047" spans="3:6">
@@ -61022,7 +61034,7 @@
         <v>6146</v>
       </c>
     </row>
-    <row r="3063" ht="15" customHeight="1" spans="3:6">
+    <row r="3063" spans="3:6">
       <c r="C3063" s="3">
         <v>202946</v>
       </c>
@@ -61046,7 +61058,7 @@
         <v>6150</v>
       </c>
     </row>
-    <row r="3065" spans="3:6">
+    <row r="3065" ht="15" customHeight="1" spans="3:6">
       <c r="C3065" s="3">
         <v>202948</v>
       </c>
@@ -61379,7 +61391,7 @@
         <v>6205</v>
       </c>
       <c r="F3092" s="6" t="s">
-        <v>1530</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="3093" spans="3:6">
@@ -61388,10 +61400,10 @@
       </c>
       <c r="D3093" s="4"/>
       <c r="E3093" s="1" t="s">
-        <v>6206</v>
+        <v>6207</v>
       </c>
       <c r="F3093" s="6" t="s">
-        <v>6207</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="3094" spans="3:6">
@@ -61400,10 +61412,10 @@
       </c>
       <c r="D3094" s="4"/>
       <c r="E3094" s="1" t="s">
-        <v>6208</v>
+        <v>6209</v>
       </c>
       <c r="F3094" s="6" t="s">
-        <v>6209</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="3095" spans="3:6">
@@ -61763,7 +61775,7 @@
         <v>6268</v>
       </c>
       <c r="F3124" s="6" t="s">
-        <v>5703</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="3125" spans="3:6">
@@ -61772,10 +61784,10 @@
       </c>
       <c r="D3125" s="4"/>
       <c r="E3125" s="1" t="s">
-        <v>6269</v>
+        <v>6270</v>
       </c>
       <c r="F3125" s="6" t="s">
-        <v>6270</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="3126" spans="3:6">
@@ -61784,10 +61796,10 @@
       </c>
       <c r="D3126" s="4"/>
       <c r="E3126" s="1" t="s">
-        <v>6271</v>
+        <v>6272</v>
       </c>
       <c r="F3126" s="6" t="s">
-        <v>6272</v>
+        <v>5705</v>
       </c>
     </row>
     <row r="3127" spans="3:6">
@@ -62411,7 +62423,7 @@
         <v>6375</v>
       </c>
       <c r="F3178" s="6" t="s">
-        <v>2915</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="3179" spans="3:6">
@@ -62420,10 +62432,10 @@
       </c>
       <c r="D3179" s="4"/>
       <c r="E3179" s="1" t="s">
-        <v>6376</v>
+        <v>6377</v>
       </c>
       <c r="F3179" s="6" t="s">
-        <v>6377</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="3180" spans="3:6">
@@ -62432,10 +62444,10 @@
       </c>
       <c r="D3180" s="4"/>
       <c r="E3180" s="1" t="s">
-        <v>6378</v>
+        <v>6379</v>
       </c>
       <c r="F3180" s="6" t="s">
-        <v>4892</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="3181" spans="3:6">
@@ -62444,10 +62456,10 @@
       </c>
       <c r="D3181" s="4"/>
       <c r="E3181" s="1" t="s">
-        <v>6379</v>
+        <v>6380</v>
       </c>
       <c r="F3181" s="6" t="s">
-        <v>6380</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="3182" spans="3:6">
@@ -62456,10 +62468,10 @@
       </c>
       <c r="D3182" s="4"/>
       <c r="E3182" s="1" t="s">
-        <v>6381</v>
+        <v>6382</v>
       </c>
       <c r="F3182" s="6" t="s">
-        <v>6382</v>
+        <v>4894</v>
       </c>
     </row>
     <row r="3183" spans="3:6">
@@ -62591,7 +62603,7 @@
         <v>6403</v>
       </c>
       <c r="F3193" s="6" t="s">
-        <v>4922</v>
+        <v>6404</v>
       </c>
     </row>
     <row r="3194" spans="3:6">
@@ -62600,10 +62612,10 @@
       </c>
       <c r="D3194" s="4"/>
       <c r="E3194" s="1" t="s">
-        <v>6404</v>
+        <v>6405</v>
       </c>
       <c r="F3194" s="6" t="s">
-        <v>6405</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="3195" spans="3:6">
@@ -62612,10 +62624,10 @@
       </c>
       <c r="D3195" s="4"/>
       <c r="E3195" s="1" t="s">
-        <v>6406</v>
+        <v>6407</v>
       </c>
       <c r="F3195" s="6" t="s">
-        <v>6407</v>
+        <v>4924</v>
       </c>
     </row>
     <row r="3196" spans="3:6">
@@ -62723,7 +62735,7 @@
         <v>6424</v>
       </c>
       <c r="F3204" s="6" t="s">
-        <v>1921</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="3205" spans="3:6">
@@ -62732,10 +62744,10 @@
       </c>
       <c r="D3205" s="4"/>
       <c r="E3205" s="1" t="s">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F3205" s="6" t="s">
-        <v>6426</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="3206" spans="3:6">
@@ -62744,10 +62756,10 @@
       </c>
       <c r="D3206" s="4"/>
       <c r="E3206" s="1" t="s">
-        <v>6427</v>
+        <v>6428</v>
       </c>
       <c r="F3206" s="6" t="s">
-        <v>6428</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="3207" spans="3:6">
@@ -62855,7 +62867,7 @@
         <v>6445</v>
       </c>
       <c r="F3215" s="6" t="s">
-        <v>6440</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="3216" spans="3:6">
@@ -62864,10 +62876,10 @@
       </c>
       <c r="D3216" s="4"/>
       <c r="E3216" s="1" t="s">
-        <v>6446</v>
+        <v>6447</v>
       </c>
       <c r="F3216" s="6" t="s">
-        <v>6447</v>
+        <v>6448</v>
       </c>
     </row>
     <row r="3217" spans="3:6">
@@ -62876,10 +62888,10 @@
       </c>
       <c r="D3217" s="4"/>
       <c r="E3217" s="1" t="s">
-        <v>6448</v>
+        <v>6449</v>
       </c>
       <c r="F3217" s="6" t="s">
-        <v>6449</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="3218" spans="3:6">
@@ -63563,7 +63575,7 @@
         <v>6562</v>
       </c>
       <c r="F3274" s="6" t="s">
-        <v>735</v>
+        <v>6563</v>
       </c>
     </row>
     <row r="3275" spans="3:6">
@@ -63572,10 +63584,10 @@
       </c>
       <c r="D3275" s="4"/>
       <c r="E3275" s="1" t="s">
-        <v>6563</v>
+        <v>6564</v>
       </c>
       <c r="F3275" s="6" t="s">
-        <v>6564</v>
+        <v>6565</v>
       </c>
     </row>
     <row r="3276" spans="3:6">
@@ -63584,10 +63596,10 @@
       </c>
       <c r="D3276" s="4"/>
       <c r="E3276" s="1" t="s">
-        <v>6565</v>
+        <v>6566</v>
       </c>
       <c r="F3276" s="6" t="s">
-        <v>6566</v>
+        <v>735</v>
       </c>
     </row>
     <row r="3277" spans="3:6">
@@ -64079,7 +64091,7 @@
         <v>6647</v>
       </c>
       <c r="F3317" s="6" t="s">
-        <v>6636</v>
+        <v>6648</v>
       </c>
     </row>
     <row r="3318" spans="3:6">
@@ -64088,10 +64100,10 @@
       </c>
       <c r="D3318" s="4"/>
       <c r="E3318" s="1" t="s">
-        <v>6648</v>
+        <v>6649</v>
       </c>
       <c r="F3318" s="6" t="s">
-        <v>6649</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="3319" spans="3:6">
@@ -64100,10 +64112,10 @@
       </c>
       <c r="D3319" s="4"/>
       <c r="E3319" s="1" t="s">
-        <v>6650</v>
+        <v>6651</v>
       </c>
       <c r="F3319" s="6" t="s">
-        <v>6651</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="3320" spans="3:6">
@@ -64163,7 +64175,7 @@
         <v>6660</v>
       </c>
       <c r="F3324" s="6" t="s">
-        <v>4914</v>
+        <v>6661</v>
       </c>
     </row>
     <row r="3325" spans="3:6">
@@ -64172,10 +64184,10 @@
       </c>
       <c r="D3325" s="4"/>
       <c r="E3325" s="1" t="s">
-        <v>6661</v>
+        <v>6662</v>
       </c>
       <c r="F3325" s="6" t="s">
-        <v>6662</v>
+        <v>6663</v>
       </c>
     </row>
     <row r="3326" spans="3:6">
@@ -64184,10 +64196,10 @@
       </c>
       <c r="D3326" s="4"/>
       <c r="E3326" s="1" t="s">
-        <v>6663</v>
+        <v>6664</v>
       </c>
       <c r="F3326" s="6" t="s">
-        <v>6664</v>
+        <v>4916</v>
       </c>
     </row>
     <row r="3327" spans="3:6">
@@ -64223,7 +64235,7 @@
         <v>6669</v>
       </c>
       <c r="F3329" s="6" t="s">
-        <v>5814</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="3330" spans="3:6">
@@ -64232,10 +64244,10 @@
       </c>
       <c r="D3330" s="4"/>
       <c r="E3330" s="1" t="s">
-        <v>6670</v>
+        <v>6671</v>
       </c>
       <c r="F3330" s="6" t="s">
-        <v>6671</v>
+        <v>6672</v>
       </c>
     </row>
     <row r="3331" spans="3:6">
@@ -64244,10 +64256,10 @@
       </c>
       <c r="D3331" s="4"/>
       <c r="E3331" s="1" t="s">
-        <v>6672</v>
+        <v>6673</v>
       </c>
       <c r="F3331" s="6" t="s">
-        <v>6673</v>
+        <v>5818</v>
       </c>
     </row>
     <row r="3332" spans="3:6">
@@ -64451,7 +64463,7 @@
         <v>6706</v>
       </c>
       <c r="F3348" s="6" t="s">
-        <v>6699</v>
+        <v>6707</v>
       </c>
     </row>
     <row r="3349" spans="3:6">
@@ -64460,10 +64472,10 @@
       </c>
       <c r="D3349" s="4"/>
       <c r="E3349" s="1" t="s">
-        <v>6707</v>
+        <v>6708</v>
       </c>
       <c r="F3349" s="6" t="s">
-        <v>6708</v>
+        <v>6709</v>
       </c>
     </row>
     <row r="3350" spans="3:6">
@@ -64472,10 +64484,10 @@
       </c>
       <c r="D3350" s="4"/>
       <c r="E3350" s="1" t="s">
-        <v>6709</v>
+        <v>6710</v>
       </c>
       <c r="F3350" s="6" t="s">
-        <v>6710</v>
+        <v>6703</v>
       </c>
     </row>
     <row r="3351" spans="3:6">
@@ -64631,7 +64643,7 @@
         <v>6735</v>
       </c>
       <c r="F3363" s="6" t="s">
-        <v>2889</v>
+        <v>6736</v>
       </c>
     </row>
     <row r="3364" spans="3:6">
@@ -64640,10 +64652,10 @@
       </c>
       <c r="D3364" s="4"/>
       <c r="E3364" s="1" t="s">
-        <v>6736</v>
+        <v>6737</v>
       </c>
       <c r="F3364" s="6" t="s">
-        <v>6737</v>
+        <v>6738</v>
       </c>
     </row>
     <row r="3365" spans="3:6">
@@ -64652,10 +64664,10 @@
       </c>
       <c r="D3365" s="4"/>
       <c r="E3365" s="1" t="s">
-        <v>6738</v>
+        <v>6739</v>
       </c>
       <c r="F3365" s="6" t="s">
-        <v>2891</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="3366" spans="3:6">
@@ -64664,10 +64676,10 @@
       </c>
       <c r="D3366" s="4"/>
       <c r="E3366" s="1" t="s">
-        <v>6739</v>
+        <v>6740</v>
       </c>
       <c r="F3366" s="6" t="s">
-        <v>6740</v>
+        <v>6741</v>
       </c>
     </row>
     <row r="3367" spans="3:6">
@@ -64676,10 +64688,10 @@
       </c>
       <c r="D3367" s="4"/>
       <c r="E3367" s="1" t="s">
-        <v>6741</v>
+        <v>6742</v>
       </c>
       <c r="F3367" s="6" t="s">
-        <v>6742</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="3368" spans="3:6">
@@ -65231,7 +65243,7 @@
         <v>6833</v>
       </c>
       <c r="F3413" s="6" t="s">
-        <v>5634</v>
+        <v>6834</v>
       </c>
     </row>
     <row r="3414" spans="3:6">
@@ -65240,10 +65252,10 @@
       </c>
       <c r="D3414" s="4"/>
       <c r="E3414" s="1" t="s">
-        <v>6834</v>
+        <v>6835</v>
       </c>
       <c r="F3414" s="6" t="s">
-        <v>6835</v>
+        <v>6836</v>
       </c>
     </row>
     <row r="3415" spans="3:6">
@@ -65252,10 +65264,10 @@
       </c>
       <c r="D3415" s="4"/>
       <c r="E3415" s="1" t="s">
-        <v>6836</v>
+        <v>6837</v>
       </c>
       <c r="F3415" s="6" t="s">
-        <v>6837</v>
+        <v>5636</v>
       </c>
     </row>
     <row r="3416" spans="3:6">
@@ -65543,7 +65555,7 @@
         <v>6884</v>
       </c>
       <c r="F3439" s="6" t="s">
-        <v>6865</v>
+        <v>6885</v>
       </c>
     </row>
     <row r="3440" spans="3:6">
@@ -65552,10 +65564,10 @@
       </c>
       <c r="D3440" s="4"/>
       <c r="E3440" s="1" t="s">
-        <v>6885</v>
+        <v>6886</v>
       </c>
       <c r="F3440" s="6" t="s">
-        <v>6886</v>
+        <v>6887</v>
       </c>
     </row>
     <row r="3441" spans="3:6">
@@ -65564,10 +65576,10 @@
       </c>
       <c r="D3441" s="4"/>
       <c r="E3441" s="1" t="s">
-        <v>6887</v>
+        <v>6888</v>
       </c>
       <c r="F3441" s="6" t="s">
-        <v>6888</v>
+        <v>6869</v>
       </c>
     </row>
     <row r="3442" spans="3:6">
@@ -65795,7 +65807,7 @@
         <v>6925</v>
       </c>
       <c r="F3460" s="6" t="s">
-        <v>2756</v>
+        <v>6926</v>
       </c>
     </row>
     <row r="3461" spans="3:6">
@@ -65804,10 +65816,10 @@
       </c>
       <c r="D3461" s="4"/>
       <c r="E3461" s="1" t="s">
-        <v>6926</v>
+        <v>6927</v>
       </c>
       <c r="F3461" s="6" t="s">
-        <v>6927</v>
+        <v>6928</v>
       </c>
     </row>
     <row r="3462" spans="3:6">
@@ -65816,10 +65828,10 @@
       </c>
       <c r="D3462" s="4"/>
       <c r="E3462" s="1" t="s">
-        <v>6928</v>
+        <v>6929</v>
       </c>
       <c r="F3462" s="6" t="s">
-        <v>6929</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="3463" spans="3:6">
@@ -65999,7 +66011,7 @@
         <v>6958</v>
       </c>
       <c r="F3477" s="6" t="s">
-        <v>6105</v>
+        <v>6959</v>
       </c>
     </row>
     <row r="3478" spans="3:6">
@@ -66008,10 +66020,10 @@
       </c>
       <c r="D3478" s="4"/>
       <c r="E3478" s="1" t="s">
-        <v>6959</v>
+        <v>6960</v>
       </c>
       <c r="F3478" s="6" t="s">
-        <v>6960</v>
+        <v>6961</v>
       </c>
     </row>
     <row r="3479" spans="3:6">
@@ -66020,10 +66032,10 @@
       </c>
       <c r="D3479" s="4"/>
       <c r="E3479" s="1" t="s">
-        <v>6961</v>
+        <v>6962</v>
       </c>
       <c r="F3479" s="6" t="s">
-        <v>6962</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="3480" spans="3:6">
@@ -66059,7 +66071,7 @@
         <v>6967</v>
       </c>
       <c r="F3482" s="6" t="s">
-        <v>6148</v>
+        <v>6968</v>
       </c>
     </row>
     <row r="3483" spans="3:6">
@@ -66068,10 +66080,10 @@
       </c>
       <c r="D3483" s="4"/>
       <c r="E3483" s="1" t="s">
-        <v>6968</v>
+        <v>6969</v>
       </c>
       <c r="F3483" s="6" t="s">
-        <v>6969</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="3484" spans="3:6">
@@ -66080,10 +66092,10 @@
       </c>
       <c r="D3484" s="4"/>
       <c r="E3484" s="1" t="s">
-        <v>6970</v>
+        <v>6971</v>
       </c>
       <c r="F3484" s="6" t="s">
-        <v>6971</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="3485" spans="3:6">
@@ -66779,7 +66791,7 @@
         <v>7086</v>
       </c>
       <c r="F3542" s="6" t="s">
-        <v>1273</v>
+        <v>7087</v>
       </c>
     </row>
     <row r="3543" spans="3:6">
@@ -66788,10 +66800,10 @@
       </c>
       <c r="D3543" s="4"/>
       <c r="E3543" s="1" t="s">
-        <v>7087</v>
+        <v>7088</v>
       </c>
       <c r="F3543" s="6" t="s">
-        <v>7088</v>
+        <v>7089</v>
       </c>
     </row>
     <row r="3544" spans="3:6">
@@ -66800,10 +66812,10 @@
       </c>
       <c r="D3544" s="4"/>
       <c r="E3544" s="1" t="s">
-        <v>7089</v>
+        <v>7090</v>
       </c>
       <c r="F3544" s="6" t="s">
-        <v>7090</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="3545" spans="3:6">
@@ -67439,7 +67451,7 @@
         <v>7195</v>
       </c>
       <c r="F3597" s="6" t="s">
-        <v>4912</v>
+        <v>7196</v>
       </c>
     </row>
     <row r="3598" spans="3:6">
@@ -67448,10 +67460,10 @@
       </c>
       <c r="D3598" s="4"/>
       <c r="E3598" s="1" t="s">
-        <v>7196</v>
+        <v>7197</v>
       </c>
       <c r="F3598" s="6" t="s">
-        <v>7197</v>
+        <v>7198</v>
       </c>
     </row>
     <row r="3599" spans="3:6">
@@ -67460,10 +67472,10 @@
       </c>
       <c r="D3599" s="4"/>
       <c r="E3599" s="1" t="s">
-        <v>7198</v>
+        <v>7199</v>
       </c>
       <c r="F3599" s="6" t="s">
-        <v>7199</v>
+        <v>4914</v>
       </c>
     </row>
     <row r="3600" spans="3:6">
@@ -67871,7 +67883,7 @@
         <v>7266</v>
       </c>
       <c r="F3633" s="6" t="s">
-        <v>6894</v>
+        <v>7267</v>
       </c>
     </row>
     <row r="3634" spans="3:6">
@@ -67880,10 +67892,10 @@
       </c>
       <c r="D3634" s="4"/>
       <c r="E3634" s="1" t="s">
-        <v>7267</v>
+        <v>7268</v>
       </c>
       <c r="F3634" s="6" t="s">
-        <v>7268</v>
+        <v>7269</v>
       </c>
     </row>
     <row r="3635" spans="3:6">
@@ -67892,10 +67904,10 @@
       </c>
       <c r="D3635" s="4"/>
       <c r="E3635" s="1" t="s">
-        <v>7269</v>
+        <v>7270</v>
       </c>
       <c r="F3635" s="6" t="s">
-        <v>7270</v>
+        <v>6898</v>
       </c>
     </row>
     <row r="3636" spans="3:6">
@@ -68327,7 +68339,7 @@
         <v>7341</v>
       </c>
       <c r="F3671" s="6" t="s">
-        <v>6594</v>
+        <v>7342</v>
       </c>
     </row>
     <row r="3672" spans="3:6">
@@ -68336,10 +68348,10 @@
       </c>
       <c r="D3672" s="4"/>
       <c r="E3672" s="1" t="s">
-        <v>7342</v>
+        <v>7343</v>
       </c>
       <c r="F3672" s="6" t="s">
-        <v>7343</v>
+        <v>7344</v>
       </c>
     </row>
     <row r="3673" spans="3:6">
@@ -68348,10 +68360,10 @@
       </c>
       <c r="D3673" s="4"/>
       <c r="E3673" s="1" t="s">
-        <v>7344</v>
+        <v>7345</v>
       </c>
       <c r="F3673" s="6" t="s">
-        <v>7345</v>
+        <v>6598</v>
       </c>
     </row>
     <row r="3674" spans="3:6">
@@ -68639,7 +68651,7 @@
         <v>7392</v>
       </c>
       <c r="F3697" s="6" t="s">
-        <v>4914</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="3698" spans="3:6">
@@ -68648,10 +68660,10 @@
       </c>
       <c r="D3698" s="4"/>
       <c r="E3698" s="1" t="s">
-        <v>7393</v>
+        <v>7394</v>
       </c>
       <c r="F3698" s="6" t="s">
-        <v>7394</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="3699" spans="3:6">
@@ -68660,10 +68672,10 @@
       </c>
       <c r="D3699" s="4"/>
       <c r="E3699" s="1" t="s">
-        <v>7395</v>
+        <v>7396</v>
       </c>
       <c r="F3699" s="6" t="s">
-        <v>4912</v>
+        <v>4916</v>
       </c>
     </row>
     <row r="3700" spans="3:6">
@@ -68672,10 +68684,10 @@
       </c>
       <c r="D3700" s="4"/>
       <c r="E3700" s="1" t="s">
-        <v>7396</v>
+        <v>7397</v>
       </c>
       <c r="F3700" s="6" t="s">
-        <v>7397</v>
+        <v>7398</v>
       </c>
     </row>
     <row r="3701" spans="3:6">
@@ -68684,10 +68696,10 @@
       </c>
       <c r="D3701" s="4"/>
       <c r="E3701" s="1" t="s">
-        <v>7398</v>
+        <v>7399</v>
       </c>
       <c r="F3701" s="6" t="s">
-        <v>7399</v>
+        <v>4914</v>
       </c>
     </row>
     <row r="3702" spans="3:6">
@@ -68795,7 +68807,7 @@
         <v>7416</v>
       </c>
       <c r="F3710" s="6" t="s">
-        <v>7132</v>
+        <v>7417</v>
       </c>
     </row>
     <row r="3711" spans="3:6">
@@ -68804,10 +68816,10 @@
       </c>
       <c r="D3711" s="4"/>
       <c r="E3711" s="1" t="s">
-        <v>7417</v>
+        <v>7418</v>
       </c>
       <c r="F3711" s="6" t="s">
-        <v>7418</v>
+        <v>7419</v>
       </c>
     </row>
     <row r="3712" spans="3:6">
@@ -68816,10 +68828,10 @@
       </c>
       <c r="D3712" s="4"/>
       <c r="E3712" s="1" t="s">
-        <v>7419</v>
+        <v>7420</v>
       </c>
       <c r="F3712" s="6" t="s">
-        <v>7420</v>
+        <v>7136</v>
       </c>
     </row>
     <row r="3713" spans="3:6">
@@ -69479,7 +69491,7 @@
         <v>7529</v>
       </c>
       <c r="F3767" s="6" t="s">
-        <v>3864</v>
+        <v>7530</v>
       </c>
     </row>
     <row r="3768" spans="3:6">
@@ -69488,10 +69500,10 @@
       </c>
       <c r="D3768" s="4"/>
       <c r="E3768" s="1" t="s">
-        <v>7530</v>
+        <v>7531</v>
       </c>
       <c r="F3768" s="6" t="s">
-        <v>7531</v>
+        <v>7532</v>
       </c>
     </row>
     <row r="3769" spans="3:6">
@@ -69500,10 +69512,10 @@
       </c>
       <c r="D3769" s="4"/>
       <c r="E3769" s="1" t="s">
-        <v>7532</v>
+        <v>7533</v>
       </c>
       <c r="F3769" s="6" t="s">
-        <v>7533</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="3770" spans="3:6">
@@ -69947,7 +69959,7 @@
         <v>7606</v>
       </c>
       <c r="F3806" s="6" t="s">
-        <v>4908</v>
+        <v>7607</v>
       </c>
     </row>
     <row r="3807" spans="3:6">
@@ -69956,10 +69968,10 @@
       </c>
       <c r="D3807" s="4"/>
       <c r="E3807" s="1" t="s">
-        <v>7607</v>
+        <v>7608</v>
       </c>
       <c r="F3807" s="6" t="s">
-        <v>7608</v>
+        <v>7609</v>
       </c>
     </row>
     <row r="3808" spans="3:6">
@@ -69968,10 +69980,10 @@
       </c>
       <c r="D3808" s="4"/>
       <c r="E3808" s="1" t="s">
-        <v>7609</v>
+        <v>7610</v>
       </c>
       <c r="F3808" s="6" t="s">
-        <v>7610</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="3809" spans="3:6">
@@ -70043,31 +70055,31 @@
         <v>7621</v>
       </c>
       <c r="F3814" s="6" t="s">
-        <v>5919</v>
+        <v>7622</v>
       </c>
     </row>
     <row r="3815" spans="3:6">
       <c r="C3815" s="3">
         <v>203698</v>
       </c>
-      <c r="D3815"/>
+      <c r="D3815" s="4"/>
       <c r="E3815" s="1" t="s">
-        <v>7622</v>
+        <v>7623</v>
       </c>
       <c r="F3815" s="6" t="s">
-        <v>7623</v>
+        <v>7624</v>
       </c>
     </row>
     <row r="3816" spans="3:6">
       <c r="C3816" s="3">
         <v>203699</v>
       </c>
-      <c r="D3816"/>
+      <c r="D3816" s="4"/>
       <c r="E3816" s="1" t="s">
-        <v>7624</v>
+        <v>7625</v>
       </c>
       <c r="F3816" s="6" t="s">
-        <v>7625</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="3817" spans="3:6">
@@ -70079,7 +70091,7 @@
         <v>7626</v>
       </c>
       <c r="F3817" s="6" t="s">
-        <v>3621</v>
+        <v>7627</v>
       </c>
     </row>
     <row r="3818" spans="3:6">
@@ -70088,29 +70100,29 @@
       </c>
       <c r="D3818"/>
       <c r="E3818" s="1" t="s">
-        <v>7627</v>
+        <v>7628</v>
       </c>
       <c r="F3818" s="6" t="s">
-        <v>7628</v>
+        <v>7629</v>
       </c>
     </row>
     <row r="3819" spans="3:6">
       <c r="C3819" s="3">
         <v>203702</v>
       </c>
-      <c r="D3819" s="4"/>
+      <c r="D3819"/>
       <c r="E3819" s="1" t="s">
-        <v>7629</v>
+        <v>7630</v>
       </c>
       <c r="F3819" s="6" t="s">
-        <v>7630</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="3820" spans="3:6">
       <c r="C3820" s="3">
         <v>203703</v>
       </c>
-      <c r="D3820" s="4"/>
+      <c r="D3820"/>
       <c r="E3820" s="1" t="s">
         <v>7631</v>
       </c>
@@ -70247,7 +70259,7 @@
         <v>7653</v>
       </c>
       <c r="F3831" s="6" t="s">
-        <v>2838</v>
+        <v>7654</v>
       </c>
     </row>
     <row r="3832" spans="3:6">
@@ -70256,10 +70268,10 @@
       </c>
       <c r="D3832" s="4"/>
       <c r="E3832" s="1" t="s">
-        <v>7654</v>
+        <v>7655</v>
       </c>
       <c r="F3832" s="6" t="s">
-        <v>7655</v>
+        <v>7656</v>
       </c>
     </row>
     <row r="3833" spans="3:6">
@@ -70268,10 +70280,10 @@
       </c>
       <c r="D3833" s="4"/>
       <c r="E3833" s="1" t="s">
-        <v>7656</v>
-      </c>
-      <c r="F3833" s="10" t="s">
         <v>7657</v>
+      </c>
+      <c r="F3833" s="6" t="s">
+        <v>2838</v>
       </c>
     </row>
     <row r="3834" spans="3:6">
@@ -70282,7 +70294,7 @@
       <c r="E3834" s="1" t="s">
         <v>7658</v>
       </c>
-      <c r="F3834" s="10" t="s">
+      <c r="F3834" s="6" t="s">
         <v>7659</v>
       </c>
     </row>
@@ -70347,16 +70359,28 @@
       </c>
     </row>
     <row r="3840" spans="3:6">
-      <c r="C3840"/>
-      <c r="D3840"/>
-      <c r="E3840"/>
-      <c r="F3840"/>
+      <c r="C3840" s="3">
+        <v>203723</v>
+      </c>
+      <c r="D3840" s="4"/>
+      <c r="E3840" s="1" t="s">
+        <v>7670</v>
+      </c>
+      <c r="F3840" s="10" t="s">
+        <v>7671</v>
+      </c>
     </row>
     <row r="3841" spans="3:6">
-      <c r="C3841"/>
-      <c r="D3841"/>
-      <c r="E3841"/>
-      <c r="F3841"/>
+      <c r="C3841" s="3">
+        <v>203724</v>
+      </c>
+      <c r="D3841" s="4"/>
+      <c r="E3841" s="1" t="s">
+        <v>7672</v>
+      </c>
+      <c r="F3841" s="10" t="s">
+        <v>7673</v>
+      </c>
     </row>
     <row r="3842" spans="3:6">
       <c r="C3842"/>
@@ -71257,6 +71281,18 @@
       <c r="D3991"/>
       <c r="E3991"/>
       <c r="F3991"/>
+    </row>
+    <row r="3992" spans="3:6">
+      <c r="C3992"/>
+      <c r="D3992"/>
+      <c r="E3992"/>
+      <c r="F3992"/>
+    </row>
+    <row r="3993" spans="3:6">
+      <c r="C3993"/>
+      <c r="D3993"/>
+      <c r="E3993"/>
+      <c r="F3993"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28695" windowHeight="14085"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="MulLanguageProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7799" uniqueCount="7659">
   <si>
     <t>c</t>
   </si>
@@ -21652,7 +21665,7 @@
     <t>熟练度:{0}-{1}点 上限:{2}点</t>
   </si>
   <si>
-    <t>Proficiency: {0}-{1} Points Upper Limit: {2} Points</t>
+    <t>Proficiency: {0}-{1}\nPoints Upper Limit: {2} Points</t>
   </si>
   <si>
     <t>当前活力:  {0}</t>
@@ -22996,12 +23009,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -23037,32 +23050,34 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -23075,47 +23090,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -23127,8 +23105,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -23143,16 +23129,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -23167,17 +23145,52 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -23196,7 +23209,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -23208,37 +23287,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -23256,7 +23317,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -23268,103 +23365,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -23376,7 +23383,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -23391,6 +23404,39 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -23401,35 +23447,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -23449,15 +23466,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -23473,165 +23481,170 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -23656,56 +23669,61 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -23994,7 +24012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C2:F3993"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7801" uniqueCount="7618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7805" uniqueCount="7622">
   <si>
     <t>c</t>
   </si>
@@ -14243,10 +14243,22 @@
     <t>Tik Tok login failed!</t>
   </si>
   <si>
+    <t>暴击</t>
+  </si>
+  <si>
+    <t>Critical Hit</t>
+  </si>
+  <si>
     <t>闪避</t>
   </si>
   <si>
     <t>Evasion</t>
+  </si>
+  <si>
+    <t>抵抗</t>
+  </si>
+  <si>
+    <t>Resistance</t>
   </si>
   <si>
     <t>免疫</t>
@@ -23889,7 +23901,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:F3994"/>
+  <dimension ref="C2:F3996"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -52677,7 +52689,7 @@
         <v>4746</v>
       </c>
       <c r="F2380" s="6" t="s">
-        <v>3142</v>
+        <v>4747</v>
       </c>
     </row>
     <row r="2381" spans="3:6">
@@ -52686,10 +52698,10 @@
       </c>
       <c r="D2381" s="4"/>
       <c r="E2381" s="1" t="s">
-        <v>4747</v>
+        <v>4748</v>
       </c>
       <c r="F2381" s="6" t="s">
-        <v>4748</v>
+        <v>4749</v>
       </c>
     </row>
     <row r="2382" spans="3:6">
@@ -52698,10 +52710,10 @@
       </c>
       <c r="D2382" s="4"/>
       <c r="E2382" s="1" t="s">
-        <v>4749</v>
+        <v>4750</v>
       </c>
       <c r="F2382" s="6" t="s">
-        <v>4750</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="2383" spans="3:6">
@@ -55641,7 +55653,7 @@
         <v>5239</v>
       </c>
       <c r="F2627" s="6" t="s">
-        <v>2193</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="2628" spans="3:6">
@@ -55650,10 +55662,10 @@
       </c>
       <c r="D2628" s="4"/>
       <c r="E2628" s="1" t="s">
-        <v>5240</v>
+        <v>5241</v>
       </c>
       <c r="F2628" s="6" t="s">
-        <v>5241</v>
+        <v>5242</v>
       </c>
     </row>
     <row r="2629" spans="3:6">
@@ -55662,10 +55674,10 @@
       </c>
       <c r="D2629" s="4"/>
       <c r="E2629" s="1" t="s">
-        <v>5242</v>
+        <v>5243</v>
       </c>
       <c r="F2629" s="6" t="s">
-        <v>5243</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="2630" spans="3:6">
@@ -57885,7 +57897,7 @@
         <v>5612</v>
       </c>
       <c r="F2814" s="6" t="s">
-        <v>4940</v>
+        <v>5613</v>
       </c>
     </row>
     <row r="2815" spans="3:6">
@@ -57894,10 +57906,10 @@
       </c>
       <c r="D2815" s="4"/>
       <c r="E2815" s="1" t="s">
-        <v>5613</v>
+        <v>5614</v>
       </c>
       <c r="F2815" s="6" t="s">
-        <v>5614</v>
+        <v>5615</v>
       </c>
     </row>
     <row r="2816" spans="3:6">
@@ -57906,10 +57918,10 @@
       </c>
       <c r="D2816" s="4"/>
       <c r="E2816" s="1" t="s">
-        <v>5615</v>
+        <v>5616</v>
       </c>
       <c r="F2816" s="6" t="s">
-        <v>5616</v>
+        <v>4944</v>
       </c>
     </row>
     <row r="2817" spans="3:6">
@@ -58257,7 +58269,7 @@
         <v>5673</v>
       </c>
       <c r="F2845" s="6" t="s">
-        <v>5603</v>
+        <v>5674</v>
       </c>
     </row>
     <row r="2846" spans="3:6">
@@ -58266,10 +58278,10 @@
       </c>
       <c r="D2846" s="4"/>
       <c r="E2846" s="1" t="s">
-        <v>5674</v>
+        <v>5675</v>
       </c>
       <c r="F2846" s="6" t="s">
-        <v>5675</v>
+        <v>5676</v>
       </c>
     </row>
     <row r="2847" spans="3:6">
@@ -58278,10 +58290,10 @@
       </c>
       <c r="D2847" s="4"/>
       <c r="E2847" s="1" t="s">
-        <v>5676</v>
+        <v>5677</v>
       </c>
       <c r="F2847" s="6" t="s">
-        <v>5677</v>
+        <v>5607</v>
       </c>
     </row>
     <row r="2848" spans="3:6">
@@ -58293,7 +58305,7 @@
         <v>5678</v>
       </c>
       <c r="F2848" s="6" t="s">
-        <v>4940</v>
+        <v>5679</v>
       </c>
     </row>
     <row r="2849" spans="3:6">
@@ -58302,10 +58314,10 @@
       </c>
       <c r="D2849" s="4"/>
       <c r="E2849" s="1" t="s">
-        <v>5679</v>
+        <v>5680</v>
       </c>
       <c r="F2849" s="6" t="s">
-        <v>5680</v>
+        <v>5681</v>
       </c>
     </row>
     <row r="2850" spans="3:6">
@@ -58314,10 +58326,10 @@
       </c>
       <c r="D2850" s="4"/>
       <c r="E2850" s="1" t="s">
-        <v>5681</v>
+        <v>5682</v>
       </c>
       <c r="F2850" s="6" t="s">
-        <v>5682</v>
+        <v>4944</v>
       </c>
     </row>
     <row r="2851" spans="3:6">
@@ -58425,7 +58437,7 @@
         <v>5699</v>
       </c>
       <c r="F2859" s="6" t="s">
-        <v>4864</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="2860" spans="3:6">
@@ -58434,10 +58446,10 @@
       </c>
       <c r="D2860" s="4"/>
       <c r="E2860" s="1" t="s">
-        <v>5700</v>
+        <v>5701</v>
       </c>
       <c r="F2860" s="6" t="s">
-        <v>5701</v>
+        <v>5702</v>
       </c>
     </row>
     <row r="2861" spans="3:6">
@@ -58446,10 +58458,10 @@
       </c>
       <c r="D2861" s="4"/>
       <c r="E2861" s="1" t="s">
-        <v>5702</v>
+        <v>5703</v>
       </c>
       <c r="F2861" s="6" t="s">
-        <v>5703</v>
+        <v>4868</v>
       </c>
     </row>
     <row r="2862" spans="3:6">
@@ -58521,7 +58533,7 @@
         <v>5714</v>
       </c>
       <c r="F2867" s="6" t="s">
-        <v>5259</v>
+        <v>5715</v>
       </c>
     </row>
     <row r="2868" spans="3:6">
@@ -58530,10 +58542,10 @@
       </c>
       <c r="D2868" s="4"/>
       <c r="E2868" s="1" t="s">
-        <v>5715</v>
+        <v>5716</v>
       </c>
       <c r="F2868" s="6" t="s">
-        <v>5716</v>
+        <v>5717</v>
       </c>
     </row>
     <row r="2869" spans="3:6">
@@ -58542,10 +58554,10 @@
       </c>
       <c r="D2869" s="4"/>
       <c r="E2869" s="1" t="s">
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="F2869" s="6" t="s">
-        <v>5718</v>
+        <v>5263</v>
       </c>
     </row>
     <row r="2870" spans="3:6">
@@ -58557,7 +58569,7 @@
         <v>5719</v>
       </c>
       <c r="F2870" s="6" t="s">
-        <v>1543</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="2871" spans="3:6">
@@ -58566,10 +58578,10 @@
       </c>
       <c r="D2871" s="4"/>
       <c r="E2871" s="1" t="s">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="F2871" s="6" t="s">
-        <v>5721</v>
+        <v>5722</v>
       </c>
     </row>
     <row r="2872" spans="3:6">
@@ -58578,10 +58590,10 @@
       </c>
       <c r="D2872" s="4"/>
       <c r="E2872" s="1" t="s">
-        <v>5722</v>
+        <v>5723</v>
       </c>
       <c r="F2872" s="6" t="s">
-        <v>5723</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="2873" spans="3:6">
@@ -58881,7 +58893,7 @@
         <v>5772</v>
       </c>
       <c r="F2897" s="6" t="s">
-        <v>1261</v>
+        <v>5773</v>
       </c>
     </row>
     <row r="2898" spans="3:6">
@@ -58890,10 +58902,10 @@
       </c>
       <c r="D2898" s="4"/>
       <c r="E2898" s="1" t="s">
-        <v>5773</v>
+        <v>5774</v>
       </c>
       <c r="F2898" s="6" t="s">
-        <v>5774</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="2899" spans="3:6">
@@ -58902,10 +58914,10 @@
       </c>
       <c r="D2899" s="4"/>
       <c r="E2899" s="1" t="s">
-        <v>5775</v>
+        <v>5776</v>
       </c>
       <c r="F2899" s="6" t="s">
-        <v>5776</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="2900" spans="3:6">
@@ -59097,7 +59109,7 @@
         <v>5807</v>
       </c>
       <c r="F2915" s="6" t="s">
-        <v>4719</v>
+        <v>5808</v>
       </c>
     </row>
     <row r="2916" spans="3:6">
@@ -59106,10 +59118,10 @@
       </c>
       <c r="D2916" s="4"/>
       <c r="E2916" s="1" t="s">
-        <v>5808</v>
+        <v>5809</v>
       </c>
       <c r="F2916" s="6" t="s">
-        <v>5809</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="2917" spans="3:6">
@@ -59118,10 +59130,10 @@
       </c>
       <c r="D2917" s="4"/>
       <c r="E2917" s="1" t="s">
-        <v>5810</v>
+        <v>5811</v>
       </c>
       <c r="F2917" s="6" t="s">
-        <v>5811</v>
+        <v>4719</v>
       </c>
     </row>
     <row r="2918" spans="3:6">
@@ -59553,7 +59565,7 @@
         <v>5882</v>
       </c>
       <c r="F2953" s="6" t="s">
-        <v>4996</v>
+        <v>5883</v>
       </c>
     </row>
     <row r="2954" spans="3:6">
@@ -59562,10 +59574,10 @@
       </c>
       <c r="D2954" s="4"/>
       <c r="E2954" s="1" t="s">
-        <v>5883</v>
+        <v>5884</v>
       </c>
       <c r="F2954" s="6" t="s">
-        <v>5884</v>
+        <v>5885</v>
       </c>
     </row>
     <row r="2955" spans="3:6">
@@ -59574,10 +59586,10 @@
       </c>
       <c r="D2955" s="4"/>
       <c r="E2955" s="1" t="s">
-        <v>5885</v>
+        <v>5886</v>
       </c>
       <c r="F2955" s="6" t="s">
-        <v>5886</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="2956" spans="3:6">
@@ -59733,7 +59745,7 @@
         <v>5911</v>
       </c>
       <c r="F2968" s="6" t="s">
-        <v>5806</v>
+        <v>5912</v>
       </c>
     </row>
     <row r="2969" spans="3:6">
@@ -59742,10 +59754,10 @@
       </c>
       <c r="D2969" s="4"/>
       <c r="E2969" s="1" t="s">
-        <v>5912</v>
+        <v>5913</v>
       </c>
       <c r="F2969" s="6" t="s">
-        <v>5913</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="2970" spans="3:6">
@@ -59754,10 +59766,10 @@
       </c>
       <c r="D2970" s="4"/>
       <c r="E2970" s="1" t="s">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="F2970" s="6" t="s">
-        <v>5915</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="2971" spans="3:6">
@@ -59949,7 +59961,7 @@
         <v>5946</v>
       </c>
       <c r="F2986" s="6" t="s">
-        <v>5845</v>
+        <v>5947</v>
       </c>
     </row>
     <row r="2987" spans="3:6">
@@ -59958,10 +59970,10 @@
       </c>
       <c r="D2987" s="4"/>
       <c r="E2987" s="1" t="s">
-        <v>5947</v>
+        <v>5948</v>
       </c>
       <c r="F2987" s="6" t="s">
-        <v>5948</v>
+        <v>5949</v>
       </c>
     </row>
     <row r="2988" spans="3:6">
@@ -59970,10 +59982,10 @@
       </c>
       <c r="D2988" s="4"/>
       <c r="E2988" s="1" t="s">
-        <v>5949</v>
+        <v>5950</v>
       </c>
       <c r="F2988" s="6" t="s">
-        <v>5950</v>
+        <v>5849</v>
       </c>
     </row>
     <row r="2989" spans="3:6">
@@ -60021,7 +60033,7 @@
         <v>5957</v>
       </c>
       <c r="F2992" s="6" t="s">
-        <v>5950</v>
+        <v>5958</v>
       </c>
     </row>
     <row r="2993" spans="3:6">
@@ -60030,10 +60042,10 @@
       </c>
       <c r="D2993" s="4"/>
       <c r="E2993" s="1" t="s">
-        <v>5958</v>
+        <v>5959</v>
       </c>
       <c r="F2993" s="6" t="s">
-        <v>5959</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="2994" spans="3:6">
@@ -60042,10 +60054,10 @@
       </c>
       <c r="D2994" s="4"/>
       <c r="E2994" s="1" t="s">
-        <v>5960</v>
+        <v>5961</v>
       </c>
       <c r="F2994" s="6" t="s">
-        <v>5961</v>
+        <v>5954</v>
       </c>
     </row>
     <row r="2995" spans="3:6">
@@ -60141,7 +60153,7 @@
         <v>5976</v>
       </c>
       <c r="F3002" s="6" t="s">
-        <v>4868</v>
+        <v>5977</v>
       </c>
     </row>
     <row r="3003" spans="3:6">
@@ -60150,10 +60162,10 @@
       </c>
       <c r="D3003" s="4"/>
       <c r="E3003" s="1" t="s">
-        <v>5977</v>
+        <v>5978</v>
       </c>
       <c r="F3003" s="6" t="s">
-        <v>5978</v>
+        <v>5979</v>
       </c>
     </row>
     <row r="3004" spans="3:6">
@@ -60162,10 +60174,10 @@
       </c>
       <c r="D3004" s="4"/>
       <c r="E3004" s="1" t="s">
-        <v>5979</v>
+        <v>5980</v>
       </c>
       <c r="F3004" s="6" t="s">
-        <v>5980</v>
+        <v>4872</v>
       </c>
     </row>
     <row r="3005" spans="3:6">
@@ -60309,7 +60321,7 @@
         <v>6003</v>
       </c>
       <c r="F3016" s="6" t="s">
-        <v>4938</v>
+        <v>6004</v>
       </c>
     </row>
     <row r="3017" spans="3:6">
@@ -60318,10 +60330,10 @@
       </c>
       <c r="D3017" s="4"/>
       <c r="E3017" s="1" t="s">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="F3017" s="6" t="s">
-        <v>6005</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="3018" spans="3:6">
@@ -60330,10 +60342,10 @@
       </c>
       <c r="D3018" s="4"/>
       <c r="E3018" s="1" t="s">
-        <v>6006</v>
+        <v>6007</v>
       </c>
       <c r="F3018" s="6" t="s">
-        <v>6007</v>
+        <v>4942</v>
       </c>
     </row>
     <row r="3019" spans="3:6">
@@ -60681,7 +60693,7 @@
         <v>6064</v>
       </c>
       <c r="F3047" s="6" t="s">
-        <v>5407</v>
+        <v>6065</v>
       </c>
     </row>
     <row r="3048" spans="3:6">
@@ -60690,10 +60702,10 @@
       </c>
       <c r="D3048" s="4"/>
       <c r="E3048" s="1" t="s">
-        <v>6065</v>
+        <v>6066</v>
       </c>
       <c r="F3048" s="6" t="s">
-        <v>6066</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="3049" spans="3:6">
@@ -60702,10 +60714,10 @@
       </c>
       <c r="D3049" s="4"/>
       <c r="E3049" s="1" t="s">
-        <v>6067</v>
+        <v>6068</v>
       </c>
       <c r="F3049" s="6" t="s">
-        <v>6068</v>
+        <v>5411</v>
       </c>
     </row>
     <row r="3050" spans="3:6">
@@ -60900,7 +60912,7 @@
         <v>6100</v>
       </c>
     </row>
-    <row r="3066" ht="15" customHeight="1" spans="3:6">
+    <row r="3066" spans="3:6">
       <c r="C3066" s="3">
         <v>202949</v>
       </c>
@@ -60924,7 +60936,7 @@
         <v>6104</v>
       </c>
     </row>
-    <row r="3068" spans="3:6">
+    <row r="3068" ht="15" customHeight="1" spans="3:6">
       <c r="C3068" s="3">
         <v>202951</v>
       </c>
@@ -61257,7 +61269,7 @@
         <v>6159</v>
       </c>
       <c r="F3095" s="6" t="s">
-        <v>1515</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="3096" spans="3:6">
@@ -61266,10 +61278,10 @@
       </c>
       <c r="D3096" s="4"/>
       <c r="E3096" s="1" t="s">
-        <v>6160</v>
+        <v>6161</v>
       </c>
       <c r="F3096" s="6" t="s">
-        <v>6161</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="3097" spans="3:6">
@@ -61278,10 +61290,10 @@
       </c>
       <c r="D3097" s="4"/>
       <c r="E3097" s="1" t="s">
-        <v>6162</v>
+        <v>6163</v>
       </c>
       <c r="F3097" s="6" t="s">
-        <v>6163</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="3098" spans="3:6">
@@ -61641,7 +61653,7 @@
         <v>6222</v>
       </c>
       <c r="F3127" s="6" t="s">
-        <v>5656</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="3128" spans="3:6">
@@ -61650,10 +61662,10 @@
       </c>
       <c r="D3128" s="4"/>
       <c r="E3128" s="1" t="s">
-        <v>6223</v>
+        <v>6224</v>
       </c>
       <c r="F3128" s="6" t="s">
-        <v>6224</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="3129" spans="3:6">
@@ -61662,10 +61674,10 @@
       </c>
       <c r="D3129" s="4"/>
       <c r="E3129" s="1" t="s">
-        <v>6225</v>
+        <v>6226</v>
       </c>
       <c r="F3129" s="6" t="s">
-        <v>6226</v>
+        <v>5660</v>
       </c>
     </row>
     <row r="3130" spans="3:6">
@@ -62277,7 +62289,7 @@
         <v>6327</v>
       </c>
       <c r="F3180" s="6" t="s">
-        <v>6063</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="3181" spans="3:6">
@@ -62286,10 +62298,10 @@
       </c>
       <c r="D3181" s="4"/>
       <c r="E3181" s="1" t="s">
-        <v>6328</v>
+        <v>6329</v>
       </c>
       <c r="F3181" s="6" t="s">
-        <v>2884</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="3182" spans="3:6">
@@ -62298,10 +62310,10 @@
       </c>
       <c r="D3182" s="4"/>
       <c r="E3182" s="1" t="s">
-        <v>6329</v>
+        <v>6331</v>
       </c>
       <c r="F3182" s="6" t="s">
-        <v>6330</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="3183" spans="3:6">
@@ -62310,10 +62322,10 @@
       </c>
       <c r="D3183" s="4"/>
       <c r="E3183" s="1" t="s">
-        <v>6331</v>
+        <v>6332</v>
       </c>
       <c r="F3183" s="6" t="s">
-        <v>4844</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="3184" spans="3:6">
@@ -62322,10 +62334,10 @@
       </c>
       <c r="D3184" s="4"/>
       <c r="E3184" s="1" t="s">
-        <v>6332</v>
+        <v>6333</v>
       </c>
       <c r="F3184" s="6" t="s">
-        <v>6333</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="3185" spans="3:6">
@@ -62334,10 +62346,10 @@
       </c>
       <c r="D3185" s="4"/>
       <c r="E3185" s="1" t="s">
-        <v>6334</v>
+        <v>6335</v>
       </c>
       <c r="F3185" s="6" t="s">
-        <v>6335</v>
+        <v>4848</v>
       </c>
     </row>
     <row r="3186" spans="3:6">
@@ -62469,7 +62481,7 @@
         <v>6356</v>
       </c>
       <c r="F3196" s="6" t="s">
-        <v>4874</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="3197" spans="3:6">
@@ -62478,10 +62490,10 @@
       </c>
       <c r="D3197" s="4"/>
       <c r="E3197" s="1" t="s">
-        <v>6357</v>
+        <v>6358</v>
       </c>
       <c r="F3197" s="6" t="s">
-        <v>6358</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="3198" spans="3:6">
@@ -62490,10 +62502,10 @@
       </c>
       <c r="D3198" s="4"/>
       <c r="E3198" s="1" t="s">
-        <v>6359</v>
+        <v>6360</v>
       </c>
       <c r="F3198" s="6" t="s">
-        <v>6360</v>
+        <v>4878</v>
       </c>
     </row>
     <row r="3199" spans="3:6">
@@ -62601,7 +62613,7 @@
         <v>6377</v>
       </c>
       <c r="F3207" s="6" t="s">
-        <v>1905</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="3208" spans="3:6">
@@ -62610,10 +62622,10 @@
       </c>
       <c r="D3208" s="4"/>
       <c r="E3208" s="1" t="s">
-        <v>6378</v>
+        <v>6379</v>
       </c>
       <c r="F3208" s="6" t="s">
-        <v>6379</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="3209" spans="3:6">
@@ -62622,10 +62634,10 @@
       </c>
       <c r="D3209" s="4"/>
       <c r="E3209" s="1" t="s">
-        <v>6380</v>
+        <v>6381</v>
       </c>
       <c r="F3209" s="6" t="s">
-        <v>6381</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="3210" spans="3:6">
@@ -62733,7 +62745,7 @@
         <v>6398</v>
       </c>
       <c r="F3218" s="6" t="s">
-        <v>6393</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="3219" spans="3:6">
@@ -62742,10 +62754,10 @@
       </c>
       <c r="D3219" s="4"/>
       <c r="E3219" s="1" t="s">
-        <v>6399</v>
+        <v>6400</v>
       </c>
       <c r="F3219" s="6" t="s">
-        <v>6400</v>
+        <v>6401</v>
       </c>
     </row>
     <row r="3220" spans="3:6">
@@ -62754,10 +62766,10 @@
       </c>
       <c r="D3220" s="4"/>
       <c r="E3220" s="1" t="s">
-        <v>6401</v>
+        <v>6402</v>
       </c>
       <c r="F3220" s="6" t="s">
-        <v>6402</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="3221" spans="3:6">
@@ -63441,7 +63453,7 @@
         <v>6515</v>
       </c>
       <c r="F3277" s="6" t="s">
-        <v>731</v>
+        <v>6516</v>
       </c>
     </row>
     <row r="3278" spans="3:6">
@@ -63450,10 +63462,10 @@
       </c>
       <c r="D3278" s="4"/>
       <c r="E3278" s="1" t="s">
-        <v>6516</v>
+        <v>6517</v>
       </c>
       <c r="F3278" s="6" t="s">
-        <v>6517</v>
+        <v>6518</v>
       </c>
     </row>
     <row r="3279" spans="3:6">
@@ -63462,10 +63474,10 @@
       </c>
       <c r="D3279" s="4"/>
       <c r="E3279" s="1" t="s">
-        <v>6518</v>
+        <v>6519</v>
       </c>
       <c r="F3279" s="6" t="s">
-        <v>6519</v>
+        <v>731</v>
       </c>
     </row>
     <row r="3280" spans="3:6">
@@ -63957,7 +63969,7 @@
         <v>6600</v>
       </c>
       <c r="F3320" s="6" t="s">
-        <v>6589</v>
+        <v>6601</v>
       </c>
     </row>
     <row r="3321" spans="3:6">
@@ -63966,10 +63978,10 @@
       </c>
       <c r="D3321" s="4"/>
       <c r="E3321" s="1" t="s">
-        <v>6601</v>
+        <v>6602</v>
       </c>
       <c r="F3321" s="6" t="s">
-        <v>6602</v>
+        <v>6603</v>
       </c>
     </row>
     <row r="3322" spans="3:6">
@@ -63978,10 +63990,10 @@
       </c>
       <c r="D3322" s="4"/>
       <c r="E3322" s="1" t="s">
-        <v>6603</v>
+        <v>6604</v>
       </c>
       <c r="F3322" s="6" t="s">
-        <v>6604</v>
+        <v>6593</v>
       </c>
     </row>
     <row r="3323" spans="3:6">
@@ -64041,7 +64053,7 @@
         <v>6613</v>
       </c>
       <c r="F3327" s="6" t="s">
-        <v>4866</v>
+        <v>6614</v>
       </c>
     </row>
     <row r="3328" spans="3:6">
@@ -64050,10 +64062,10 @@
       </c>
       <c r="D3328" s="4"/>
       <c r="E3328" s="1" t="s">
-        <v>6614</v>
+        <v>6615</v>
       </c>
       <c r="F3328" s="6" t="s">
-        <v>6615</v>
+        <v>6616</v>
       </c>
     </row>
     <row r="3329" spans="3:6">
@@ -64062,10 +64074,10 @@
       </c>
       <c r="D3329" s="4"/>
       <c r="E3329" s="1" t="s">
-        <v>6616</v>
+        <v>6617</v>
       </c>
       <c r="F3329" s="6" t="s">
-        <v>6617</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="3330" spans="3:6">
@@ -64101,7 +64113,7 @@
         <v>6622</v>
       </c>
       <c r="F3332" s="6" t="s">
-        <v>5769</v>
+        <v>6623</v>
       </c>
     </row>
     <row r="3333" spans="3:6">
@@ -64110,10 +64122,10 @@
       </c>
       <c r="D3333" s="4"/>
       <c r="E3333" s="1" t="s">
-        <v>6623</v>
+        <v>6624</v>
       </c>
       <c r="F3333" s="6" t="s">
-        <v>6624</v>
+        <v>6625</v>
       </c>
     </row>
     <row r="3334" spans="3:6">
@@ -64122,10 +64134,10 @@
       </c>
       <c r="D3334" s="4"/>
       <c r="E3334" s="1" t="s">
-        <v>6625</v>
+        <v>6626</v>
       </c>
       <c r="F3334" s="6" t="s">
-        <v>6626</v>
+        <v>5773</v>
       </c>
     </row>
     <row r="3335" spans="3:6">
@@ -64329,7 +64341,7 @@
         <v>6659</v>
       </c>
       <c r="F3351" s="6" t="s">
-        <v>6652</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="3352" spans="3:6">
@@ -64338,10 +64350,10 @@
       </c>
       <c r="D3352" s="4"/>
       <c r="E3352" s="1" t="s">
-        <v>6660</v>
+        <v>6661</v>
       </c>
       <c r="F3352" s="6" t="s">
-        <v>6661</v>
+        <v>6662</v>
       </c>
     </row>
     <row r="3353" spans="3:6">
@@ -64350,10 +64362,10 @@
       </c>
       <c r="D3353" s="4"/>
       <c r="E3353" s="1" t="s">
-        <v>6662</v>
+        <v>6663</v>
       </c>
       <c r="F3353" s="6" t="s">
-        <v>6663</v>
+        <v>6656</v>
       </c>
     </row>
     <row r="3354" spans="3:6">
@@ -64509,7 +64521,7 @@
         <v>6688</v>
       </c>
       <c r="F3366" s="6" t="s">
-        <v>2858</v>
+        <v>6689</v>
       </c>
     </row>
     <row r="3367" spans="3:6">
@@ -64518,10 +64530,10 @@
       </c>
       <c r="D3367" s="4"/>
       <c r="E3367" s="1" t="s">
-        <v>6689</v>
+        <v>6690</v>
       </c>
       <c r="F3367" s="6" t="s">
-        <v>6690</v>
+        <v>6691</v>
       </c>
     </row>
     <row r="3368" spans="3:6">
@@ -64530,10 +64542,10 @@
       </c>
       <c r="D3368" s="4"/>
       <c r="E3368" s="1" t="s">
-        <v>6691</v>
+        <v>6692</v>
       </c>
       <c r="F3368" s="6" t="s">
-        <v>2860</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="3369" spans="3:6">
@@ -64542,10 +64554,10 @@
       </c>
       <c r="D3369" s="4"/>
       <c r="E3369" s="1" t="s">
-        <v>6692</v>
+        <v>6693</v>
       </c>
       <c r="F3369" s="6" t="s">
-        <v>6693</v>
+        <v>6694</v>
       </c>
     </row>
     <row r="3370" spans="3:6">
@@ -64554,10 +64566,10 @@
       </c>
       <c r="D3370" s="4"/>
       <c r="E3370" s="1" t="s">
-        <v>6694</v>
+        <v>6695</v>
       </c>
       <c r="F3370" s="6" t="s">
-        <v>6695</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="3371" spans="3:6">
@@ -65109,7 +65121,7 @@
         <v>6786</v>
       </c>
       <c r="F3416" s="6" t="s">
-        <v>5587</v>
+        <v>6787</v>
       </c>
     </row>
     <row r="3417" spans="3:6">
@@ -65118,10 +65130,10 @@
       </c>
       <c r="D3417" s="4"/>
       <c r="E3417" s="1" t="s">
-        <v>6787</v>
+        <v>6788</v>
       </c>
       <c r="F3417" s="6" t="s">
-        <v>6788</v>
+        <v>6789</v>
       </c>
     </row>
     <row r="3418" spans="3:6">
@@ -65130,10 +65142,10 @@
       </c>
       <c r="D3418" s="4"/>
       <c r="E3418" s="1" t="s">
-        <v>6789</v>
+        <v>6790</v>
       </c>
       <c r="F3418" s="6" t="s">
-        <v>6790</v>
+        <v>5591</v>
       </c>
     </row>
     <row r="3419" spans="3:6">
@@ -65421,7 +65433,7 @@
         <v>6837</v>
       </c>
       <c r="F3442" s="6" t="s">
-        <v>6818</v>
+        <v>6838</v>
       </c>
     </row>
     <row r="3443" spans="3:6">
@@ -65430,10 +65442,10 @@
       </c>
       <c r="D3443" s="4"/>
       <c r="E3443" s="1" t="s">
-        <v>6838</v>
+        <v>6839</v>
       </c>
       <c r="F3443" s="6" t="s">
-        <v>6839</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="3444" spans="3:6">
@@ -65442,10 +65454,10 @@
       </c>
       <c r="D3444" s="4"/>
       <c r="E3444" s="1" t="s">
-        <v>6840</v>
+        <v>6841</v>
       </c>
       <c r="F3444" s="6" t="s">
-        <v>6841</v>
+        <v>6822</v>
       </c>
     </row>
     <row r="3445" spans="3:6">
@@ -65673,7 +65685,7 @@
         <v>6878</v>
       </c>
       <c r="F3463" s="6" t="s">
-        <v>2732</v>
+        <v>6879</v>
       </c>
     </row>
     <row r="3464" spans="3:6">
@@ -65682,10 +65694,10 @@
       </c>
       <c r="D3464" s="4"/>
       <c r="E3464" s="1" t="s">
-        <v>6879</v>
+        <v>6880</v>
       </c>
       <c r="F3464" s="6" t="s">
-        <v>6880</v>
+        <v>6881</v>
       </c>
     </row>
     <row r="3465" spans="3:6">
@@ -65694,10 +65706,10 @@
       </c>
       <c r="D3465" s="4"/>
       <c r="E3465" s="1" t="s">
-        <v>6881</v>
+        <v>6882</v>
       </c>
       <c r="F3465" s="6" t="s">
-        <v>6882</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="3466" spans="3:6">
@@ -65877,7 +65889,7 @@
         <v>6911</v>
       </c>
       <c r="F3480" s="6" t="s">
-        <v>6059</v>
+        <v>6912</v>
       </c>
     </row>
     <row r="3481" spans="3:6">
@@ -65886,10 +65898,10 @@
       </c>
       <c r="D3481" s="4"/>
       <c r="E3481" s="1" t="s">
-        <v>6912</v>
+        <v>6913</v>
       </c>
       <c r="F3481" s="6" t="s">
-        <v>2765</v>
+        <v>6914</v>
       </c>
     </row>
     <row r="3482" spans="3:6">
@@ -65898,10 +65910,10 @@
       </c>
       <c r="D3482" s="4"/>
       <c r="E3482" s="1" t="s">
-        <v>6913</v>
+        <v>6915</v>
       </c>
       <c r="F3482" s="6" t="s">
-        <v>6914</v>
+        <v>6063</v>
       </c>
     </row>
     <row r="3483" spans="3:6">
@@ -65910,10 +65922,10 @@
       </c>
       <c r="D3483" s="4"/>
       <c r="E3483" s="1" t="s">
-        <v>6915</v>
+        <v>6916</v>
       </c>
       <c r="F3483" s="6" t="s">
-        <v>6916</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="3484" spans="3:6">
@@ -65937,7 +65949,7 @@
         <v>6919</v>
       </c>
       <c r="F3485" s="6" t="s">
-        <v>6102</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="3486" spans="3:6">
@@ -65946,10 +65958,10 @@
       </c>
       <c r="D3486" s="4"/>
       <c r="E3486" s="1" t="s">
-        <v>6920</v>
+        <v>6921</v>
       </c>
       <c r="F3486" s="6" t="s">
-        <v>6921</v>
+        <v>6922</v>
       </c>
     </row>
     <row r="3487" spans="3:6">
@@ -65958,10 +65970,10 @@
       </c>
       <c r="D3487" s="4"/>
       <c r="E3487" s="1" t="s">
-        <v>6922</v>
+        <v>6923</v>
       </c>
       <c r="F3487" s="6" t="s">
-        <v>6923</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="3488" spans="3:6">
@@ -66657,7 +66669,7 @@
         <v>7038</v>
       </c>
       <c r="F3545" s="6" t="s">
-        <v>1261</v>
+        <v>7039</v>
       </c>
     </row>
     <row r="3546" spans="3:6">
@@ -66666,10 +66678,10 @@
       </c>
       <c r="D3546" s="4"/>
       <c r="E3546" s="1" t="s">
-        <v>7039</v>
+        <v>7040</v>
       </c>
       <c r="F3546" s="6" t="s">
-        <v>7040</v>
+        <v>7041</v>
       </c>
     </row>
     <row r="3547" spans="3:6">
@@ -66678,10 +66690,10 @@
       </c>
       <c r="D3547" s="4"/>
       <c r="E3547" s="1" t="s">
-        <v>7041</v>
+        <v>7042</v>
       </c>
       <c r="F3547" s="6" t="s">
-        <v>7042</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="3548" spans="3:6">
@@ -67317,7 +67329,7 @@
         <v>7147</v>
       </c>
       <c r="F3600" s="6" t="s">
-        <v>4864</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="3601" spans="3:6">
@@ -67326,10 +67338,10 @@
       </c>
       <c r="D3601" s="4"/>
       <c r="E3601" s="1" t="s">
-        <v>7148</v>
+        <v>7149</v>
       </c>
       <c r="F3601" s="6" t="s">
-        <v>7149</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="3602" spans="3:6">
@@ -67338,10 +67350,10 @@
       </c>
       <c r="D3602" s="4"/>
       <c r="E3602" s="1" t="s">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="F3602" s="6" t="s">
-        <v>7151</v>
+        <v>4868</v>
       </c>
     </row>
     <row r="3603" spans="3:6">
@@ -67749,7 +67761,7 @@
         <v>7218</v>
       </c>
       <c r="F3636" s="6" t="s">
-        <v>6847</v>
+        <v>7219</v>
       </c>
     </row>
     <row r="3637" spans="3:6">
@@ -67758,10 +67770,10 @@
       </c>
       <c r="D3637" s="4"/>
       <c r="E3637" s="1" t="s">
-        <v>7219</v>
+        <v>7220</v>
       </c>
       <c r="F3637" s="6" t="s">
-        <v>7220</v>
+        <v>7221</v>
       </c>
     </row>
     <row r="3638" spans="3:6">
@@ -67770,10 +67782,10 @@
       </c>
       <c r="D3638" s="4"/>
       <c r="E3638" s="1" t="s">
-        <v>7221</v>
+        <v>7222</v>
       </c>
       <c r="F3638" s="6" t="s">
-        <v>7222</v>
+        <v>6851</v>
       </c>
     </row>
     <row r="3639" spans="3:6">
@@ -68517,7 +68529,7 @@
         <v>7345</v>
       </c>
       <c r="F3700" s="6" t="s">
-        <v>4866</v>
+        <v>7346</v>
       </c>
     </row>
     <row r="3701" spans="3:6">
@@ -68526,10 +68538,10 @@
       </c>
       <c r="D3701" s="4"/>
       <c r="E3701" s="1" t="s">
-        <v>7346</v>
+        <v>7347</v>
       </c>
       <c r="F3701" s="6" t="s">
-        <v>7347</v>
+        <v>7348</v>
       </c>
     </row>
     <row r="3702" spans="3:6">
@@ -68538,10 +68550,10 @@
       </c>
       <c r="D3702" s="4"/>
       <c r="E3702" s="1" t="s">
-        <v>7348</v>
+        <v>7349</v>
       </c>
       <c r="F3702" s="6" t="s">
-        <v>4864</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="3703" spans="3:6">
@@ -68550,10 +68562,10 @@
       </c>
       <c r="D3703" s="4"/>
       <c r="E3703" s="1" t="s">
-        <v>7349</v>
+        <v>7350</v>
       </c>
       <c r="F3703" s="6" t="s">
-        <v>7350</v>
+        <v>7351</v>
       </c>
     </row>
     <row r="3704" spans="3:6">
@@ -68562,10 +68574,10 @@
       </c>
       <c r="D3704" s="4"/>
       <c r="E3704" s="1" t="s">
-        <v>7351</v>
+        <v>7352</v>
       </c>
       <c r="F3704" s="6" t="s">
-        <v>7352</v>
+        <v>4868</v>
       </c>
     </row>
     <row r="3705" spans="3:6">
@@ -68673,7 +68685,7 @@
         <v>7369</v>
       </c>
       <c r="F3713" s="6" t="s">
-        <v>7084</v>
+        <v>7370</v>
       </c>
     </row>
     <row r="3714" spans="3:6">
@@ -68682,10 +68694,10 @@
       </c>
       <c r="D3714" s="4"/>
       <c r="E3714" s="1" t="s">
-        <v>7370</v>
+        <v>7371</v>
       </c>
       <c r="F3714" s="6" t="s">
-        <v>7371</v>
+        <v>7372</v>
       </c>
     </row>
     <row r="3715" spans="3:6">
@@ -68694,10 +68706,10 @@
       </c>
       <c r="D3715" s="4"/>
       <c r="E3715" s="1" t="s">
-        <v>7372</v>
+        <v>7373</v>
       </c>
       <c r="F3715" s="6" t="s">
-        <v>7373</v>
+        <v>7088</v>
       </c>
     </row>
     <row r="3716" spans="3:6">
@@ -69357,7 +69369,7 @@
         <v>7482</v>
       </c>
       <c r="F3770" s="6" t="s">
-        <v>3821</v>
+        <v>7483</v>
       </c>
     </row>
     <row r="3771" spans="3:6">
@@ -69366,10 +69378,10 @@
       </c>
       <c r="D3771" s="4"/>
       <c r="E3771" s="1" t="s">
-        <v>7483</v>
+        <v>7484</v>
       </c>
       <c r="F3771" s="6" t="s">
-        <v>7484</v>
+        <v>7485</v>
       </c>
     </row>
     <row r="3772" spans="3:6">
@@ -69378,10 +69390,10 @@
       </c>
       <c r="D3772" s="4"/>
       <c r="E3772" s="1" t="s">
-        <v>7485</v>
+        <v>7486</v>
       </c>
       <c r="F3772" s="6" t="s">
-        <v>7486</v>
+        <v>3821</v>
       </c>
     </row>
     <row r="3773" spans="3:6">
@@ -69825,7 +69837,7 @@
         <v>7559</v>
       </c>
       <c r="F3809" s="6" t="s">
-        <v>4860</v>
+        <v>7560</v>
       </c>
     </row>
     <row r="3810" spans="3:6">
@@ -69834,10 +69846,10 @@
       </c>
       <c r="D3810" s="4"/>
       <c r="E3810" s="1" t="s">
-        <v>7560</v>
+        <v>7561</v>
       </c>
       <c r="F3810" s="6" t="s">
-        <v>7561</v>
+        <v>7562</v>
       </c>
     </row>
     <row r="3811" spans="3:6">
@@ -69846,10 +69858,10 @@
       </c>
       <c r="D3811" s="4"/>
       <c r="E3811" s="1" t="s">
-        <v>7562</v>
+        <v>7563</v>
       </c>
       <c r="F3811" s="6" t="s">
-        <v>7563</v>
+        <v>4864</v>
       </c>
     </row>
     <row r="3812" spans="3:6">
@@ -69921,31 +69933,31 @@
         <v>7574</v>
       </c>
       <c r="F3817" s="6" t="s">
-        <v>5873</v>
+        <v>7575</v>
       </c>
     </row>
     <row r="3818" spans="3:6">
       <c r="C3818" s="3">
         <v>203701</v>
       </c>
-      <c r="D3818"/>
+      <c r="D3818" s="4"/>
       <c r="E3818" s="1" t="s">
-        <v>7575</v>
+        <v>7576</v>
       </c>
       <c r="F3818" s="6" t="s">
-        <v>7576</v>
+        <v>7577</v>
       </c>
     </row>
     <row r="3819" spans="3:6">
       <c r="C3819" s="3">
         <v>203702</v>
       </c>
-      <c r="D3819"/>
+      <c r="D3819" s="4"/>
       <c r="E3819" s="1" t="s">
-        <v>7577</v>
+        <v>7578</v>
       </c>
       <c r="F3819" s="6" t="s">
-        <v>7578</v>
+        <v>5877</v>
       </c>
     </row>
     <row r="3820" spans="3:6">
@@ -69957,7 +69969,7 @@
         <v>7579</v>
       </c>
       <c r="F3820" s="6" t="s">
-        <v>390</v>
+        <v>7580</v>
       </c>
     </row>
     <row r="3821" spans="3:6">
@@ -69966,34 +69978,34 @@
       </c>
       <c r="D3821"/>
       <c r="E3821" s="1" t="s">
-        <v>7580</v>
+        <v>7581</v>
       </c>
       <c r="F3821" s="6" t="s">
-        <v>7581</v>
+        <v>7582</v>
       </c>
     </row>
     <row r="3822" spans="3:6">
       <c r="C3822" s="3">
         <v>203705</v>
       </c>
-      <c r="D3822" s="4"/>
+      <c r="D3822"/>
       <c r="E3822" s="1" t="s">
-        <v>7582</v>
+        <v>7583</v>
       </c>
       <c r="F3822" s="6" t="s">
-        <v>7583</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3823" spans="3:6">
       <c r="C3823" s="3">
         <v>203706</v>
       </c>
-      <c r="D3823" s="4"/>
+      <c r="D3823"/>
       <c r="E3823" s="1" t="s">
         <v>7584</v>
       </c>
       <c r="F3823" s="6" t="s">
-        <v>1280</v>
+        <v>7585</v>
       </c>
     </row>
     <row r="3824" spans="3:6">
@@ -70002,10 +70014,10 @@
       </c>
       <c r="D3824" s="4"/>
       <c r="E3824" s="1" t="s">
-        <v>7585</v>
+        <v>7586</v>
       </c>
       <c r="F3824" s="6" t="s">
-        <v>1284</v>
+        <v>7587</v>
       </c>
     </row>
     <row r="3825" spans="3:6">
@@ -70014,10 +70026,10 @@
       </c>
       <c r="D3825" s="4"/>
       <c r="E3825" s="1" t="s">
-        <v>7586</v>
+        <v>7588</v>
       </c>
       <c r="F3825" s="6" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="3826" spans="3:6">
@@ -70026,10 +70038,10 @@
       </c>
       <c r="D3826" s="4"/>
       <c r="E3826" s="1" t="s">
-        <v>7587</v>
+        <v>7589</v>
       </c>
       <c r="F3826" s="6" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="3827" spans="3:6">
@@ -70038,10 +70050,10 @@
       </c>
       <c r="D3827" s="4"/>
       <c r="E3827" s="1" t="s">
-        <v>7588</v>
+        <v>7590</v>
       </c>
       <c r="F3827" s="6" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="3828" spans="3:6">
@@ -70050,10 +70062,10 @@
       </c>
       <c r="D3828" s="4"/>
       <c r="E3828" s="1" t="s">
-        <v>7589</v>
+        <v>7591</v>
       </c>
       <c r="F3828" s="6" t="s">
-        <v>7590</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="3829" spans="3:6">
@@ -70062,10 +70074,10 @@
       </c>
       <c r="D3829" s="4"/>
       <c r="E3829" s="1" t="s">
-        <v>7591</v>
+        <v>7592</v>
       </c>
       <c r="F3829" s="6" t="s">
-        <v>7592</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="3830" spans="3:6">
@@ -70125,7 +70137,7 @@
         <v>7601</v>
       </c>
       <c r="F3834" s="6" t="s">
-        <v>1450</v>
+        <v>7602</v>
       </c>
     </row>
     <row r="3835" spans="3:6">
@@ -70134,10 +70146,10 @@
       </c>
       <c r="D3835" s="4"/>
       <c r="E3835" s="1" t="s">
-        <v>7602</v>
+        <v>7603</v>
       </c>
       <c r="F3835" s="6" t="s">
-        <v>7603</v>
+        <v>7604</v>
       </c>
     </row>
     <row r="3836" spans="3:6">
@@ -70146,10 +70158,10 @@
       </c>
       <c r="D3836" s="4"/>
       <c r="E3836" s="1" t="s">
-        <v>7604</v>
-      </c>
-      <c r="F3836" s="8" t="s">
         <v>7605</v>
+      </c>
+      <c r="F3836" s="6" t="s">
+        <v>1450</v>
       </c>
     </row>
     <row r="3837" spans="3:6">
@@ -70160,7 +70172,7 @@
       <c r="E3837" s="1" t="s">
         <v>7606</v>
       </c>
-      <c r="F3837" s="8" t="s">
+      <c r="F3837" s="6" t="s">
         <v>7607</v>
       </c>
     </row>
@@ -70225,16 +70237,28 @@
       </c>
     </row>
     <row r="3843" spans="3:6">
-      <c r="C3843"/>
-      <c r="D3843"/>
-      <c r="E3843"/>
-      <c r="F3843"/>
+      <c r="C3843" s="3">
+        <v>203726</v>
+      </c>
+      <c r="D3843" s="4"/>
+      <c r="E3843" s="1" t="s">
+        <v>7618</v>
+      </c>
+      <c r="F3843" s="8" t="s">
+        <v>7619</v>
+      </c>
     </row>
     <row r="3844" spans="3:6">
-      <c r="C3844"/>
-      <c r="D3844"/>
-      <c r="E3844"/>
-      <c r="F3844"/>
+      <c r="C3844" s="3">
+        <v>203727</v>
+      </c>
+      <c r="D3844" s="4"/>
+      <c r="E3844" s="1" t="s">
+        <v>7620</v>
+      </c>
+      <c r="F3844" s="8" t="s">
+        <v>7621</v>
+      </c>
     </row>
     <row r="3845" spans="3:6">
       <c r="C3845"/>
@@ -71135,6 +71159,18 @@
       <c r="D3994"/>
       <c r="E3994"/>
       <c r="F3994"/>
+    </row>
+    <row r="3995" spans="3:6">
+      <c r="C3995"/>
+      <c r="D3995"/>
+      <c r="E3995"/>
+      <c r="F3995"/>
+    </row>
+    <row r="3996" spans="3:6">
+      <c r="C3996"/>
+      <c r="D3996"/>
+      <c r="E3996"/>
+      <c r="F3996"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7805" uniqueCount="7622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7894" uniqueCount="7704">
   <si>
     <t>c</t>
   </si>
@@ -22893,6 +22893,252 @@
   </si>
   <si>
     <t>Arena</t>
+  </si>
+  <si>
+    <t>合区补偿</t>
+  </si>
+  <si>
+    <t>Zone-wide compensation</t>
+  </si>
+  <si>
+    <t>合区补偿改名卡</t>
+  </si>
+  <si>
+    <t>Union Area Compensation Renaming Card</t>
+  </si>
+  <si>
+    <t>角斗场排名奖励</t>
+  </si>
+  <si>
+    <t>Gladiator Ranking Reward</t>
+  </si>
+  <si>
+    <t>恭喜你在角斗场中获得第{0}名,获得如下奖励</t>
+  </si>
+  <si>
+    <t>Congratulations! You have won the {0}th place in the arena and received the following rewards.</t>
+  </si>
+  <si>
+    <t>参与角斗场,获得如下奖励</t>
+  </si>
+  <si>
+    <t>Participate in the arena and receive the following rewards</t>
+  </si>
+  <si>
+    <t>战场奖励</t>
+  </si>
+  <si>
+    <t>Battlefield Rewards</t>
+  </si>
+  <si>
+    <t>恶魔活动奖励</t>
+  </si>
+  <si>
+    <t>Demonic Activity Reward</t>
+  </si>
+  <si>
+    <t>恶魔活动胜利奖励</t>
+  </si>
+  <si>
+    <t>Reward for the Success of Demon Activities</t>
+  </si>
+  <si>
+    <t>恶魔活动参与奖励</t>
+  </si>
+  <si>
+    <t>Reward for participating in demon activities</t>
+  </si>
+  <si>
+    <t>秘境领主排名奖励</t>
+  </si>
+  <si>
+    <t>Reward for the ranking in the Secret Realm Lord Competition</t>
+  </si>
+  <si>
+    <t>恭喜你在秘境中获得第{0}名,获得如下奖励</t>
+  </si>
+  <si>
+    <t>Congratulations! You have ranked {0}th in the secret area and received the following rewards.</t>
+  </si>
+  <si>
+    <t>竞拍道具</t>
+  </si>
+  <si>
+    <t>Bidding for props</t>
+  </si>
+  <si>
+    <t>金币小于{0},竞拍失败</t>
+  </si>
+  <si>
+    <t>The gold coin is less than {0}, the auction failed.</t>
+  </si>
+  <si>
+    <t>竞拍失败</t>
+  </si>
+  <si>
+    <t>The auction failed.</t>
+  </si>
+  <si>
+    <t>退还保证金</t>
+  </si>
+  <si>
+    <t>Refund of deposit</t>
+  </si>
+  <si>
+    <t>恶魔排行榜奖励</t>
+  </si>
+  <si>
+    <t>Demonic Ranking List Reward</t>
+  </si>
+  <si>
+    <t>恭喜您获得恶魔排行榜第{0}名奖励</t>
+  </si>
+  <si>
+    <t>Congratulations! You have been awarded the reward for being ranked {0}th on the Demon Ranking List.</t>
+  </si>
+  <si>
+    <t>家族战排行榜奖励</t>
+  </si>
+  <si>
+    <t>Family Battle Ranking Rewards</t>
+  </si>
+  <si>
+    <t>恭喜您获得家族战排行榜第{0}名奖励</t>
+  </si>
+  <si>
+    <t>Congratulations! You have been awarded the Family Battle Ranking 1st place prize.</t>
+  </si>
+  <si>
+    <t>狩猎排行榜奖励</t>
+  </si>
+  <si>
+    <t>Hunting Ranking Rewards</t>
+  </si>
+  <si>
+    <t>恭喜您获得狩猎排行榜第{0}名奖励</t>
+  </si>
+  <si>
+    <t>Congratulations! You have been awarded the prize for being ranked {0}th on the hunting leaderboard.</t>
+  </si>
+  <si>
+    <t>Ranking list rewards</t>
+  </si>
+  <si>
+    <t>恭喜您获得试炼排行榜第{0}名奖励</t>
+  </si>
+  <si>
+    <t>Congratulations! You have been awarded the prize for ranking {0}th on the Trial Leaderboard.</t>
+  </si>
+  <si>
+    <t>赛季之塔奖励</t>
+  </si>
+  <si>
+    <t>Season Tower Reward</t>
+  </si>
+  <si>
+    <t>恭喜您获得赛季之塔第{0}名奖励</t>
+  </si>
+  <si>
+    <t>Congratulations! You have received the Season Tower {0}th place award.</t>
+  </si>
+  <si>
+    <t>恭喜您获得排行榜第{0}名奖励</t>
+  </si>
+  <si>
+    <t>Congratulations! You have been awarded the prize for ranking {0}th on the leaderboard.</t>
+  </si>
+  <si>
+    <t>赛跑大赛排行榜奖励</t>
+  </si>
+  <si>
+    <t>Race Competition Ranking Awards</t>
+  </si>
+  <si>
+    <t>竞技场第{0}名</t>
+  </si>
+  <si>
+    <t>The {0}th place in the arena</t>
+  </si>
+  <si>
+    <t>恭喜你获得竞技场第{0}名,奖励如下</t>
+  </si>
+  <si>
+    <t>Congratulations! You have won the {0}th place in the arena. The rewards are as follows.</t>
+  </si>
+  <si>
+    <t>家族争霸赛奖励</t>
+  </si>
+  <si>
+    <t>Family Championship Competition Rewards</t>
+  </si>
+  <si>
+    <t>发送家族争霸赛胜利奖励</t>
+  </si>
+  <si>
+    <t>Send the victory rewards for the clan championship competition</t>
+  </si>
+  <si>
+    <t>发送家族争霸赛失败奖励</t>
+  </si>
+  <si>
+    <t>Send the failure reward of the clan championship competition</t>
+  </si>
+  <si>
+    <t>首杀奖励</t>
+  </si>
+  <si>
+    <t>First Kill Reward</t>
+  </si>
+  <si>
+    <t>小龟竞猜奖励</t>
+  </si>
+  <si>
+    <t>Little Turtle's Guessing Contest Reward</t>
+  </si>
+  <si>
+    <t>拍卖下架</t>
+  </si>
+  <si>
+    <t>Auction has been removed from listing.</t>
+  </si>
+  <si>
+    <t>福利发放</t>
+  </si>
+  <si>
+    <t>Distribution of benefits</t>
+  </si>
+  <si>
+    <t>Copy Reward</t>
+  </si>
+  <si>
+    <t>Family Upgrade</t>
+  </si>
+  <si>
+    <t>恭喜您!您所在得家族等级获得提升,这是家族升级的奖励!</t>
+  </si>
+  <si>
+    <t>Congratulations! Your family's rank has been upgraded. This is a reward for your family's upgrade.</t>
+  </si>
+  <si>
+    <t>拍卖行邮件</t>
+  </si>
+  <si>
+    <t>Auction House Email</t>
+  </si>
+  <si>
+    <t>你拍卖行出售的道具:{0},已经被其他玩家购买{1}个。</t>
+  </si>
+  <si>
+    <t>The props sold by your auction house: {0}, have been purchased by other players {1} times.</t>
+  </si>
+  <si>
+    <t>全服补偿邮件</t>
+  </si>
+  <si>
+    <t>Global Server Compensation Email</t>
+  </si>
+  <si>
+    <t>Season-end rewards</t>
   </si>
 </sst>
 </file>
@@ -23901,7 +24147,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:F3996"/>
+  <dimension ref="C2:F3993"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -70261,268 +70507,534 @@
       </c>
     </row>
     <row r="3845" spans="3:6">
-      <c r="C3845"/>
-      <c r="D3845"/>
-      <c r="E3845"/>
-      <c r="F3845"/>
+      <c r="C3845" s="3">
+        <v>300001</v>
+      </c>
+      <c r="D3845" s="4" t="s">
+        <v>1962</v>
+      </c>
+      <c r="E3845" s="1" t="s">
+        <v>7622</v>
+      </c>
+      <c r="F3845" s="8" t="s">
+        <v>7623</v>
+      </c>
     </row>
     <row r="3846" spans="3:6">
-      <c r="C3846"/>
-      <c r="D3846"/>
-      <c r="E3846"/>
-      <c r="F3846"/>
+      <c r="C3846" s="3">
+        <v>300002</v>
+      </c>
+      <c r="D3846" s="4"/>
+      <c r="E3846" s="1" t="s">
+        <v>7624</v>
+      </c>
+      <c r="F3846" s="8" t="s">
+        <v>7625</v>
+      </c>
     </row>
     <row r="3847" spans="3:6">
-      <c r="C3847"/>
-      <c r="D3847"/>
-      <c r="E3847"/>
-      <c r="F3847"/>
+      <c r="C3847" s="3">
+        <v>300003</v>
+      </c>
+      <c r="D3847" s="4"/>
+      <c r="E3847" s="1" t="s">
+        <v>7626</v>
+      </c>
+      <c r="F3847" s="8" t="s">
+        <v>7627</v>
+      </c>
     </row>
     <row r="3848" spans="3:6">
-      <c r="C3848"/>
-      <c r="D3848"/>
-      <c r="E3848"/>
-      <c r="F3848"/>
+      <c r="C3848" s="3">
+        <v>300004</v>
+      </c>
+      <c r="D3848" s="4"/>
+      <c r="E3848" s="1" t="s">
+        <v>7628</v>
+      </c>
+      <c r="F3848" s="8" t="s">
+        <v>7629</v>
+      </c>
     </row>
     <row r="3849" spans="3:6">
-      <c r="C3849"/>
-      <c r="D3849"/>
-      <c r="E3849"/>
-      <c r="F3849"/>
+      <c r="C3849" s="3">
+        <v>300005</v>
+      </c>
+      <c r="D3849" s="4"/>
+      <c r="E3849" s="1" t="s">
+        <v>7630</v>
+      </c>
+      <c r="F3849" s="8" t="s">
+        <v>7631</v>
+      </c>
     </row>
     <row r="3850" spans="3:6">
-      <c r="C3850"/>
-      <c r="D3850"/>
-      <c r="E3850"/>
-      <c r="F3850"/>
+      <c r="C3850" s="3">
+        <v>300006</v>
+      </c>
+      <c r="D3850" s="4"/>
+      <c r="E3850" s="1" t="s">
+        <v>7632</v>
+      </c>
+      <c r="F3850" s="8" t="s">
+        <v>7633</v>
+      </c>
     </row>
     <row r="3851" spans="3:6">
-      <c r="C3851"/>
-      <c r="D3851"/>
-      <c r="E3851"/>
-      <c r="F3851"/>
+      <c r="C3851" s="3">
+        <v>300007</v>
+      </c>
+      <c r="D3851" s="4"/>
+      <c r="E3851" s="1" t="s">
+        <v>7634</v>
+      </c>
+      <c r="F3851" s="8" t="s">
+        <v>7635</v>
+      </c>
     </row>
     <row r="3852" spans="3:6">
-      <c r="C3852"/>
-      <c r="D3852"/>
-      <c r="E3852"/>
-      <c r="F3852"/>
+      <c r="C3852" s="3">
+        <v>300008</v>
+      </c>
+      <c r="D3852" s="4"/>
+      <c r="E3852" s="1" t="s">
+        <v>7636</v>
+      </c>
+      <c r="F3852" s="8" t="s">
+        <v>7637</v>
+      </c>
     </row>
     <row r="3853" spans="3:6">
-      <c r="C3853"/>
-      <c r="D3853"/>
-      <c r="E3853"/>
-      <c r="F3853"/>
+      <c r="C3853" s="3">
+        <v>300009</v>
+      </c>
+      <c r="D3853" s="4"/>
+      <c r="E3853" s="1" t="s">
+        <v>7638</v>
+      </c>
+      <c r="F3853" s="8" t="s">
+        <v>7639</v>
+      </c>
     </row>
     <row r="3854" spans="3:6">
-      <c r="C3854"/>
-      <c r="D3854"/>
-      <c r="E3854"/>
-      <c r="F3854"/>
+      <c r="C3854" s="3">
+        <v>300010</v>
+      </c>
+      <c r="D3854" s="4"/>
+      <c r="E3854" s="1" t="s">
+        <v>7640</v>
+      </c>
+      <c r="F3854" s="8" t="s">
+        <v>7641</v>
+      </c>
     </row>
     <row r="3855" spans="3:6">
-      <c r="C3855"/>
-      <c r="D3855"/>
-      <c r="E3855"/>
-      <c r="F3855"/>
+      <c r="C3855" s="3">
+        <v>300011</v>
+      </c>
+      <c r="D3855" s="4"/>
+      <c r="E3855" s="1" t="s">
+        <v>7642</v>
+      </c>
+      <c r="F3855" s="8" t="s">
+        <v>7643</v>
+      </c>
     </row>
     <row r="3856" spans="3:6">
-      <c r="C3856"/>
-      <c r="D3856"/>
-      <c r="E3856"/>
-      <c r="F3856"/>
+      <c r="C3856" s="3">
+        <v>300012</v>
+      </c>
+      <c r="D3856" s="4"/>
+      <c r="E3856" s="1" t="s">
+        <v>7644</v>
+      </c>
+      <c r="F3856" s="8" t="s">
+        <v>7645</v>
+      </c>
     </row>
     <row r="3857" spans="3:6">
-      <c r="C3857"/>
-      <c r="D3857"/>
-      <c r="E3857"/>
-      <c r="F3857"/>
+      <c r="C3857" s="3">
+        <v>300013</v>
+      </c>
+      <c r="D3857" s="4"/>
+      <c r="E3857" s="1" t="s">
+        <v>7646</v>
+      </c>
+      <c r="F3857" s="8" t="s">
+        <v>7647</v>
+      </c>
     </row>
     <row r="3858" spans="3:6">
-      <c r="C3858"/>
-      <c r="D3858"/>
-      <c r="E3858"/>
-      <c r="F3858"/>
+      <c r="C3858" s="3">
+        <v>300014</v>
+      </c>
+      <c r="D3858" s="4"/>
+      <c r="E3858" s="1" t="s">
+        <v>7648</v>
+      </c>
+      <c r="F3858" s="8" t="s">
+        <v>7649</v>
+      </c>
     </row>
     <row r="3859" spans="3:6">
-      <c r="C3859"/>
-      <c r="D3859"/>
-      <c r="E3859"/>
-      <c r="F3859"/>
+      <c r="C3859" s="3">
+        <v>300015</v>
+      </c>
+      <c r="D3859" s="4"/>
+      <c r="E3859" s="1" t="s">
+        <v>7650</v>
+      </c>
+      <c r="F3859" s="8" t="s">
+        <v>7651</v>
+      </c>
     </row>
     <row r="3860" spans="3:6">
-      <c r="C3860"/>
-      <c r="D3860"/>
-      <c r="E3860"/>
-      <c r="F3860"/>
+      <c r="C3860" s="3">
+        <v>300016</v>
+      </c>
+      <c r="D3860" s="4"/>
+      <c r="E3860" s="1" t="s">
+        <v>7652</v>
+      </c>
+      <c r="F3860" s="8" t="s">
+        <v>7653</v>
+      </c>
     </row>
     <row r="3861" spans="3:6">
-      <c r="C3861"/>
-      <c r="D3861"/>
-      <c r="E3861"/>
-      <c r="F3861"/>
+      <c r="C3861" s="3">
+        <v>300017</v>
+      </c>
+      <c r="D3861" s="4"/>
+      <c r="E3861" s="1" t="s">
+        <v>7654</v>
+      </c>
+      <c r="F3861" s="8" t="s">
+        <v>7655</v>
+      </c>
     </row>
     <row r="3862" spans="3:6">
-      <c r="C3862"/>
-      <c r="D3862"/>
-      <c r="E3862"/>
-      <c r="F3862"/>
+      <c r="C3862" s="3">
+        <v>300018</v>
+      </c>
+      <c r="D3862" s="4"/>
+      <c r="E3862" s="1" t="s">
+        <v>7656</v>
+      </c>
+      <c r="F3862" s="8" t="s">
+        <v>7657</v>
+      </c>
     </row>
     <row r="3863" spans="3:6">
-      <c r="C3863"/>
-      <c r="D3863"/>
-      <c r="E3863"/>
-      <c r="F3863"/>
+      <c r="C3863" s="3">
+        <v>300019</v>
+      </c>
+      <c r="D3863" s="4"/>
+      <c r="E3863" s="1" t="s">
+        <v>7658</v>
+      </c>
+      <c r="F3863" s="8" t="s">
+        <v>7659</v>
+      </c>
     </row>
     <row r="3864" spans="3:6">
-      <c r="C3864"/>
-      <c r="D3864"/>
-      <c r="E3864"/>
-      <c r="F3864"/>
+      <c r="C3864" s="3">
+        <v>300020</v>
+      </c>
+      <c r="D3864" s="4"/>
+      <c r="E3864" s="1" t="s">
+        <v>7660</v>
+      </c>
+      <c r="F3864" s="8" t="s">
+        <v>7661</v>
+      </c>
     </row>
     <row r="3865" spans="3:6">
-      <c r="C3865"/>
-      <c r="D3865"/>
-      <c r="E3865"/>
-      <c r="F3865"/>
+      <c r="C3865" s="3">
+        <v>300021</v>
+      </c>
+      <c r="D3865" s="4"/>
+      <c r="E3865" s="1" t="s">
+        <v>7662</v>
+      </c>
+      <c r="F3865" s="8" t="s">
+        <v>7663</v>
+      </c>
     </row>
     <row r="3866" spans="3:6">
-      <c r="C3866"/>
-      <c r="D3866"/>
-      <c r="E3866"/>
-      <c r="F3866"/>
+      <c r="C3866" s="3">
+        <v>300022</v>
+      </c>
+      <c r="D3866" s="4"/>
+      <c r="E3866" s="1" t="s">
+        <v>4221</v>
+      </c>
+      <c r="F3866" s="8" t="s">
+        <v>7664</v>
+      </c>
     </row>
     <row r="3867" spans="3:6">
-      <c r="C3867"/>
-      <c r="D3867"/>
-      <c r="E3867"/>
-      <c r="F3867"/>
+      <c r="C3867" s="3">
+        <v>300023</v>
+      </c>
+      <c r="D3867" s="4"/>
+      <c r="E3867" s="1" t="s">
+        <v>7665</v>
+      </c>
+      <c r="F3867" s="8" t="s">
+        <v>7666</v>
+      </c>
     </row>
     <row r="3868" spans="3:6">
-      <c r="C3868"/>
-      <c r="D3868"/>
-      <c r="E3868"/>
-      <c r="F3868"/>
+      <c r="C3868" s="3">
+        <v>300024</v>
+      </c>
+      <c r="D3868" s="4"/>
+      <c r="E3868" s="1" t="s">
+        <v>7667</v>
+      </c>
+      <c r="F3868" s="8" t="s">
+        <v>7668</v>
+      </c>
     </row>
     <row r="3869" spans="3:6">
-      <c r="C3869"/>
-      <c r="D3869"/>
-      <c r="E3869"/>
-      <c r="F3869"/>
+      <c r="C3869" s="3">
+        <v>300025</v>
+      </c>
+      <c r="D3869" s="4"/>
+      <c r="E3869" s="1" t="s">
+        <v>7669</v>
+      </c>
+      <c r="F3869" s="8" t="s">
+        <v>7670</v>
+      </c>
     </row>
     <row r="3870" spans="3:6">
-      <c r="C3870"/>
-      <c r="D3870"/>
-      <c r="E3870"/>
-      <c r="F3870"/>
+      <c r="C3870" s="3">
+        <v>300026</v>
+      </c>
+      <c r="D3870" s="4"/>
+      <c r="E3870" s="1" t="s">
+        <v>7671</v>
+      </c>
+      <c r="F3870" s="8" t="s">
+        <v>7672</v>
+      </c>
     </row>
     <row r="3871" spans="3:6">
-      <c r="C3871"/>
-      <c r="D3871"/>
-      <c r="E3871"/>
-      <c r="F3871"/>
+      <c r="C3871" s="3">
+        <v>300027</v>
+      </c>
+      <c r="D3871" s="4"/>
+      <c r="E3871" s="1" t="s">
+        <v>7673</v>
+      </c>
+      <c r="F3871" s="8" t="s">
+        <v>7674</v>
+      </c>
     </row>
     <row r="3872" spans="3:6">
-      <c r="C3872"/>
-      <c r="D3872"/>
-      <c r="E3872"/>
-      <c r="F3872"/>
+      <c r="C3872" s="3">
+        <v>300028</v>
+      </c>
+      <c r="D3872" s="4"/>
+      <c r="E3872" s="1" t="s">
+        <v>7675</v>
+      </c>
+      <c r="F3872" s="8" t="s">
+        <v>7676</v>
+      </c>
     </row>
     <row r="3873" spans="3:6">
-      <c r="C3873"/>
-      <c r="D3873"/>
-      <c r="E3873"/>
-      <c r="F3873"/>
+      <c r="C3873" s="3">
+        <v>300029</v>
+      </c>
+      <c r="D3873" s="4"/>
+      <c r="E3873" s="1" t="s">
+        <v>7677</v>
+      </c>
+      <c r="F3873" s="8" t="s">
+        <v>7678</v>
+      </c>
     </row>
     <row r="3874" spans="3:6">
-      <c r="C3874"/>
-      <c r="D3874"/>
-      <c r="E3874"/>
-      <c r="F3874"/>
+      <c r="C3874" s="3">
+        <v>300030</v>
+      </c>
+      <c r="D3874" s="4"/>
+      <c r="E3874" s="1" t="s">
+        <v>7679</v>
+      </c>
+      <c r="F3874" s="8" t="s">
+        <v>7680</v>
+      </c>
     </row>
     <row r="3875" spans="3:6">
-      <c r="C3875"/>
-      <c r="D3875"/>
-      <c r="E3875"/>
-      <c r="F3875"/>
+      <c r="C3875" s="3">
+        <v>300031</v>
+      </c>
+      <c r="D3875" s="4"/>
+      <c r="E3875" s="1" t="s">
+        <v>7681</v>
+      </c>
+      <c r="F3875" s="8" t="s">
+        <v>7682</v>
+      </c>
     </row>
     <row r="3876" spans="3:6">
-      <c r="C3876"/>
-      <c r="D3876"/>
-      <c r="E3876"/>
-      <c r="F3876"/>
+      <c r="C3876" s="3">
+        <v>300032</v>
+      </c>
+      <c r="D3876" s="4"/>
+      <c r="E3876" s="1" t="s">
+        <v>7683</v>
+      </c>
+      <c r="F3876" s="8" t="s">
+        <v>7684</v>
+      </c>
     </row>
     <row r="3877" spans="3:6">
-      <c r="C3877"/>
-      <c r="D3877"/>
-      <c r="E3877"/>
-      <c r="F3877"/>
+      <c r="C3877" s="3">
+        <v>300033</v>
+      </c>
+      <c r="D3877" s="4"/>
+      <c r="E3877" s="1" t="s">
+        <v>7685</v>
+      </c>
+      <c r="F3877" s="8" t="s">
+        <v>7686</v>
+      </c>
     </row>
     <row r="3878" spans="3:6">
-      <c r="C3878"/>
-      <c r="D3878"/>
-      <c r="E3878"/>
-      <c r="F3878"/>
+      <c r="C3878" s="3">
+        <v>300034</v>
+      </c>
+      <c r="D3878" s="4"/>
+      <c r="E3878" s="1" t="s">
+        <v>7687</v>
+      </c>
+      <c r="F3878" s="8" t="s">
+        <v>7688</v>
+      </c>
     </row>
     <row r="3879" spans="3:6">
-      <c r="C3879"/>
-      <c r="D3879"/>
-      <c r="E3879"/>
-      <c r="F3879"/>
+      <c r="C3879" s="3">
+        <v>300035</v>
+      </c>
+      <c r="D3879" s="4"/>
+      <c r="E3879" s="1" t="s">
+        <v>7689</v>
+      </c>
+      <c r="F3879" s="8" t="s">
+        <v>7690</v>
+      </c>
     </row>
     <row r="3880" spans="3:6">
-      <c r="C3880"/>
-      <c r="D3880"/>
-      <c r="E3880"/>
-      <c r="F3880"/>
+      <c r="C3880" s="3">
+        <v>300036</v>
+      </c>
+      <c r="D3880" s="4"/>
+      <c r="E3880" s="1" t="s">
+        <v>7691</v>
+      </c>
+      <c r="F3880" s="8" t="s">
+        <v>7692</v>
+      </c>
     </row>
     <row r="3881" spans="3:6">
-      <c r="C3881"/>
-      <c r="D3881"/>
-      <c r="E3881"/>
-      <c r="F3881"/>
+      <c r="C3881" s="3">
+        <v>300037</v>
+      </c>
+      <c r="D3881" s="4"/>
+      <c r="E3881" s="1" t="s">
+        <v>5916</v>
+      </c>
+      <c r="F3881" s="8" t="s">
+        <v>7693</v>
+      </c>
     </row>
     <row r="3882" spans="3:6">
-      <c r="C3882"/>
-      <c r="D3882"/>
-      <c r="E3882"/>
-      <c r="F3882"/>
+      <c r="C3882" s="3">
+        <v>300038</v>
+      </c>
+      <c r="D3882" s="4"/>
+      <c r="E3882" s="1" t="s">
+        <v>4277</v>
+      </c>
+      <c r="F3882" s="8" t="s">
+        <v>7694</v>
+      </c>
     </row>
     <row r="3883" spans="3:6">
-      <c r="C3883"/>
-      <c r="D3883"/>
-      <c r="E3883"/>
-      <c r="F3883"/>
+      <c r="C3883" s="3">
+        <v>300039</v>
+      </c>
+      <c r="D3883" s="4"/>
+      <c r="E3883" s="1" t="s">
+        <v>7695</v>
+      </c>
+      <c r="F3883" s="8" t="s">
+        <v>7696</v>
+      </c>
     </row>
     <row r="3884" spans="3:6">
-      <c r="C3884"/>
-      <c r="D3884"/>
-      <c r="E3884"/>
-      <c r="F3884"/>
+      <c r="C3884" s="3">
+        <v>300040</v>
+      </c>
+      <c r="D3884" s="4"/>
+      <c r="E3884" s="1" t="s">
+        <v>7697</v>
+      </c>
+      <c r="F3884" s="8" t="s">
+        <v>7698</v>
+      </c>
     </row>
     <row r="3885" spans="3:6">
-      <c r="C3885"/>
-      <c r="D3885"/>
-      <c r="E3885"/>
-      <c r="F3885"/>
+      <c r="C3885" s="3">
+        <v>300041</v>
+      </c>
+      <c r="D3885" s="4"/>
+      <c r="E3885" s="1" t="s">
+        <v>7699</v>
+      </c>
+      <c r="F3885" s="8" t="s">
+        <v>7700</v>
+      </c>
     </row>
     <row r="3886" spans="3:6">
-      <c r="C3886"/>
-      <c r="D3886"/>
-      <c r="E3886"/>
-      <c r="F3886"/>
+      <c r="C3886" s="3">
+        <v>300042</v>
+      </c>
+      <c r="D3886" s="4"/>
+      <c r="E3886" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F3886" s="8" t="s">
+        <v>1042</v>
+      </c>
     </row>
     <row r="3887" spans="3:6">
-      <c r="C3887"/>
-      <c r="D3887"/>
-      <c r="E3887"/>
-      <c r="F3887"/>
+      <c r="C3887" s="3">
+        <v>300043</v>
+      </c>
+      <c r="D3887" s="4"/>
+      <c r="E3887" s="1" t="s">
+        <v>7701</v>
+      </c>
+      <c r="F3887" s="8" t="s">
+        <v>7702</v>
+      </c>
     </row>
     <row r="3888" spans="3:6">
-      <c r="C3888"/>
-      <c r="D3888"/>
-      <c r="E3888"/>
-      <c r="F3888"/>
+      <c r="C3888" s="3">
+        <v>300044</v>
+      </c>
+      <c r="D3888" s="4"/>
+      <c r="E3888" s="1" t="s">
+        <v>4724</v>
+      </c>
+      <c r="F3888" s="8" t="s">
+        <v>7703</v>
+      </c>
     </row>
     <row r="3889" spans="3:6">
       <c r="C3889"/>
@@ -71153,24 +71665,6 @@
       <c r="D3993"/>
       <c r="E3993"/>
       <c r="F3993"/>
-    </row>
-    <row r="3994" spans="3:6">
-      <c r="C3994"/>
-      <c r="D3994"/>
-      <c r="E3994"/>
-      <c r="F3994"/>
-    </row>
-    <row r="3995" spans="3:6">
-      <c r="C3995"/>
-      <c r="D3995"/>
-      <c r="E3995"/>
-      <c r="F3995"/>
-    </row>
-    <row r="3996" spans="3:6">
-      <c r="C3996"/>
-      <c r="D3996"/>
-      <c r="E3996"/>
-      <c r="F3996"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7898" uniqueCount="7705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7900" uniqueCount="7707">
   <si>
     <t>c</t>
   </si>
@@ -23142,6 +23142,12 @@
   </si>
   <si>
     <t>Pet carrying limit reached!</t>
+  </si>
+  <si>
+    <t>移动在冷却中!</t>
+  </si>
+  <si>
+    <t>Movement on Cooldown!</t>
   </si>
 </sst>
 </file>
@@ -23154,7 +23160,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -23184,18 +23190,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -23668,137 +23662,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -23810,9 +23804,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="31" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -29911,7 +29903,7 @@
       <c r="E460" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="F460" s="7" t="s">
+      <c r="F460" s="6" t="s">
         <v>999</v>
       </c>
     </row>
@@ -29923,7 +29915,7 @@
       <c r="E461" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="F461" s="7" t="s">
+      <c r="F461" s="6" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -41287,7 +41279,7 @@
       <c r="E1408" s="1" t="s">
         <v>2841</v>
       </c>
-      <c r="F1408" s="7" t="s">
+      <c r="F1408" s="6" t="s">
         <v>2842</v>
       </c>
     </row>
@@ -41299,7 +41291,7 @@
       <c r="E1409" s="1" t="s">
         <v>2843</v>
       </c>
-      <c r="F1409" s="7" t="s">
+      <c r="F1409" s="6" t="s">
         <v>2844</v>
       </c>
     </row>
@@ -41311,7 +41303,7 @@
       <c r="E1410" s="1" t="s">
         <v>2845</v>
       </c>
-      <c r="F1410" s="7" t="s">
+      <c r="F1410" s="6" t="s">
         <v>2846</v>
       </c>
     </row>
@@ -43456,10 +43448,10 @@
         <v>201472</v>
       </c>
       <c r="D1589" s="4"/>
-      <c r="E1589" s="8">
+      <c r="E1589" s="7">
         <v>44703</v>
       </c>
-      <c r="F1589" s="8">
+      <c r="F1589" s="7">
         <v>44703</v>
       </c>
     </row>
@@ -60592,10 +60584,10 @@
         <v>202900</v>
       </c>
       <c r="D3017" s="4"/>
-      <c r="E3017" s="9" t="s">
+      <c r="E3017" s="1" t="s">
         <v>6002</v>
       </c>
-      <c r="F3017" s="7" t="s">
+      <c r="F3017" s="6" t="s">
         <v>6003</v>
       </c>
     </row>
@@ -70447,7 +70439,7 @@
       <c r="E3838" s="1" t="s">
         <v>7605</v>
       </c>
-      <c r="F3838" s="10" t="s">
+      <c r="F3838" s="8" t="s">
         <v>7606</v>
       </c>
     </row>
@@ -70459,7 +70451,7 @@
       <c r="E3839" s="1" t="s">
         <v>7607</v>
       </c>
-      <c r="F3839" s="10" t="s">
+      <c r="F3839" s="8" t="s">
         <v>7608</v>
       </c>
     </row>
@@ -70471,7 +70463,7 @@
       <c r="E3840" s="1" t="s">
         <v>7609</v>
       </c>
-      <c r="F3840" s="10" t="s">
+      <c r="F3840" s="8" t="s">
         <v>7610</v>
       </c>
     </row>
@@ -70483,7 +70475,7 @@
       <c r="E3841" s="1" t="s">
         <v>7611</v>
       </c>
-      <c r="F3841" s="10" t="s">
+      <c r="F3841" s="8" t="s">
         <v>7612</v>
       </c>
     </row>
@@ -70495,7 +70487,7 @@
       <c r="E3842" s="1" t="s">
         <v>7613</v>
       </c>
-      <c r="F3842" s="10" t="s">
+      <c r="F3842" s="8" t="s">
         <v>7614</v>
       </c>
     </row>
@@ -70507,7 +70499,7 @@
       <c r="E3843" s="1" t="s">
         <v>7615</v>
       </c>
-      <c r="F3843" s="10" t="s">
+      <c r="F3843" s="8" t="s">
         <v>7616</v>
       </c>
     </row>
@@ -70519,7 +70511,7 @@
       <c r="E3844" s="1" t="s">
         <v>7617</v>
       </c>
-      <c r="F3844" s="10" t="s">
+      <c r="F3844" s="8" t="s">
         <v>7618</v>
       </c>
     </row>
@@ -70531,7 +70523,7 @@
       <c r="E3845" s="1" t="s">
         <v>7619</v>
       </c>
-      <c r="F3845" s="10" t="s">
+      <c r="F3845" s="8" t="s">
         <v>7620</v>
       </c>
     </row>
@@ -70545,7 +70537,7 @@
       <c r="E3846" s="1" t="s">
         <v>7621</v>
       </c>
-      <c r="F3846" s="10" t="s">
+      <c r="F3846" s="8" t="s">
         <v>7622</v>
       </c>
     </row>
@@ -70557,7 +70549,7 @@
       <c r="E3847" s="1" t="s">
         <v>7623</v>
       </c>
-      <c r="F3847" s="10" t="s">
+      <c r="F3847" s="8" t="s">
         <v>7624</v>
       </c>
     </row>
@@ -70569,7 +70561,7 @@
       <c r="E3848" s="1" t="s">
         <v>7625</v>
       </c>
-      <c r="F3848" s="10" t="s">
+      <c r="F3848" s="8" t="s">
         <v>7626</v>
       </c>
     </row>
@@ -70581,7 +70573,7 @@
       <c r="E3849" s="1" t="s">
         <v>7627</v>
       </c>
-      <c r="F3849" s="10" t="s">
+      <c r="F3849" s="8" t="s">
         <v>7628</v>
       </c>
     </row>
@@ -70593,7 +70585,7 @@
       <c r="E3850" s="1" t="s">
         <v>7629</v>
       </c>
-      <c r="F3850" s="10" t="s">
+      <c r="F3850" s="8" t="s">
         <v>7630</v>
       </c>
     </row>
@@ -70605,7 +70597,7 @@
       <c r="E3851" s="1" t="s">
         <v>7631</v>
       </c>
-      <c r="F3851" s="10" t="s">
+      <c r="F3851" s="8" t="s">
         <v>7632</v>
       </c>
     </row>
@@ -70617,7 +70609,7 @@
       <c r="E3852" s="1" t="s">
         <v>7633</v>
       </c>
-      <c r="F3852" s="10" t="s">
+      <c r="F3852" s="8" t="s">
         <v>7634</v>
       </c>
     </row>
@@ -70629,7 +70621,7 @@
       <c r="E3853" s="1" t="s">
         <v>7635</v>
       </c>
-      <c r="F3853" s="10" t="s">
+      <c r="F3853" s="8" t="s">
         <v>7636</v>
       </c>
     </row>
@@ -70641,7 +70633,7 @@
       <c r="E3854" s="1" t="s">
         <v>7637</v>
       </c>
-      <c r="F3854" s="10" t="s">
+      <c r="F3854" s="8" t="s">
         <v>7638</v>
       </c>
     </row>
@@ -70653,7 +70645,7 @@
       <c r="E3855" s="1" t="s">
         <v>7639</v>
       </c>
-      <c r="F3855" s="10" t="s">
+      <c r="F3855" s="8" t="s">
         <v>7640</v>
       </c>
     </row>
@@ -70665,7 +70657,7 @@
       <c r="E3856" s="1" t="s">
         <v>7641</v>
       </c>
-      <c r="F3856" s="10" t="s">
+      <c r="F3856" s="8" t="s">
         <v>7642</v>
       </c>
     </row>
@@ -70677,7 +70669,7 @@
       <c r="E3857" s="1" t="s">
         <v>7643</v>
       </c>
-      <c r="F3857" s="10" t="s">
+      <c r="F3857" s="8" t="s">
         <v>7644</v>
       </c>
     </row>
@@ -70689,7 +70681,7 @@
       <c r="E3858" s="1" t="s">
         <v>7645</v>
       </c>
-      <c r="F3858" s="10" t="s">
+      <c r="F3858" s="8" t="s">
         <v>7646</v>
       </c>
     </row>
@@ -70701,7 +70693,7 @@
       <c r="E3859" s="1" t="s">
         <v>7647</v>
       </c>
-      <c r="F3859" s="10" t="s">
+      <c r="F3859" s="8" t="s">
         <v>7648</v>
       </c>
     </row>
@@ -70713,7 +70705,7 @@
       <c r="E3860" s="1" t="s">
         <v>7649</v>
       </c>
-      <c r="F3860" s="10" t="s">
+      <c r="F3860" s="8" t="s">
         <v>7650</v>
       </c>
     </row>
@@ -70725,7 +70717,7 @@
       <c r="E3861" s="1" t="s">
         <v>7651</v>
       </c>
-      <c r="F3861" s="10" t="s">
+      <c r="F3861" s="8" t="s">
         <v>7652</v>
       </c>
     </row>
@@ -70737,7 +70729,7 @@
       <c r="E3862" s="1" t="s">
         <v>7653</v>
       </c>
-      <c r="F3862" s="10" t="s">
+      <c r="F3862" s="8" t="s">
         <v>7654</v>
       </c>
     </row>
@@ -70749,7 +70741,7 @@
       <c r="E3863" s="1" t="s">
         <v>7655</v>
       </c>
-      <c r="F3863" s="10" t="s">
+      <c r="F3863" s="8" t="s">
         <v>7656</v>
       </c>
     </row>
@@ -70761,7 +70753,7 @@
       <c r="E3864" s="1" t="s">
         <v>7657</v>
       </c>
-      <c r="F3864" s="10" t="s">
+      <c r="F3864" s="8" t="s">
         <v>7658</v>
       </c>
     </row>
@@ -70773,7 +70765,7 @@
       <c r="E3865" s="1" t="s">
         <v>7659</v>
       </c>
-      <c r="F3865" s="10" t="s">
+      <c r="F3865" s="8" t="s">
         <v>7660</v>
       </c>
     </row>
@@ -70785,7 +70777,7 @@
       <c r="E3866" s="1" t="s">
         <v>7661</v>
       </c>
-      <c r="F3866" s="10" t="s">
+      <c r="F3866" s="8" t="s">
         <v>7662</v>
       </c>
     </row>
@@ -70797,7 +70789,7 @@
       <c r="E3867" s="1" t="s">
         <v>4218</v>
       </c>
-      <c r="F3867" s="10" t="s">
+      <c r="F3867" s="8" t="s">
         <v>7663</v>
       </c>
     </row>
@@ -70809,7 +70801,7 @@
       <c r="E3868" s="1" t="s">
         <v>7664</v>
       </c>
-      <c r="F3868" s="10" t="s">
+      <c r="F3868" s="8" t="s">
         <v>7665</v>
       </c>
     </row>
@@ -70821,7 +70813,7 @@
       <c r="E3869" s="1" t="s">
         <v>7666</v>
       </c>
-      <c r="F3869" s="10" t="s">
+      <c r="F3869" s="8" t="s">
         <v>7667</v>
       </c>
     </row>
@@ -70833,7 +70825,7 @@
       <c r="E3870" s="1" t="s">
         <v>7668</v>
       </c>
-      <c r="F3870" s="10" t="s">
+      <c r="F3870" s="8" t="s">
         <v>7669</v>
       </c>
     </row>
@@ -70845,7 +70837,7 @@
       <c r="E3871" s="1" t="s">
         <v>7670</v>
       </c>
-      <c r="F3871" s="10" t="s">
+      <c r="F3871" s="8" t="s">
         <v>7671</v>
       </c>
     </row>
@@ -70857,7 +70849,7 @@
       <c r="E3872" s="1" t="s">
         <v>7672</v>
       </c>
-      <c r="F3872" s="10" t="s">
+      <c r="F3872" s="8" t="s">
         <v>7673</v>
       </c>
     </row>
@@ -70869,7 +70861,7 @@
       <c r="E3873" s="1" t="s">
         <v>7674</v>
       </c>
-      <c r="F3873" s="10" t="s">
+      <c r="F3873" s="8" t="s">
         <v>7675</v>
       </c>
     </row>
@@ -70881,7 +70873,7 @@
       <c r="E3874" s="1" t="s">
         <v>7676</v>
       </c>
-      <c r="F3874" s="10" t="s">
+      <c r="F3874" s="8" t="s">
         <v>7677</v>
       </c>
     </row>
@@ -70893,7 +70885,7 @@
       <c r="E3875" s="1" t="s">
         <v>7678</v>
       </c>
-      <c r="F3875" s="10" t="s">
+      <c r="F3875" s="8" t="s">
         <v>7679</v>
       </c>
     </row>
@@ -70905,7 +70897,7 @@
       <c r="E3876" s="1" t="s">
         <v>7680</v>
       </c>
-      <c r="F3876" s="10" t="s">
+      <c r="F3876" s="8" t="s">
         <v>7681</v>
       </c>
     </row>
@@ -70917,7 +70909,7 @@
       <c r="E3877" s="1" t="s">
         <v>7682</v>
       </c>
-      <c r="F3877" s="10" t="s">
+      <c r="F3877" s="8" t="s">
         <v>7683</v>
       </c>
     </row>
@@ -70929,7 +70921,7 @@
       <c r="E3878" s="1" t="s">
         <v>7684</v>
       </c>
-      <c r="F3878" s="10" t="s">
+      <c r="F3878" s="8" t="s">
         <v>7685</v>
       </c>
     </row>
@@ -70941,7 +70933,7 @@
       <c r="E3879" s="1" t="s">
         <v>7686</v>
       </c>
-      <c r="F3879" s="10" t="s">
+      <c r="F3879" s="8" t="s">
         <v>7687</v>
       </c>
     </row>
@@ -70953,7 +70945,7 @@
       <c r="E3880" s="1" t="s">
         <v>7688</v>
       </c>
-      <c r="F3880" s="10" t="s">
+      <c r="F3880" s="8" t="s">
         <v>7689</v>
       </c>
     </row>
@@ -70965,7 +70957,7 @@
       <c r="E3881" s="1" t="s">
         <v>7690</v>
       </c>
-      <c r="F3881" s="10" t="s">
+      <c r="F3881" s="8" t="s">
         <v>7691</v>
       </c>
     </row>
@@ -70977,7 +70969,7 @@
       <c r="E3882" s="1" t="s">
         <v>5913</v>
       </c>
-      <c r="F3882" s="10" t="s">
+      <c r="F3882" s="8" t="s">
         <v>7692</v>
       </c>
     </row>
@@ -70989,7 +70981,7 @@
       <c r="E3883" s="1" t="s">
         <v>4274</v>
       </c>
-      <c r="F3883" s="10" t="s">
+      <c r="F3883" s="8" t="s">
         <v>7693</v>
       </c>
     </row>
@@ -71001,7 +70993,7 @@
       <c r="E3884" s="1" t="s">
         <v>7694</v>
       </c>
-      <c r="F3884" s="10" t="s">
+      <c r="F3884" s="8" t="s">
         <v>7695</v>
       </c>
     </row>
@@ -71013,7 +71005,7 @@
       <c r="E3885" s="1" t="s">
         <v>7696</v>
       </c>
-      <c r="F3885" s="10" t="s">
+      <c r="F3885" s="8" t="s">
         <v>7697</v>
       </c>
     </row>
@@ -71025,7 +71017,7 @@
       <c r="E3886" s="1" t="s">
         <v>7698</v>
       </c>
-      <c r="F3886" s="10" t="s">
+      <c r="F3886" s="8" t="s">
         <v>7699</v>
       </c>
     </row>
@@ -71037,7 +71029,7 @@
       <c r="E3887" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="F3887" s="10" t="s">
+      <c r="F3887" s="8" t="s">
         <v>1041</v>
       </c>
     </row>
@@ -71049,7 +71041,7 @@
       <c r="E3888" s="1" t="s">
         <v>7700</v>
       </c>
-      <c r="F3888" s="10" t="s">
+      <c r="F3888" s="8" t="s">
         <v>7701</v>
       </c>
     </row>
@@ -71061,7 +71053,7 @@
       <c r="E3889" s="1" t="s">
         <v>4721</v>
       </c>
-      <c r="F3889" s="10" t="s">
+      <c r="F3889" s="8" t="s">
         <v>7702</v>
       </c>
     </row>
@@ -71078,10 +71070,16 @@
       </c>
     </row>
     <row r="3891" spans="3:6">
-      <c r="C3891"/>
+      <c r="C3891" s="3">
+        <v>300046</v>
+      </c>
       <c r="D3891"/>
-      <c r="E3891"/>
-      <c r="F3891"/>
+      <c r="E3891" t="s">
+        <v>7705</v>
+      </c>
+      <c r="F3891" t="s">
+        <v>7706</v>
+      </c>
     </row>
     <row r="3892" spans="3:6">
       <c r="C3892"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7900" uniqueCount="7707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8026" uniqueCount="7833">
   <si>
     <t>c</t>
   </si>
@@ -23148,6 +23148,384 @@
   </si>
   <si>
     <t>Movement on Cooldown!</t>
+  </si>
+  <si>
+    <t>击败&lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt; {3}</t>
+  </si>
+  <si>
+    <t>Defeat &lt;color=#EAFF39&gt;{0} {1}/{2} &lt;/color&gt;{3}</t>
+  </si>
+  <si>
+    <t>寻找道具&lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Find Prop &lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>等级提升至&lt;color=#EAFF39&gt;{0}级 {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Level increased to &lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>击败任意怪物 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Defeat any monster &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>击败任意领主级怪物 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Defeat any Lord Monster &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>通关副本&lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Clearance copy &lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>进行转职&lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Transfer &lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>给予符合要求的道具 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Give qualified props &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>获得宠物数量 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Get pet count &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>制造道具数量 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Make Prop Qty &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>装备洗练次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Equip training times &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>宠物天梯次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Pet ladder times &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>兑换金币次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Number of Gold Redemption &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>装备回收次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Equip recovery times &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>最大强化等级 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Maximum Reinforcement Level &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>技能宠物 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Skill Pets &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>宠物探险通关&lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Pet Adventure Clearance &lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>消耗金币 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Cost Gold &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>击杀玩家数量 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Number of players killed &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>家园等级 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Home Level &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>宠物合成次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Pet composition times &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>拥有宠物数量 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Number of pets owned &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>给予一个宠物 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Give a pet &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>使用普通藏宝图 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Use Normal Treasure Map &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>使用高级藏宝图 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Use Advanced Treasure Map &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>封印之塔挑战 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Tower of the Seal Challenge &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>使用药剂或者合剂次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Times of using medicine or mixture &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>获得X只新的宠物 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Get X new pets &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>合成1只战力达到X点的宠物 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Synthesize 1 pet &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt; with combat power up to X</t>
+  </si>
+  <si>
+    <t>宠物使用宠之晶洗炼宠物次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Pet uses pet crystal to wash and refine pet times &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>在孵化系统中孵化成功宠物 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Successfully hatched pet &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt; in hatching system</t>
+  </si>
+  <si>
+    <t>在孵化系统中孵化指定的宠物蛋成功 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Successfully hatched the specified pet eggs in the hatching system &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>宠物使用技能书次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Pet uses skill book times  &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>宠物天梯战斗胜利次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Pet ladder battle wins &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>使用N点品质的鉴定附魔道具给装备附魔 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Enchant Equip &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt; with an enchant item with an N-point quality.</t>
+  </si>
+  <si>
+    <t>使用N点品质的鉴定道具给装备鉴定 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Use N-point quality appraisal item to equip appraisal &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>鉴定装备时出一个大于N条属性的装备 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>A piece of Equip &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt; with more than N attributes was found when the Equip was identified</t>
+  </si>
+  <si>
+    <t>洗炼出带有任何隐藏技能的装备 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Refine Equip with any hidden skill &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>洗炼出带有指定属性的装备 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color</t>
+  </si>
+  <si>
+    <t>Refine the Equip &lt;color=#EAFF39&gt;{0}/{1}&lt;/color with the specified attribute</t>
+  </si>
+  <si>
+    <t>增幅装备次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Increase Equip Times &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>试炼之地的输出排行榜进入前 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Trial Land's Output Leaderboard Top &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>宠物天梯进入排行榜前 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Pet Ladder Top Leaderboard &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>战力排行榜进入前 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Battle Power Ranking Top &lt;color=#EAFF39&gt;{{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>家园烹饪次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Home Cooking Times &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>家园种地种植次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Home land planting times &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>家园种地收获次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Harvest times of homestead farming &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>家园牧场饲养次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Home Ranch Feeding Times &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>家园牧场收货次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Homestead Ranch Receipts &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>家园美味品尝次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Home Delicious Tasting Times &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>加入家族 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Join Family &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>击败挑战级的 &lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Defeat Challenged &lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>击败地狱级的 &lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color</t>
+  </si>
+  <si>
+    <t>Defeat Inferno's &lt;color=#EAFF39&gt;{0} {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>通关挑战级-&lt;color=#EAFF39&gt;{0}副本 {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Pass Challenge-&lt;color=#EAFF39&gt;{0} Copy {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>通关地狱级-&lt;color=#EAFF39&gt;{0}副本 {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Pass Hell Level-&lt;color=#EAFF39&gt;{0} Replica {1}/{2}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>击败挑战级任意怪物&lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Defeat any Monster at Challenge Level &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>击败地狱级任意怪物&lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Defeat any inferno monsters &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>击败挑战级任意领主怪物&lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Defeat Challenging Any Lord Monster &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>战力提升至&lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Combat power increased to &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>通关试练塔&lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Pass Trial Tower &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>挑战深渊模式的副本 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Copy of Challenge Abyss Mode &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>组队副本伤害值 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Team Instance Damage &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>矿场占领次数 &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Mine occupation times &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>击败地狱级任意领主怪物&lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Defeat Infernal Any Lord Monsters &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
   </si>
 </sst>
 </file>
@@ -24163,7 +24541,7 @@
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="42.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="61" style="1" customWidth="1"/>
     <col min="6" max="6" width="112.375" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -71082,382 +71460,760 @@
       </c>
     </row>
     <row r="3892" spans="3:6">
-      <c r="C3892"/>
-      <c r="D3892"/>
-      <c r="E3892"/>
-      <c r="F3892"/>
+      <c r="C3892" s="3">
+        <v>300047</v>
+      </c>
+      <c r="D3892" s="4"/>
+      <c r="E3892" s="1" t="s">
+        <v>7707</v>
+      </c>
+      <c r="F3892" s="6" t="s">
+        <v>7708</v>
+      </c>
     </row>
     <row r="3893" spans="3:6">
-      <c r="C3893"/>
-      <c r="D3893"/>
-      <c r="E3893"/>
-      <c r="F3893"/>
+      <c r="C3893" s="3">
+        <v>300048</v>
+      </c>
+      <c r="D3893" s="4"/>
+      <c r="E3893" s="1" t="s">
+        <v>7709</v>
+      </c>
+      <c r="F3893" s="6" t="s">
+        <v>7710</v>
+      </c>
     </row>
     <row r="3894" spans="3:6">
-      <c r="C3894"/>
-      <c r="D3894"/>
-      <c r="E3894"/>
-      <c r="F3894"/>
+      <c r="C3894" s="3">
+        <v>300049</v>
+      </c>
+      <c r="D3894" s="4"/>
+      <c r="E3894" s="1" t="s">
+        <v>7711</v>
+      </c>
+      <c r="F3894" s="6" t="s">
+        <v>7712</v>
+      </c>
     </row>
     <row r="3895" spans="3:6">
-      <c r="C3895"/>
-      <c r="D3895"/>
-      <c r="E3895"/>
-      <c r="F3895"/>
+      <c r="C3895" s="3">
+        <v>300050</v>
+      </c>
+      <c r="D3895" s="4"/>
+      <c r="E3895" s="1" t="s">
+        <v>7713</v>
+      </c>
+      <c r="F3895" s="6" t="s">
+        <v>7714</v>
+      </c>
     </row>
     <row r="3896" spans="3:6">
-      <c r="C3896"/>
-      <c r="D3896"/>
-      <c r="E3896"/>
-      <c r="F3896"/>
+      <c r="C3896" s="3">
+        <v>300051</v>
+      </c>
+      <c r="D3896" s="4"/>
+      <c r="E3896" s="1" t="s">
+        <v>7715</v>
+      </c>
+      <c r="F3896" s="6" t="s">
+        <v>7716</v>
+      </c>
     </row>
     <row r="3897" spans="3:6">
-      <c r="C3897"/>
-      <c r="D3897"/>
-      <c r="E3897"/>
-      <c r="F3897"/>
+      <c r="C3897" s="3">
+        <v>300052</v>
+      </c>
+      <c r="D3897" s="4"/>
+      <c r="E3897" s="1" t="s">
+        <v>7717</v>
+      </c>
+      <c r="F3897" s="6" t="s">
+        <v>7718</v>
+      </c>
     </row>
     <row r="3898" spans="3:6">
-      <c r="C3898"/>
-      <c r="D3898"/>
-      <c r="E3898"/>
-      <c r="F3898"/>
+      <c r="C3898" s="3">
+        <v>300053</v>
+      </c>
+      <c r="D3898" s="4"/>
+      <c r="E3898" s="1" t="s">
+        <v>7719</v>
+      </c>
+      <c r="F3898" s="6" t="s">
+        <v>7720</v>
+      </c>
     </row>
     <row r="3899" spans="3:6">
-      <c r="C3899"/>
-      <c r="D3899"/>
-      <c r="E3899"/>
-      <c r="F3899"/>
+      <c r="C3899" s="3">
+        <v>300054</v>
+      </c>
+      <c r="D3899" s="4"/>
+      <c r="E3899" s="1" t="s">
+        <v>7721</v>
+      </c>
+      <c r="F3899" s="6" t="s">
+        <v>7722</v>
+      </c>
     </row>
     <row r="3900" spans="3:6">
-      <c r="C3900"/>
-      <c r="D3900"/>
-      <c r="E3900"/>
-      <c r="F3900"/>
+      <c r="C3900" s="3">
+        <v>300055</v>
+      </c>
+      <c r="D3900" s="4"/>
+      <c r="E3900" s="1" t="s">
+        <v>7723</v>
+      </c>
+      <c r="F3900" s="6" t="s">
+        <v>7724</v>
+      </c>
     </row>
     <row r="3901" spans="3:6">
-      <c r="C3901"/>
-      <c r="D3901"/>
-      <c r="E3901"/>
-      <c r="F3901"/>
+      <c r="C3901" s="3">
+        <v>300056</v>
+      </c>
+      <c r="D3901" s="4"/>
+      <c r="E3901" s="1" t="s">
+        <v>7725</v>
+      </c>
+      <c r="F3901" s="6" t="s">
+        <v>7726</v>
+      </c>
     </row>
     <row r="3902" spans="3:6">
-      <c r="C3902"/>
-      <c r="D3902"/>
-      <c r="E3902"/>
-      <c r="F3902"/>
+      <c r="C3902" s="3">
+        <v>300057</v>
+      </c>
+      <c r="D3902" s="4"/>
+      <c r="E3902" s="1" t="s">
+        <v>7727</v>
+      </c>
+      <c r="F3902" s="6" t="s">
+        <v>7728</v>
+      </c>
     </row>
     <row r="3903" spans="3:6">
-      <c r="C3903"/>
-      <c r="D3903"/>
-      <c r="E3903"/>
-      <c r="F3903"/>
+      <c r="C3903" s="3">
+        <v>300058</v>
+      </c>
+      <c r="D3903" s="4"/>
+      <c r="E3903" s="1" t="s">
+        <v>7729</v>
+      </c>
+      <c r="F3903" s="6" t="s">
+        <v>7730</v>
+      </c>
     </row>
     <row r="3904" spans="3:6">
-      <c r="C3904"/>
-      <c r="D3904"/>
-      <c r="E3904"/>
-      <c r="F3904"/>
+      <c r="C3904" s="3">
+        <v>300059</v>
+      </c>
+      <c r="D3904" s="4"/>
+      <c r="E3904" s="1" t="s">
+        <v>7731</v>
+      </c>
+      <c r="F3904" s="6" t="s">
+        <v>7732</v>
+      </c>
     </row>
     <row r="3905" spans="3:6">
-      <c r="C3905"/>
-      <c r="D3905"/>
-      <c r="E3905"/>
-      <c r="F3905"/>
+      <c r="C3905" s="3">
+        <v>300060</v>
+      </c>
+      <c r="D3905" s="4"/>
+      <c r="E3905" s="1" t="s">
+        <v>7733</v>
+      </c>
+      <c r="F3905" s="6" t="s">
+        <v>7734</v>
+      </c>
     </row>
     <row r="3906" spans="3:6">
-      <c r="C3906"/>
-      <c r="D3906"/>
-      <c r="E3906"/>
-      <c r="F3906"/>
+      <c r="C3906" s="3">
+        <v>300061</v>
+      </c>
+      <c r="D3906" s="4"/>
+      <c r="E3906" s="1" t="s">
+        <v>7735</v>
+      </c>
+      <c r="F3906" s="6" t="s">
+        <v>7736</v>
+      </c>
     </row>
     <row r="3907" spans="3:6">
-      <c r="C3907"/>
-      <c r="D3907"/>
-      <c r="E3907"/>
-      <c r="F3907"/>
+      <c r="C3907" s="3">
+        <v>300062</v>
+      </c>
+      <c r="D3907" s="4"/>
+      <c r="E3907" s="1" t="s">
+        <v>7737</v>
+      </c>
+      <c r="F3907" s="6" t="s">
+        <v>7738</v>
+      </c>
     </row>
     <row r="3908" spans="3:6">
-      <c r="C3908"/>
-      <c r="D3908"/>
-      <c r="E3908"/>
-      <c r="F3908"/>
+      <c r="C3908" s="3">
+        <v>300063</v>
+      </c>
+      <c r="D3908" s="4"/>
+      <c r="E3908" s="1" t="s">
+        <v>7739</v>
+      </c>
+      <c r="F3908" s="6" t="s">
+        <v>7740</v>
+      </c>
     </row>
     <row r="3909" spans="3:6">
-      <c r="C3909"/>
-      <c r="D3909"/>
-      <c r="E3909"/>
-      <c r="F3909"/>
+      <c r="C3909" s="3">
+        <v>300064</v>
+      </c>
+      <c r="D3909" s="4"/>
+      <c r="E3909" s="1" t="s">
+        <v>7741</v>
+      </c>
+      <c r="F3909" s="6" t="s">
+        <v>7742</v>
+      </c>
     </row>
     <row r="3910" spans="3:6">
-      <c r="C3910"/>
-      <c r="D3910"/>
-      <c r="E3910"/>
-      <c r="F3910"/>
+      <c r="C3910" s="3">
+        <v>300065</v>
+      </c>
+      <c r="D3910" s="4"/>
+      <c r="E3910" s="1" t="s">
+        <v>7743</v>
+      </c>
+      <c r="F3910" s="6" t="s">
+        <v>7744</v>
+      </c>
     </row>
     <row r="3911" spans="3:6">
-      <c r="C3911"/>
-      <c r="D3911"/>
-      <c r="E3911"/>
-      <c r="F3911"/>
+      <c r="C3911" s="3">
+        <v>300066</v>
+      </c>
+      <c r="D3911" s="4"/>
+      <c r="E3911" s="1" t="s">
+        <v>7745</v>
+      </c>
+      <c r="F3911" s="6" t="s">
+        <v>7746</v>
+      </c>
     </row>
     <row r="3912" spans="3:6">
-      <c r="C3912"/>
-      <c r="D3912"/>
-      <c r="E3912"/>
-      <c r="F3912"/>
+      <c r="C3912" s="3">
+        <v>300067</v>
+      </c>
+      <c r="D3912" s="4"/>
+      <c r="E3912" s="1" t="s">
+        <v>7747</v>
+      </c>
+      <c r="F3912" s="6" t="s">
+        <v>7748</v>
+      </c>
     </row>
     <row r="3913" spans="3:6">
-      <c r="C3913"/>
-      <c r="D3913"/>
-      <c r="E3913"/>
-      <c r="F3913"/>
+      <c r="C3913" s="3">
+        <v>300068</v>
+      </c>
+      <c r="D3913" s="4"/>
+      <c r="E3913" s="1" t="s">
+        <v>7749</v>
+      </c>
+      <c r="F3913" s="6" t="s">
+        <v>7750</v>
+      </c>
     </row>
     <row r="3914" spans="3:6">
-      <c r="C3914"/>
-      <c r="D3914"/>
-      <c r="E3914"/>
-      <c r="F3914"/>
+      <c r="C3914" s="3">
+        <v>300069</v>
+      </c>
+      <c r="D3914" s="4"/>
+      <c r="E3914" s="1" t="s">
+        <v>7751</v>
+      </c>
+      <c r="F3914" s="6" t="s">
+        <v>7752</v>
+      </c>
     </row>
     <row r="3915" spans="3:6">
-      <c r="C3915"/>
-      <c r="D3915"/>
-      <c r="E3915"/>
-      <c r="F3915"/>
+      <c r="C3915" s="3">
+        <v>300070</v>
+      </c>
+      <c r="D3915" s="4"/>
+      <c r="E3915" s="1" t="s">
+        <v>7753</v>
+      </c>
+      <c r="F3915" s="6" t="s">
+        <v>7754</v>
+      </c>
     </row>
     <row r="3916" spans="3:6">
-      <c r="C3916"/>
-      <c r="D3916"/>
-      <c r="E3916"/>
-      <c r="F3916"/>
+      <c r="C3916" s="3">
+        <v>300071</v>
+      </c>
+      <c r="D3916" s="4"/>
+      <c r="E3916" s="1" t="s">
+        <v>7755</v>
+      </c>
+      <c r="F3916" s="6" t="s">
+        <v>7756</v>
+      </c>
     </row>
     <row r="3917" spans="3:6">
-      <c r="C3917"/>
-      <c r="D3917"/>
-      <c r="E3917"/>
-      <c r="F3917"/>
+      <c r="C3917" s="3">
+        <v>300072</v>
+      </c>
+      <c r="D3917" s="4"/>
+      <c r="E3917" s="1" t="s">
+        <v>7757</v>
+      </c>
+      <c r="F3917" s="6" t="s">
+        <v>7758</v>
+      </c>
     </row>
     <row r="3918" spans="3:6">
-      <c r="C3918"/>
-      <c r="D3918"/>
-      <c r="E3918"/>
-      <c r="F3918"/>
+      <c r="C3918" s="3">
+        <v>300073</v>
+      </c>
+      <c r="D3918" s="4"/>
+      <c r="E3918" s="1" t="s">
+        <v>7759</v>
+      </c>
+      <c r="F3918" s="6" t="s">
+        <v>7760</v>
+      </c>
     </row>
     <row r="3919" spans="3:6">
-      <c r="C3919"/>
-      <c r="D3919"/>
-      <c r="E3919"/>
-      <c r="F3919"/>
+      <c r="C3919" s="3">
+        <v>300074</v>
+      </c>
+      <c r="D3919" s="4"/>
+      <c r="E3919" s="1" t="s">
+        <v>7761</v>
+      </c>
+      <c r="F3919" s="6" t="s">
+        <v>7762</v>
+      </c>
     </row>
     <row r="3920" spans="3:6">
-      <c r="C3920"/>
-      <c r="D3920"/>
-      <c r="E3920"/>
-      <c r="F3920"/>
+      <c r="C3920" s="3">
+        <v>300075</v>
+      </c>
+      <c r="D3920" s="4"/>
+      <c r="E3920" s="1" t="s">
+        <v>7763</v>
+      </c>
+      <c r="F3920" s="6" t="s">
+        <v>7764</v>
+      </c>
     </row>
     <row r="3921" spans="3:6">
-      <c r="C3921"/>
-      <c r="D3921"/>
-      <c r="E3921"/>
-      <c r="F3921"/>
+      <c r="C3921" s="3">
+        <v>300076</v>
+      </c>
+      <c r="D3921" s="4"/>
+      <c r="E3921" s="1" t="s">
+        <v>7765</v>
+      </c>
+      <c r="F3921" s="6" t="s">
+        <v>7766</v>
+      </c>
     </row>
     <row r="3922" spans="3:6">
-      <c r="C3922"/>
-      <c r="D3922"/>
-      <c r="E3922"/>
-      <c r="F3922"/>
+      <c r="C3922" s="3">
+        <v>300077</v>
+      </c>
+      <c r="D3922" s="4"/>
+      <c r="E3922" s="1" t="s">
+        <v>7767</v>
+      </c>
+      <c r="F3922" s="6" t="s">
+        <v>7768</v>
+      </c>
     </row>
     <row r="3923" spans="3:6">
-      <c r="C3923"/>
-      <c r="D3923"/>
-      <c r="E3923"/>
-      <c r="F3923"/>
+      <c r="C3923" s="3">
+        <v>300078</v>
+      </c>
+      <c r="D3923" s="4"/>
+      <c r="E3923" s="1" t="s">
+        <v>7769</v>
+      </c>
+      <c r="F3923" s="6" t="s">
+        <v>7770</v>
+      </c>
     </row>
     <row r="3924" spans="3:6">
-      <c r="C3924"/>
-      <c r="D3924"/>
-      <c r="E3924"/>
-      <c r="F3924"/>
+      <c r="C3924" s="3">
+        <v>300079</v>
+      </c>
+      <c r="D3924" s="4"/>
+      <c r="E3924" s="1" t="s">
+        <v>7771</v>
+      </c>
+      <c r="F3924" s="6" t="s">
+        <v>7772</v>
+      </c>
     </row>
     <row r="3925" spans="3:6">
-      <c r="C3925"/>
-      <c r="D3925"/>
-      <c r="E3925"/>
-      <c r="F3925"/>
+      <c r="C3925" s="3">
+        <v>300080</v>
+      </c>
+      <c r="D3925" s="4"/>
+      <c r="E3925" s="1" t="s">
+        <v>7773</v>
+      </c>
+      <c r="F3925" s="6" t="s">
+        <v>7774</v>
+      </c>
     </row>
     <row r="3926" spans="3:6">
-      <c r="C3926"/>
-      <c r="D3926"/>
-      <c r="E3926"/>
-      <c r="F3926"/>
+      <c r="C3926" s="3">
+        <v>300081</v>
+      </c>
+      <c r="D3926" s="4"/>
+      <c r="E3926" s="1" t="s">
+        <v>7775</v>
+      </c>
+      <c r="F3926" s="6" t="s">
+        <v>7776</v>
+      </c>
     </row>
     <row r="3927" spans="3:6">
-      <c r="C3927"/>
-      <c r="D3927"/>
-      <c r="E3927"/>
-      <c r="F3927"/>
+      <c r="C3927" s="3">
+        <v>300082</v>
+      </c>
+      <c r="D3927" s="4"/>
+      <c r="E3927" s="1" t="s">
+        <v>7777</v>
+      </c>
+      <c r="F3927" s="6" t="s">
+        <v>7778</v>
+      </c>
     </row>
     <row r="3928" spans="3:6">
-      <c r="C3928"/>
-      <c r="D3928"/>
-      <c r="E3928"/>
-      <c r="F3928"/>
+      <c r="C3928" s="3">
+        <v>300083</v>
+      </c>
+      <c r="D3928" s="4"/>
+      <c r="E3928" s="1" t="s">
+        <v>7779</v>
+      </c>
+      <c r="F3928" s="6" t="s">
+        <v>7780</v>
+      </c>
     </row>
     <row r="3929" spans="3:6">
-      <c r="C3929"/>
-      <c r="D3929"/>
-      <c r="E3929"/>
-      <c r="F3929"/>
+      <c r="C3929" s="3">
+        <v>300084</v>
+      </c>
+      <c r="D3929" s="4"/>
+      <c r="E3929" s="1" t="s">
+        <v>7781</v>
+      </c>
+      <c r="F3929" s="6" t="s">
+        <v>7782</v>
+      </c>
     </row>
     <row r="3930" spans="3:6">
-      <c r="C3930"/>
-      <c r="D3930"/>
-      <c r="E3930"/>
-      <c r="F3930"/>
+      <c r="C3930" s="3">
+        <v>300085</v>
+      </c>
+      <c r="D3930" s="4"/>
+      <c r="E3930" s="1" t="s">
+        <v>7783</v>
+      </c>
+      <c r="F3930" s="6" t="s">
+        <v>7784</v>
+      </c>
     </row>
     <row r="3931" spans="3:6">
-      <c r="C3931"/>
-      <c r="D3931"/>
-      <c r="E3931"/>
-      <c r="F3931"/>
+      <c r="C3931" s="3">
+        <v>300086</v>
+      </c>
+      <c r="D3931" s="4"/>
+      <c r="E3931" s="1" t="s">
+        <v>7785</v>
+      </c>
+      <c r="F3931" s="6" t="s">
+        <v>7786</v>
+      </c>
     </row>
     <row r="3932" spans="3:6">
-      <c r="C3932"/>
-      <c r="D3932"/>
-      <c r="E3932"/>
-      <c r="F3932"/>
+      <c r="C3932" s="3">
+        <v>300087</v>
+      </c>
+      <c r="D3932" s="4"/>
+      <c r="E3932" s="1" t="s">
+        <v>7787</v>
+      </c>
+      <c r="F3932" s="6" t="s">
+        <v>7788</v>
+      </c>
     </row>
     <row r="3933" spans="3:6">
-      <c r="C3933"/>
-      <c r="D3933"/>
-      <c r="E3933"/>
-      <c r="F3933"/>
+      <c r="C3933" s="3">
+        <v>300088</v>
+      </c>
+      <c r="D3933" s="4"/>
+      <c r="E3933" s="1" t="s">
+        <v>7789</v>
+      </c>
+      <c r="F3933" s="6" t="s">
+        <v>7790</v>
+      </c>
     </row>
     <row r="3934" spans="3:6">
-      <c r="C3934"/>
-      <c r="D3934"/>
-      <c r="E3934"/>
-      <c r="F3934"/>
+      <c r="C3934" s="3">
+        <v>300089</v>
+      </c>
+      <c r="D3934" s="4"/>
+      <c r="E3934" s="1" t="s">
+        <v>7791</v>
+      </c>
+      <c r="F3934" s="6" t="s">
+        <v>7792</v>
+      </c>
     </row>
     <row r="3935" spans="3:6">
-      <c r="C3935"/>
-      <c r="D3935"/>
-      <c r="E3935"/>
-      <c r="F3935"/>
+      <c r="C3935" s="3">
+        <v>300090</v>
+      </c>
+      <c r="D3935" s="4"/>
+      <c r="E3935" s="1" t="s">
+        <v>7793</v>
+      </c>
+      <c r="F3935" s="6" t="s">
+        <v>7794</v>
+      </c>
     </row>
     <row r="3936" spans="3:6">
-      <c r="C3936"/>
-      <c r="D3936"/>
-      <c r="E3936"/>
-      <c r="F3936"/>
+      <c r="C3936" s="3">
+        <v>300091</v>
+      </c>
+      <c r="D3936" s="4"/>
+      <c r="E3936" s="1" t="s">
+        <v>7795</v>
+      </c>
+      <c r="F3936" s="6" t="s">
+        <v>7796</v>
+      </c>
     </row>
     <row r="3937" spans="3:6">
-      <c r="C3937"/>
-      <c r="D3937"/>
-      <c r="E3937"/>
-      <c r="F3937"/>
+      <c r="C3937" s="3">
+        <v>300092</v>
+      </c>
+      <c r="D3937" s="4"/>
+      <c r="E3937" s="1" t="s">
+        <v>7797</v>
+      </c>
+      <c r="F3937" s="6" t="s">
+        <v>7798</v>
+      </c>
     </row>
     <row r="3938" spans="3:6">
-      <c r="C3938"/>
-      <c r="D3938"/>
-      <c r="E3938"/>
-      <c r="F3938"/>
+      <c r="C3938" s="3">
+        <v>300093</v>
+      </c>
+      <c r="D3938" s="4"/>
+      <c r="E3938" s="1" t="s">
+        <v>7799</v>
+      </c>
+      <c r="F3938" s="6" t="s">
+        <v>7800</v>
+      </c>
     </row>
     <row r="3939" spans="3:6">
-      <c r="C3939"/>
-      <c r="D3939"/>
-      <c r="E3939"/>
-      <c r="F3939"/>
+      <c r="C3939" s="3">
+        <v>300094</v>
+      </c>
+      <c r="D3939" s="4"/>
+      <c r="E3939" s="1" t="s">
+        <v>7801</v>
+      </c>
+      <c r="F3939" s="6" t="s">
+        <v>7802</v>
+      </c>
     </row>
     <row r="3940" spans="3:6">
-      <c r="C3940"/>
-      <c r="D3940"/>
-      <c r="E3940"/>
-      <c r="F3940"/>
+      <c r="C3940" s="3">
+        <v>300095</v>
+      </c>
+      <c r="D3940" s="4"/>
+      <c r="E3940" s="1" t="s">
+        <v>7803</v>
+      </c>
+      <c r="F3940" s="6" t="s">
+        <v>7804</v>
+      </c>
     </row>
     <row r="3941" spans="3:6">
-      <c r="C3941"/>
-      <c r="D3941"/>
-      <c r="E3941"/>
-      <c r="F3941"/>
+      <c r="C3941" s="3">
+        <v>300096</v>
+      </c>
+      <c r="D3941" s="4"/>
+      <c r="E3941" s="1" t="s">
+        <v>7805</v>
+      </c>
+      <c r="F3941" s="6" t="s">
+        <v>7806</v>
+      </c>
     </row>
     <row r="3942" spans="3:6">
-      <c r="C3942"/>
-      <c r="D3942"/>
-      <c r="E3942"/>
-      <c r="F3942"/>
+      <c r="C3942" s="3">
+        <v>300097</v>
+      </c>
+      <c r="D3942" s="4"/>
+      <c r="E3942" s="1" t="s">
+        <v>7807</v>
+      </c>
+      <c r="F3942" s="6" t="s">
+        <v>7808</v>
+      </c>
     </row>
     <row r="3943" spans="3:6">
-      <c r="C3943"/>
-      <c r="D3943"/>
-      <c r="E3943"/>
-      <c r="F3943"/>
+      <c r="C3943" s="3">
+        <v>300098</v>
+      </c>
+      <c r="D3943" s="4"/>
+      <c r="E3943" s="1" t="s">
+        <v>7809</v>
+      </c>
+      <c r="F3943" s="6" t="s">
+        <v>7810</v>
+      </c>
     </row>
     <row r="3944" spans="3:6">
-      <c r="C3944"/>
-      <c r="D3944"/>
-      <c r="E3944"/>
-      <c r="F3944"/>
+      <c r="C3944" s="3">
+        <v>300099</v>
+      </c>
+      <c r="D3944" s="4"/>
+      <c r="E3944" s="1" t="s">
+        <v>7811</v>
+      </c>
+      <c r="F3944" s="6" t="s">
+        <v>7812</v>
+      </c>
     </row>
     <row r="3945" spans="3:6">
-      <c r="C3945"/>
-      <c r="D3945"/>
-      <c r="E3945"/>
-      <c r="F3945"/>
+      <c r="C3945" s="3">
+        <v>300100</v>
+      </c>
+      <c r="D3945" s="4"/>
+      <c r="E3945" s="1" t="s">
+        <v>7813</v>
+      </c>
+      <c r="F3945" s="6" t="s">
+        <v>7814</v>
+      </c>
     </row>
     <row r="3946" spans="3:6">
-      <c r="C3946"/>
-      <c r="D3946"/>
-      <c r="E3946"/>
-      <c r="F3946"/>
+      <c r="C3946" s="3">
+        <v>300101</v>
+      </c>
+      <c r="D3946" s="4"/>
+      <c r="E3946" s="1" t="s">
+        <v>7815</v>
+      </c>
+      <c r="F3946" s="6" t="s">
+        <v>7816</v>
+      </c>
     </row>
     <row r="3947" spans="3:6">
-      <c r="C3947"/>
-      <c r="D3947"/>
-      <c r="E3947"/>
-      <c r="F3947"/>
+      <c r="C3947" s="3">
+        <v>300102</v>
+      </c>
+      <c r="D3947" s="4"/>
+      <c r="E3947" s="1" t="s">
+        <v>7817</v>
+      </c>
+      <c r="F3947" s="6" t="s">
+        <v>7818</v>
+      </c>
     </row>
     <row r="3948" spans="3:6">
-      <c r="C3948"/>
-      <c r="D3948"/>
-      <c r="E3948"/>
-      <c r="F3948"/>
+      <c r="C3948" s="3">
+        <v>300103</v>
+      </c>
+      <c r="D3948" s="4"/>
+      <c r="E3948" s="1" t="s">
+        <v>7819</v>
+      </c>
+      <c r="F3948" s="6" t="s">
+        <v>7820</v>
+      </c>
     </row>
     <row r="3949" spans="3:6">
-      <c r="C3949"/>
-      <c r="D3949"/>
-      <c r="E3949"/>
-      <c r="F3949"/>
+      <c r="C3949" s="3">
+        <v>300104</v>
+      </c>
+      <c r="D3949" s="4"/>
+      <c r="E3949" s="1" t="s">
+        <v>7821</v>
+      </c>
+      <c r="F3949" s="6" t="s">
+        <v>7822</v>
+      </c>
     </row>
     <row r="3950" spans="3:6">
-      <c r="C3950"/>
-      <c r="D3950"/>
-      <c r="E3950"/>
-      <c r="F3950"/>
+      <c r="C3950" s="3">
+        <v>300105</v>
+      </c>
+      <c r="D3950" s="4"/>
+      <c r="E3950" s="1" t="s">
+        <v>7823</v>
+      </c>
+      <c r="F3950" s="6" t="s">
+        <v>7824</v>
+      </c>
     </row>
     <row r="3951" spans="3:6">
-      <c r="C3951"/>
-      <c r="D3951"/>
-      <c r="E3951"/>
-      <c r="F3951"/>
+      <c r="C3951" s="3">
+        <v>300106</v>
+      </c>
+      <c r="D3951" s="4"/>
+      <c r="E3951" s="1" t="s">
+        <v>7825</v>
+      </c>
+      <c r="F3951" s="6" t="s">
+        <v>7826</v>
+      </c>
     </row>
     <row r="3952" spans="3:6">
-      <c r="C3952"/>
-      <c r="D3952"/>
-      <c r="E3952"/>
-      <c r="F3952"/>
+      <c r="C3952" s="3">
+        <v>300107</v>
+      </c>
+      <c r="D3952" s="4"/>
+      <c r="E3952" s="1" t="s">
+        <v>7827</v>
+      </c>
+      <c r="F3952" s="6" t="s">
+        <v>7828</v>
+      </c>
     </row>
     <row r="3953" spans="3:6">
-      <c r="C3953"/>
-      <c r="D3953"/>
-      <c r="E3953"/>
-      <c r="F3953"/>
+      <c r="C3953" s="3">
+        <v>300108</v>
+      </c>
+      <c r="D3953" s="4"/>
+      <c r="E3953" s="1" t="s">
+        <v>7829</v>
+      </c>
+      <c r="F3953" s="6" t="s">
+        <v>7830</v>
+      </c>
     </row>
     <row r="3954" spans="3:6">
-      <c r="C3954"/>
-      <c r="D3954"/>
-      <c r="E3954"/>
-      <c r="F3954"/>
+      <c r="C3954" s="3">
+        <v>300109</v>
+      </c>
+      <c r="D3954" s="4"/>
+      <c r="E3954" s="1" t="s">
+        <v>7831</v>
+      </c>
+      <c r="F3954" s="6" t="s">
+        <v>7832</v>
+      </c>
     </row>
     <row r="3955" spans="3:6">
       <c r="C3955"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8026" uniqueCount="7833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8028" uniqueCount="7835">
   <si>
     <t>c</t>
   </si>
@@ -23526,6 +23526,12 @@
   </si>
   <si>
     <t>Defeat Infernal Any Lord Monsters &lt;color=#EAFF39&gt;{0}/{1}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>恭喜您!激活新的地图传送:{0}</t>
+  </si>
+  <si>
+    <t>Congratulations! You've unlocked map travel:{0}</t>
   </si>
 </sst>
 </file>
@@ -72216,10 +72222,16 @@
       </c>
     </row>
     <row r="3955" spans="3:6">
-      <c r="C3955"/>
+      <c r="C3955" s="3">
+        <v>300110</v>
+      </c>
       <c r="D3955"/>
-      <c r="E3955"/>
-      <c r="F3955"/>
+      <c r="E3955" s="1" t="s">
+        <v>7833</v>
+      </c>
+      <c r="F3955" s="6" t="s">
+        <v>7834</v>
+      </c>
     </row>
     <row r="3956" spans="3:6">
       <c r="C3956"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8028" uniqueCount="7835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8030" uniqueCount="7837">
   <si>
     <t>c</t>
   </si>
@@ -23532,6 +23532,12 @@
   </si>
   <si>
     <t>Congratulations! You've unlocked map travel:{0}</t>
+  </si>
+  <si>
+    <t>暂无出战宠物!</t>
+  </si>
+  <si>
+    <t>No active pet!</t>
   </si>
 </sst>
 </file>
@@ -72234,10 +72240,16 @@
       </c>
     </row>
     <row r="3956" spans="3:6">
-      <c r="C3956"/>
+      <c r="C3956" s="3">
+        <v>300111</v>
+      </c>
       <c r="D3956"/>
-      <c r="E3956"/>
-      <c r="F3956"/>
+      <c r="E3956" t="s">
+        <v>7835</v>
+      </c>
+      <c r="F3956" s="6" t="s">
+        <v>7836</v>
+      </c>
     </row>
     <row r="3957" spans="3:6">
       <c r="C3957"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8030" uniqueCount="7837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8048" uniqueCount="7854">
   <si>
     <t>c</t>
   </si>
@@ -23538,6 +23538,57 @@
   </si>
   <si>
     <t>No active pet!</t>
+  </si>
+  <si>
+    <t>待领取</t>
+  </si>
+  <si>
+    <t>Available</t>
+  </si>
+  <si>
+    <t>下次领取时间：</t>
+  </si>
+  <si>
+    <t>Next Claim Time:</t>
+  </si>
+  <si>
+    <t>可抽奖!</t>
+  </si>
+  <si>
+    <t>Draw Available!</t>
+  </si>
+  <si>
+    <t>点击抽奖</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>在线奖励</t>
+  </si>
+  <si>
+    <t>Online Reward</t>
+  </si>
+  <si>
+    <t>If the game feels laggy, switch back to Normal Mode in Settings.</t>
+  </si>
+  <si>
+    <t>猎人是擅长追踪、狩猎的职业，熟悉野外环境与猎物习性，运用弓箭、陷阱等工具，需具备敏锐观察力和野外生存能力。</t>
+  </si>
+  <si>
+    <t>Hunters are masters of tracking and hunting. They possess an intimate knowledge of the wild and their prey, utilizing bows, traps, and their keen senses to survive and thrive in the wilderness.</t>
+  </si>
+  <si>
+    <t>驾驭魔力的智者，借符文与魔法引动冰火等力量，可远程打击敌人、施展防护法术，需精深学识支撑魔力运用。</t>
+  </si>
+  <si>
+    <t>The Mage is a sage who wields arcane wisdom. Using runes and magic to channel elemental powers like ice and fire, they can strike foes from a distance and cast protective spells, all requiring profound knowledge to control their magic.</t>
+  </si>
+  <si>
+    <t>巨剑士以沉重巨剑为武器，凭惊人力量劈砍破防，兼顾近战压制与范围攻击，需强悍体能驾驭兵器、抗住敌方冲击。</t>
+  </si>
+  <si>
+    <t>The Greatsword Warrior wields a massive blade as their weapon. Relying on immense strength to cleave through enemy defenses, they excel at both close-quarters suppression and area-of-effect attacks. This requires a formidable physique to master the weapon and withstand enemy assaults.</t>
   </si>
 </sst>
 </file>
@@ -72235,7 +72286,7 @@
       <c r="E3955" s="1" t="s">
         <v>7833</v>
       </c>
-      <c r="F3955" s="6" t="s">
+      <c r="F3955" s="1" t="s">
         <v>7834</v>
       </c>
     </row>
@@ -72244,150 +72295,162 @@
         <v>300111</v>
       </c>
       <c r="D3956"/>
-      <c r="E3956" t="s">
+      <c r="E3956" s="1" t="s">
         <v>7835</v>
       </c>
-      <c r="F3956" s="6" t="s">
+      <c r="F3956" s="1" t="s">
         <v>7836</v>
       </c>
     </row>
     <row r="3957" spans="3:6">
-      <c r="C3957"/>
-      <c r="D3957"/>
-      <c r="E3957"/>
-      <c r="F3957"/>
+      <c r="C3957" s="3">
+        <v>300112</v>
+      </c>
+      <c r="D3957" s="1"/>
+      <c r="E3957" s="1" t="s">
+        <v>7837</v>
+      </c>
+      <c r="F3957" s="1" t="s">
+        <v>7838</v>
+      </c>
     </row>
     <row r="3958" spans="3:6">
-      <c r="C3958"/>
-      <c r="D3958"/>
-      <c r="E3958"/>
-      <c r="F3958"/>
+      <c r="C3958" s="3">
+        <v>300113</v>
+      </c>
+      <c r="D3958" s="1"/>
+      <c r="E3958" s="1" t="s">
+        <v>7839</v>
+      </c>
+      <c r="F3958" s="1" t="s">
+        <v>7840</v>
+      </c>
     </row>
     <row r="3959" spans="3:6">
-      <c r="C3959"/>
-      <c r="D3959"/>
-      <c r="E3959"/>
-      <c r="F3959"/>
+      <c r="C3959" s="3">
+        <v>300114</v>
+      </c>
+      <c r="D3959" s="1"/>
+      <c r="E3959" s="1" t="s">
+        <v>7841</v>
+      </c>
+      <c r="F3959" s="1" t="s">
+        <v>7842</v>
+      </c>
     </row>
     <row r="3960" spans="3:6">
-      <c r="C3960"/>
-      <c r="D3960"/>
-      <c r="E3960"/>
-      <c r="F3960"/>
+      <c r="C3960" s="3">
+        <v>300115</v>
+      </c>
+      <c r="D3960" s="1"/>
+      <c r="E3960" s="1" t="s">
+        <v>7843</v>
+      </c>
+      <c r="F3960" s="1" t="s">
+        <v>7844</v>
+      </c>
     </row>
     <row r="3961" spans="3:6">
-      <c r="C3961"/>
-      <c r="D3961"/>
-      <c r="E3961"/>
-      <c r="F3961"/>
+      <c r="C3961" s="3">
+        <v>300116</v>
+      </c>
+      <c r="D3961" s="1"/>
+      <c r="E3961" s="1" t="s">
+        <v>7845</v>
+      </c>
+      <c r="F3961" s="1" t="s">
+        <v>7846</v>
+      </c>
     </row>
     <row r="3962" spans="3:6">
-      <c r="C3962"/>
-      <c r="D3962"/>
-      <c r="E3962"/>
-      <c r="F3962"/>
+      <c r="C3962" s="3">
+        <v>300117</v>
+      </c>
+      <c r="D3962" s="1"/>
+      <c r="E3962" s="1" t="s">
+        <v>3182</v>
+      </c>
+      <c r="F3962" s="1" t="s">
+        <v>7847</v>
+      </c>
     </row>
     <row r="3963" spans="3:6">
-      <c r="C3963"/>
-      <c r="D3963"/>
-      <c r="E3963"/>
-      <c r="F3963"/>
+      <c r="C3963" s="3">
+        <v>300118</v>
+      </c>
+      <c r="D3963" s="1"/>
+      <c r="E3963" s="1" t="s">
+        <v>7848</v>
+      </c>
+      <c r="F3963" s="1" t="s">
+        <v>7849</v>
+      </c>
     </row>
     <row r="3964" spans="3:6">
-      <c r="C3964"/>
-      <c r="D3964"/>
-      <c r="E3964"/>
-      <c r="F3964"/>
+      <c r="C3964" s="3">
+        <v>300119</v>
+      </c>
+      <c r="D3964" s="1"/>
+      <c r="E3964" s="1" t="s">
+        <v>7850</v>
+      </c>
+      <c r="F3964" s="1" t="s">
+        <v>7851</v>
+      </c>
     </row>
     <row r="3965" spans="3:6">
-      <c r="C3965"/>
-      <c r="D3965"/>
-      <c r="E3965"/>
-      <c r="F3965"/>
-    </row>
-    <row r="3966" spans="3:6">
+      <c r="C3965" s="3">
+        <v>300120</v>
+      </c>
+      <c r="D3965" s="1"/>
+      <c r="E3965" s="1" t="s">
+        <v>7852</v>
+      </c>
+      <c r="F3965" s="1" t="s">
+        <v>7853</v>
+      </c>
+    </row>
+    <row r="3966" spans="3:3">
       <c r="C3966"/>
-      <c r="D3966"/>
-      <c r="E3966"/>
-      <c r="F3966"/>
-    </row>
-    <row r="3967" spans="3:6">
+    </row>
+    <row r="3967" spans="3:3">
       <c r="C3967"/>
-      <c r="D3967"/>
-      <c r="E3967"/>
-      <c r="F3967"/>
-    </row>
-    <row r="3968" spans="3:6">
+    </row>
+    <row r="3968" spans="3:3">
       <c r="C3968"/>
-      <c r="D3968"/>
-      <c r="E3968"/>
-      <c r="F3968"/>
-    </row>
-    <row r="3969" spans="3:6">
+    </row>
+    <row r="3969" spans="3:3">
       <c r="C3969"/>
-      <c r="D3969"/>
-      <c r="E3969"/>
-      <c r="F3969"/>
-    </row>
-    <row r="3970" spans="3:6">
+    </row>
+    <row r="3970" spans="3:3">
       <c r="C3970"/>
-      <c r="D3970"/>
-      <c r="E3970"/>
-      <c r="F3970"/>
-    </row>
-    <row r="3971" spans="3:6">
+    </row>
+    <row r="3971" spans="3:3">
       <c r="C3971"/>
-      <c r="D3971"/>
-      <c r="E3971"/>
-      <c r="F3971"/>
-    </row>
-    <row r="3972" spans="3:6">
+    </row>
+    <row r="3972" spans="3:3">
       <c r="C3972"/>
-      <c r="D3972"/>
-      <c r="E3972"/>
-      <c r="F3972"/>
-    </row>
-    <row r="3973" spans="3:6">
+    </row>
+    <row r="3973" spans="3:3">
       <c r="C3973"/>
-      <c r="D3973"/>
-      <c r="E3973"/>
-      <c r="F3973"/>
-    </row>
-    <row r="3974" spans="3:6">
+    </row>
+    <row r="3974" spans="3:3">
       <c r="C3974"/>
-      <c r="D3974"/>
-      <c r="E3974"/>
-      <c r="F3974"/>
-    </row>
-    <row r="3975" spans="3:6">
+    </row>
+    <row r="3975" spans="3:3">
       <c r="C3975"/>
-      <c r="D3975"/>
-      <c r="E3975"/>
-      <c r="F3975"/>
-    </row>
-    <row r="3976" spans="3:6">
+    </row>
+    <row r="3976" spans="3:3">
       <c r="C3976"/>
-      <c r="D3976"/>
-      <c r="E3976"/>
-      <c r="F3976"/>
-    </row>
-    <row r="3977" spans="3:6">
+    </row>
+    <row r="3977" spans="3:3">
       <c r="C3977"/>
-      <c r="D3977"/>
-      <c r="E3977"/>
-      <c r="F3977"/>
-    </row>
-    <row r="3978" spans="3:6">
+    </row>
+    <row r="3978" spans="3:3">
       <c r="C3978"/>
-      <c r="D3978"/>
-      <c r="E3978"/>
-      <c r="F3978"/>
-    </row>
-    <row r="3979" spans="3:6">
+    </row>
+    <row r="3979" spans="3:3">
       <c r="C3979"/>
-      <c r="D3979"/>
-      <c r="E3979"/>
-      <c r="F3979"/>
     </row>
     <row r="3980" spans="3:6">
       <c r="C3980"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8048" uniqueCount="7854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8052" uniqueCount="7858">
   <si>
     <t>c</t>
   </si>
@@ -23567,7 +23567,7 @@
     <t>在线奖励</t>
   </si>
   <si>
-    <t>Online Reward</t>
+    <t>OnlineReward</t>
   </si>
   <si>
     <t>If the game feels laggy, switch back to Normal Mode in Settings.</t>
@@ -23589,6 +23589,18 @@
   </si>
   <si>
     <t>The Greatsword Warrior wields a massive blade as their weapon. Relying on immense strength to cleave through enemy defenses, they excel at both close-quarters suppression and area-of-effect attacks. This requires a formidable physique to master the weapon and withstand enemy assaults.</t>
+  </si>
+  <si>
+    <t>&lt;color=#{0}&gt;{1}领取&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#{0}&gt;{1}Recvive&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>{0}后领取</t>
+  </si>
+  <si>
+    <t>Claim in {0}</t>
   </si>
 </sst>
 </file>
@@ -72306,7 +72318,6 @@
       <c r="C3957" s="3">
         <v>300112</v>
       </c>
-      <c r="D3957" s="1"/>
       <c r="E3957" s="1" t="s">
         <v>7837</v>
       </c>
@@ -72318,7 +72329,6 @@
       <c r="C3958" s="3">
         <v>300113</v>
       </c>
-      <c r="D3958" s="1"/>
       <c r="E3958" s="1" t="s">
         <v>7839</v>
       </c>
@@ -72330,7 +72340,6 @@
       <c r="C3959" s="3">
         <v>300114</v>
       </c>
-      <c r="D3959" s="1"/>
       <c r="E3959" s="1" t="s">
         <v>7841</v>
       </c>
@@ -72342,7 +72351,6 @@
       <c r="C3960" s="3">
         <v>300115</v>
       </c>
-      <c r="D3960" s="1"/>
       <c r="E3960" s="1" t="s">
         <v>7843</v>
       </c>
@@ -72354,7 +72362,6 @@
       <c r="C3961" s="3">
         <v>300116</v>
       </c>
-      <c r="D3961" s="1"/>
       <c r="E3961" s="1" t="s">
         <v>7845</v>
       </c>
@@ -72366,7 +72373,6 @@
       <c r="C3962" s="3">
         <v>300117</v>
       </c>
-      <c r="D3962" s="1"/>
       <c r="E3962" s="1" t="s">
         <v>3182</v>
       </c>
@@ -72378,7 +72384,6 @@
       <c r="C3963" s="3">
         <v>300118</v>
       </c>
-      <c r="D3963" s="1"/>
       <c r="E3963" s="1" t="s">
         <v>7848</v>
       </c>
@@ -72390,7 +72395,6 @@
       <c r="C3964" s="3">
         <v>300119</v>
       </c>
-      <c r="D3964" s="1"/>
       <c r="E3964" s="1" t="s">
         <v>7850</v>
       </c>
@@ -72402,7 +72406,6 @@
       <c r="C3965" s="3">
         <v>300120</v>
       </c>
-      <c r="D3965" s="1"/>
       <c r="E3965" s="1" t="s">
         <v>7852</v>
       </c>
@@ -72410,11 +72413,27 @@
         <v>7853</v>
       </c>
     </row>
-    <row r="3966" spans="3:3">
-      <c r="C3966"/>
-    </row>
-    <row r="3967" spans="3:3">
-      <c r="C3967"/>
+    <row r="3966" spans="3:6">
+      <c r="C3966" s="3">
+        <v>300121</v>
+      </c>
+      <c r="E3966" s="1" t="s">
+        <v>7854</v>
+      </c>
+      <c r="F3966" s="1" t="s">
+        <v>7855</v>
+      </c>
+    </row>
+    <row r="3967" spans="3:6">
+      <c r="C3967" s="3">
+        <v>300122</v>
+      </c>
+      <c r="E3967" s="1" t="s">
+        <v>7856</v>
+      </c>
+      <c r="F3967" s="1" t="s">
+        <v>7857</v>
+      </c>
     </row>
     <row r="3968" spans="3:3">
       <c r="C3968"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8052" uniqueCount="7858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8052" uniqueCount="7857">
   <si>
     <t>c</t>
   </si>
@@ -23565,9 +23565,6 @@
   </si>
   <si>
     <t>在线奖励</t>
-  </si>
-  <si>
-    <t>OnlineReward</t>
   </si>
   <si>
     <t>If the game feels laggy, switch back to Normal Mode in Settings.</t>
@@ -72366,7 +72363,7 @@
         <v>7845</v>
       </c>
       <c r="F3961" s="1" t="s">
-        <v>7846</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="3962" spans="3:6">
@@ -72377,7 +72374,7 @@
         <v>3182</v>
       </c>
       <c r="F3962" s="1" t="s">
-        <v>7847</v>
+        <v>7846</v>
       </c>
     </row>
     <row r="3963" spans="3:6">
@@ -72385,10 +72382,10 @@
         <v>300118</v>
       </c>
       <c r="E3963" s="1" t="s">
+        <v>7847</v>
+      </c>
+      <c r="F3963" s="1" t="s">
         <v>7848</v>
-      </c>
-      <c r="F3963" s="1" t="s">
-        <v>7849</v>
       </c>
     </row>
     <row r="3964" spans="3:6">
@@ -72396,10 +72393,10 @@
         <v>300119</v>
       </c>
       <c r="E3964" s="1" t="s">
+        <v>7849</v>
+      </c>
+      <c r="F3964" s="1" t="s">
         <v>7850</v>
-      </c>
-      <c r="F3964" s="1" t="s">
-        <v>7851</v>
       </c>
     </row>
     <row r="3965" spans="3:6">
@@ -72407,10 +72404,10 @@
         <v>300120</v>
       </c>
       <c r="E3965" s="1" t="s">
+        <v>7851</v>
+      </c>
+      <c r="F3965" s="1" t="s">
         <v>7852</v>
-      </c>
-      <c r="F3965" s="1" t="s">
-        <v>7853</v>
       </c>
     </row>
     <row r="3966" spans="3:6">
@@ -72418,10 +72415,10 @@
         <v>300121</v>
       </c>
       <c r="E3966" s="1" t="s">
+        <v>7853</v>
+      </c>
+      <c r="F3966" s="1" t="s">
         <v>7854</v>
-      </c>
-      <c r="F3966" s="1" t="s">
-        <v>7855</v>
       </c>
     </row>
     <row r="3967" spans="3:6">
@@ -72429,10 +72426,10 @@
         <v>300122</v>
       </c>
       <c r="E3967" s="1" t="s">
+        <v>7855</v>
+      </c>
+      <c r="F3967" s="1" t="s">
         <v>7856</v>
-      </c>
-      <c r="F3967" s="1" t="s">
-        <v>7857</v>
       </c>
     </row>
     <row r="3968" spans="3:3">

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8052" uniqueCount="7857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8054" uniqueCount="7858">
   <si>
     <t>c</t>
   </si>
@@ -23598,6 +23598,9 @@
   </si>
   <si>
     <t>Claim in {0}</t>
+  </si>
+  <si>
+    <t>战斗</t>
   </si>
 </sst>
 </file>
@@ -72432,8 +72435,16 @@
         <v>7856</v>
       </c>
     </row>
-    <row r="3968" spans="3:3">
-      <c r="C3968"/>
+    <row r="3968" spans="3:6">
+      <c r="C3968" s="3">
+        <v>300123</v>
+      </c>
+      <c r="E3968" s="1" t="s">
+        <v>7857</v>
+      </c>
+      <c r="F3968" s="1" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="3969" spans="3:3">
       <c r="C3969"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8054" uniqueCount="7858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8056" uniqueCount="7860">
   <si>
     <t>c</t>
   </si>
@@ -23601,6 +23601,12 @@
   </si>
   <si>
     <t>战斗</t>
+  </si>
+  <si>
+    <t>距离目标{0}米</t>
+  </si>
+  <si>
+    <t>Target Distance: {0}m</t>
   </si>
 </sst>
 </file>
@@ -72446,8 +72452,16 @@
         <v>343</v>
       </c>
     </row>
-    <row r="3969" spans="3:3">
-      <c r="C3969"/>
+    <row r="3969" spans="3:6">
+      <c r="C3969" s="3">
+        <v>300124</v>
+      </c>
+      <c r="E3969" s="1" t="s">
+        <v>7858</v>
+      </c>
+      <c r="F3969" s="1" t="s">
+        <v>7859</v>
+      </c>
     </row>
     <row r="3970" spans="3:3">
       <c r="C3970"/>
@@ -72479,11 +72493,9 @@
     <row r="3979" spans="3:3">
       <c r="C3979"/>
     </row>
-    <row r="3980" spans="3:6">
+    <row r="3980" spans="3:4">
       <c r="C3980"/>
       <c r="D3980"/>
-      <c r="E3980"/>
-      <c r="F3980"/>
     </row>
     <row r="3981" spans="3:6">
       <c r="C3981"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8056" uniqueCount="7860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8058" uniqueCount="7862">
   <si>
     <t>c</t>
   </si>
@@ -23607,6 +23607,12 @@
   </si>
   <si>
     <t>Target Distance: {0}m</t>
+  </si>
+  <si>
+    <t>寻路中...</t>
+  </si>
+  <si>
+    <t>Pathfinding...</t>
   </si>
 </sst>
 </file>
@@ -72463,8 +72469,16 @@
         <v>7859</v>
       </c>
     </row>
-    <row r="3970" spans="3:3">
-      <c r="C3970"/>
+    <row r="3970" spans="3:6">
+      <c r="C3970" s="3">
+        <v>300125</v>
+      </c>
+      <c r="E3970" s="1" t="s">
+        <v>7860</v>
+      </c>
+      <c r="F3970" s="1" t="s">
+        <v>7861</v>
+      </c>
     </row>
     <row r="3971" spans="3:3">
       <c r="C3971"/>
@@ -72493,27 +72507,17 @@
     <row r="3979" spans="3:3">
       <c r="C3979"/>
     </row>
-    <row r="3980" spans="3:4">
+    <row r="3980" spans="3:3">
       <c r="C3980"/>
-      <c r="D3980"/>
-    </row>
-    <row r="3981" spans="3:6">
+    </row>
+    <row r="3981" spans="3:3">
       <c r="C3981"/>
-      <c r="D3981"/>
-      <c r="E3981"/>
-      <c r="F3981"/>
-    </row>
-    <row r="3982" spans="3:6">
+    </row>
+    <row r="3982" spans="3:3">
       <c r="C3982"/>
-      <c r="D3982"/>
-      <c r="E3982"/>
-      <c r="F3982"/>
-    </row>
-    <row r="3983" spans="3:6">
+    </row>
+    <row r="3983" spans="3:3">
       <c r="C3983"/>
-      <c r="D3983"/>
-      <c r="E3983"/>
-      <c r="F3983"/>
     </row>
     <row r="3984" spans="3:6">
       <c r="C3984"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8058" uniqueCount="7862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8074" uniqueCount="7878">
   <si>
     <t>c</t>
   </si>
@@ -23613,6 +23613,54 @@
   </si>
   <si>
     <t>Pathfinding...</t>
+  </si>
+  <si>
+    <t>魔能</t>
+  </si>
+  <si>
+    <t>MagicKa</t>
+  </si>
+  <si>
+    <t>总等级:</t>
+  </si>
+  <si>
+    <t>TotalLevel:</t>
+  </si>
+  <si>
+    <t>栏位属性：</t>
+  </si>
+  <si>
+    <t>Slot Properties</t>
+  </si>
+  <si>
+    <t>消耗列表</t>
+  </si>
+  <si>
+    <t>Cost List</t>
+  </si>
+  <si>
+    <t>合成</t>
+  </si>
+  <si>
+    <t>Crafting</t>
+  </si>
+  <si>
+    <t>魔能列表</t>
+  </si>
+  <si>
+    <t>MagicKa List</t>
+  </si>
+  <si>
+    <t>提示：放置三个同等级魔能，有50%概率合成下一级魔能</t>
+  </si>
+  <si>
+    <t>Combine three same-level Magicka for a 50% chance to create a higher-level one.</t>
+  </si>
+  <si>
+    <t>开始合成</t>
+  </si>
+  <si>
+    <t>Begin Crafting</t>
   </si>
 </sst>
 </file>
@@ -24621,7 +24669,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:F3994"/>
+  <dimension ref="C2:F3993"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -24633,7 +24681,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:4">
+    <row r="2" spans="3:6">
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
@@ -72480,86 +72528,134 @@
         <v>7861</v>
       </c>
     </row>
-    <row r="3971" spans="3:3">
-      <c r="C3971"/>
-    </row>
-    <row r="3972" spans="3:3">
-      <c r="C3972"/>
-    </row>
-    <row r="3973" spans="3:3">
-      <c r="C3973"/>
-    </row>
-    <row r="3974" spans="3:3">
-      <c r="C3974"/>
-    </row>
-    <row r="3975" spans="3:3">
-      <c r="C3975"/>
-    </row>
-    <row r="3976" spans="3:3">
-      <c r="C3976"/>
-    </row>
-    <row r="3977" spans="3:3">
-      <c r="C3977"/>
-    </row>
-    <row r="3978" spans="3:3">
-      <c r="C3978"/>
-    </row>
-    <row r="3979" spans="3:3">
+    <row r="3971" spans="3:6">
+      <c r="C3971" s="3">
+        <v>300126</v>
+      </c>
+      <c r="E3971" s="1" t="s">
+        <v>7862</v>
+      </c>
+      <c r="F3971" s="1" t="s">
+        <v>7863</v>
+      </c>
+    </row>
+    <row r="3972" spans="3:6">
+      <c r="C3972" s="3">
+        <v>300127</v>
+      </c>
+      <c r="E3972" s="1" t="s">
+        <v>7864</v>
+      </c>
+      <c r="F3972" s="1" t="s">
+        <v>7865</v>
+      </c>
+    </row>
+    <row r="3973" spans="3:6">
+      <c r="C3973" s="3">
+        <v>300128</v>
+      </c>
+      <c r="E3973" s="1" t="s">
+        <v>7866</v>
+      </c>
+      <c r="F3973" s="1" t="s">
+        <v>7867</v>
+      </c>
+    </row>
+    <row r="3974" spans="3:6">
+      <c r="C3974" s="3">
+        <v>300129</v>
+      </c>
+      <c r="E3974" s="1" t="s">
+        <v>7868</v>
+      </c>
+      <c r="F3974" s="1" t="s">
+        <v>7869</v>
+      </c>
+    </row>
+    <row r="3975" spans="3:6">
+      <c r="C3975" s="3">
+        <v>300130</v>
+      </c>
+      <c r="E3975" s="1" t="s">
+        <v>7870</v>
+      </c>
+      <c r="F3975" s="1" t="s">
+        <v>7871</v>
+      </c>
+    </row>
+    <row r="3976" spans="3:6">
+      <c r="C3976" s="3">
+        <v>300131</v>
+      </c>
+      <c r="E3976" s="1" t="s">
+        <v>7872</v>
+      </c>
+      <c r="F3976" s="1" t="s">
+        <v>7873</v>
+      </c>
+    </row>
+    <row r="3977" spans="3:6">
+      <c r="C3977" s="3">
+        <v>300132</v>
+      </c>
+      <c r="E3977" s="1" t="s">
+        <v>7874</v>
+      </c>
+      <c r="F3977" s="1" t="s">
+        <v>7875</v>
+      </c>
+    </row>
+    <row r="3978" spans="3:6">
+      <c r="C3978" s="3">
+        <v>300133</v>
+      </c>
+      <c r="E3978" s="1" t="s">
+        <v>7876</v>
+      </c>
+      <c r="F3978" s="1" t="s">
+        <v>7877</v>
+      </c>
+    </row>
+    <row r="3979" spans="3:6">
       <c r="C3979"/>
     </row>
-    <row r="3980" spans="3:3">
+    <row r="3980" spans="3:6">
       <c r="C3980"/>
     </row>
-    <row r="3981" spans="3:3">
+    <row r="3981" spans="3:6">
       <c r="C3981"/>
     </row>
-    <row r="3982" spans="3:3">
+    <row r="3982" spans="3:6">
       <c r="C3982"/>
     </row>
-    <row r="3983" spans="3:3">
+    <row r="3983" spans="3:6">
       <c r="C3983"/>
     </row>
     <row r="3984" spans="3:6">
       <c r="C3984"/>
-      <c r="D3984"/>
-      <c r="E3984"/>
-      <c r="F3984"/>
     </row>
     <row r="3985" spans="3:6">
       <c r="C3985"/>
-      <c r="D3985"/>
-      <c r="E3985"/>
-      <c r="F3985"/>
     </row>
     <row r="3986" spans="3:6">
       <c r="C3986"/>
       <c r="D3986"/>
-      <c r="E3986"/>
-      <c r="F3986"/>
     </row>
     <row r="3987" spans="3:6">
       <c r="C3987"/>
       <c r="D3987"/>
-      <c r="E3987"/>
-      <c r="F3987"/>
     </row>
     <row r="3988" spans="3:6">
       <c r="C3988"/>
       <c r="D3988"/>
-      <c r="E3988"/>
-      <c r="F3988"/>
     </row>
     <row r="3989" spans="3:6">
       <c r="C3989"/>
       <c r="D3989"/>
-      <c r="E3989"/>
-      <c r="F3989"/>
     </row>
     <row r="3990" spans="3:6">
       <c r="C3990"/>
       <c r="D3990"/>
-      <c r="E3990"/>
-      <c r="F3990"/>
     </row>
     <row r="3991" spans="3:6">
       <c r="C3991"/>
@@ -72578,12 +72674,6 @@
       <c r="D3993"/>
       <c r="E3993"/>
       <c r="F3993"/>
-    </row>
-    <row r="3994" spans="3:6">
-      <c r="C3994"/>
-      <c r="D3994"/>
-      <c r="E3994"/>
-      <c r="F3994"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8074" uniqueCount="7878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8076" uniqueCount="7880">
   <si>
     <t>c</t>
   </si>
@@ -23661,6 +23661,12 @@
   </si>
   <si>
     <t>Begin Crafting</t>
+  </si>
+  <si>
+    <t>需要道具</t>
+  </si>
+  <si>
+    <t>Need Items</t>
   </si>
 </sst>
 </file>
@@ -72617,7 +72623,15 @@
       </c>
     </row>
     <row r="3979" spans="3:6">
-      <c r="C3979"/>
+      <c r="C3979" s="3">
+        <v>300134</v>
+      </c>
+      <c r="E3979" s="1" t="s">
+        <v>7878</v>
+      </c>
+      <c r="F3979" s="1" t="s">
+        <v>7879</v>
+      </c>
     </row>
     <row r="3980" spans="3:6">
       <c r="C3980"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8076" uniqueCount="7880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8078" uniqueCount="7882">
   <si>
     <t>c</t>
   </si>
@@ -23667,6 +23667,12 @@
   </si>
   <si>
     <t>Need Items</t>
+  </si>
+  <si>
+    <t>当前栏位未开启!</t>
+  </si>
+  <si>
+    <t>This slot is inactive!</t>
   </si>
 </sst>
 </file>
@@ -72634,7 +72640,15 @@
       </c>
     </row>
     <row r="3980" spans="3:6">
-      <c r="C3980"/>
+      <c r="C3980" s="3">
+        <v>300135</v>
+      </c>
+      <c r="E3980" s="1" t="s">
+        <v>7880</v>
+      </c>
+      <c r="F3980" s="1" t="s">
+        <v>7881</v>
+      </c>
     </row>
     <row r="3981" spans="3:6">
       <c r="C3981"/>
@@ -72653,19 +72667,15 @@
     </row>
     <row r="3986" spans="3:6">
       <c r="C3986"/>
-      <c r="D3986"/>
     </row>
     <row r="3987" spans="3:6">
       <c r="C3987"/>
-      <c r="D3987"/>
     </row>
     <row r="3988" spans="3:6">
       <c r="C3988"/>
-      <c r="D3988"/>
     </row>
     <row r="3989" spans="3:6">
       <c r="C3989"/>
-      <c r="D3989"/>
     </row>
     <row r="3990" spans="3:6">
       <c r="C3990"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8078" uniqueCount="7882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8082" uniqueCount="7886">
   <si>
     <t>c</t>
   </si>
@@ -23673,6 +23673,18 @@
   </si>
   <si>
     <t>This slot is inactive!</t>
+  </si>
+  <si>
+    <t>当前经验超过200%无法获得新的经验！请完成进阶之路任务开启新的等级，或前往主城经验老头处用多余的经验兑换奖励喔！</t>
+  </si>
+  <si>
+    <t>XP capped at 200%! Complete "Adv. Path" tasks to unlock new levels, or trade surplus XP with the XP Merchant in the main city!</t>
+  </si>
+  <si>
+    <t>当前经验超过200%，请前往主城经验老头处用多余的经验兑换奖励喔！</t>
+  </si>
+  <si>
+    <t>XP capped at 200%! Visit the XP Merchant in the main city to trade surplus XP for rewards!</t>
   </si>
 </sst>
 </file>
@@ -72651,10 +72663,26 @@
       </c>
     </row>
     <row r="3981" spans="3:6">
-      <c r="C3981"/>
+      <c r="C3981" s="3">
+        <v>300136</v>
+      </c>
+      <c r="E3981" s="1" t="s">
+        <v>7882</v>
+      </c>
+      <c r="F3981" s="1" t="s">
+        <v>7883</v>
+      </c>
     </row>
     <row r="3982" spans="3:6">
-      <c r="C3982"/>
+      <c r="C3982" s="3">
+        <v>300137</v>
+      </c>
+      <c r="E3982" s="1" t="s">
+        <v>7884</v>
+      </c>
+      <c r="F3982" s="1" t="s">
+        <v>7885</v>
+      </c>
     </row>
     <row r="3983" spans="3:6">
       <c r="C3983"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -23678,7 +23678,7 @@
     <t>当前经验超过200%无法获得新的经验！请完成进阶之路任务开启新的等级，或前往主城经验老头处用多余的经验兑换奖励喔！</t>
   </si>
   <si>
-    <t>XP capped at 200%! Complete "Adv. Path" tasks to unlock new levels, or trade surplus XP with the XP Merchant in the main city!</t>
+    <t>XP capped at 200%! Complete Adv. Path tasks to unlock new levels, or trade surplus XP with the XP Merchant in the main city!</t>
   </si>
   <si>
     <t>当前经验超过200%，请前往主城经验老头处用多余的经验兑换奖励喔！</t>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8082" uniqueCount="7886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8086" uniqueCount="7890">
   <si>
     <t>c</t>
   </si>
@@ -23685,6 +23685,18 @@
   </si>
   <si>
     <t>XP capped at 200%! Visit the XP Merchant in the main city to trade surplus XP for rewards!</t>
+  </si>
+  <si>
+    <t>进阶之路系列任务</t>
+  </si>
+  <si>
+    <t>Advanced Path Series Missions</t>
+  </si>
+  <si>
+    <t>完成所有进阶之路后，可以将等级上限突破至75级！</t>
+  </si>
+  <si>
+    <t>After completing all Advanced Path Missions, the level cap can be increased to 75!</t>
   </si>
 </sst>
 </file>
@@ -23697,7 +23709,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -23728,6 +23740,12 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -24199,16 +24217,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -24217,119 +24232,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -24345,6 +24363,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -72685,47 +72704,57 @@
       </c>
     </row>
     <row r="3983" spans="3:6">
-      <c r="C3983"/>
-    </row>
-    <row r="3984" spans="3:6">
-      <c r="C3984"/>
-    </row>
-    <row r="3985" spans="3:6">
+      <c r="C3983" s="3">
+        <v>300138</v>
+      </c>
+      <c r="E3983" s="1" t="s">
+        <v>7886</v>
+      </c>
+      <c r="F3983" s="1" t="s">
+        <v>7887</v>
+      </c>
+    </row>
+    <row r="3984" ht="17.25" spans="3:6">
+      <c r="C3984" s="3">
+        <v>300139</v>
+      </c>
+      <c r="E3984" s="1" t="s">
+        <v>7888</v>
+      </c>
+      <c r="F3984" s="9" t="s">
+        <v>7889</v>
+      </c>
+    </row>
+    <row r="3985" spans="3:4">
       <c r="C3985"/>
     </row>
-    <row r="3986" spans="3:6">
+    <row r="3986" spans="3:4">
       <c r="C3986"/>
     </row>
-    <row r="3987" spans="3:6">
+    <row r="3987" spans="3:4">
       <c r="C3987"/>
     </row>
-    <row r="3988" spans="3:6">
+    <row r="3988" spans="3:4">
       <c r="C3988"/>
     </row>
-    <row r="3989" spans="3:6">
+    <row r="3989" spans="3:4">
       <c r="C3989"/>
     </row>
-    <row r="3990" spans="3:6">
+    <row r="3990" spans="3:4">
       <c r="C3990"/>
       <c r="D3990"/>
     </row>
-    <row r="3991" spans="3:6">
+    <row r="3991" spans="3:4">
       <c r="C3991"/>
       <c r="D3991"/>
-      <c r="E3991"/>
-      <c r="F3991"/>
-    </row>
-    <row r="3992" spans="3:6">
+    </row>
+    <row r="3992" spans="3:4">
       <c r="C3992"/>
       <c r="D3992"/>
-      <c r="E3992"/>
-      <c r="F3992"/>
-    </row>
-    <row r="3993" spans="3:6">
+    </row>
+    <row r="3993" spans="3:4">
       <c r="C3993"/>
       <c r="D3993"/>
-      <c r="E3993"/>
-      <c r="F3993"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8086" uniqueCount="7890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8088" uniqueCount="7892">
   <si>
     <t>c</t>
   </si>
@@ -23697,6 +23697,12 @@
   </si>
   <si>
     <t>After completing all Advanced Path Missions, the level cap can be increased to 75!</t>
+  </si>
+  <si>
+    <t>已达到最大等级</t>
+  </si>
+  <si>
+    <t>Max Leve</t>
   </si>
 </sst>
 </file>
@@ -72725,34 +72731,42 @@
         <v>7889</v>
       </c>
     </row>
-    <row r="3985" spans="3:4">
-      <c r="C3985"/>
-    </row>
-    <row r="3986" spans="3:4">
+    <row r="3985" spans="3:6">
+      <c r="C3985" s="3">
+        <v>300140</v>
+      </c>
+      <c r="E3985" s="1" t="s">
+        <v>7890</v>
+      </c>
+      <c r="F3985" s="1" t="s">
+        <v>7891</v>
+      </c>
+    </row>
+    <row r="3986" spans="3:6">
       <c r="C3986"/>
     </row>
-    <row r="3987" spans="3:4">
+    <row r="3987" spans="3:6">
       <c r="C3987"/>
     </row>
-    <row r="3988" spans="3:4">
+    <row r="3988" spans="3:6">
       <c r="C3988"/>
     </row>
-    <row r="3989" spans="3:4">
+    <row r="3989" spans="3:6">
       <c r="C3989"/>
     </row>
-    <row r="3990" spans="3:4">
+    <row r="3990" spans="3:6">
       <c r="C3990"/>
       <c r="D3990"/>
     </row>
-    <row r="3991" spans="3:4">
+    <row r="3991" spans="3:6">
       <c r="C3991"/>
       <c r="D3991"/>
     </row>
-    <row r="3992" spans="3:4">
+    <row r="3992" spans="3:6">
       <c r="C3992"/>
       <c r="D3992"/>
     </row>
-    <row r="3993" spans="3:4">
+    <row r="3993" spans="3:6">
       <c r="C3993"/>
       <c r="D3993"/>
     </row>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8088" uniqueCount="7892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8094" uniqueCount="7898">
   <si>
     <t>c</t>
   </si>
@@ -23703,6 +23703,24 @@
   </si>
   <si>
     <t>Max Leve</t>
+  </si>
+  <si>
+    <t>攻击型</t>
+  </si>
+  <si>
+    <t>Attack Type</t>
+  </si>
+  <si>
+    <t>恢复型</t>
+  </si>
+  <si>
+    <t>Healing Type</t>
+  </si>
+  <si>
+    <t>全能型</t>
+  </si>
+  <si>
+    <t>All-Rounder</t>
   </si>
 </sst>
 </file>
@@ -72743,13 +72761,37 @@
       </c>
     </row>
     <row r="3986" spans="3:6">
-      <c r="C3986"/>
+      <c r="C3986" s="3">
+        <v>300141</v>
+      </c>
+      <c r="E3986" s="1" t="s">
+        <v>7892</v>
+      </c>
+      <c r="F3986" s="1" t="s">
+        <v>7893</v>
+      </c>
     </row>
     <row r="3987" spans="3:6">
-      <c r="C3987"/>
+      <c r="C3987" s="3">
+        <v>300142</v>
+      </c>
+      <c r="E3987" s="1" t="s">
+        <v>7894</v>
+      </c>
+      <c r="F3987" s="1" t="s">
+        <v>7895</v>
+      </c>
     </row>
     <row r="3988" spans="3:6">
-      <c r="C3988"/>
+      <c r="C3988" s="3">
+        <v>300143</v>
+      </c>
+      <c r="E3988" s="1" t="s">
+        <v>7896</v>
+      </c>
+      <c r="F3988" s="1" t="s">
+        <v>7897</v>
+      </c>
     </row>
     <row r="3989" spans="3:6">
       <c r="C3989"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -23708,19 +23708,19 @@
     <t>攻击型</t>
   </si>
   <si>
-    <t>Attack Type</t>
+    <t>AttackType</t>
   </si>
   <si>
     <t>恢复型</t>
   </si>
   <si>
-    <t>Healing Type</t>
+    <t>HealingType</t>
   </si>
   <si>
     <t>全能型</t>
   </si>
   <si>
-    <t>All-Rounder</t>
+    <t>AllRounder</t>
   </si>
 </sst>
 </file>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8094" uniqueCount="7898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8097" uniqueCount="7901">
   <si>
     <t>c</t>
   </si>
@@ -23721,6 +23721,15 @@
   </si>
   <si>
     <t>AllRounder</t>
+  </si>
+  <si>
+    <t>阶段说明</t>
+  </si>
+  <si>
+    <t>Stage Description</t>
+  </si>
+  <si>
+    <t>提示:当饱食度达到一定阶段时,会为每位贡献者赠送一个礼包哦！</t>
   </si>
 </sst>
 </file>
@@ -24371,7 +24380,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -24388,6 +24397,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -24743,7 +24755,7 @@
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="42.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="61" style="1" customWidth="1"/>
+    <col min="5" max="5" width="77.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="112.375" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -72794,11 +72806,24 @@
       </c>
     </row>
     <row r="3989" spans="3:6">
-      <c r="C3989"/>
+      <c r="C3989" s="3">
+        <v>300144</v>
+      </c>
+      <c r="E3989" s="1" t="s">
+        <v>7898</v>
+      </c>
+      <c r="F3989" s="1" t="s">
+        <v>7899</v>
+      </c>
     </row>
     <row r="3990" spans="3:6">
-      <c r="C3990"/>
+      <c r="C3990" s="3">
+        <v>300145</v>
+      </c>
       <c r="D3990"/>
+      <c r="E3990" s="10" t="s">
+        <v>7900</v>
+      </c>
     </row>
     <row r="3991" spans="3:6">
       <c r="C3991"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8097" uniqueCount="7901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8098" uniqueCount="7902">
   <si>
     <t>c</t>
   </si>
@@ -23730,6 +23730,9 @@
   </si>
   <si>
     <t>提示:当饱食度达到一定阶段时,会为每位贡献者赠送一个礼包哦！</t>
+  </si>
+  <si>
+    <t>Hint: When Satiety reaches a certain level, a gift package will be given to each contributor!</t>
   </si>
 </sst>
 </file>
@@ -24380,7 +24383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -24397,6 +24400,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -72824,6 +72830,9 @@
       <c r="E3990" s="10" t="s">
         <v>7900</v>
       </c>
+      <c r="F3990" s="11" t="s">
+        <v>7901</v>
+      </c>
     </row>
     <row r="3991" spans="3:6">
       <c r="C3991"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8098" uniqueCount="7902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8104" uniqueCount="7908">
   <si>
     <t>c</t>
   </si>
@@ -23733,6 +23733,24 @@
   </si>
   <si>
     <t>Hint: When Satiety reaches a certain level, a gift package will be given to each contributor!</t>
+  </si>
+  <si>
+    <t>周任务</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly Tasks </t>
+  </si>
+  <si>
+    <t>1.在野外击败怪物时会掉落对应的活动道具。</t>
+  </si>
+  <si>
+    <t>Defeating wild monsters drops event items.</t>
+  </si>
+  <si>
+    <t>2.喂食道具会获得不同的奖励哦！</t>
+  </si>
+  <si>
+    <t>Feed items for different rewards!</t>
   </si>
 </sst>
 </file>
@@ -24383,7 +24401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -24400,12 +24418,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -24754,14 +24766,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:F3993"/>
+  <dimension ref="B2:F3997"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="42.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="77.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="88.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="112.375" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -72591,7 +72603,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="3969" spans="3:6">
+    <row r="3969" spans="2:6">
       <c r="C3969" s="3">
         <v>300124</v>
       </c>
@@ -72602,7 +72614,7 @@
         <v>7859</v>
       </c>
     </row>
-    <row r="3970" spans="3:6">
+    <row r="3970" spans="2:6">
       <c r="C3970" s="3">
         <v>300125</v>
       </c>
@@ -72613,7 +72625,7 @@
         <v>7861</v>
       </c>
     </row>
-    <row r="3971" spans="3:6">
+    <row r="3971" spans="2:6">
       <c r="C3971" s="3">
         <v>300126</v>
       </c>
@@ -72624,7 +72636,7 @@
         <v>7863</v>
       </c>
     </row>
-    <row r="3972" spans="3:6">
+    <row r="3972" spans="2:6">
       <c r="C3972" s="3">
         <v>300127</v>
       </c>
@@ -72635,7 +72647,7 @@
         <v>7865</v>
       </c>
     </row>
-    <row r="3973" spans="3:6">
+    <row r="3973" spans="2:6">
       <c r="C3973" s="3">
         <v>300128</v>
       </c>
@@ -72646,7 +72658,7 @@
         <v>7867</v>
       </c>
     </row>
-    <row r="3974" spans="3:6">
+    <row r="3974" spans="2:6">
       <c r="C3974" s="3">
         <v>300129</v>
       </c>
@@ -72657,7 +72669,7 @@
         <v>7869</v>
       </c>
     </row>
-    <row r="3975" spans="3:6">
+    <row r="3975" spans="2:6">
       <c r="C3975" s="3">
         <v>300130</v>
       </c>
@@ -72668,7 +72680,7 @@
         <v>7871</v>
       </c>
     </row>
-    <row r="3976" spans="3:6">
+    <row r="3976" spans="2:6">
       <c r="C3976" s="3">
         <v>300131</v>
       </c>
@@ -72679,7 +72691,7 @@
         <v>7873</v>
       </c>
     </row>
-    <row r="3977" spans="3:6">
+    <row r="3977" spans="2:6">
       <c r="C3977" s="3">
         <v>300132</v>
       </c>
@@ -72690,7 +72702,7 @@
         <v>7875</v>
       </c>
     </row>
-    <row r="3978" spans="3:6">
+    <row r="3978" spans="2:6">
       <c r="C3978" s="3">
         <v>300133</v>
       </c>
@@ -72701,7 +72713,7 @@
         <v>7877</v>
       </c>
     </row>
-    <row r="3979" spans="3:6">
+    <row r="3979" spans="2:6">
       <c r="C3979" s="3">
         <v>300134</v>
       </c>
@@ -72712,7 +72724,7 @@
         <v>7879</v>
       </c>
     </row>
-    <row r="3980" spans="3:6">
+    <row r="3980" spans="2:6">
       <c r="C3980" s="3">
         <v>300135</v>
       </c>
@@ -72723,10 +72735,12 @@
         <v>7881</v>
       </c>
     </row>
-    <row r="3981" spans="3:6">
+    <row r="3981" spans="2:6">
+      <c r="B3981" s="3"/>
       <c r="C3981" s="3">
         <v>300136</v>
       </c>
+      <c r="D3981" s="1"/>
       <c r="E3981" s="1" t="s">
         <v>7882</v>
       </c>
@@ -72734,10 +72748,12 @@
         <v>7883</v>
       </c>
     </row>
-    <row r="3982" spans="3:6">
+    <row r="3982" spans="2:6">
+      <c r="B3982" s="3"/>
       <c r="C3982" s="3">
         <v>300137</v>
       </c>
+      <c r="D3982" s="1"/>
       <c r="E3982" s="1" t="s">
         <v>7884</v>
       </c>
@@ -72745,10 +72761,12 @@
         <v>7885</v>
       </c>
     </row>
-    <row r="3983" spans="3:6">
+    <row r="3983" spans="2:6">
+      <c r="B3983" s="3"/>
       <c r="C3983" s="3">
         <v>300138</v>
       </c>
+      <c r="D3983" s="1"/>
       <c r="E3983" s="1" t="s">
         <v>7886</v>
       </c>
@@ -72756,21 +72774,25 @@
         <v>7887</v>
       </c>
     </row>
-    <row r="3984" ht="17.25" spans="3:6">
+    <row r="3984" spans="2:6">
+      <c r="B3984" s="3"/>
       <c r="C3984" s="3">
         <v>300139</v>
       </c>
+      <c r="D3984" s="1"/>
       <c r="E3984" s="1" t="s">
         <v>7888</v>
       </c>
-      <c r="F3984" s="9" t="s">
+      <c r="F3984" s="1" t="s">
         <v>7889</v>
       </c>
     </row>
-    <row r="3985" spans="3:6">
+    <row r="3985" spans="2:6">
+      <c r="B3985" s="3"/>
       <c r="C3985" s="3">
         <v>300140</v>
       </c>
+      <c r="D3985" s="1"/>
       <c r="E3985" s="1" t="s">
         <v>7890</v>
       </c>
@@ -72778,10 +72800,12 @@
         <v>7891</v>
       </c>
     </row>
-    <row r="3986" spans="3:6">
+    <row r="3986" spans="2:6">
+      <c r="B3986" s="3"/>
       <c r="C3986" s="3">
         <v>300141</v>
       </c>
+      <c r="D3986" s="1"/>
       <c r="E3986" s="1" t="s">
         <v>7892</v>
       </c>
@@ -72789,10 +72813,12 @@
         <v>7893</v>
       </c>
     </row>
-    <row r="3987" spans="3:6">
+    <row r="3987" spans="2:6">
+      <c r="B3987" s="3"/>
       <c r="C3987" s="3">
         <v>300142</v>
       </c>
+      <c r="D3987" s="1"/>
       <c r="E3987" s="1" t="s">
         <v>7894</v>
       </c>
@@ -72800,10 +72826,12 @@
         <v>7895</v>
       </c>
     </row>
-    <row r="3988" spans="3:6">
+    <row r="3988" spans="2:6">
+      <c r="B3988" s="3"/>
       <c r="C3988" s="3">
         <v>300143</v>
       </c>
+      <c r="D3988" s="1"/>
       <c r="E3988" s="1" t="s">
         <v>7896</v>
       </c>
@@ -72811,10 +72839,12 @@
         <v>7897</v>
       </c>
     </row>
-    <row r="3989" spans="3:6">
+    <row r="3989" spans="2:6">
+      <c r="B3989" s="3"/>
       <c r="C3989" s="3">
         <v>300144</v>
       </c>
+      <c r="D3989" s="1"/>
       <c r="E3989" s="1" t="s">
         <v>7898</v>
       </c>
@@ -72822,29 +72852,73 @@
         <v>7899</v>
       </c>
     </row>
-    <row r="3990" spans="3:6">
+    <row r="3990" spans="2:6">
+      <c r="B3990" s="3"/>
       <c r="C3990" s="3">
         <v>300145</v>
       </c>
-      <c r="D3990"/>
-      <c r="E3990" s="10" t="s">
+      <c r="D3990" s="1"/>
+      <c r="E3990" s="1" t="s">
         <v>7900</v>
       </c>
-      <c r="F3990" s="11" t="s">
+      <c r="F3990" s="1" t="s">
         <v>7901</v>
       </c>
     </row>
-    <row r="3991" spans="3:6">
-      <c r="C3991"/>
-      <c r="D3991"/>
-    </row>
-    <row r="3992" spans="3:6">
-      <c r="C3992"/>
-      <c r="D3992"/>
-    </row>
-    <row r="3993" spans="3:6">
-      <c r="C3993"/>
-      <c r="D3993"/>
+    <row r="3991" spans="2:6">
+      <c r="B3991" s="3"/>
+      <c r="C3991" s="3">
+        <v>300146</v>
+      </c>
+      <c r="D3991" s="1"/>
+      <c r="E3991" s="1" t="s">
+        <v>7902</v>
+      </c>
+      <c r="F3991" s="1" t="s">
+        <v>7903</v>
+      </c>
+    </row>
+    <row r="3992" ht="17.25" spans="2:6">
+      <c r="B3992" s="3"/>
+      <c r="C3992" s="3">
+        <v>300147</v>
+      </c>
+      <c r="D3992" s="1"/>
+      <c r="E3992" s="1" t="s">
+        <v>7904</v>
+      </c>
+      <c r="F3992" s="9" t="s">
+        <v>7905</v>
+      </c>
+    </row>
+    <row r="3993" ht="17.25" spans="2:6">
+      <c r="B3993" s="3"/>
+      <c r="C3993" s="3">
+        <v>300148</v>
+      </c>
+      <c r="D3993" s="1"/>
+      <c r="E3993" s="1" t="s">
+        <v>7906</v>
+      </c>
+      <c r="F3993" s="9" t="s">
+        <v>7907</v>
+      </c>
+    </row>
+    <row r="3994" spans="2:6">
+      <c r="B3994" s="3"/>
+      <c r="C3994" s="3"/>
+    </row>
+    <row r="3995" spans="2:6">
+      <c r="B3995" s="3"/>
+      <c r="C3995" s="3"/>
+    </row>
+    <row r="3996" spans="2:6">
+      <c r="B3996" s="3"/>
+      <c r="C3996" s="3"/>
+    </row>
+    <row r="3997" spans="2:6">
+      <c r="B3997" s="3"/>
+      <c r="C3997" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -23744,13 +23744,13 @@
     <t>1.在野外击败怪物时会掉落对应的活动道具。</t>
   </si>
   <si>
-    <t>Defeating wild monsters drops event items.</t>
+    <t>1.Defeating wild monsters drops event items.</t>
   </si>
   <si>
     <t>2.喂食道具会获得不同的奖励哦！</t>
   </si>
   <si>
-    <t>Feed items for different rewards!</t>
+    <t>2.Feed items for different rewards!</t>
   </si>
 </sst>
 </file>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8104" uniqueCount="7908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8112" uniqueCount="7915">
   <si>
     <t>c</t>
   </si>
@@ -23751,6 +23751,27 @@
   </si>
   <si>
     <t>2.Feed items for different rewards!</t>
+  </si>
+  <si>
+    <t>Satiety</t>
+  </si>
+  <si>
+    <t>活动任务列表</t>
+  </si>
+  <si>
+    <t>Activity Task List</t>
+  </si>
+  <si>
+    <t>活动时间：</t>
+  </si>
+  <si>
+    <t>Active Time:</t>
+  </si>
+  <si>
+    <t>提示:当奖励已经领取超过6次可进行免费刷新。</t>
+  </si>
+  <si>
+    <t>Hint: You can refresh for free after claiming rewards 6 times.</t>
   </si>
 </sst>
 </file>
@@ -23763,7 +23784,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -23794,12 +23815,6 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -24271,13 +24286,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -24286,122 +24304,119 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -24417,7 +24432,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -72878,7 +72892,7 @@
         <v>7903</v>
       </c>
     </row>
-    <row r="3992" ht="17.25" spans="2:6">
+    <row r="3992" spans="2:6">
       <c r="B3992" s="3"/>
       <c r="C3992" s="3">
         <v>300147</v>
@@ -72887,11 +72901,11 @@
       <c r="E3992" s="1" t="s">
         <v>7904</v>
       </c>
-      <c r="F3992" s="9" t="s">
+      <c r="F3992" s="1" t="s">
         <v>7905</v>
       </c>
     </row>
-    <row r="3993" ht="17.25" spans="2:6">
+    <row r="3993" spans="2:6">
       <c r="B3993" s="3"/>
       <c r="C3993" s="3">
         <v>300148</v>
@@ -72900,25 +72914,61 @@
       <c r="E3993" s="1" t="s">
         <v>7906</v>
       </c>
-      <c r="F3993" s="9" t="s">
+      <c r="F3993" s="1" t="s">
         <v>7907</v>
       </c>
     </row>
     <row r="3994" spans="2:6">
       <c r="B3994" s="3"/>
-      <c r="C3994" s="3"/>
+      <c r="C3994" s="3">
+        <v>300149</v>
+      </c>
+      <c r="D3994" s="1"/>
+      <c r="E3994" s="1" t="s">
+        <v>2906</v>
+      </c>
+      <c r="F3994" s="1" t="s">
+        <v>7908</v>
+      </c>
     </row>
     <row r="3995" spans="2:6">
       <c r="B3995" s="3"/>
-      <c r="C3995" s="3"/>
+      <c r="C3995" s="3">
+        <v>300150</v>
+      </c>
+      <c r="D3995" s="1"/>
+      <c r="E3995" s="1" t="s">
+        <v>7909</v>
+      </c>
+      <c r="F3995" s="1" t="s">
+        <v>7910</v>
+      </c>
     </row>
     <row r="3996" spans="2:6">
       <c r="B3996" s="3"/>
-      <c r="C3996" s="3"/>
+      <c r="C3996" s="3">
+        <v>300151</v>
+      </c>
+      <c r="D3996" s="1"/>
+      <c r="E3996" s="1" t="s">
+        <v>7911</v>
+      </c>
+      <c r="F3996" s="1" t="s">
+        <v>7912</v>
+      </c>
     </row>
     <row r="3997" spans="2:6">
       <c r="B3997" s="3"/>
-      <c r="C3997" s="3"/>
+      <c r="C3997" s="3">
+        <v>300152</v>
+      </c>
+      <c r="D3997" s="1"/>
+      <c r="E3997" s="1" t="s">
+        <v>7913</v>
+      </c>
+      <c r="F3997" s="1" t="s">
+        <v>7914</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8112" uniqueCount="7915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8122" uniqueCount="7925">
   <si>
     <t>c</t>
   </si>
@@ -23772,6 +23772,36 @@
   </si>
   <si>
     <t>Hint: You can refresh for free after claiming rewards 6 times.</t>
+  </si>
+  <si>
+    <t>提示:消耗100钻石得1积分。</t>
+  </si>
+  <si>
+    <t>Hint: Spend 100 Diamonds to get 1 Point.</t>
+  </si>
+  <si>
+    <t>每次活动结束时会扣除100积分，兑换任意积分可免扣除。</t>
+  </si>
+  <si>
+    <t>Avoid a 100-point end-of-event charge by redeeming points.</t>
+  </si>
+  <si>
+    <t>积分奖励列表</t>
+  </si>
+  <si>
+    <t>Points Reward List</t>
+  </si>
+  <si>
+    <t>当前积分：</t>
+  </si>
+  <si>
+    <t>Points:</t>
+  </si>
+  <si>
+    <t>{0}积分</t>
+  </si>
+  <si>
+    <t>{0}Points</t>
   </si>
 </sst>
 </file>
@@ -23784,7 +23814,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -23815,6 +23845,12 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -24286,16 +24322,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -24304,119 +24337,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -24430,6 +24466,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="31" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -24780,7 +24819,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F3997"/>
+  <dimension ref="B2:F4002"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -72970,6 +73009,61 @@
         <v>7914</v>
       </c>
     </row>
+    <row r="3998" spans="2:6">
+      <c r="C3998" s="3">
+        <v>300153</v>
+      </c>
+      <c r="E3998" s="1" t="s">
+        <v>7915</v>
+      </c>
+      <c r="F3998" s="1" t="s">
+        <v>7916</v>
+      </c>
+    </row>
+    <row r="3999" ht="17.25" spans="2:6">
+      <c r="C3999" s="3">
+        <v>300154</v>
+      </c>
+      <c r="E3999" s="1" t="s">
+        <v>7917</v>
+      </c>
+      <c r="F3999" s="9" t="s">
+        <v>7918</v>
+      </c>
+    </row>
+    <row r="4000" spans="2:6">
+      <c r="C4000" s="3">
+        <v>300155</v>
+      </c>
+      <c r="E4000" s="1" t="s">
+        <v>7919</v>
+      </c>
+      <c r="F4000" s="1" t="s">
+        <v>7920</v>
+      </c>
+    </row>
+    <row r="4001" spans="3:6">
+      <c r="C4001" s="3">
+        <v>300156</v>
+      </c>
+      <c r="E4001" s="1" t="s">
+        <v>7921</v>
+      </c>
+      <c r="F4001" s="1" t="s">
+        <v>7922</v>
+      </c>
+    </row>
+    <row r="4002" spans="3:6">
+      <c r="C4002" s="3">
+        <v>300157</v>
+      </c>
+      <c r="E4002" s="1" t="s">
+        <v>7923</v>
+      </c>
+      <c r="F4002" s="1" t="s">
+        <v>7924</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8122" uniqueCount="7925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8128" uniqueCount="7931">
   <si>
     <t>c</t>
   </si>
@@ -23802,6 +23802,24 @@
   </si>
   <si>
     <t>{0}Points</t>
+  </si>
+  <si>
+    <t>消耗30积分</t>
+  </si>
+  <si>
+    <t>Cost 30 Points</t>
+  </si>
+  <si>
+    <t>今日抽奖次数：</t>
+  </si>
+  <si>
+    <t>Today's Draw Chances:</t>
+  </si>
+  <si>
+    <t>抽奖列表</t>
+  </si>
+  <si>
+    <t>Prize Pool</t>
   </si>
 </sst>
 </file>
@@ -23814,7 +23832,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -23845,12 +23863,6 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -24322,13 +24334,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -24337,122 +24352,119 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -24466,9 +24478,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="31" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -24819,7 +24828,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4002"/>
+  <dimension ref="B2:F4005"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -73020,14 +73029,14 @@
         <v>7916</v>
       </c>
     </row>
-    <row r="3999" ht="17.25" spans="2:6">
+    <row r="3999" spans="2:6">
       <c r="C3999" s="3">
         <v>300154</v>
       </c>
       <c r="E3999" s="1" t="s">
         <v>7917</v>
       </c>
-      <c r="F3999" s="9" t="s">
+      <c r="F3999" s="1" t="s">
         <v>7918</v>
       </c>
     </row>
@@ -73062,6 +73071,39 @@
       </c>
       <c r="F4002" s="1" t="s">
         <v>7924</v>
+      </c>
+    </row>
+    <row r="4003" spans="3:6">
+      <c r="C4003" s="3">
+        <v>300158</v>
+      </c>
+      <c r="E4003" s="1" t="s">
+        <v>7925</v>
+      </c>
+      <c r="F4003" s="1" t="s">
+        <v>7926</v>
+      </c>
+    </row>
+    <row r="4004" spans="3:6">
+      <c r="C4004" s="3">
+        <v>300159</v>
+      </c>
+      <c r="E4004" s="1" t="s">
+        <v>7927</v>
+      </c>
+      <c r="F4004" s="1" t="s">
+        <v>7928</v>
+      </c>
+    </row>
+    <row r="4005" spans="3:6">
+      <c r="C4005" s="3">
+        <v>300160</v>
+      </c>
+      <c r="E4005" s="1" t="s">
+        <v>7929</v>
+      </c>
+      <c r="F4005" s="1" t="s">
+        <v>7930</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -23813,7 +23813,7 @@
     <t>今日抽奖次数：</t>
   </si>
   <si>
-    <t>Today's Draw Chances:</t>
+    <t>Today's Draw Chances：</t>
   </si>
   <si>
     <t>抽奖列表</t>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8128" uniqueCount="7931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8132" uniqueCount="7935">
   <si>
     <t>c</t>
   </si>
@@ -23820,6 +23820,18 @@
   </si>
   <si>
     <t>Prize Pool</t>
+  </si>
+  <si>
+    <t>剩余积分：</t>
+  </si>
+  <si>
+    <t>Remaining Points:</t>
+  </si>
+  <si>
+    <t>累计消耗：</t>
+  </si>
+  <si>
+    <t>Total Spent:</t>
   </si>
 </sst>
 </file>
@@ -24828,7 +24840,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4005"/>
+  <dimension ref="B2:F4007"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -73106,6 +73118,28 @@
         <v>7930</v>
       </c>
     </row>
+    <row r="4006" spans="3:6">
+      <c r="C4006" s="3">
+        <v>300161</v>
+      </c>
+      <c r="E4006" s="1" t="s">
+        <v>7931</v>
+      </c>
+      <c r="F4006" s="1" t="s">
+        <v>7932</v>
+      </c>
+    </row>
+    <row r="4007" spans="3:6">
+      <c r="C4007" s="3">
+        <v>300162</v>
+      </c>
+      <c r="E4007" s="1" t="s">
+        <v>7933</v>
+      </c>
+      <c r="F4007" s="1" t="s">
+        <v>7934</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -23831,7 +23831,7 @@
     <t>累计消耗：</t>
   </si>
   <si>
-    <t>Total Spent:</t>
+    <t>Total Spent：</t>
   </si>
 </sst>
 </file>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8132" uniqueCount="7935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8146" uniqueCount="7945">
   <si>
     <t>c</t>
   </si>
@@ -23832,6 +23832,36 @@
   </si>
   <si>
     <t>Total Spent：</t>
+  </si>
+  <si>
+    <t>订单</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>成长树</t>
+  </si>
+  <si>
+    <t>Growth Tree</t>
+  </si>
+  <si>
+    <t>积分2</t>
+  </si>
+  <si>
+    <t>Point2</t>
+  </si>
+  <si>
+    <t>1.Wild monsters may drop various letters.</t>
+  </si>
+  <si>
+    <t>2.Choose to redeem single or all.</t>
+  </si>
+  <si>
+    <t>3.Exchange a single letter for 100,000 gold.</t>
+  </si>
+  <si>
+    <t>4. Exchange a full set of letters for a gold bar.</t>
   </si>
 </sst>
 </file>
@@ -24476,7 +24506,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -24490,6 +24520,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="31" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -24840,7 +24873,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4007"/>
+  <dimension ref="B2:F4014"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -73140,6 +73173,83 @@
         <v>7934</v>
       </c>
     </row>
+    <row r="4008" spans="3:6">
+      <c r="C4008" s="3">
+        <v>300163</v>
+      </c>
+      <c r="E4008" s="1" t="s">
+        <v>7935</v>
+      </c>
+      <c r="F4008" s="1" t="s">
+        <v>7936</v>
+      </c>
+    </row>
+    <row r="4009" spans="3:6">
+      <c r="C4009" s="3">
+        <v>300164</v>
+      </c>
+      <c r="E4009" s="1" t="s">
+        <v>7937</v>
+      </c>
+      <c r="F4009" s="1" t="s">
+        <v>7938</v>
+      </c>
+    </row>
+    <row r="4010" spans="3:6">
+      <c r="C4010" s="3">
+        <v>300165</v>
+      </c>
+      <c r="E4010" s="1" t="s">
+        <v>7939</v>
+      </c>
+      <c r="F4010" s="1" t="s">
+        <v>7940</v>
+      </c>
+    </row>
+    <row r="4011" spans="3:6">
+      <c r="C4011" s="3">
+        <v>300166</v>
+      </c>
+      <c r="E4011" s="9" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F4011" s="1" t="s">
+        <v>7941</v>
+      </c>
+    </row>
+    <row r="4012" spans="3:6">
+      <c r="C4012" s="3">
+        <v>300167</v>
+      </c>
+      <c r="E4012" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F4012" s="1" t="s">
+        <v>7942</v>
+      </c>
+    </row>
+    <row r="4013" spans="3:6">
+      <c r="C4013" s="3">
+        <v>300168</v>
+      </c>
+      <c r="E4013" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F4013" s="1" t="s">
+        <v>7943</v>
+      </c>
+    </row>
+    <row r="4014" spans="3:6">
+      <c r="C4014" s="3">
+        <v>300169</v>
+      </c>
+      <c r="E4014" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F4014" s="1" t="s">
+        <v>7944</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8146" uniqueCount="7945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8156" uniqueCount="7954">
   <si>
     <t>c</t>
   </si>
@@ -23862,6 +23862,33 @@
   </si>
   <si>
     <t>4. Exchange a full set of letters for a gold bar.</t>
+  </si>
+  <si>
+    <t>奖励内容</t>
+  </si>
+  <si>
+    <t>魔能礼包</t>
+  </si>
+  <si>
+    <t>Magic Bundle</t>
+  </si>
+  <si>
+    <t>生肖礼包</t>
+  </si>
+  <si>
+    <t>Zodiac Bundle</t>
+  </si>
+  <si>
+    <t>宝石礼包</t>
+  </si>
+  <si>
+    <t>Gem Bundle</t>
+  </si>
+  <si>
+    <t>宠物礼包</t>
+  </si>
+  <si>
+    <t>Pet Bundle</t>
   </si>
 </sst>
 </file>
@@ -24506,7 +24533,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -24520,9 +24547,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="31" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -24873,7 +24897,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4014"/>
+  <dimension ref="B2:F4019"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -73210,7 +73234,7 @@
       <c r="C4011" s="3">
         <v>300166</v>
       </c>
-      <c r="E4011" s="9" t="s">
+      <c r="E4011" s="1" t="s">
         <v>1068</v>
       </c>
       <c r="F4011" s="1" t="s">
@@ -73248,6 +73272,61 @@
       </c>
       <c r="F4014" s="1" t="s">
         <v>7944</v>
+      </c>
+    </row>
+    <row r="4015" spans="3:6">
+      <c r="C4015" s="3">
+        <v>300170</v>
+      </c>
+      <c r="E4015" s="1" t="s">
+        <v>7945</v>
+      </c>
+      <c r="F4015" s="1" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="4016" spans="3:6">
+      <c r="C4016" s="3">
+        <v>300171</v>
+      </c>
+      <c r="E4016" s="1" t="s">
+        <v>7946</v>
+      </c>
+      <c r="F4016" s="1" t="s">
+        <v>7947</v>
+      </c>
+    </row>
+    <row r="4017" spans="3:6">
+      <c r="C4017" s="3">
+        <v>300172</v>
+      </c>
+      <c r="E4017" s="1" t="s">
+        <v>7948</v>
+      </c>
+      <c r="F4017" s="1" t="s">
+        <v>7949</v>
+      </c>
+    </row>
+    <row r="4018" spans="3:6">
+      <c r="C4018" s="3">
+        <v>300173</v>
+      </c>
+      <c r="E4018" s="1" t="s">
+        <v>7950</v>
+      </c>
+      <c r="F4018" s="1" t="s">
+        <v>7951</v>
+      </c>
+    </row>
+    <row r="4019" spans="3:6">
+      <c r="C4019" s="3">
+        <v>300174</v>
+      </c>
+      <c r="E4019" s="1" t="s">
+        <v>7952</v>
+      </c>
+      <c r="F4019" s="1" t="s">
+        <v>7953</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8156" uniqueCount="7954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8172" uniqueCount="7968">
   <si>
     <t>c</t>
   </si>
@@ -23889,6 +23889,48 @@
   </si>
   <si>
     <t>Pet Bundle</t>
+  </si>
+  <si>
+    <t>积分不足</t>
+  </si>
+  <si>
+    <t>Insufficient Points</t>
+  </si>
+  <si>
+    <t>刷新订单</t>
+  </si>
+  <si>
+    <t>Refresh Orders</t>
+  </si>
+  <si>
+    <t>简介</t>
+  </si>
+  <si>
+    <t>亲爱的勇士，这次我们需要一些珍贵的材料制造一个东西，你可以帮我们找到这些材料吗？</t>
+  </si>
+  <si>
+    <t>Brave warrior, we need rare materials to craft something. Can you help us find them?</t>
+  </si>
+  <si>
+    <t>配方</t>
+  </si>
+  <si>
+    <t>订单奖励</t>
+  </si>
+  <si>
+    <t>Order Rewards</t>
+  </si>
+  <si>
+    <t>提交订单</t>
+  </si>
+  <si>
+    <t>Submit Order</t>
+  </si>
+  <si>
+    <t>订单剩余时间:{0}</t>
+  </si>
+  <si>
+    <t>Time Left: {0}</t>
   </si>
 </sst>
 </file>
@@ -24897,7 +24939,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4019"/>
+  <dimension ref="B2:F4027"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -73329,6 +73371,94 @@
         <v>7953</v>
       </c>
     </row>
+    <row r="4020" spans="3:6">
+      <c r="C4020" s="3">
+        <v>300175</v>
+      </c>
+      <c r="E4020" s="1" t="s">
+        <v>7954</v>
+      </c>
+      <c r="F4020" s="1" t="s">
+        <v>7955</v>
+      </c>
+    </row>
+    <row r="4021" spans="3:6">
+      <c r="C4021" s="3">
+        <v>300176</v>
+      </c>
+      <c r="E4021" s="1" t="s">
+        <v>7956</v>
+      </c>
+      <c r="F4021" s="1" t="s">
+        <v>7957</v>
+      </c>
+    </row>
+    <row r="4022" spans="3:6">
+      <c r="C4022" s="3">
+        <v>300177</v>
+      </c>
+      <c r="E4022" s="1" t="s">
+        <v>7958</v>
+      </c>
+      <c r="F4022" s="1" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="4023" spans="3:6">
+      <c r="C4023" s="3">
+        <v>300178</v>
+      </c>
+      <c r="E4023" s="1" t="s">
+        <v>7959</v>
+      </c>
+      <c r="F4023" s="1" t="s">
+        <v>7960</v>
+      </c>
+    </row>
+    <row r="4024" spans="3:6">
+      <c r="C4024" s="3">
+        <v>300179</v>
+      </c>
+      <c r="E4024" s="1" t="s">
+        <v>7961</v>
+      </c>
+      <c r="F4024" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="4025" spans="3:6">
+      <c r="C4025" s="3">
+        <v>300180</v>
+      </c>
+      <c r="E4025" s="1" t="s">
+        <v>7962</v>
+      </c>
+      <c r="F4025" s="1" t="s">
+        <v>7963</v>
+      </c>
+    </row>
+    <row r="4026" spans="3:6">
+      <c r="C4026" s="3">
+        <v>300181</v>
+      </c>
+      <c r="E4026" s="1" t="s">
+        <v>7964</v>
+      </c>
+      <c r="F4026" s="1" t="s">
+        <v>7965</v>
+      </c>
+    </row>
+    <row r="4027" spans="3:6">
+      <c r="C4027" s="3">
+        <v>300182</v>
+      </c>
+      <c r="E4027" s="1" t="s">
+        <v>7966</v>
+      </c>
+      <c r="F4027" s="1" t="s">
+        <v>7967</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8172" uniqueCount="7968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8196" uniqueCount="7989">
   <si>
     <t>c</t>
   </si>
@@ -23931,6 +23931,69 @@
   </si>
   <si>
     <t>Time Left: {0}</t>
+  </si>
+  <si>
+    <t>幼苗期</t>
+  </si>
+  <si>
+    <t>Seedling</t>
+  </si>
+  <si>
+    <t>盛开期</t>
+  </si>
+  <si>
+    <t>Bloom</t>
+  </si>
+  <si>
+    <t>成长值</t>
+  </si>
+  <si>
+    <t>亲爱的勇士，这次我们需要帮助这棵植物快快成长，你在世界各地可以拾取到水或者肥料道具可以在这里使用帮助植物尽快成长哦！</t>
+  </si>
+  <si>
+    <t>Help this plant grow! Collect water and fertilizer from your travels and use them here to speed up its growth.</t>
+  </si>
+  <si>
+    <t>奖励说明</t>
+  </si>
+  <si>
+    <t>Reward Description</t>
+  </si>
+  <si>
+    <t>预计增加</t>
+  </si>
+  <si>
+    <t>Estimated Increase</t>
+  </si>
+  <si>
+    <t>预计增加{0}点成长值</t>
+  </si>
+  <si>
+    <t>Estimated Increase{0}Growth</t>
+  </si>
+  <si>
+    <t>照顾果树</t>
+  </si>
+  <si>
+    <t>Tend Orchard</t>
+  </si>
+  <si>
+    <t>提示：根据每次照顾获得成长值匹配不同区间的奖励</t>
+  </si>
+  <si>
+    <t>Tip: Care to earn growth points and claim tiered rewards.</t>
+  </si>
+  <si>
+    <t>提示：果树成长到不同阶段会发送奖励</t>
+  </si>
+  <si>
+    <t>Rewards granted as fruit trees grow through different stages.</t>
+  </si>
+  <si>
+    <t>栏位</t>
+  </si>
+  <si>
+    <t>Field</t>
   </si>
 </sst>
 </file>
@@ -24939,7 +25002,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4027"/>
+  <dimension ref="B2:F4039"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -73459,6 +73522,138 @@
         <v>7967</v>
       </c>
     </row>
+    <row r="4028" spans="3:6">
+      <c r="C4028" s="3">
+        <v>300183</v>
+      </c>
+      <c r="E4028" s="1" t="s">
+        <v>7968</v>
+      </c>
+      <c r="F4028" s="1" t="s">
+        <v>7969</v>
+      </c>
+    </row>
+    <row r="4029" spans="3:6">
+      <c r="C4029" s="3">
+        <v>300184</v>
+      </c>
+      <c r="E4029" s="1" t="s">
+        <v>4328</v>
+      </c>
+      <c r="F4029" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="4030" spans="3:6">
+      <c r="C4030" s="3">
+        <v>300185</v>
+      </c>
+      <c r="E4030" s="1" t="s">
+        <v>7970</v>
+      </c>
+      <c r="F4030" s="1" t="s">
+        <v>7971</v>
+      </c>
+    </row>
+    <row r="4031" spans="3:6">
+      <c r="C4031" s="3">
+        <v>300186</v>
+      </c>
+      <c r="E4031" s="1" t="s">
+        <v>7972</v>
+      </c>
+      <c r="F4031" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="4032" spans="3:6">
+      <c r="C4032" s="3">
+        <v>300187</v>
+      </c>
+      <c r="E4032" s="1" t="s">
+        <v>7973</v>
+      </c>
+      <c r="F4032" s="1" t="s">
+        <v>7974</v>
+      </c>
+    </row>
+    <row r="4033" spans="3:6">
+      <c r="C4033" s="3">
+        <v>300188</v>
+      </c>
+      <c r="E4033" s="1" t="s">
+        <v>7975</v>
+      </c>
+      <c r="F4033" s="1" t="s">
+        <v>7976</v>
+      </c>
+    </row>
+    <row r="4034" spans="3:6">
+      <c r="C4034" s="3">
+        <v>300189</v>
+      </c>
+      <c r="E4034" s="1" t="s">
+        <v>7977</v>
+      </c>
+      <c r="F4034" s="1" t="s">
+        <v>7978</v>
+      </c>
+    </row>
+    <row r="4035" spans="3:6">
+      <c r="C4035" s="3">
+        <v>300190</v>
+      </c>
+      <c r="E4035" s="1" t="s">
+        <v>7979</v>
+      </c>
+      <c r="F4035" s="1" t="s">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="4036" spans="3:6">
+      <c r="C4036" s="3">
+        <v>300191</v>
+      </c>
+      <c r="E4036" s="1" t="s">
+        <v>7981</v>
+      </c>
+      <c r="F4036" s="1" t="s">
+        <v>7982</v>
+      </c>
+    </row>
+    <row r="4037" spans="3:6">
+      <c r="C4037" s="3">
+        <v>300192</v>
+      </c>
+      <c r="E4037" s="1" t="s">
+        <v>7983</v>
+      </c>
+      <c r="F4037" s="1" t="s">
+        <v>7984</v>
+      </c>
+    </row>
+    <row r="4038" spans="3:6">
+      <c r="C4038" s="3">
+        <v>300193</v>
+      </c>
+      <c r="E4038" s="1" t="s">
+        <v>7985</v>
+      </c>
+      <c r="F4038" s="1" t="s">
+        <v>7986</v>
+      </c>
+    </row>
+    <row r="4039" spans="3:6">
+      <c r="C4039" s="3">
+        <v>300194</v>
+      </c>
+      <c r="E4039" s="1" t="s">
+        <v>7987</v>
+      </c>
+      <c r="F4039" s="1" t="s">
+        <v>7988</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8196" uniqueCount="7989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8204" uniqueCount="7997">
   <si>
     <t>c</t>
   </si>
@@ -23994,6 +23994,30 @@
   </si>
   <si>
     <t>Field</t>
+  </si>
+  <si>
+    <t>是否花费</t>
+  </si>
+  <si>
+    <t>Does it cost</t>
+  </si>
+  <si>
+    <t>刷新道具?</t>
+  </si>
+  <si>
+    <t>Refresh Item?</t>
+  </si>
+  <si>
+    <t>刷新道具</t>
+  </si>
+  <si>
+    <t>Refresh Item</t>
+  </si>
+  <si>
+    <t>积分不足!</t>
+  </si>
+  <si>
+    <t>Insufficient Points!</t>
   </si>
 </sst>
 </file>
@@ -25002,7 +25026,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4039"/>
+  <dimension ref="B2:F4043"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -73654,6 +73678,50 @@
         <v>7988</v>
       </c>
     </row>
+    <row r="4040" spans="3:6">
+      <c r="C4040" s="3">
+        <v>300195</v>
+      </c>
+      <c r="E4040" s="1" t="s">
+        <v>7989</v>
+      </c>
+      <c r="F4040" s="1" t="s">
+        <v>7990</v>
+      </c>
+    </row>
+    <row r="4041" spans="3:6">
+      <c r="C4041" s="3">
+        <v>300196</v>
+      </c>
+      <c r="E4041" s="1" t="s">
+        <v>7991</v>
+      </c>
+      <c r="F4041" s="1" t="s">
+        <v>7992</v>
+      </c>
+    </row>
+    <row r="4042" spans="3:6">
+      <c r="C4042" s="3">
+        <v>300197</v>
+      </c>
+      <c r="E4042" s="1" t="s">
+        <v>7993</v>
+      </c>
+      <c r="F4042" s="1" t="s">
+        <v>7994</v>
+      </c>
+    </row>
+    <row r="4043" spans="3:6">
+      <c r="C4043" s="3">
+        <v>300198</v>
+      </c>
+      <c r="E4043" s="1" t="s">
+        <v>7995</v>
+      </c>
+      <c r="F4043" s="1" t="s">
+        <v>7996</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8204" uniqueCount="7997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8206" uniqueCount="7999">
   <si>
     <t>c</t>
   </si>
@@ -24018,6 +24018,12 @@
   </si>
   <si>
     <t>Insufficient Points!</t>
+  </si>
+  <si>
+    <t>当前宠物身上有对应的宠物装备，请先将宠物装备卸下在执行此操作！</t>
+  </si>
+  <si>
+    <t>Please first unequip the pet equipment before performing this action!</t>
   </si>
 </sst>
 </file>
@@ -25026,7 +25032,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4043"/>
+  <dimension ref="B2:F4044"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -73000,7 +73006,6 @@
       <c r="C3981" s="3">
         <v>300136</v>
       </c>
-      <c r="D3981" s="1"/>
       <c r="E3981" s="1" t="s">
         <v>7882</v>
       </c>
@@ -73013,7 +73018,6 @@
       <c r="C3982" s="3">
         <v>300137</v>
       </c>
-      <c r="D3982" s="1"/>
       <c r="E3982" s="1" t="s">
         <v>7884</v>
       </c>
@@ -73026,7 +73030,6 @@
       <c r="C3983" s="3">
         <v>300138</v>
       </c>
-      <c r="D3983" s="1"/>
       <c r="E3983" s="1" t="s">
         <v>7886</v>
       </c>
@@ -73039,7 +73042,6 @@
       <c r="C3984" s="3">
         <v>300139</v>
       </c>
-      <c r="D3984" s="1"/>
       <c r="E3984" s="1" t="s">
         <v>7888</v>
       </c>
@@ -73052,7 +73054,6 @@
       <c r="C3985" s="3">
         <v>300140</v>
       </c>
-      <c r="D3985" s="1"/>
       <c r="E3985" s="1" t="s">
         <v>7890</v>
       </c>
@@ -73065,7 +73066,6 @@
       <c r="C3986" s="3">
         <v>300141</v>
       </c>
-      <c r="D3986" s="1"/>
       <c r="E3986" s="1" t="s">
         <v>7892</v>
       </c>
@@ -73078,7 +73078,6 @@
       <c r="C3987" s="3">
         <v>300142</v>
       </c>
-      <c r="D3987" s="1"/>
       <c r="E3987" s="1" t="s">
         <v>7894</v>
       </c>
@@ -73091,7 +73090,6 @@
       <c r="C3988" s="3">
         <v>300143</v>
       </c>
-      <c r="D3988" s="1"/>
       <c r="E3988" s="1" t="s">
         <v>7896</v>
       </c>
@@ -73104,7 +73102,6 @@
       <c r="C3989" s="3">
         <v>300144</v>
       </c>
-      <c r="D3989" s="1"/>
       <c r="E3989" s="1" t="s">
         <v>7898</v>
       </c>
@@ -73117,7 +73114,6 @@
       <c r="C3990" s="3">
         <v>300145</v>
       </c>
-      <c r="D3990" s="1"/>
       <c r="E3990" s="1" t="s">
         <v>7900</v>
       </c>
@@ -73130,7 +73126,6 @@
       <c r="C3991" s="3">
         <v>300146</v>
       </c>
-      <c r="D3991" s="1"/>
       <c r="E3991" s="1" t="s">
         <v>7902</v>
       </c>
@@ -73143,7 +73138,6 @@
       <c r="C3992" s="3">
         <v>300147</v>
       </c>
-      <c r="D3992" s="1"/>
       <c r="E3992" s="1" t="s">
         <v>7904</v>
       </c>
@@ -73156,7 +73150,6 @@
       <c r="C3993" s="3">
         <v>300148</v>
       </c>
-      <c r="D3993" s="1"/>
       <c r="E3993" s="1" t="s">
         <v>7906</v>
       </c>
@@ -73169,7 +73162,6 @@
       <c r="C3994" s="3">
         <v>300149</v>
       </c>
-      <c r="D3994" s="1"/>
       <c r="E3994" s="1" t="s">
         <v>2906</v>
       </c>
@@ -73182,7 +73174,6 @@
       <c r="C3995" s="3">
         <v>300150</v>
       </c>
-      <c r="D3995" s="1"/>
       <c r="E3995" s="1" t="s">
         <v>7909</v>
       </c>
@@ -73195,7 +73186,6 @@
       <c r="C3996" s="3">
         <v>300151</v>
       </c>
-      <c r="D3996" s="1"/>
       <c r="E3996" s="1" t="s">
         <v>7911</v>
       </c>
@@ -73208,7 +73198,6 @@
       <c r="C3997" s="3">
         <v>300152</v>
       </c>
-      <c r="D3997" s="1"/>
       <c r="E3997" s="1" t="s">
         <v>7913</v>
       </c>
@@ -73720,6 +73709,17 @@
       </c>
       <c r="F4043" s="1" t="s">
         <v>7996</v>
+      </c>
+    </row>
+    <row r="4044" spans="3:6">
+      <c r="C4044" s="3">
+        <v>300199</v>
+      </c>
+      <c r="E4044" s="1" t="s">
+        <v>7997</v>
+      </c>
+      <c r="F4044" s="1" t="s">
+        <v>7998</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="MulLanguageProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8206" uniqueCount="7999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8208" uniqueCount="8001">
   <si>
     <t>c</t>
   </si>
@@ -17934,6 +17934,12 @@
   </si>
   <si>
     <t>My Rank: {0}</t>
+  </si>
+  <si>
+    <t>家园提醒</t>
+  </si>
+  <si>
+    <t>Home Reminder</t>
   </si>
   <si>
     <t xml:space="preserve"> {0}层({1}/秒)</t>
@@ -25032,7 +25038,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4044"/>
+  <dimension ref="B2:F4045"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -61308,7 +61314,7 @@
         <v>5977</v>
       </c>
       <c r="F3004" s="6" t="s">
-        <v>4869</v>
+        <v>5978</v>
       </c>
     </row>
     <row r="3005" spans="3:6">
@@ -61317,10 +61323,10 @@
       </c>
       <c r="D3005" s="4"/>
       <c r="E3005" s="1" t="s">
-        <v>5978</v>
+        <v>5979</v>
       </c>
       <c r="F3005" s="6" t="s">
-        <v>5979</v>
+        <v>4869</v>
       </c>
     </row>
     <row r="3006" spans="3:6">
@@ -61476,7 +61482,7 @@
         <v>6004</v>
       </c>
       <c r="F3018" s="6" t="s">
-        <v>4939</v>
+        <v>6005</v>
       </c>
     </row>
     <row r="3019" spans="3:6">
@@ -61485,10 +61491,10 @@
       </c>
       <c r="D3019" s="4"/>
       <c r="E3019" s="1" t="s">
-        <v>6005</v>
+        <v>6006</v>
       </c>
       <c r="F3019" s="6" t="s">
-        <v>6006</v>
+        <v>4939</v>
       </c>
     </row>
     <row r="3020" spans="3:6">
@@ -61848,7 +61854,7 @@
         <v>6065</v>
       </c>
       <c r="F3049" s="6" t="s">
-        <v>5408</v>
+        <v>6066</v>
       </c>
     </row>
     <row r="3050" spans="3:6">
@@ -61857,10 +61863,10 @@
       </c>
       <c r="D3050" s="4"/>
       <c r="E3050" s="1" t="s">
-        <v>6066</v>
+        <v>6067</v>
       </c>
       <c r="F3050" s="6" t="s">
-        <v>6067</v>
+        <v>5408</v>
       </c>
     </row>
     <row r="3051" spans="3:6">
@@ -62067,7 +62073,7 @@
         <v>6101</v>
       </c>
     </row>
-    <row r="3068" ht="15" customHeight="1" spans="3:6">
+    <row r="3068" spans="3:6">
       <c r="C3068" s="3">
         <v>202951</v>
       </c>
@@ -62079,7 +62085,7 @@
         <v>6103</v>
       </c>
     </row>
-    <row r="3069" spans="3:6">
+    <row r="3069" ht="15" customHeight="1" spans="3:6">
       <c r="C3069" s="3">
         <v>202952</v>
       </c>
@@ -62424,7 +62430,7 @@
         <v>6160</v>
       </c>
       <c r="F3097" s="6" t="s">
-        <v>1514</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="3098" spans="3:6">
@@ -62433,10 +62439,10 @@
       </c>
       <c r="D3098" s="4"/>
       <c r="E3098" s="1" t="s">
-        <v>6161</v>
+        <v>6162</v>
       </c>
       <c r="F3098" s="6" t="s">
-        <v>6162</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="3099" spans="3:6">
@@ -62808,7 +62814,7 @@
         <v>6223</v>
       </c>
       <c r="F3129" s="6" t="s">
-        <v>5657</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="3130" spans="3:6">
@@ -62817,10 +62823,10 @@
       </c>
       <c r="D3130" s="4"/>
       <c r="E3130" s="1" t="s">
-        <v>6224</v>
+        <v>6225</v>
       </c>
       <c r="F3130" s="6" t="s">
-        <v>6225</v>
+        <v>5657</v>
       </c>
     </row>
     <row r="3131" spans="3:6">
@@ -63444,7 +63450,7 @@
         <v>6328</v>
       </c>
       <c r="F3182" s="6" t="s">
-        <v>6064</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="3183" spans="3:6">
@@ -63453,10 +63459,10 @@
       </c>
       <c r="D3183" s="4"/>
       <c r="E3183" s="1" t="s">
-        <v>6329</v>
+        <v>6330</v>
       </c>
       <c r="F3183" s="6" t="s">
-        <v>2881</v>
+        <v>6066</v>
       </c>
     </row>
     <row r="3184" spans="3:6">
@@ -63465,10 +63471,10 @@
       </c>
       <c r="D3184" s="4"/>
       <c r="E3184" s="1" t="s">
-        <v>6330</v>
+        <v>6331</v>
       </c>
       <c r="F3184" s="6" t="s">
-        <v>6331</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="3185" spans="3:6">
@@ -63480,7 +63486,7 @@
         <v>6332</v>
       </c>
       <c r="F3185" s="6" t="s">
-        <v>4845</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="3186" spans="3:6">
@@ -63489,10 +63495,10 @@
       </c>
       <c r="D3186" s="4"/>
       <c r="E3186" s="1" t="s">
-        <v>6333</v>
+        <v>6334</v>
       </c>
       <c r="F3186" s="6" t="s">
-        <v>6334</v>
+        <v>4845</v>
       </c>
     </row>
     <row r="3187" spans="3:6">
@@ -63636,7 +63642,7 @@
         <v>6357</v>
       </c>
       <c r="F3198" s="6" t="s">
-        <v>4875</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="3199" spans="3:6">
@@ -63645,10 +63651,10 @@
       </c>
       <c r="D3199" s="4"/>
       <c r="E3199" s="1" t="s">
-        <v>6358</v>
+        <v>6359</v>
       </c>
       <c r="F3199" s="6" t="s">
-        <v>6359</v>
+        <v>4875</v>
       </c>
     </row>
     <row r="3200" spans="3:6">
@@ -63768,7 +63774,7 @@
         <v>6378</v>
       </c>
       <c r="F3209" s="6" t="s">
-        <v>1904</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="3210" spans="3:6">
@@ -63777,10 +63783,10 @@
       </c>
       <c r="D3210" s="4"/>
       <c r="E3210" s="1" t="s">
-        <v>6379</v>
+        <v>6380</v>
       </c>
       <c r="F3210" s="6" t="s">
-        <v>6380</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="3211" spans="3:6">
@@ -63900,7 +63906,7 @@
         <v>6399</v>
       </c>
       <c r="F3220" s="6" t="s">
-        <v>6394</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="3221" spans="3:6">
@@ -63909,10 +63915,10 @@
       </c>
       <c r="D3221" s="4"/>
       <c r="E3221" s="1" t="s">
-        <v>6400</v>
+        <v>6401</v>
       </c>
       <c r="F3221" s="6" t="s">
-        <v>6401</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="3222" spans="3:6">
@@ -64608,7 +64614,7 @@
         <v>6516</v>
       </c>
       <c r="F3279" s="6" t="s">
-        <v>730</v>
+        <v>6517</v>
       </c>
     </row>
     <row r="3280" spans="3:6">
@@ -64617,10 +64623,10 @@
       </c>
       <c r="D3280" s="4"/>
       <c r="E3280" s="1" t="s">
-        <v>6517</v>
+        <v>6518</v>
       </c>
       <c r="F3280" s="6" t="s">
-        <v>6518</v>
+        <v>730</v>
       </c>
     </row>
     <row r="3281" spans="3:6">
@@ -65124,7 +65130,7 @@
         <v>6601</v>
       </c>
       <c r="F3322" s="6" t="s">
-        <v>6590</v>
+        <v>6602</v>
       </c>
     </row>
     <row r="3323" spans="3:6">
@@ -65133,10 +65139,10 @@
       </c>
       <c r="D3323" s="4"/>
       <c r="E3323" s="1" t="s">
-        <v>6602</v>
+        <v>6603</v>
       </c>
       <c r="F3323" s="6" t="s">
-        <v>6603</v>
+        <v>6592</v>
       </c>
     </row>
     <row r="3324" spans="3:6">
@@ -65208,7 +65214,7 @@
         <v>6614</v>
       </c>
       <c r="F3329" s="6" t="s">
-        <v>4867</v>
+        <v>6615</v>
       </c>
     </row>
     <row r="3330" spans="3:6">
@@ -65217,10 +65223,10 @@
       </c>
       <c r="D3330" s="4"/>
       <c r="E3330" s="1" t="s">
-        <v>6615</v>
+        <v>6616</v>
       </c>
       <c r="F3330" s="6" t="s">
-        <v>6616</v>
+        <v>4867</v>
       </c>
     </row>
     <row r="3331" spans="3:6">
@@ -65268,7 +65274,7 @@
         <v>6623</v>
       </c>
       <c r="F3334" s="6" t="s">
-        <v>5770</v>
+        <v>6624</v>
       </c>
     </row>
     <row r="3335" spans="3:6">
@@ -65277,10 +65283,10 @@
       </c>
       <c r="D3335" s="4"/>
       <c r="E3335" s="1" t="s">
-        <v>6624</v>
+        <v>6625</v>
       </c>
       <c r="F3335" s="6" t="s">
-        <v>6625</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="3336" spans="3:6">
@@ -65496,7 +65502,7 @@
         <v>6660</v>
       </c>
       <c r="F3353" s="6" t="s">
-        <v>6653</v>
+        <v>6661</v>
       </c>
     </row>
     <row r="3354" spans="3:6">
@@ -65505,10 +65511,10 @@
       </c>
       <c r="D3354" s="4"/>
       <c r="E3354" s="1" t="s">
-        <v>6661</v>
+        <v>6662</v>
       </c>
       <c r="F3354" s="6" t="s">
-        <v>6662</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="3355" spans="3:6">
@@ -65676,7 +65682,7 @@
         <v>6689</v>
       </c>
       <c r="F3368" s="6" t="s">
-        <v>2855</v>
+        <v>6690</v>
       </c>
     </row>
     <row r="3369" spans="3:6">
@@ -65685,10 +65691,10 @@
       </c>
       <c r="D3369" s="4"/>
       <c r="E3369" s="1" t="s">
-        <v>6690</v>
+        <v>6691</v>
       </c>
       <c r="F3369" s="6" t="s">
-        <v>6691</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="3370" spans="3:6">
@@ -65700,7 +65706,7 @@
         <v>6692</v>
       </c>
       <c r="F3370" s="6" t="s">
-        <v>2857</v>
+        <v>6693</v>
       </c>
     </row>
     <row r="3371" spans="3:6">
@@ -65709,10 +65715,10 @@
       </c>
       <c r="D3371" s="4"/>
       <c r="E3371" s="1" t="s">
-        <v>6693</v>
+        <v>6694</v>
       </c>
       <c r="F3371" s="6" t="s">
-        <v>6694</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="3372" spans="3:6">
@@ -66276,7 +66282,7 @@
         <v>6787</v>
       </c>
       <c r="F3418" s="6" t="s">
-        <v>5588</v>
+        <v>6788</v>
       </c>
     </row>
     <row r="3419" spans="3:6">
@@ -66285,10 +66291,10 @@
       </c>
       <c r="D3419" s="4"/>
       <c r="E3419" s="1" t="s">
-        <v>6788</v>
+        <v>6789</v>
       </c>
       <c r="F3419" s="6" t="s">
-        <v>6789</v>
+        <v>5588</v>
       </c>
     </row>
     <row r="3420" spans="3:6">
@@ -66588,7 +66594,7 @@
         <v>6838</v>
       </c>
       <c r="F3444" s="6" t="s">
-        <v>6819</v>
+        <v>6839</v>
       </c>
     </row>
     <row r="3445" spans="3:6">
@@ -66597,10 +66603,10 @@
       </c>
       <c r="D3445" s="4"/>
       <c r="E3445" s="1" t="s">
-        <v>6839</v>
+        <v>6840</v>
       </c>
       <c r="F3445" s="6" t="s">
-        <v>6840</v>
+        <v>6821</v>
       </c>
     </row>
     <row r="3446" spans="3:6">
@@ -66840,7 +66846,7 @@
         <v>6879</v>
       </c>
       <c r="F3465" s="6" t="s">
-        <v>2729</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="3466" spans="3:6">
@@ -66849,10 +66855,10 @@
       </c>
       <c r="D3466" s="4"/>
       <c r="E3466" s="1" t="s">
-        <v>6880</v>
+        <v>6881</v>
       </c>
       <c r="F3466" s="6" t="s">
-        <v>6881</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="3467" spans="3:6">
@@ -67044,7 +67050,7 @@
         <v>6912</v>
       </c>
       <c r="F3482" s="6" t="s">
-        <v>6060</v>
+        <v>6913</v>
       </c>
     </row>
     <row r="3483" spans="3:6">
@@ -67053,10 +67059,10 @@
       </c>
       <c r="D3483" s="4"/>
       <c r="E3483" s="1" t="s">
-        <v>6913</v>
+        <v>6914</v>
       </c>
       <c r="F3483" s="6" t="s">
-        <v>2762</v>
+        <v>6062</v>
       </c>
     </row>
     <row r="3484" spans="3:6">
@@ -67065,10 +67071,10 @@
       </c>
       <c r="D3484" s="4"/>
       <c r="E3484" s="1" t="s">
-        <v>6914</v>
+        <v>6915</v>
       </c>
       <c r="F3484" s="6" t="s">
-        <v>6915</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="3485" spans="3:6">
@@ -67104,7 +67110,7 @@
         <v>6920</v>
       </c>
       <c r="F3487" s="6" t="s">
-        <v>6103</v>
+        <v>6921</v>
       </c>
     </row>
     <row r="3488" spans="3:6">
@@ -67113,10 +67119,10 @@
       </c>
       <c r="D3488" s="4"/>
       <c r="E3488" s="1" t="s">
-        <v>6921</v>
+        <v>6922</v>
       </c>
       <c r="F3488" s="6" t="s">
-        <v>6922</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="3489" spans="3:6">
@@ -67824,7 +67830,7 @@
         <v>7039</v>
       </c>
       <c r="F3547" s="6" t="s">
-        <v>1260</v>
+        <v>7040</v>
       </c>
     </row>
     <row r="3548" spans="3:6">
@@ -67833,10 +67839,10 @@
       </c>
       <c r="D3548" s="4"/>
       <c r="E3548" s="1" t="s">
-        <v>7040</v>
+        <v>7041</v>
       </c>
       <c r="F3548" s="6" t="s">
-        <v>7041</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="3549" spans="3:6">
@@ -68484,7 +68490,7 @@
         <v>7148</v>
       </c>
       <c r="F3602" s="6" t="s">
-        <v>4865</v>
+        <v>7149</v>
       </c>
     </row>
     <row r="3603" spans="3:6">
@@ -68493,10 +68499,10 @@
       </c>
       <c r="D3603" s="4"/>
       <c r="E3603" s="1" t="s">
-        <v>7149</v>
+        <v>7150</v>
       </c>
       <c r="F3603" s="6" t="s">
-        <v>7150</v>
+        <v>4865</v>
       </c>
     </row>
     <row r="3604" spans="3:6">
@@ -68916,7 +68922,7 @@
         <v>7219</v>
       </c>
       <c r="F3638" s="6" t="s">
-        <v>6848</v>
+        <v>7220</v>
       </c>
     </row>
     <row r="3639" spans="3:6">
@@ -68925,10 +68931,10 @@
       </c>
       <c r="D3639" s="4"/>
       <c r="E3639" s="1" t="s">
-        <v>7220</v>
+        <v>7221</v>
       </c>
       <c r="F3639" s="6" t="s">
-        <v>7221</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="3640" spans="3:6">
@@ -69684,7 +69690,7 @@
         <v>7346</v>
       </c>
       <c r="F3702" s="6" t="s">
-        <v>4867</v>
+        <v>7347</v>
       </c>
     </row>
     <row r="3703" spans="3:6">
@@ -69693,10 +69699,10 @@
       </c>
       <c r="D3703" s="4"/>
       <c r="E3703" s="1" t="s">
-        <v>7347</v>
+        <v>7348</v>
       </c>
       <c r="F3703" s="6" t="s">
-        <v>7348</v>
+        <v>4867</v>
       </c>
     </row>
     <row r="3704" spans="3:6">
@@ -69708,7 +69714,7 @@
         <v>7349</v>
       </c>
       <c r="F3704" s="6" t="s">
-        <v>4865</v>
+        <v>7350</v>
       </c>
     </row>
     <row r="3705" spans="3:6">
@@ -69717,10 +69723,10 @@
       </c>
       <c r="D3705" s="4"/>
       <c r="E3705" s="1" t="s">
-        <v>7350</v>
+        <v>7351</v>
       </c>
       <c r="F3705" s="6" t="s">
-        <v>7351</v>
+        <v>4865</v>
       </c>
     </row>
     <row r="3706" spans="3:6">
@@ -69840,7 +69846,7 @@
         <v>7370</v>
       </c>
       <c r="F3715" s="6" t="s">
-        <v>7085</v>
+        <v>7371</v>
       </c>
     </row>
     <row r="3716" spans="3:6">
@@ -69849,10 +69855,10 @@
       </c>
       <c r="D3716" s="4"/>
       <c r="E3716" s="1" t="s">
-        <v>7371</v>
+        <v>7372</v>
       </c>
       <c r="F3716" s="6" t="s">
-        <v>7372</v>
+        <v>7087</v>
       </c>
     </row>
     <row r="3717" spans="3:6">
@@ -70524,7 +70530,7 @@
         <v>7483</v>
       </c>
       <c r="F3772" s="6" t="s">
-        <v>3818</v>
+        <v>7484</v>
       </c>
     </row>
     <row r="3773" spans="3:6">
@@ -70533,10 +70539,10 @@
       </c>
       <c r="D3773" s="4"/>
       <c r="E3773" s="1" t="s">
-        <v>7484</v>
+        <v>7485</v>
       </c>
       <c r="F3773" s="6" t="s">
-        <v>7485</v>
+        <v>3818</v>
       </c>
     </row>
     <row r="3774" spans="3:6">
@@ -70992,7 +70998,7 @@
         <v>7560</v>
       </c>
       <c r="F3811" s="6" t="s">
-        <v>4861</v>
+        <v>7561</v>
       </c>
     </row>
     <row r="3812" spans="3:6">
@@ -71001,10 +71007,10 @@
       </c>
       <c r="D3812" s="4"/>
       <c r="E3812" s="1" t="s">
-        <v>7561</v>
+        <v>7562</v>
       </c>
       <c r="F3812" s="6" t="s">
-        <v>7562</v>
+        <v>4861</v>
       </c>
     </row>
     <row r="3813" spans="3:6">
@@ -71088,19 +71094,19 @@
         <v>7575</v>
       </c>
       <c r="F3819" s="6" t="s">
-        <v>5874</v>
+        <v>7576</v>
       </c>
     </row>
     <row r="3820" spans="3:6">
       <c r="C3820" s="3">
         <v>203703</v>
       </c>
-      <c r="D3820"/>
+      <c r="D3820" s="4"/>
       <c r="E3820" s="1" t="s">
-        <v>7576</v>
+        <v>7577</v>
       </c>
       <c r="F3820" s="6" t="s">
-        <v>7577</v>
+        <v>5874</v>
       </c>
     </row>
     <row r="3821" spans="3:6">
@@ -71124,7 +71130,7 @@
         <v>7580</v>
       </c>
       <c r="F3822" s="6" t="s">
-        <v>390</v>
+        <v>7581</v>
       </c>
     </row>
     <row r="3823" spans="3:6">
@@ -71133,17 +71139,17 @@
       </c>
       <c r="D3823"/>
       <c r="E3823" s="1" t="s">
-        <v>7581</v>
+        <v>7582</v>
       </c>
       <c r="F3823" s="6" t="s">
-        <v>7582</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3824" spans="3:6">
       <c r="C3824" s="3">
         <v>203707</v>
       </c>
-      <c r="D3824" s="4"/>
+      <c r="D3824"/>
       <c r="E3824" s="1" t="s">
         <v>7583</v>
       </c>
@@ -71160,7 +71166,7 @@
         <v>7585</v>
       </c>
       <c r="F3825" s="6" t="s">
-        <v>1279</v>
+        <v>7586</v>
       </c>
     </row>
     <row r="3826" spans="3:6">
@@ -71169,10 +71175,10 @@
       </c>
       <c r="D3826" s="4"/>
       <c r="E3826" s="1" t="s">
-        <v>7586</v>
+        <v>7587</v>
       </c>
       <c r="F3826" s="6" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="3827" spans="3:6">
@@ -71181,10 +71187,10 @@
       </c>
       <c r="D3827" s="4"/>
       <c r="E3827" s="1" t="s">
-        <v>7587</v>
+        <v>7588</v>
       </c>
       <c r="F3827" s="6" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="3828" spans="3:6">
@@ -71193,10 +71199,10 @@
       </c>
       <c r="D3828" s="4"/>
       <c r="E3828" s="1" t="s">
-        <v>7588</v>
+        <v>7589</v>
       </c>
       <c r="F3828" s="6" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="3829" spans="3:6">
@@ -71205,10 +71211,10 @@
       </c>
       <c r="D3829" s="4"/>
       <c r="E3829" s="1" t="s">
-        <v>7589</v>
+        <v>7590</v>
       </c>
       <c r="F3829" s="6" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="3830" spans="3:6">
@@ -71217,10 +71223,10 @@
       </c>
       <c r="D3830" s="4"/>
       <c r="E3830" s="1" t="s">
-        <v>7590</v>
+        <v>7591</v>
       </c>
       <c r="F3830" s="6" t="s">
-        <v>7591</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="3831" spans="3:6">
@@ -71292,7 +71298,7 @@
         <v>7602</v>
       </c>
       <c r="F3836" s="6" t="s">
-        <v>1449</v>
+        <v>7603</v>
       </c>
     </row>
     <row r="3837" spans="3:6">
@@ -71301,10 +71307,10 @@
       </c>
       <c r="D3837" s="4"/>
       <c r="E3837" s="1" t="s">
-        <v>7603</v>
+        <v>7604</v>
       </c>
       <c r="F3837" s="6" t="s">
-        <v>7604</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="3838" spans="3:6">
@@ -71315,7 +71321,7 @@
       <c r="E3838" s="1" t="s">
         <v>7605</v>
       </c>
-      <c r="F3838" s="8" t="s">
+      <c r="F3838" s="6" t="s">
         <v>7606</v>
       </c>
     </row>
@@ -71405,11 +71411,9 @@
     </row>
     <row r="3846" spans="3:6">
       <c r="C3846" s="3">
-        <v>300001</v>
-      </c>
-      <c r="D3846" s="4" t="s">
-        <v>1961</v>
-      </c>
+        <v>203729</v>
+      </c>
+      <c r="D3846" s="4"/>
       <c r="E3846" s="1" t="s">
         <v>7621</v>
       </c>
@@ -71419,9 +71423,11 @@
     </row>
     <row r="3847" spans="3:6">
       <c r="C3847" s="3">
-        <v>300002</v>
-      </c>
-      <c r="D3847" s="4"/>
+        <v>300001</v>
+      </c>
+      <c r="D3847" s="4" t="s">
+        <v>1961</v>
+      </c>
       <c r="E3847" s="1" t="s">
         <v>7623</v>
       </c>
@@ -71431,7 +71437,7 @@
     </row>
     <row r="3848" spans="3:6">
       <c r="C3848" s="3">
-        <v>300003</v>
+        <v>300002</v>
       </c>
       <c r="D3848" s="4"/>
       <c r="E3848" s="1" t="s">
@@ -71443,7 +71449,7 @@
     </row>
     <row r="3849" spans="3:6">
       <c r="C3849" s="3">
-        <v>300004</v>
+        <v>300003</v>
       </c>
       <c r="D3849" s="4"/>
       <c r="E3849" s="1" t="s">
@@ -71455,7 +71461,7 @@
     </row>
     <row r="3850" spans="3:6">
       <c r="C3850" s="3">
-        <v>300005</v>
+        <v>300004</v>
       </c>
       <c r="D3850" s="4"/>
       <c r="E3850" s="1" t="s">
@@ -71467,7 +71473,7 @@
     </row>
     <row r="3851" spans="3:6">
       <c r="C3851" s="3">
-        <v>300006</v>
+        <v>300005</v>
       </c>
       <c r="D3851" s="4"/>
       <c r="E3851" s="1" t="s">
@@ -71479,7 +71485,7 @@
     </row>
     <row r="3852" spans="3:6">
       <c r="C3852" s="3">
-        <v>300007</v>
+        <v>300006</v>
       </c>
       <c r="D3852" s="4"/>
       <c r="E3852" s="1" t="s">
@@ -71491,7 +71497,7 @@
     </row>
     <row r="3853" spans="3:6">
       <c r="C3853" s="3">
-        <v>300008</v>
+        <v>300007</v>
       </c>
       <c r="D3853" s="4"/>
       <c r="E3853" s="1" t="s">
@@ -71503,7 +71509,7 @@
     </row>
     <row r="3854" spans="3:6">
       <c r="C3854" s="3">
-        <v>300009</v>
+        <v>300008</v>
       </c>
       <c r="D3854" s="4"/>
       <c r="E3854" s="1" t="s">
@@ -71515,7 +71521,7 @@
     </row>
     <row r="3855" spans="3:6">
       <c r="C3855" s="3">
-        <v>300010</v>
+        <v>300009</v>
       </c>
       <c r="D3855" s="4"/>
       <c r="E3855" s="1" t="s">
@@ -71527,7 +71533,7 @@
     </row>
     <row r="3856" spans="3:6">
       <c r="C3856" s="3">
-        <v>300011</v>
+        <v>300010</v>
       </c>
       <c r="D3856" s="4"/>
       <c r="E3856" s="1" t="s">
@@ -71539,7 +71545,7 @@
     </row>
     <row r="3857" spans="3:6">
       <c r="C3857" s="3">
-        <v>300012</v>
+        <v>300011</v>
       </c>
       <c r="D3857" s="4"/>
       <c r="E3857" s="1" t="s">
@@ -71551,7 +71557,7 @@
     </row>
     <row r="3858" spans="3:6">
       <c r="C3858" s="3">
-        <v>300013</v>
+        <v>300012</v>
       </c>
       <c r="D3858" s="4"/>
       <c r="E3858" s="1" t="s">
@@ -71563,7 +71569,7 @@
     </row>
     <row r="3859" spans="3:6">
       <c r="C3859" s="3">
-        <v>300014</v>
+        <v>300013</v>
       </c>
       <c r="D3859" s="4"/>
       <c r="E3859" s="1" t="s">
@@ -71575,7 +71581,7 @@
     </row>
     <row r="3860" spans="3:6">
       <c r="C3860" s="3">
-        <v>300015</v>
+        <v>300014</v>
       </c>
       <c r="D3860" s="4"/>
       <c r="E3860" s="1" t="s">
@@ -71587,7 +71593,7 @@
     </row>
     <row r="3861" spans="3:6">
       <c r="C3861" s="3">
-        <v>300016</v>
+        <v>300015</v>
       </c>
       <c r="D3861" s="4"/>
       <c r="E3861" s="1" t="s">
@@ -71599,7 +71605,7 @@
     </row>
     <row r="3862" spans="3:6">
       <c r="C3862" s="3">
-        <v>300017</v>
+        <v>300016</v>
       </c>
       <c r="D3862" s="4"/>
       <c r="E3862" s="1" t="s">
@@ -71611,7 +71617,7 @@
     </row>
     <row r="3863" spans="3:6">
       <c r="C3863" s="3">
-        <v>300018</v>
+        <v>300017</v>
       </c>
       <c r="D3863" s="4"/>
       <c r="E3863" s="1" t="s">
@@ -71623,7 +71629,7 @@
     </row>
     <row r="3864" spans="3:6">
       <c r="C3864" s="3">
-        <v>300019</v>
+        <v>300018</v>
       </c>
       <c r="D3864" s="4"/>
       <c r="E3864" s="1" t="s">
@@ -71635,7 +71641,7 @@
     </row>
     <row r="3865" spans="3:6">
       <c r="C3865" s="3">
-        <v>300020</v>
+        <v>300019</v>
       </c>
       <c r="D3865" s="4"/>
       <c r="E3865" s="1" t="s">
@@ -71647,7 +71653,7 @@
     </row>
     <row r="3866" spans="3:6">
       <c r="C3866" s="3">
-        <v>300021</v>
+        <v>300020</v>
       </c>
       <c r="D3866" s="4"/>
       <c r="E3866" s="1" t="s">
@@ -71659,23 +71665,23 @@
     </row>
     <row r="3867" spans="3:6">
       <c r="C3867" s="3">
-        <v>300022</v>
+        <v>300021</v>
       </c>
       <c r="D3867" s="4"/>
       <c r="E3867" s="1" t="s">
-        <v>4218</v>
+        <v>7663</v>
       </c>
       <c r="F3867" s="8" t="s">
-        <v>7663</v>
+        <v>7664</v>
       </c>
     </row>
     <row r="3868" spans="3:6">
       <c r="C3868" s="3">
-        <v>300023</v>
+        <v>300022</v>
       </c>
       <c r="D3868" s="4"/>
       <c r="E3868" s="1" t="s">
-        <v>7664</v>
+        <v>4218</v>
       </c>
       <c r="F3868" s="8" t="s">
         <v>7665</v>
@@ -71683,7 +71689,7 @@
     </row>
     <row r="3869" spans="3:6">
       <c r="C3869" s="3">
-        <v>300024</v>
+        <v>300023</v>
       </c>
       <c r="D3869" s="4"/>
       <c r="E3869" s="1" t="s">
@@ -71695,7 +71701,7 @@
     </row>
     <row r="3870" spans="3:6">
       <c r="C3870" s="3">
-        <v>300025</v>
+        <v>300024</v>
       </c>
       <c r="D3870" s="4"/>
       <c r="E3870" s="1" t="s">
@@ -71707,7 +71713,7 @@
     </row>
     <row r="3871" spans="3:6">
       <c r="C3871" s="3">
-        <v>300026</v>
+        <v>300025</v>
       </c>
       <c r="D3871" s="4"/>
       <c r="E3871" s="1" t="s">
@@ -71719,7 +71725,7 @@
     </row>
     <row r="3872" spans="3:6">
       <c r="C3872" s="3">
-        <v>300027</v>
+        <v>300026</v>
       </c>
       <c r="D3872" s="4"/>
       <c r="E3872" s="1" t="s">
@@ -71731,7 +71737,7 @@
     </row>
     <row r="3873" spans="3:6">
       <c r="C3873" s="3">
-        <v>300028</v>
+        <v>300027</v>
       </c>
       <c r="D3873" s="4"/>
       <c r="E3873" s="1" t="s">
@@ -71743,7 +71749,7 @@
     </row>
     <row r="3874" spans="3:6">
       <c r="C3874" s="3">
-        <v>300029</v>
+        <v>300028</v>
       </c>
       <c r="D3874" s="4"/>
       <c r="E3874" s="1" t="s">
@@ -71755,7 +71761,7 @@
     </row>
     <row r="3875" spans="3:6">
       <c r="C3875" s="3">
-        <v>300030</v>
+        <v>300029</v>
       </c>
       <c r="D3875" s="4"/>
       <c r="E3875" s="1" t="s">
@@ -71767,7 +71773,7 @@
     </row>
     <row r="3876" spans="3:6">
       <c r="C3876" s="3">
-        <v>300031</v>
+        <v>300030</v>
       </c>
       <c r="D3876" s="4"/>
       <c r="E3876" s="1" t="s">
@@ -71779,7 +71785,7 @@
     </row>
     <row r="3877" spans="3:6">
       <c r="C3877" s="3">
-        <v>300032</v>
+        <v>300031</v>
       </c>
       <c r="D3877" s="4"/>
       <c r="E3877" s="1" t="s">
@@ -71791,7 +71797,7 @@
     </row>
     <row r="3878" spans="3:6">
       <c r="C3878" s="3">
-        <v>300033</v>
+        <v>300032</v>
       </c>
       <c r="D3878" s="4"/>
       <c r="E3878" s="1" t="s">
@@ -71803,7 +71809,7 @@
     </row>
     <row r="3879" spans="3:6">
       <c r="C3879" s="3">
-        <v>300034</v>
+        <v>300033</v>
       </c>
       <c r="D3879" s="4"/>
       <c r="E3879" s="1" t="s">
@@ -71815,7 +71821,7 @@
     </row>
     <row r="3880" spans="3:6">
       <c r="C3880" s="3">
-        <v>300035</v>
+        <v>300034</v>
       </c>
       <c r="D3880" s="4"/>
       <c r="E3880" s="1" t="s">
@@ -71827,7 +71833,7 @@
     </row>
     <row r="3881" spans="3:6">
       <c r="C3881" s="3">
-        <v>300036</v>
+        <v>300035</v>
       </c>
       <c r="D3881" s="4"/>
       <c r="E3881" s="1" t="s">
@@ -71839,35 +71845,35 @@
     </row>
     <row r="3882" spans="3:6">
       <c r="C3882" s="3">
-        <v>300037</v>
+        <v>300036</v>
       </c>
       <c r="D3882" s="4"/>
       <c r="E3882" s="1" t="s">
-        <v>5913</v>
+        <v>7692</v>
       </c>
       <c r="F3882" s="8" t="s">
-        <v>7692</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="3883" spans="3:6">
       <c r="C3883" s="3">
-        <v>300038</v>
+        <v>300037</v>
       </c>
       <c r="D3883" s="4"/>
       <c r="E3883" s="1" t="s">
-        <v>4274</v>
+        <v>5913</v>
       </c>
       <c r="F3883" s="8" t="s">
-        <v>7693</v>
+        <v>7694</v>
       </c>
     </row>
     <row r="3884" spans="3:6">
       <c r="C3884" s="3">
-        <v>300039</v>
+        <v>300038</v>
       </c>
       <c r="D3884" s="4"/>
       <c r="E3884" s="1" t="s">
-        <v>7694</v>
+        <v>4274</v>
       </c>
       <c r="F3884" s="8" t="s">
         <v>7695</v>
@@ -71875,7 +71881,7 @@
     </row>
     <row r="3885" spans="3:6">
       <c r="C3885" s="3">
-        <v>300040</v>
+        <v>300039</v>
       </c>
       <c r="D3885" s="4"/>
       <c r="E3885" s="1" t="s">
@@ -71887,7 +71893,7 @@
     </row>
     <row r="3886" spans="3:6">
       <c r="C3886" s="3">
-        <v>300041</v>
+        <v>300040</v>
       </c>
       <c r="D3886" s="4"/>
       <c r="E3886" s="1" t="s">
@@ -71899,58 +71905,58 @@
     </row>
     <row r="3887" spans="3:6">
       <c r="C3887" s="3">
-        <v>300042</v>
+        <v>300041</v>
       </c>
       <c r="D3887" s="4"/>
       <c r="E3887" s="1" t="s">
-        <v>1222</v>
+        <v>7700</v>
       </c>
       <c r="F3887" s="8" t="s">
-        <v>1041</v>
+        <v>7701</v>
       </c>
     </row>
     <row r="3888" spans="3:6">
       <c r="C3888" s="3">
-        <v>300043</v>
+        <v>300042</v>
       </c>
       <c r="D3888" s="4"/>
       <c r="E3888" s="1" t="s">
-        <v>7700</v>
+        <v>1222</v>
       </c>
       <c r="F3888" s="8" t="s">
-        <v>7701</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="3889" spans="3:6">
       <c r="C3889" s="3">
-        <v>300044</v>
+        <v>300043</v>
       </c>
       <c r="D3889" s="4"/>
       <c r="E3889" s="1" t="s">
-        <v>4721</v>
+        <v>7702</v>
       </c>
       <c r="F3889" s="8" t="s">
-        <v>7702</v>
+        <v>7703</v>
       </c>
     </row>
     <row r="3890" spans="3:6">
       <c r="C3890" s="3">
-        <v>300045</v>
-      </c>
-      <c r="D3890"/>
+        <v>300044</v>
+      </c>
+      <c r="D3890" s="4"/>
       <c r="E3890" s="1" t="s">
-        <v>7703</v>
-      </c>
-      <c r="F3890" t="s">
+        <v>4721</v>
+      </c>
+      <c r="F3890" s="8" t="s">
         <v>7704</v>
       </c>
     </row>
     <row r="3891" spans="3:6">
       <c r="C3891" s="3">
-        <v>300046</v>
+        <v>300045</v>
       </c>
       <c r="D3891"/>
-      <c r="E3891" t="s">
+      <c r="E3891" s="1" t="s">
         <v>7705</v>
       </c>
       <c r="F3891" t="s">
@@ -71959,19 +71965,19 @@
     </row>
     <row r="3892" spans="3:6">
       <c r="C3892" s="3">
-        <v>300047</v>
-      </c>
-      <c r="D3892" s="4"/>
-      <c r="E3892" s="1" t="s">
+        <v>300046</v>
+      </c>
+      <c r="D3892"/>
+      <c r="E3892" t="s">
         <v>7707</v>
       </c>
-      <c r="F3892" s="6" t="s">
+      <c r="F3892" t="s">
         <v>7708</v>
       </c>
     </row>
     <row r="3893" spans="3:6">
       <c r="C3893" s="3">
-        <v>300048</v>
+        <v>300047</v>
       </c>
       <c r="D3893" s="4"/>
       <c r="E3893" s="1" t="s">
@@ -71983,7 +71989,7 @@
     </row>
     <row r="3894" spans="3:6">
       <c r="C3894" s="3">
-        <v>300049</v>
+        <v>300048</v>
       </c>
       <c r="D3894" s="4"/>
       <c r="E3894" s="1" t="s">
@@ -71995,7 +72001,7 @@
     </row>
     <row r="3895" spans="3:6">
       <c r="C3895" s="3">
-        <v>300050</v>
+        <v>300049</v>
       </c>
       <c r="D3895" s="4"/>
       <c r="E3895" s="1" t="s">
@@ -72007,7 +72013,7 @@
     </row>
     <row r="3896" spans="3:6">
       <c r="C3896" s="3">
-        <v>300051</v>
+        <v>300050</v>
       </c>
       <c r="D3896" s="4"/>
       <c r="E3896" s="1" t="s">
@@ -72019,7 +72025,7 @@
     </row>
     <row r="3897" spans="3:6">
       <c r="C3897" s="3">
-        <v>300052</v>
+        <v>300051</v>
       </c>
       <c r="D3897" s="4"/>
       <c r="E3897" s="1" t="s">
@@ -72031,7 +72037,7 @@
     </row>
     <row r="3898" spans="3:6">
       <c r="C3898" s="3">
-        <v>300053</v>
+        <v>300052</v>
       </c>
       <c r="D3898" s="4"/>
       <c r="E3898" s="1" t="s">
@@ -72043,7 +72049,7 @@
     </row>
     <row r="3899" spans="3:6">
       <c r="C3899" s="3">
-        <v>300054</v>
+        <v>300053</v>
       </c>
       <c r="D3899" s="4"/>
       <c r="E3899" s="1" t="s">
@@ -72055,7 +72061,7 @@
     </row>
     <row r="3900" spans="3:6">
       <c r="C3900" s="3">
-        <v>300055</v>
+        <v>300054</v>
       </c>
       <c r="D3900" s="4"/>
       <c r="E3900" s="1" t="s">
@@ -72067,7 +72073,7 @@
     </row>
     <row r="3901" spans="3:6">
       <c r="C3901" s="3">
-        <v>300056</v>
+        <v>300055</v>
       </c>
       <c r="D3901" s="4"/>
       <c r="E3901" s="1" t="s">
@@ -72079,7 +72085,7 @@
     </row>
     <row r="3902" spans="3:6">
       <c r="C3902" s="3">
-        <v>300057</v>
+        <v>300056</v>
       </c>
       <c r="D3902" s="4"/>
       <c r="E3902" s="1" t="s">
@@ -72091,7 +72097,7 @@
     </row>
     <row r="3903" spans="3:6">
       <c r="C3903" s="3">
-        <v>300058</v>
+        <v>300057</v>
       </c>
       <c r="D3903" s="4"/>
       <c r="E3903" s="1" t="s">
@@ -72103,7 +72109,7 @@
     </row>
     <row r="3904" spans="3:6">
       <c r="C3904" s="3">
-        <v>300059</v>
+        <v>300058</v>
       </c>
       <c r="D3904" s="4"/>
       <c r="E3904" s="1" t="s">
@@ -72115,7 +72121,7 @@
     </row>
     <row r="3905" spans="3:6">
       <c r="C3905" s="3">
-        <v>300060</v>
+        <v>300059</v>
       </c>
       <c r="D3905" s="4"/>
       <c r="E3905" s="1" t="s">
@@ -72127,7 +72133,7 @@
     </row>
     <row r="3906" spans="3:6">
       <c r="C3906" s="3">
-        <v>300061</v>
+        <v>300060</v>
       </c>
       <c r="D3906" s="4"/>
       <c r="E3906" s="1" t="s">
@@ -72139,7 +72145,7 @@
     </row>
     <row r="3907" spans="3:6">
       <c r="C3907" s="3">
-        <v>300062</v>
+        <v>300061</v>
       </c>
       <c r="D3907" s="4"/>
       <c r="E3907" s="1" t="s">
@@ -72151,7 +72157,7 @@
     </row>
     <row r="3908" spans="3:6">
       <c r="C3908" s="3">
-        <v>300063</v>
+        <v>300062</v>
       </c>
       <c r="D3908" s="4"/>
       <c r="E3908" s="1" t="s">
@@ -72163,7 +72169,7 @@
     </row>
     <row r="3909" spans="3:6">
       <c r="C3909" s="3">
-        <v>300064</v>
+        <v>300063</v>
       </c>
       <c r="D3909" s="4"/>
       <c r="E3909" s="1" t="s">
@@ -72175,7 +72181,7 @@
     </row>
     <row r="3910" spans="3:6">
       <c r="C3910" s="3">
-        <v>300065</v>
+        <v>300064</v>
       </c>
       <c r="D3910" s="4"/>
       <c r="E3910" s="1" t="s">
@@ -72187,7 +72193,7 @@
     </row>
     <row r="3911" spans="3:6">
       <c r="C3911" s="3">
-        <v>300066</v>
+        <v>300065</v>
       </c>
       <c r="D3911" s="4"/>
       <c r="E3911" s="1" t="s">
@@ -72199,7 +72205,7 @@
     </row>
     <row r="3912" spans="3:6">
       <c r="C3912" s="3">
-        <v>300067</v>
+        <v>300066</v>
       </c>
       <c r="D3912" s="4"/>
       <c r="E3912" s="1" t="s">
@@ -72211,7 +72217,7 @@
     </row>
     <row r="3913" spans="3:6">
       <c r="C3913" s="3">
-        <v>300068</v>
+        <v>300067</v>
       </c>
       <c r="D3913" s="4"/>
       <c r="E3913" s="1" t="s">
@@ -72223,7 +72229,7 @@
     </row>
     <row r="3914" spans="3:6">
       <c r="C3914" s="3">
-        <v>300069</v>
+        <v>300068</v>
       </c>
       <c r="D3914" s="4"/>
       <c r="E3914" s="1" t="s">
@@ -72235,7 +72241,7 @@
     </row>
     <row r="3915" spans="3:6">
       <c r="C3915" s="3">
-        <v>300070</v>
+        <v>300069</v>
       </c>
       <c r="D3915" s="4"/>
       <c r="E3915" s="1" t="s">
@@ -72247,7 +72253,7 @@
     </row>
     <row r="3916" spans="3:6">
       <c r="C3916" s="3">
-        <v>300071</v>
+        <v>300070</v>
       </c>
       <c r="D3916" s="4"/>
       <c r="E3916" s="1" t="s">
@@ -72259,7 +72265,7 @@
     </row>
     <row r="3917" spans="3:6">
       <c r="C3917" s="3">
-        <v>300072</v>
+        <v>300071</v>
       </c>
       <c r="D3917" s="4"/>
       <c r="E3917" s="1" t="s">
@@ -72271,7 +72277,7 @@
     </row>
     <row r="3918" spans="3:6">
       <c r="C3918" s="3">
-        <v>300073</v>
+        <v>300072</v>
       </c>
       <c r="D3918" s="4"/>
       <c r="E3918" s="1" t="s">
@@ -72283,7 +72289,7 @@
     </row>
     <row r="3919" spans="3:6">
       <c r="C3919" s="3">
-        <v>300074</v>
+        <v>300073</v>
       </c>
       <c r="D3919" s="4"/>
       <c r="E3919" s="1" t="s">
@@ -72295,7 +72301,7 @@
     </row>
     <row r="3920" spans="3:6">
       <c r="C3920" s="3">
-        <v>300075</v>
+        <v>300074</v>
       </c>
       <c r="D3920" s="4"/>
       <c r="E3920" s="1" t="s">
@@ -72307,7 +72313,7 @@
     </row>
     <row r="3921" spans="3:6">
       <c r="C3921" s="3">
-        <v>300076</v>
+        <v>300075</v>
       </c>
       <c r="D3921" s="4"/>
       <c r="E3921" s="1" t="s">
@@ -72319,7 +72325,7 @@
     </row>
     <row r="3922" spans="3:6">
       <c r="C3922" s="3">
-        <v>300077</v>
+        <v>300076</v>
       </c>
       <c r="D3922" s="4"/>
       <c r="E3922" s="1" t="s">
@@ -72331,7 +72337,7 @@
     </row>
     <row r="3923" spans="3:6">
       <c r="C3923" s="3">
-        <v>300078</v>
+        <v>300077</v>
       </c>
       <c r="D3923" s="4"/>
       <c r="E3923" s="1" t="s">
@@ -72343,7 +72349,7 @@
     </row>
     <row r="3924" spans="3:6">
       <c r="C3924" s="3">
-        <v>300079</v>
+        <v>300078</v>
       </c>
       <c r="D3924" s="4"/>
       <c r="E3924" s="1" t="s">
@@ -72355,7 +72361,7 @@
     </row>
     <row r="3925" spans="3:6">
       <c r="C3925" s="3">
-        <v>300080</v>
+        <v>300079</v>
       </c>
       <c r="D3925" s="4"/>
       <c r="E3925" s="1" t="s">
@@ -72367,7 +72373,7 @@
     </row>
     <row r="3926" spans="3:6">
       <c r="C3926" s="3">
-        <v>300081</v>
+        <v>300080</v>
       </c>
       <c r="D3926" s="4"/>
       <c r="E3926" s="1" t="s">
@@ -72379,7 +72385,7 @@
     </row>
     <row r="3927" spans="3:6">
       <c r="C3927" s="3">
-        <v>300082</v>
+        <v>300081</v>
       </c>
       <c r="D3927" s="4"/>
       <c r="E3927" s="1" t="s">
@@ -72391,7 +72397,7 @@
     </row>
     <row r="3928" spans="3:6">
       <c r="C3928" s="3">
-        <v>300083</v>
+        <v>300082</v>
       </c>
       <c r="D3928" s="4"/>
       <c r="E3928" s="1" t="s">
@@ -72403,7 +72409,7 @@
     </row>
     <row r="3929" spans="3:6">
       <c r="C3929" s="3">
-        <v>300084</v>
+        <v>300083</v>
       </c>
       <c r="D3929" s="4"/>
       <c r="E3929" s="1" t="s">
@@ -72415,7 +72421,7 @@
     </row>
     <row r="3930" spans="3:6">
       <c r="C3930" s="3">
-        <v>300085</v>
+        <v>300084</v>
       </c>
       <c r="D3930" s="4"/>
       <c r="E3930" s="1" t="s">
@@ -72427,7 +72433,7 @@
     </row>
     <row r="3931" spans="3:6">
       <c r="C3931" s="3">
-        <v>300086</v>
+        <v>300085</v>
       </c>
       <c r="D3931" s="4"/>
       <c r="E3931" s="1" t="s">
@@ -72439,7 +72445,7 @@
     </row>
     <row r="3932" spans="3:6">
       <c r="C3932" s="3">
-        <v>300087</v>
+        <v>300086</v>
       </c>
       <c r="D3932" s="4"/>
       <c r="E3932" s="1" t="s">
@@ -72451,7 +72457,7 @@
     </row>
     <row r="3933" spans="3:6">
       <c r="C3933" s="3">
-        <v>300088</v>
+        <v>300087</v>
       </c>
       <c r="D3933" s="4"/>
       <c r="E3933" s="1" t="s">
@@ -72463,7 +72469,7 @@
     </row>
     <row r="3934" spans="3:6">
       <c r="C3934" s="3">
-        <v>300089</v>
+        <v>300088</v>
       </c>
       <c r="D3934" s="4"/>
       <c r="E3934" s="1" t="s">
@@ -72475,7 +72481,7 @@
     </row>
     <row r="3935" spans="3:6">
       <c r="C3935" s="3">
-        <v>300090</v>
+        <v>300089</v>
       </c>
       <c r="D3935" s="4"/>
       <c r="E3935" s="1" t="s">
@@ -72487,7 +72493,7 @@
     </row>
     <row r="3936" spans="3:6">
       <c r="C3936" s="3">
-        <v>300091</v>
+        <v>300090</v>
       </c>
       <c r="D3936" s="4"/>
       <c r="E3936" s="1" t="s">
@@ -72499,7 +72505,7 @@
     </row>
     <row r="3937" spans="3:6">
       <c r="C3937" s="3">
-        <v>300092</v>
+        <v>300091</v>
       </c>
       <c r="D3937" s="4"/>
       <c r="E3937" s="1" t="s">
@@ -72511,7 +72517,7 @@
     </row>
     <row r="3938" spans="3:6">
       <c r="C3938" s="3">
-        <v>300093</v>
+        <v>300092</v>
       </c>
       <c r="D3938" s="4"/>
       <c r="E3938" s="1" t="s">
@@ -72523,7 +72529,7 @@
     </row>
     <row r="3939" spans="3:6">
       <c r="C3939" s="3">
-        <v>300094</v>
+        <v>300093</v>
       </c>
       <c r="D3939" s="4"/>
       <c r="E3939" s="1" t="s">
@@ -72535,7 +72541,7 @@
     </row>
     <row r="3940" spans="3:6">
       <c r="C3940" s="3">
-        <v>300095</v>
+        <v>300094</v>
       </c>
       <c r="D3940" s="4"/>
       <c r="E3940" s="1" t="s">
@@ -72547,7 +72553,7 @@
     </row>
     <row r="3941" spans="3:6">
       <c r="C3941" s="3">
-        <v>300096</v>
+        <v>300095</v>
       </c>
       <c r="D3941" s="4"/>
       <c r="E3941" s="1" t="s">
@@ -72559,7 +72565,7 @@
     </row>
     <row r="3942" spans="3:6">
       <c r="C3942" s="3">
-        <v>300097</v>
+        <v>300096</v>
       </c>
       <c r="D3942" s="4"/>
       <c r="E3942" s="1" t="s">
@@ -72571,7 +72577,7 @@
     </row>
     <row r="3943" spans="3:6">
       <c r="C3943" s="3">
-        <v>300098</v>
+        <v>300097</v>
       </c>
       <c r="D3943" s="4"/>
       <c r="E3943" s="1" t="s">
@@ -72583,7 +72589,7 @@
     </row>
     <row r="3944" spans="3:6">
       <c r="C3944" s="3">
-        <v>300099</v>
+        <v>300098</v>
       </c>
       <c r="D3944" s="4"/>
       <c r="E3944" s="1" t="s">
@@ -72595,7 +72601,7 @@
     </row>
     <row r="3945" spans="3:6">
       <c r="C3945" s="3">
-        <v>300100</v>
+        <v>300099</v>
       </c>
       <c r="D3945" s="4"/>
       <c r="E3945" s="1" t="s">
@@ -72607,7 +72613,7 @@
     </row>
     <row r="3946" spans="3:6">
       <c r="C3946" s="3">
-        <v>300101</v>
+        <v>300100</v>
       </c>
       <c r="D3946" s="4"/>
       <c r="E3946" s="1" t="s">
@@ -72619,7 +72625,7 @@
     </row>
     <row r="3947" spans="3:6">
       <c r="C3947" s="3">
-        <v>300102</v>
+        <v>300101</v>
       </c>
       <c r="D3947" s="4"/>
       <c r="E3947" s="1" t="s">
@@ -72631,7 +72637,7 @@
     </row>
     <row r="3948" spans="3:6">
       <c r="C3948" s="3">
-        <v>300103</v>
+        <v>300102</v>
       </c>
       <c r="D3948" s="4"/>
       <c r="E3948" s="1" t="s">
@@ -72643,7 +72649,7 @@
     </row>
     <row r="3949" spans="3:6">
       <c r="C3949" s="3">
-        <v>300104</v>
+        <v>300103</v>
       </c>
       <c r="D3949" s="4"/>
       <c r="E3949" s="1" t="s">
@@ -72655,7 +72661,7 @@
     </row>
     <row r="3950" spans="3:6">
       <c r="C3950" s="3">
-        <v>300105</v>
+        <v>300104</v>
       </c>
       <c r="D3950" s="4"/>
       <c r="E3950" s="1" t="s">
@@ -72667,7 +72673,7 @@
     </row>
     <row r="3951" spans="3:6">
       <c r="C3951" s="3">
-        <v>300106</v>
+        <v>300105</v>
       </c>
       <c r="D3951" s="4"/>
       <c r="E3951" s="1" t="s">
@@ -72679,7 +72685,7 @@
     </row>
     <row r="3952" spans="3:6">
       <c r="C3952" s="3">
-        <v>300107</v>
+        <v>300106</v>
       </c>
       <c r="D3952" s="4"/>
       <c r="E3952" s="1" t="s">
@@ -72691,7 +72697,7 @@
     </row>
     <row r="3953" spans="3:6">
       <c r="C3953" s="3">
-        <v>300108</v>
+        <v>300107</v>
       </c>
       <c r="D3953" s="4"/>
       <c r="E3953" s="1" t="s">
@@ -72703,7 +72709,7 @@
     </row>
     <row r="3954" spans="3:6">
       <c r="C3954" s="3">
-        <v>300109</v>
+        <v>300108</v>
       </c>
       <c r="D3954" s="4"/>
       <c r="E3954" s="1" t="s">
@@ -72715,19 +72721,19 @@
     </row>
     <row r="3955" spans="3:6">
       <c r="C3955" s="3">
-        <v>300110</v>
-      </c>
-      <c r="D3955"/>
+        <v>300109</v>
+      </c>
+      <c r="D3955" s="4"/>
       <c r="E3955" s="1" t="s">
         <v>7833</v>
       </c>
-      <c r="F3955" s="1" t="s">
+      <c r="F3955" s="6" t="s">
         <v>7834</v>
       </c>
     </row>
     <row r="3956" spans="3:6">
       <c r="C3956" s="3">
-        <v>300111</v>
+        <v>300110</v>
       </c>
       <c r="D3956"/>
       <c r="E3956" s="1" t="s">
@@ -72739,8 +72745,9 @@
     </row>
     <row r="3957" spans="3:6">
       <c r="C3957" s="3">
-        <v>300112</v>
-      </c>
+        <v>300111</v>
+      </c>
+      <c r="D3957"/>
       <c r="E3957" s="1" t="s">
         <v>7837</v>
       </c>
@@ -72750,7 +72757,7 @@
     </row>
     <row r="3958" spans="3:6">
       <c r="C3958" s="3">
-        <v>300113</v>
+        <v>300112</v>
       </c>
       <c r="E3958" s="1" t="s">
         <v>7839</v>
@@ -72761,7 +72768,7 @@
     </row>
     <row r="3959" spans="3:6">
       <c r="C3959" s="3">
-        <v>300114</v>
+        <v>300113</v>
       </c>
       <c r="E3959" s="1" t="s">
         <v>7841</v>
@@ -72772,7 +72779,7 @@
     </row>
     <row r="3960" spans="3:6">
       <c r="C3960" s="3">
-        <v>300115</v>
+        <v>300114</v>
       </c>
       <c r="E3960" s="1" t="s">
         <v>7843</v>
@@ -72783,32 +72790,32 @@
     </row>
     <row r="3961" spans="3:6">
       <c r="C3961" s="3">
-        <v>300116</v>
+        <v>300115</v>
       </c>
       <c r="E3961" s="1" t="s">
         <v>7845</v>
       </c>
       <c r="F3961" s="1" t="s">
-        <v>1734</v>
+        <v>7846</v>
       </c>
     </row>
     <row r="3962" spans="3:6">
       <c r="C3962" s="3">
-        <v>300117</v>
+        <v>300116</v>
       </c>
       <c r="E3962" s="1" t="s">
-        <v>3182</v>
+        <v>7847</v>
       </c>
       <c r="F3962" s="1" t="s">
-        <v>7846</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="3963" spans="3:6">
       <c r="C3963" s="3">
-        <v>300118</v>
+        <v>300117</v>
       </c>
       <c r="E3963" s="1" t="s">
-        <v>7847</v>
+        <v>3182</v>
       </c>
       <c r="F3963" s="1" t="s">
         <v>7848</v>
@@ -72816,7 +72823,7 @@
     </row>
     <row r="3964" spans="3:6">
       <c r="C3964" s="3">
-        <v>300119</v>
+        <v>300118</v>
       </c>
       <c r="E3964" s="1" t="s">
         <v>7849</v>
@@ -72827,7 +72834,7 @@
     </row>
     <row r="3965" spans="3:6">
       <c r="C3965" s="3">
-        <v>300120</v>
+        <v>300119</v>
       </c>
       <c r="E3965" s="1" t="s">
         <v>7851</v>
@@ -72838,7 +72845,7 @@
     </row>
     <row r="3966" spans="3:6">
       <c r="C3966" s="3">
-        <v>300121</v>
+        <v>300120</v>
       </c>
       <c r="E3966" s="1" t="s">
         <v>7853</v>
@@ -72849,7 +72856,7 @@
     </row>
     <row r="3967" spans="3:6">
       <c r="C3967" s="3">
-        <v>300122</v>
+        <v>300121</v>
       </c>
       <c r="E3967" s="1" t="s">
         <v>7855</v>
@@ -72860,29 +72867,29 @@
     </row>
     <row r="3968" spans="3:6">
       <c r="C3968" s="3">
-        <v>300123</v>
+        <v>300122</v>
       </c>
       <c r="E3968" s="1" t="s">
         <v>7857</v>
       </c>
       <c r="F3968" s="1" t="s">
-        <v>343</v>
+        <v>7858</v>
       </c>
     </row>
     <row r="3969" spans="2:6">
       <c r="C3969" s="3">
-        <v>300124</v>
+        <v>300123</v>
       </c>
       <c r="E3969" s="1" t="s">
-        <v>7858</v>
+        <v>7859</v>
       </c>
       <c r="F3969" s="1" t="s">
-        <v>7859</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3970" spans="2:6">
       <c r="C3970" s="3">
-        <v>300125</v>
+        <v>300124</v>
       </c>
       <c r="E3970" s="1" t="s">
         <v>7860</v>
@@ -72893,7 +72900,7 @@
     </row>
     <row r="3971" spans="2:6">
       <c r="C3971" s="3">
-        <v>300126</v>
+        <v>300125</v>
       </c>
       <c r="E3971" s="1" t="s">
         <v>7862</v>
@@ -72904,7 +72911,7 @@
     </row>
     <row r="3972" spans="2:6">
       <c r="C3972" s="3">
-        <v>300127</v>
+        <v>300126</v>
       </c>
       <c r="E3972" s="1" t="s">
         <v>7864</v>
@@ -72915,7 +72922,7 @@
     </row>
     <row r="3973" spans="2:6">
       <c r="C3973" s="3">
-        <v>300128</v>
+        <v>300127</v>
       </c>
       <c r="E3973" s="1" t="s">
         <v>7866</v>
@@ -72926,7 +72933,7 @@
     </row>
     <row r="3974" spans="2:6">
       <c r="C3974" s="3">
-        <v>300129</v>
+        <v>300128</v>
       </c>
       <c r="E3974" s="1" t="s">
         <v>7868</v>
@@ -72937,7 +72944,7 @@
     </row>
     <row r="3975" spans="2:6">
       <c r="C3975" s="3">
-        <v>300130</v>
+        <v>300129</v>
       </c>
       <c r="E3975" s="1" t="s">
         <v>7870</v>
@@ -72948,7 +72955,7 @@
     </row>
     <row r="3976" spans="2:6">
       <c r="C3976" s="3">
-        <v>300131</v>
+        <v>300130</v>
       </c>
       <c r="E3976" s="1" t="s">
         <v>7872</v>
@@ -72959,7 +72966,7 @@
     </row>
     <row r="3977" spans="2:6">
       <c r="C3977" s="3">
-        <v>300132</v>
+        <v>300131</v>
       </c>
       <c r="E3977" s="1" t="s">
         <v>7874</v>
@@ -72970,7 +72977,7 @@
     </row>
     <row r="3978" spans="2:6">
       <c r="C3978" s="3">
-        <v>300133</v>
+        <v>300132</v>
       </c>
       <c r="E3978" s="1" t="s">
         <v>7876</v>
@@ -72981,7 +72988,7 @@
     </row>
     <row r="3979" spans="2:6">
       <c r="C3979" s="3">
-        <v>300134</v>
+        <v>300133</v>
       </c>
       <c r="E3979" s="1" t="s">
         <v>7878</v>
@@ -72992,7 +72999,7 @@
     </row>
     <row r="3980" spans="2:6">
       <c r="C3980" s="3">
-        <v>300135</v>
+        <v>300134</v>
       </c>
       <c r="E3980" s="1" t="s">
         <v>7880</v>
@@ -73002,9 +73009,8 @@
       </c>
     </row>
     <row r="3981" spans="2:6">
-      <c r="B3981" s="3"/>
       <c r="C3981" s="3">
-        <v>300136</v>
+        <v>300135</v>
       </c>
       <c r="E3981" s="1" t="s">
         <v>7882</v>
@@ -73016,7 +73022,7 @@
     <row r="3982" spans="2:6">
       <c r="B3982" s="3"/>
       <c r="C3982" s="3">
-        <v>300137</v>
+        <v>300136</v>
       </c>
       <c r="E3982" s="1" t="s">
         <v>7884</v>
@@ -73028,7 +73034,7 @@
     <row r="3983" spans="2:6">
       <c r="B3983" s="3"/>
       <c r="C3983" s="3">
-        <v>300138</v>
+        <v>300137</v>
       </c>
       <c r="E3983" s="1" t="s">
         <v>7886</v>
@@ -73040,7 +73046,7 @@
     <row r="3984" spans="2:6">
       <c r="B3984" s="3"/>
       <c r="C3984" s="3">
-        <v>300139</v>
+        <v>300138</v>
       </c>
       <c r="E3984" s="1" t="s">
         <v>7888</v>
@@ -73052,7 +73058,7 @@
     <row r="3985" spans="2:6">
       <c r="B3985" s="3"/>
       <c r="C3985" s="3">
-        <v>300140</v>
+        <v>300139</v>
       </c>
       <c r="E3985" s="1" t="s">
         <v>7890</v>
@@ -73064,7 +73070,7 @@
     <row r="3986" spans="2:6">
       <c r="B3986" s="3"/>
       <c r="C3986" s="3">
-        <v>300141</v>
+        <v>300140</v>
       </c>
       <c r="E3986" s="1" t="s">
         <v>7892</v>
@@ -73076,7 +73082,7 @@
     <row r="3987" spans="2:6">
       <c r="B3987" s="3"/>
       <c r="C3987" s="3">
-        <v>300142</v>
+        <v>300141</v>
       </c>
       <c r="E3987" s="1" t="s">
         <v>7894</v>
@@ -73088,7 +73094,7 @@
     <row r="3988" spans="2:6">
       <c r="B3988" s="3"/>
       <c r="C3988" s="3">
-        <v>300143</v>
+        <v>300142</v>
       </c>
       <c r="E3988" s="1" t="s">
         <v>7896</v>
@@ -73100,7 +73106,7 @@
     <row r="3989" spans="2:6">
       <c r="B3989" s="3"/>
       <c r="C3989" s="3">
-        <v>300144</v>
+        <v>300143</v>
       </c>
       <c r="E3989" s="1" t="s">
         <v>7898</v>
@@ -73112,7 +73118,7 @@
     <row r="3990" spans="2:6">
       <c r="B3990" s="3"/>
       <c r="C3990" s="3">
-        <v>300145</v>
+        <v>300144</v>
       </c>
       <c r="E3990" s="1" t="s">
         <v>7900</v>
@@ -73124,7 +73130,7 @@
     <row r="3991" spans="2:6">
       <c r="B3991" s="3"/>
       <c r="C3991" s="3">
-        <v>300146</v>
+        <v>300145</v>
       </c>
       <c r="E3991" s="1" t="s">
         <v>7902</v>
@@ -73136,7 +73142,7 @@
     <row r="3992" spans="2:6">
       <c r="B3992" s="3"/>
       <c r="C3992" s="3">
-        <v>300147</v>
+        <v>300146</v>
       </c>
       <c r="E3992" s="1" t="s">
         <v>7904</v>
@@ -73148,7 +73154,7 @@
     <row r="3993" spans="2:6">
       <c r="B3993" s="3"/>
       <c r="C3993" s="3">
-        <v>300148</v>
+        <v>300147</v>
       </c>
       <c r="E3993" s="1" t="s">
         <v>7906</v>
@@ -73160,22 +73166,22 @@
     <row r="3994" spans="2:6">
       <c r="B3994" s="3"/>
       <c r="C3994" s="3">
-        <v>300149</v>
+        <v>300148</v>
       </c>
       <c r="E3994" s="1" t="s">
-        <v>2906</v>
+        <v>7908</v>
       </c>
       <c r="F3994" s="1" t="s">
-        <v>7908</v>
+        <v>7909</v>
       </c>
     </row>
     <row r="3995" spans="2:6">
       <c r="B3995" s="3"/>
       <c r="C3995" s="3">
-        <v>300150</v>
+        <v>300149</v>
       </c>
       <c r="E3995" s="1" t="s">
-        <v>7909</v>
+        <v>2906</v>
       </c>
       <c r="F3995" s="1" t="s">
         <v>7910</v>
@@ -73184,7 +73190,7 @@
     <row r="3996" spans="2:6">
       <c r="B3996" s="3"/>
       <c r="C3996" s="3">
-        <v>300151</v>
+        <v>300150</v>
       </c>
       <c r="E3996" s="1" t="s">
         <v>7911</v>
@@ -73196,7 +73202,7 @@
     <row r="3997" spans="2:6">
       <c r="B3997" s="3"/>
       <c r="C3997" s="3">
-        <v>300152</v>
+        <v>300151</v>
       </c>
       <c r="E3997" s="1" t="s">
         <v>7913</v>
@@ -73206,8 +73212,9 @@
       </c>
     </row>
     <row r="3998" spans="2:6">
+      <c r="B3998" s="3"/>
       <c r="C3998" s="3">
-        <v>300153</v>
+        <v>300152</v>
       </c>
       <c r="E3998" s="1" t="s">
         <v>7915</v>
@@ -73218,7 +73225,7 @@
     </row>
     <row r="3999" spans="2:6">
       <c r="C3999" s="3">
-        <v>300154</v>
+        <v>300153</v>
       </c>
       <c r="E3999" s="1" t="s">
         <v>7917</v>
@@ -73229,7 +73236,7 @@
     </row>
     <row r="4000" spans="2:6">
       <c r="C4000" s="3">
-        <v>300155</v>
+        <v>300154</v>
       </c>
       <c r="E4000" s="1" t="s">
         <v>7919</v>
@@ -73240,7 +73247,7 @@
     </row>
     <row r="4001" spans="3:6">
       <c r="C4001" s="3">
-        <v>300156</v>
+        <v>300155</v>
       </c>
       <c r="E4001" s="1" t="s">
         <v>7921</v>
@@ -73251,7 +73258,7 @@
     </row>
     <row r="4002" spans="3:6">
       <c r="C4002" s="3">
-        <v>300157</v>
+        <v>300156</v>
       </c>
       <c r="E4002" s="1" t="s">
         <v>7923</v>
@@ -73262,7 +73269,7 @@
     </row>
     <row r="4003" spans="3:6">
       <c r="C4003" s="3">
-        <v>300158</v>
+        <v>300157</v>
       </c>
       <c r="E4003" s="1" t="s">
         <v>7925</v>
@@ -73273,7 +73280,7 @@
     </row>
     <row r="4004" spans="3:6">
       <c r="C4004" s="3">
-        <v>300159</v>
+        <v>300158</v>
       </c>
       <c r="E4004" s="1" t="s">
         <v>7927</v>
@@ -73284,7 +73291,7 @@
     </row>
     <row r="4005" spans="3:6">
       <c r="C4005" s="3">
-        <v>300160</v>
+        <v>300159</v>
       </c>
       <c r="E4005" s="1" t="s">
         <v>7929</v>
@@ -73295,7 +73302,7 @@
     </row>
     <row r="4006" spans="3:6">
       <c r="C4006" s="3">
-        <v>300161</v>
+        <v>300160</v>
       </c>
       <c r="E4006" s="1" t="s">
         <v>7931</v>
@@ -73306,7 +73313,7 @@
     </row>
     <row r="4007" spans="3:6">
       <c r="C4007" s="3">
-        <v>300162</v>
+        <v>300161</v>
       </c>
       <c r="E4007" s="1" t="s">
         <v>7933</v>
@@ -73317,7 +73324,7 @@
     </row>
     <row r="4008" spans="3:6">
       <c r="C4008" s="3">
-        <v>300163</v>
+        <v>300162</v>
       </c>
       <c r="E4008" s="1" t="s">
         <v>7935</v>
@@ -73328,7 +73335,7 @@
     </row>
     <row r="4009" spans="3:6">
       <c r="C4009" s="3">
-        <v>300164</v>
+        <v>300163</v>
       </c>
       <c r="E4009" s="1" t="s">
         <v>7937</v>
@@ -73339,7 +73346,7 @@
     </row>
     <row r="4010" spans="3:6">
       <c r="C4010" s="3">
-        <v>300165</v>
+        <v>300164</v>
       </c>
       <c r="E4010" s="1" t="s">
         <v>7939</v>
@@ -73350,73 +73357,73 @@
     </row>
     <row r="4011" spans="3:6">
       <c r="C4011" s="3">
-        <v>300166</v>
+        <v>300165</v>
       </c>
       <c r="E4011" s="1" t="s">
-        <v>1068</v>
+        <v>7941</v>
       </c>
       <c r="F4011" s="1" t="s">
-        <v>7941</v>
+        <v>7942</v>
       </c>
     </row>
     <row r="4012" spans="3:6">
       <c r="C4012" s="3">
-        <v>300167</v>
+        <v>300166</v>
       </c>
       <c r="E4012" s="1" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="F4012" s="1" t="s">
-        <v>7942</v>
+        <v>7943</v>
       </c>
     </row>
     <row r="4013" spans="3:6">
       <c r="C4013" s="3">
-        <v>300168</v>
+        <v>300167</v>
       </c>
       <c r="E4013" s="1" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="F4013" s="1" t="s">
-        <v>7943</v>
+        <v>7944</v>
       </c>
     </row>
     <row r="4014" spans="3:6">
       <c r="C4014" s="3">
-        <v>300169</v>
+        <v>300168</v>
       </c>
       <c r="E4014" s="1" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="F4014" s="1" t="s">
-        <v>7944</v>
+        <v>7945</v>
       </c>
     </row>
     <row r="4015" spans="3:6">
       <c r="C4015" s="3">
-        <v>300170</v>
+        <v>300169</v>
       </c>
       <c r="E4015" s="1" t="s">
-        <v>7945</v>
+        <v>1074</v>
       </c>
       <c r="F4015" s="1" t="s">
-        <v>1254</v>
+        <v>7946</v>
       </c>
     </row>
     <row r="4016" spans="3:6">
       <c r="C4016" s="3">
-        <v>300171</v>
+        <v>300170</v>
       </c>
       <c r="E4016" s="1" t="s">
-        <v>7946</v>
+        <v>7947</v>
       </c>
       <c r="F4016" s="1" t="s">
-        <v>7947</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="4017" spans="3:6">
       <c r="C4017" s="3">
-        <v>300172</v>
+        <v>300171</v>
       </c>
       <c r="E4017" s="1" t="s">
         <v>7948</v>
@@ -73427,7 +73434,7 @@
     </row>
     <row r="4018" spans="3:6">
       <c r="C4018" s="3">
-        <v>300173</v>
+        <v>300172</v>
       </c>
       <c r="E4018" s="1" t="s">
         <v>7950</v>
@@ -73438,7 +73445,7 @@
     </row>
     <row r="4019" spans="3:6">
       <c r="C4019" s="3">
-        <v>300174</v>
+        <v>300173</v>
       </c>
       <c r="E4019" s="1" t="s">
         <v>7952</v>
@@ -73449,7 +73456,7 @@
     </row>
     <row r="4020" spans="3:6">
       <c r="C4020" s="3">
-        <v>300175</v>
+        <v>300174</v>
       </c>
       <c r="E4020" s="1" t="s">
         <v>7954</v>
@@ -73460,7 +73467,7 @@
     </row>
     <row r="4021" spans="3:6">
       <c r="C4021" s="3">
-        <v>300176</v>
+        <v>300175</v>
       </c>
       <c r="E4021" s="1" t="s">
         <v>7956</v>
@@ -73471,51 +73478,51 @@
     </row>
     <row r="4022" spans="3:6">
       <c r="C4022" s="3">
-        <v>300177</v>
+        <v>300176</v>
       </c>
       <c r="E4022" s="1" t="s">
         <v>7958</v>
       </c>
       <c r="F4022" s="1" t="s">
-        <v>2357</v>
+        <v>7959</v>
       </c>
     </row>
     <row r="4023" spans="3:6">
       <c r="C4023" s="3">
-        <v>300178</v>
+        <v>300177</v>
       </c>
       <c r="E4023" s="1" t="s">
-        <v>7959</v>
+        <v>7960</v>
       </c>
       <c r="F4023" s="1" t="s">
-        <v>7960</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="4024" spans="3:6">
       <c r="C4024" s="3">
-        <v>300179</v>
+        <v>300178</v>
       </c>
       <c r="E4024" s="1" t="s">
         <v>7961</v>
       </c>
       <c r="F4024" s="1" t="s">
-        <v>678</v>
+        <v>7962</v>
       </c>
     </row>
     <row r="4025" spans="3:6">
       <c r="C4025" s="3">
-        <v>300180</v>
+        <v>300179</v>
       </c>
       <c r="E4025" s="1" t="s">
-        <v>7962</v>
+        <v>7963</v>
       </c>
       <c r="F4025" s="1" t="s">
-        <v>7963</v>
+        <v>678</v>
       </c>
     </row>
     <row r="4026" spans="3:6">
       <c r="C4026" s="3">
-        <v>300181</v>
+        <v>300180</v>
       </c>
       <c r="E4026" s="1" t="s">
         <v>7964</v>
@@ -73526,7 +73533,7 @@
     </row>
     <row r="4027" spans="3:6">
       <c r="C4027" s="3">
-        <v>300182</v>
+        <v>300181</v>
       </c>
       <c r="E4027" s="1" t="s">
         <v>7966</v>
@@ -73537,7 +73544,7 @@
     </row>
     <row r="4028" spans="3:6">
       <c r="C4028" s="3">
-        <v>300183</v>
+        <v>300182</v>
       </c>
       <c r="E4028" s="1" t="s">
         <v>7968</v>
@@ -73548,51 +73555,51 @@
     </row>
     <row r="4029" spans="3:6">
       <c r="C4029" s="3">
-        <v>300184</v>
+        <v>300183</v>
       </c>
       <c r="E4029" s="1" t="s">
-        <v>4328</v>
+        <v>7970</v>
       </c>
       <c r="F4029" s="1" t="s">
-        <v>718</v>
+        <v>7971</v>
       </c>
     </row>
     <row r="4030" spans="3:6">
       <c r="C4030" s="3">
-        <v>300185</v>
+        <v>300184</v>
       </c>
       <c r="E4030" s="1" t="s">
-        <v>7970</v>
+        <v>4328</v>
       </c>
       <c r="F4030" s="1" t="s">
-        <v>7971</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4031" spans="3:6">
       <c r="C4031" s="3">
-        <v>300186</v>
+        <v>300185</v>
       </c>
       <c r="E4031" s="1" t="s">
         <v>7972</v>
       </c>
       <c r="F4031" s="1" t="s">
-        <v>718</v>
+        <v>7973</v>
       </c>
     </row>
     <row r="4032" spans="3:6">
       <c r="C4032" s="3">
-        <v>300187</v>
+        <v>300186</v>
       </c>
       <c r="E4032" s="1" t="s">
-        <v>7973</v>
+        <v>7974</v>
       </c>
       <c r="F4032" s="1" t="s">
-        <v>7974</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4033" spans="3:6">
       <c r="C4033" s="3">
-        <v>300188</v>
+        <v>300187</v>
       </c>
       <c r="E4033" s="1" t="s">
         <v>7975</v>
@@ -73603,7 +73610,7 @@
     </row>
     <row r="4034" spans="3:6">
       <c r="C4034" s="3">
-        <v>300189</v>
+        <v>300188</v>
       </c>
       <c r="E4034" s="1" t="s">
         <v>7977</v>
@@ -73614,7 +73621,7 @@
     </row>
     <row r="4035" spans="3:6">
       <c r="C4035" s="3">
-        <v>300190</v>
+        <v>300189</v>
       </c>
       <c r="E4035" s="1" t="s">
         <v>7979</v>
@@ -73625,7 +73632,7 @@
     </row>
     <row r="4036" spans="3:6">
       <c r="C4036" s="3">
-        <v>300191</v>
+        <v>300190</v>
       </c>
       <c r="E4036" s="1" t="s">
         <v>7981</v>
@@ -73636,7 +73643,7 @@
     </row>
     <row r="4037" spans="3:6">
       <c r="C4037" s="3">
-        <v>300192</v>
+        <v>300191</v>
       </c>
       <c r="E4037" s="1" t="s">
         <v>7983</v>
@@ -73647,7 +73654,7 @@
     </row>
     <row r="4038" spans="3:6">
       <c r="C4038" s="3">
-        <v>300193</v>
+        <v>300192</v>
       </c>
       <c r="E4038" s="1" t="s">
         <v>7985</v>
@@ -73658,7 +73665,7 @@
     </row>
     <row r="4039" spans="3:6">
       <c r="C4039" s="3">
-        <v>300194</v>
+        <v>300193</v>
       </c>
       <c r="E4039" s="1" t="s">
         <v>7987</v>
@@ -73669,7 +73676,7 @@
     </row>
     <row r="4040" spans="3:6">
       <c r="C4040" s="3">
-        <v>300195</v>
+        <v>300194</v>
       </c>
       <c r="E4040" s="1" t="s">
         <v>7989</v>
@@ -73680,7 +73687,7 @@
     </row>
     <row r="4041" spans="3:6">
       <c r="C4041" s="3">
-        <v>300196</v>
+        <v>300195</v>
       </c>
       <c r="E4041" s="1" t="s">
         <v>7991</v>
@@ -73691,7 +73698,7 @@
     </row>
     <row r="4042" spans="3:6">
       <c r="C4042" s="3">
-        <v>300197</v>
+        <v>300196</v>
       </c>
       <c r="E4042" s="1" t="s">
         <v>7993</v>
@@ -73702,7 +73709,7 @@
     </row>
     <row r="4043" spans="3:6">
       <c r="C4043" s="3">
-        <v>300198</v>
+        <v>300197</v>
       </c>
       <c r="E4043" s="1" t="s">
         <v>7995</v>
@@ -73713,13 +73720,24 @@
     </row>
     <row r="4044" spans="3:6">
       <c r="C4044" s="3">
-        <v>300199</v>
+        <v>300198</v>
       </c>
       <c r="E4044" s="1" t="s">
         <v>7997</v>
       </c>
       <c r="F4044" s="1" t="s">
         <v>7998</v>
+      </c>
+    </row>
+    <row r="4045" spans="3:6">
+      <c r="C4045" s="3">
+        <v>300199</v>
+      </c>
+      <c r="E4045" s="1" t="s">
+        <v>7999</v>
+      </c>
+      <c r="F4045" s="1" t="s">
+        <v>8000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8208" uniqueCount="8001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8222" uniqueCount="8013">
   <si>
     <t>c</t>
   </si>
@@ -22896,6 +22896,42 @@
   </si>
   <si>
     <t>Robot team: {0}</t>
+  </si>
+  <si>
+    <t>支持作者</t>
+  </si>
+  <si>
+    <t>Supporting Author</t>
+  </si>
+  <si>
+    <t>礼包奖励</t>
+  </si>
+  <si>
+    <t>打开礼包</t>
+  </si>
+  <si>
+    <t>Open the package</t>
+  </si>
+  <si>
+    <t>提示:赞助任意金额即可打开礼包!</t>
+  </si>
+  <si>
+    <t>Tip: Donate any amount to open the gift pack!</t>
+  </si>
+  <si>
+    <t>点击按钮进入探险</t>
+  </si>
+  <si>
+    <t>Click the button to enter the adventure</t>
+  </si>
+  <si>
+    <t>第一赛季</t>
+  </si>
+  <si>
+    <t>First season</t>
+  </si>
+  <si>
+    <t>Level rewards</t>
   </si>
   <si>
     <t>合区补偿</t>
@@ -25038,7 +25074,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4045"/>
+  <dimension ref="B2:F4052"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -71423,11 +71459,9 @@
     </row>
     <row r="3847" spans="3:6">
       <c r="C3847" s="3">
-        <v>300001</v>
-      </c>
-      <c r="D3847" s="4" t="s">
-        <v>1961</v>
-      </c>
+        <v>203730</v>
+      </c>
+      <c r="D3847" s="4"/>
       <c r="E3847" s="1" t="s">
         <v>7623</v>
       </c>
@@ -71437,443 +71471,445 @@
     </row>
     <row r="3848" spans="3:6">
       <c r="C3848" s="3">
-        <v>300002</v>
+        <v>203731</v>
       </c>
       <c r="D3848" s="4"/>
       <c r="E3848" s="1" t="s">
         <v>7625</v>
       </c>
       <c r="F3848" s="8" t="s">
-        <v>7626</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="3849" spans="3:6">
       <c r="C3849" s="3">
-        <v>300003</v>
+        <v>203732</v>
       </c>
       <c r="D3849" s="4"/>
       <c r="E3849" s="1" t="s">
+        <v>7626</v>
+      </c>
+      <c r="F3849" s="8" t="s">
         <v>7627</v>
-      </c>
-      <c r="F3849" s="8" t="s">
-        <v>7628</v>
       </c>
     </row>
     <row r="3850" spans="3:6">
       <c r="C3850" s="3">
-        <v>300004</v>
+        <v>203733</v>
       </c>
       <c r="D3850" s="4"/>
       <c r="E3850" s="1" t="s">
+        <v>7628</v>
+      </c>
+      <c r="F3850" s="8" t="s">
         <v>7629</v>
-      </c>
-      <c r="F3850" s="8" t="s">
-        <v>7630</v>
       </c>
     </row>
     <row r="3851" spans="3:6">
       <c r="C3851" s="3">
-        <v>300005</v>
+        <v>203734</v>
       </c>
       <c r="D3851" s="4"/>
       <c r="E3851" s="1" t="s">
+        <v>7630</v>
+      </c>
+      <c r="F3851" s="8" t="s">
         <v>7631</v>
-      </c>
-      <c r="F3851" s="8" t="s">
-        <v>7632</v>
       </c>
     </row>
     <row r="3852" spans="3:6">
       <c r="C3852" s="3">
-        <v>300006</v>
+        <v>203735</v>
       </c>
       <c r="D3852" s="4"/>
       <c r="E3852" s="1" t="s">
+        <v>7632</v>
+      </c>
+      <c r="F3852" s="8" t="s">
         <v>7633</v>
-      </c>
-      <c r="F3852" s="8" t="s">
-        <v>7634</v>
       </c>
     </row>
     <row r="3853" spans="3:6">
       <c r="C3853" s="3">
-        <v>300007</v>
+        <v>203736</v>
       </c>
       <c r="D3853" s="4"/>
       <c r="E3853" s="1" t="s">
-        <v>7635</v>
+        <v>2012</v>
       </c>
       <c r="F3853" s="8" t="s">
-        <v>7636</v>
+        <v>7634</v>
       </c>
     </row>
     <row r="3854" spans="3:6">
       <c r="C3854" s="3">
-        <v>300008</v>
-      </c>
-      <c r="D3854" s="4"/>
+        <v>300001</v>
+      </c>
+      <c r="D3854" s="4" t="s">
+        <v>1961</v>
+      </c>
       <c r="E3854" s="1" t="s">
-        <v>7637</v>
+        <v>7635</v>
       </c>
       <c r="F3854" s="8" t="s">
-        <v>7638</v>
+        <v>7636</v>
       </c>
     </row>
     <row r="3855" spans="3:6">
       <c r="C3855" s="3">
-        <v>300009</v>
+        <v>300002</v>
       </c>
       <c r="D3855" s="4"/>
       <c r="E3855" s="1" t="s">
-        <v>7639</v>
+        <v>7637</v>
       </c>
       <c r="F3855" s="8" t="s">
-        <v>7640</v>
+        <v>7638</v>
       </c>
     </row>
     <row r="3856" spans="3:6">
       <c r="C3856" s="3">
-        <v>300010</v>
+        <v>300003</v>
       </c>
       <c r="D3856" s="4"/>
       <c r="E3856" s="1" t="s">
-        <v>7641</v>
+        <v>7639</v>
       </c>
       <c r="F3856" s="8" t="s">
-        <v>7642</v>
+        <v>7640</v>
       </c>
     </row>
     <row r="3857" spans="3:6">
       <c r="C3857" s="3">
-        <v>300011</v>
+        <v>300004</v>
       </c>
       <c r="D3857" s="4"/>
       <c r="E3857" s="1" t="s">
-        <v>7643</v>
+        <v>7641</v>
       </c>
       <c r="F3857" s="8" t="s">
-        <v>7644</v>
+        <v>7642</v>
       </c>
     </row>
     <row r="3858" spans="3:6">
       <c r="C3858" s="3">
-        <v>300012</v>
+        <v>300005</v>
       </c>
       <c r="D3858" s="4"/>
       <c r="E3858" s="1" t="s">
-        <v>7645</v>
+        <v>7643</v>
       </c>
       <c r="F3858" s="8" t="s">
-        <v>7646</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="3859" spans="3:6">
       <c r="C3859" s="3">
-        <v>300013</v>
+        <v>300006</v>
       </c>
       <c r="D3859" s="4"/>
       <c r="E3859" s="1" t="s">
-        <v>7647</v>
+        <v>7645</v>
       </c>
       <c r="F3859" s="8" t="s">
-        <v>7648</v>
+        <v>7646</v>
       </c>
     </row>
     <row r="3860" spans="3:6">
       <c r="C3860" s="3">
-        <v>300014</v>
+        <v>300007</v>
       </c>
       <c r="D3860" s="4"/>
       <c r="E3860" s="1" t="s">
-        <v>7649</v>
+        <v>7647</v>
       </c>
       <c r="F3860" s="8" t="s">
-        <v>7650</v>
+        <v>7648</v>
       </c>
     </row>
     <row r="3861" spans="3:6">
       <c r="C3861" s="3">
-        <v>300015</v>
+        <v>300008</v>
       </c>
       <c r="D3861" s="4"/>
       <c r="E3861" s="1" t="s">
-        <v>7651</v>
+        <v>7649</v>
       </c>
       <c r="F3861" s="8" t="s">
-        <v>7652</v>
+        <v>7650</v>
       </c>
     </row>
     <row r="3862" spans="3:6">
       <c r="C3862" s="3">
-        <v>300016</v>
+        <v>300009</v>
       </c>
       <c r="D3862" s="4"/>
       <c r="E3862" s="1" t="s">
-        <v>7653</v>
+        <v>7651</v>
       </c>
       <c r="F3862" s="8" t="s">
-        <v>7654</v>
+        <v>7652</v>
       </c>
     </row>
     <row r="3863" spans="3:6">
       <c r="C3863" s="3">
-        <v>300017</v>
+        <v>300010</v>
       </c>
       <c r="D3863" s="4"/>
       <c r="E3863" s="1" t="s">
-        <v>7655</v>
+        <v>7653</v>
       </c>
       <c r="F3863" s="8" t="s">
-        <v>7656</v>
+        <v>7654</v>
       </c>
     </row>
     <row r="3864" spans="3:6">
       <c r="C3864" s="3">
-        <v>300018</v>
+        <v>300011</v>
       </c>
       <c r="D3864" s="4"/>
       <c r="E3864" s="1" t="s">
-        <v>7657</v>
+        <v>7655</v>
       </c>
       <c r="F3864" s="8" t="s">
-        <v>7658</v>
+        <v>7656</v>
       </c>
     </row>
     <row r="3865" spans="3:6">
       <c r="C3865" s="3">
-        <v>300019</v>
+        <v>300012</v>
       </c>
       <c r="D3865" s="4"/>
       <c r="E3865" s="1" t="s">
-        <v>7659</v>
+        <v>7657</v>
       </c>
       <c r="F3865" s="8" t="s">
-        <v>7660</v>
+        <v>7658</v>
       </c>
     </row>
     <row r="3866" spans="3:6">
       <c r="C3866" s="3">
-        <v>300020</v>
+        <v>300013</v>
       </c>
       <c r="D3866" s="4"/>
       <c r="E3866" s="1" t="s">
-        <v>7661</v>
+        <v>7659</v>
       </c>
       <c r="F3866" s="8" t="s">
-        <v>7662</v>
+        <v>7660</v>
       </c>
     </row>
     <row r="3867" spans="3:6">
       <c r="C3867" s="3">
-        <v>300021</v>
+        <v>300014</v>
       </c>
       <c r="D3867" s="4"/>
       <c r="E3867" s="1" t="s">
-        <v>7663</v>
+        <v>7661</v>
       </c>
       <c r="F3867" s="8" t="s">
-        <v>7664</v>
+        <v>7662</v>
       </c>
     </row>
     <row r="3868" spans="3:6">
       <c r="C3868" s="3">
-        <v>300022</v>
+        <v>300015</v>
       </c>
       <c r="D3868" s="4"/>
       <c r="E3868" s="1" t="s">
-        <v>4218</v>
+        <v>7663</v>
       </c>
       <c r="F3868" s="8" t="s">
-        <v>7665</v>
+        <v>7664</v>
       </c>
     </row>
     <row r="3869" spans="3:6">
       <c r="C3869" s="3">
-        <v>300023</v>
+        <v>300016</v>
       </c>
       <c r="D3869" s="4"/>
       <c r="E3869" s="1" t="s">
+        <v>7665</v>
+      </c>
+      <c r="F3869" s="8" t="s">
         <v>7666</v>
-      </c>
-      <c r="F3869" s="8" t="s">
-        <v>7667</v>
       </c>
     </row>
     <row r="3870" spans="3:6">
       <c r="C3870" s="3">
-        <v>300024</v>
+        <v>300017</v>
       </c>
       <c r="D3870" s="4"/>
       <c r="E3870" s="1" t="s">
+        <v>7667</v>
+      </c>
+      <c r="F3870" s="8" t="s">
         <v>7668</v>
-      </c>
-      <c r="F3870" s="8" t="s">
-        <v>7669</v>
       </c>
     </row>
     <row r="3871" spans="3:6">
       <c r="C3871" s="3">
-        <v>300025</v>
+        <v>300018</v>
       </c>
       <c r="D3871" s="4"/>
       <c r="E3871" s="1" t="s">
+        <v>7669</v>
+      </c>
+      <c r="F3871" s="8" t="s">
         <v>7670</v>
-      </c>
-      <c r="F3871" s="8" t="s">
-        <v>7671</v>
       </c>
     </row>
     <row r="3872" spans="3:6">
       <c r="C3872" s="3">
-        <v>300026</v>
+        <v>300019</v>
       </c>
       <c r="D3872" s="4"/>
       <c r="E3872" s="1" t="s">
+        <v>7671</v>
+      </c>
+      <c r="F3872" s="8" t="s">
         <v>7672</v>
-      </c>
-      <c r="F3872" s="8" t="s">
-        <v>7673</v>
       </c>
     </row>
     <row r="3873" spans="3:6">
       <c r="C3873" s="3">
-        <v>300027</v>
+        <v>300020</v>
       </c>
       <c r="D3873" s="4"/>
       <c r="E3873" s="1" t="s">
+        <v>7673</v>
+      </c>
+      <c r="F3873" s="8" t="s">
         <v>7674</v>
-      </c>
-      <c r="F3873" s="8" t="s">
-        <v>7675</v>
       </c>
     </row>
     <row r="3874" spans="3:6">
       <c r="C3874" s="3">
-        <v>300028</v>
+        <v>300021</v>
       </c>
       <c r="D3874" s="4"/>
       <c r="E3874" s="1" t="s">
+        <v>7675</v>
+      </c>
+      <c r="F3874" s="8" t="s">
         <v>7676</v>
-      </c>
-      <c r="F3874" s="8" t="s">
-        <v>7677</v>
       </c>
     </row>
     <row r="3875" spans="3:6">
       <c r="C3875" s="3">
-        <v>300029</v>
+        <v>300022</v>
       </c>
       <c r="D3875" s="4"/>
       <c r="E3875" s="1" t="s">
-        <v>7678</v>
+        <v>4218</v>
       </c>
       <c r="F3875" s="8" t="s">
-        <v>7679</v>
+        <v>7677</v>
       </c>
     </row>
     <row r="3876" spans="3:6">
       <c r="C3876" s="3">
-        <v>300030</v>
+        <v>300023</v>
       </c>
       <c r="D3876" s="4"/>
       <c r="E3876" s="1" t="s">
-        <v>7680</v>
+        <v>7678</v>
       </c>
       <c r="F3876" s="8" t="s">
-        <v>7681</v>
+        <v>7679</v>
       </c>
     </row>
     <row r="3877" spans="3:6">
       <c r="C3877" s="3">
-        <v>300031</v>
+        <v>300024</v>
       </c>
       <c r="D3877" s="4"/>
       <c r="E3877" s="1" t="s">
-        <v>7682</v>
+        <v>7680</v>
       </c>
       <c r="F3877" s="8" t="s">
-        <v>7683</v>
+        <v>7681</v>
       </c>
     </row>
     <row r="3878" spans="3:6">
       <c r="C3878" s="3">
-        <v>300032</v>
+        <v>300025</v>
       </c>
       <c r="D3878" s="4"/>
       <c r="E3878" s="1" t="s">
-        <v>7684</v>
+        <v>7682</v>
       </c>
       <c r="F3878" s="8" t="s">
-        <v>7685</v>
+        <v>7683</v>
       </c>
     </row>
     <row r="3879" spans="3:6">
       <c r="C3879" s="3">
-        <v>300033</v>
+        <v>300026</v>
       </c>
       <c r="D3879" s="4"/>
       <c r="E3879" s="1" t="s">
-        <v>7686</v>
+        <v>7684</v>
       </c>
       <c r="F3879" s="8" t="s">
-        <v>7687</v>
+        <v>7685</v>
       </c>
     </row>
     <row r="3880" spans="3:6">
       <c r="C3880" s="3">
-        <v>300034</v>
+        <v>300027</v>
       </c>
       <c r="D3880" s="4"/>
       <c r="E3880" s="1" t="s">
-        <v>7688</v>
+        <v>7686</v>
       </c>
       <c r="F3880" s="8" t="s">
-        <v>7689</v>
+        <v>7687</v>
       </c>
     </row>
     <row r="3881" spans="3:6">
       <c r="C3881" s="3">
-        <v>300035</v>
+        <v>300028</v>
       </c>
       <c r="D3881" s="4"/>
       <c r="E3881" s="1" t="s">
-        <v>7690</v>
+        <v>7688</v>
       </c>
       <c r="F3881" s="8" t="s">
-        <v>7691</v>
+        <v>7689</v>
       </c>
     </row>
     <row r="3882" spans="3:6">
       <c r="C3882" s="3">
-        <v>300036</v>
+        <v>300029</v>
       </c>
       <c r="D3882" s="4"/>
       <c r="E3882" s="1" t="s">
-        <v>7692</v>
+        <v>7690</v>
       </c>
       <c r="F3882" s="8" t="s">
-        <v>7693</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="3883" spans="3:6">
       <c r="C3883" s="3">
-        <v>300037</v>
+        <v>300030</v>
       </c>
       <c r="D3883" s="4"/>
       <c r="E3883" s="1" t="s">
-        <v>5913</v>
+        <v>7692</v>
       </c>
       <c r="F3883" s="8" t="s">
-        <v>7694</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="3884" spans="3:6">
       <c r="C3884" s="3">
-        <v>300038</v>
+        <v>300031</v>
       </c>
       <c r="D3884" s="4"/>
       <c r="E3884" s="1" t="s">
-        <v>4274</v>
+        <v>7694</v>
       </c>
       <c r="F3884" s="8" t="s">
         <v>7695</v>
@@ -71881,7 +71917,7 @@
     </row>
     <row r="3885" spans="3:6">
       <c r="C3885" s="3">
-        <v>300039</v>
+        <v>300032</v>
       </c>
       <c r="D3885" s="4"/>
       <c r="E3885" s="1" t="s">
@@ -71893,7 +71929,7 @@
     </row>
     <row r="3886" spans="3:6">
       <c r="C3886" s="3">
-        <v>300040</v>
+        <v>300033</v>
       </c>
       <c r="D3886" s="4"/>
       <c r="E3886" s="1" t="s">
@@ -71905,7 +71941,7 @@
     </row>
     <row r="3887" spans="3:6">
       <c r="C3887" s="3">
-        <v>300041</v>
+        <v>300034</v>
       </c>
       <c r="D3887" s="4"/>
       <c r="E3887" s="1" t="s">
@@ -71917,905 +71953,911 @@
     </row>
     <row r="3888" spans="3:6">
       <c r="C3888" s="3">
-        <v>300042</v>
+        <v>300035</v>
       </c>
       <c r="D3888" s="4"/>
       <c r="E3888" s="1" t="s">
-        <v>1222</v>
+        <v>7702</v>
       </c>
       <c r="F3888" s="8" t="s">
-        <v>1041</v>
+        <v>7703</v>
       </c>
     </row>
     <row r="3889" spans="3:6">
       <c r="C3889" s="3">
-        <v>300043</v>
+        <v>300036</v>
       </c>
       <c r="D3889" s="4"/>
       <c r="E3889" s="1" t="s">
-        <v>7702</v>
+        <v>7704</v>
       </c>
       <c r="F3889" s="8" t="s">
-        <v>7703</v>
+        <v>7705</v>
       </c>
     </row>
     <row r="3890" spans="3:6">
       <c r="C3890" s="3">
-        <v>300044</v>
+        <v>300037</v>
       </c>
       <c r="D3890" s="4"/>
       <c r="E3890" s="1" t="s">
-        <v>4721</v>
+        <v>5913</v>
       </c>
       <c r="F3890" s="8" t="s">
-        <v>7704</v>
+        <v>7706</v>
       </c>
     </row>
     <row r="3891" spans="3:6">
       <c r="C3891" s="3">
-        <v>300045</v>
-      </c>
-      <c r="D3891"/>
+        <v>300038</v>
+      </c>
+      <c r="D3891" s="4"/>
       <c r="E3891" s="1" t="s">
-        <v>7705</v>
-      </c>
-      <c r="F3891" t="s">
-        <v>7706</v>
+        <v>4274</v>
+      </c>
+      <c r="F3891" s="8" t="s">
+        <v>7707</v>
       </c>
     </row>
     <row r="3892" spans="3:6">
       <c r="C3892" s="3">
-        <v>300046</v>
-      </c>
-      <c r="D3892"/>
-      <c r="E3892" t="s">
-        <v>7707</v>
-      </c>
-      <c r="F3892" t="s">
+        <v>300039</v>
+      </c>
+      <c r="D3892" s="4"/>
+      <c r="E3892" s="1" t="s">
         <v>7708</v>
+      </c>
+      <c r="F3892" s="8" t="s">
+        <v>7709</v>
       </c>
     </row>
     <row r="3893" spans="3:6">
       <c r="C3893" s="3">
-        <v>300047</v>
+        <v>300040</v>
       </c>
       <c r="D3893" s="4"/>
       <c r="E3893" s="1" t="s">
-        <v>7709</v>
-      </c>
-      <c r="F3893" s="6" t="s">
         <v>7710</v>
+      </c>
+      <c r="F3893" s="8" t="s">
+        <v>7711</v>
       </c>
     </row>
     <row r="3894" spans="3:6">
       <c r="C3894" s="3">
-        <v>300048</v>
+        <v>300041</v>
       </c>
       <c r="D3894" s="4"/>
       <c r="E3894" s="1" t="s">
-        <v>7711</v>
-      </c>
-      <c r="F3894" s="6" t="s">
         <v>7712</v>
+      </c>
+      <c r="F3894" s="8" t="s">
+        <v>7713</v>
       </c>
     </row>
     <row r="3895" spans="3:6">
       <c r="C3895" s="3">
-        <v>300049</v>
+        <v>300042</v>
       </c>
       <c r="D3895" s="4"/>
       <c r="E3895" s="1" t="s">
-        <v>7713</v>
-      </c>
-      <c r="F3895" s="6" t="s">
-        <v>7714</v>
+        <v>1222</v>
+      </c>
+      <c r="F3895" s="8" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="3896" spans="3:6">
       <c r="C3896" s="3">
-        <v>300050</v>
+        <v>300043</v>
       </c>
       <c r="D3896" s="4"/>
       <c r="E3896" s="1" t="s">
+        <v>7714</v>
+      </c>
+      <c r="F3896" s="8" t="s">
         <v>7715</v>
-      </c>
-      <c r="F3896" s="6" t="s">
-        <v>7716</v>
       </c>
     </row>
     <row r="3897" spans="3:6">
       <c r="C3897" s="3">
-        <v>300051</v>
+        <v>300044</v>
       </c>
       <c r="D3897" s="4"/>
       <c r="E3897" s="1" t="s">
-        <v>7717</v>
-      </c>
-      <c r="F3897" s="6" t="s">
-        <v>7718</v>
+        <v>4721</v>
+      </c>
+      <c r="F3897" s="8" t="s">
+        <v>7716</v>
       </c>
     </row>
     <row r="3898" spans="3:6">
       <c r="C3898" s="3">
-        <v>300052</v>
-      </c>
-      <c r="D3898" s="4"/>
+        <v>300045</v>
+      </c>
+      <c r="D3898"/>
       <c r="E3898" s="1" t="s">
-        <v>7719</v>
-      </c>
-      <c r="F3898" s="6" t="s">
-        <v>7720</v>
+        <v>7717</v>
+      </c>
+      <c r="F3898" t="s">
+        <v>7718</v>
       </c>
     </row>
     <row r="3899" spans="3:6">
       <c r="C3899" s="3">
-        <v>300053</v>
-      </c>
-      <c r="D3899" s="4"/>
-      <c r="E3899" s="1" t="s">
-        <v>7721</v>
-      </c>
-      <c r="F3899" s="6" t="s">
-        <v>7722</v>
+        <v>300046</v>
+      </c>
+      <c r="D3899"/>
+      <c r="E3899" t="s">
+        <v>7719</v>
+      </c>
+      <c r="F3899" t="s">
+        <v>7720</v>
       </c>
     </row>
     <row r="3900" spans="3:6">
       <c r="C3900" s="3">
-        <v>300054</v>
+        <v>300047</v>
       </c>
       <c r="D3900" s="4"/>
       <c r="E3900" s="1" t="s">
-        <v>7723</v>
+        <v>7721</v>
       </c>
       <c r="F3900" s="6" t="s">
-        <v>7724</v>
+        <v>7722</v>
       </c>
     </row>
     <row r="3901" spans="3:6">
       <c r="C3901" s="3">
-        <v>300055</v>
+        <v>300048</v>
       </c>
       <c r="D3901" s="4"/>
       <c r="E3901" s="1" t="s">
-        <v>7725</v>
+        <v>7723</v>
       </c>
       <c r="F3901" s="6" t="s">
-        <v>7726</v>
+        <v>7724</v>
       </c>
     </row>
     <row r="3902" spans="3:6">
       <c r="C3902" s="3">
-        <v>300056</v>
+        <v>300049</v>
       </c>
       <c r="D3902" s="4"/>
       <c r="E3902" s="1" t="s">
-        <v>7727</v>
+        <v>7725</v>
       </c>
       <c r="F3902" s="6" t="s">
-        <v>7728</v>
+        <v>7726</v>
       </c>
     </row>
     <row r="3903" spans="3:6">
       <c r="C3903" s="3">
-        <v>300057</v>
+        <v>300050</v>
       </c>
       <c r="D3903" s="4"/>
       <c r="E3903" s="1" t="s">
-        <v>7729</v>
+        <v>7727</v>
       </c>
       <c r="F3903" s="6" t="s">
-        <v>7730</v>
+        <v>7728</v>
       </c>
     </row>
     <row r="3904" spans="3:6">
       <c r="C3904" s="3">
-        <v>300058</v>
+        <v>300051</v>
       </c>
       <c r="D3904" s="4"/>
       <c r="E3904" s="1" t="s">
-        <v>7731</v>
+        <v>7729</v>
       </c>
       <c r="F3904" s="6" t="s">
-        <v>7732</v>
+        <v>7730</v>
       </c>
     </row>
     <row r="3905" spans="3:6">
       <c r="C3905" s="3">
-        <v>300059</v>
+        <v>300052</v>
       </c>
       <c r="D3905" s="4"/>
       <c r="E3905" s="1" t="s">
-        <v>7733</v>
+        <v>7731</v>
       </c>
       <c r="F3905" s="6" t="s">
-        <v>7734</v>
+        <v>7732</v>
       </c>
     </row>
     <row r="3906" spans="3:6">
       <c r="C3906" s="3">
-        <v>300060</v>
+        <v>300053</v>
       </c>
       <c r="D3906" s="4"/>
       <c r="E3906" s="1" t="s">
-        <v>7735</v>
+        <v>7733</v>
       </c>
       <c r="F3906" s="6" t="s">
-        <v>7736</v>
+        <v>7734</v>
       </c>
     </row>
     <row r="3907" spans="3:6">
       <c r="C3907" s="3">
-        <v>300061</v>
+        <v>300054</v>
       </c>
       <c r="D3907" s="4"/>
       <c r="E3907" s="1" t="s">
-        <v>7737</v>
+        <v>7735</v>
       </c>
       <c r="F3907" s="6" t="s">
-        <v>7738</v>
+        <v>7736</v>
       </c>
     </row>
     <row r="3908" spans="3:6">
       <c r="C3908" s="3">
-        <v>300062</v>
+        <v>300055</v>
       </c>
       <c r="D3908" s="4"/>
       <c r="E3908" s="1" t="s">
-        <v>7739</v>
+        <v>7737</v>
       </c>
       <c r="F3908" s="6" t="s">
-        <v>7740</v>
+        <v>7738</v>
       </c>
     </row>
     <row r="3909" spans="3:6">
       <c r="C3909" s="3">
-        <v>300063</v>
+        <v>300056</v>
       </c>
       <c r="D3909" s="4"/>
       <c r="E3909" s="1" t="s">
-        <v>7741</v>
+        <v>7739</v>
       </c>
       <c r="F3909" s="6" t="s">
-        <v>7742</v>
+        <v>7740</v>
       </c>
     </row>
     <row r="3910" spans="3:6">
       <c r="C3910" s="3">
-        <v>300064</v>
+        <v>300057</v>
       </c>
       <c r="D3910" s="4"/>
       <c r="E3910" s="1" t="s">
-        <v>7743</v>
+        <v>7741</v>
       </c>
       <c r="F3910" s="6" t="s">
-        <v>7744</v>
+        <v>7742</v>
       </c>
     </row>
     <row r="3911" spans="3:6">
       <c r="C3911" s="3">
-        <v>300065</v>
+        <v>300058</v>
       </c>
       <c r="D3911" s="4"/>
       <c r="E3911" s="1" t="s">
-        <v>7745</v>
+        <v>7743</v>
       </c>
       <c r="F3911" s="6" t="s">
-        <v>7746</v>
+        <v>7744</v>
       </c>
     </row>
     <row r="3912" spans="3:6">
       <c r="C3912" s="3">
-        <v>300066</v>
+        <v>300059</v>
       </c>
       <c r="D3912" s="4"/>
       <c r="E3912" s="1" t="s">
-        <v>7747</v>
+        <v>7745</v>
       </c>
       <c r="F3912" s="6" t="s">
-        <v>7748</v>
+        <v>7746</v>
       </c>
     </row>
     <row r="3913" spans="3:6">
       <c r="C3913" s="3">
-        <v>300067</v>
+        <v>300060</v>
       </c>
       <c r="D3913" s="4"/>
       <c r="E3913" s="1" t="s">
-        <v>7749</v>
+        <v>7747</v>
       </c>
       <c r="F3913" s="6" t="s">
-        <v>7750</v>
+        <v>7748</v>
       </c>
     </row>
     <row r="3914" spans="3:6">
       <c r="C3914" s="3">
-        <v>300068</v>
+        <v>300061</v>
       </c>
       <c r="D3914" s="4"/>
       <c r="E3914" s="1" t="s">
-        <v>7751</v>
+        <v>7749</v>
       </c>
       <c r="F3914" s="6" t="s">
-        <v>7752</v>
+        <v>7750</v>
       </c>
     </row>
     <row r="3915" spans="3:6">
       <c r="C3915" s="3">
-        <v>300069</v>
+        <v>300062</v>
       </c>
       <c r="D3915" s="4"/>
       <c r="E3915" s="1" t="s">
-        <v>7753</v>
+        <v>7751</v>
       </c>
       <c r="F3915" s="6" t="s">
-        <v>7754</v>
+        <v>7752</v>
       </c>
     </row>
     <row r="3916" spans="3:6">
       <c r="C3916" s="3">
-        <v>300070</v>
+        <v>300063</v>
       </c>
       <c r="D3916" s="4"/>
       <c r="E3916" s="1" t="s">
-        <v>7755</v>
+        <v>7753</v>
       </c>
       <c r="F3916" s="6" t="s">
-        <v>7756</v>
+        <v>7754</v>
       </c>
     </row>
     <row r="3917" spans="3:6">
       <c r="C3917" s="3">
-        <v>300071</v>
+        <v>300064</v>
       </c>
       <c r="D3917" s="4"/>
       <c r="E3917" s="1" t="s">
-        <v>7757</v>
+        <v>7755</v>
       </c>
       <c r="F3917" s="6" t="s">
-        <v>7758</v>
+        <v>7756</v>
       </c>
     </row>
     <row r="3918" spans="3:6">
       <c r="C3918" s="3">
-        <v>300072</v>
+        <v>300065</v>
       </c>
       <c r="D3918" s="4"/>
       <c r="E3918" s="1" t="s">
-        <v>7759</v>
+        <v>7757</v>
       </c>
       <c r="F3918" s="6" t="s">
-        <v>7760</v>
+        <v>7758</v>
       </c>
     </row>
     <row r="3919" spans="3:6">
       <c r="C3919" s="3">
-        <v>300073</v>
+        <v>300066</v>
       </c>
       <c r="D3919" s="4"/>
       <c r="E3919" s="1" t="s">
-        <v>7761</v>
+        <v>7759</v>
       </c>
       <c r="F3919" s="6" t="s">
-        <v>7762</v>
+        <v>7760</v>
       </c>
     </row>
     <row r="3920" spans="3:6">
       <c r="C3920" s="3">
-        <v>300074</v>
+        <v>300067</v>
       </c>
       <c r="D3920" s="4"/>
       <c r="E3920" s="1" t="s">
-        <v>7763</v>
+        <v>7761</v>
       </c>
       <c r="F3920" s="6" t="s">
-        <v>7764</v>
+        <v>7762</v>
       </c>
     </row>
     <row r="3921" spans="3:6">
       <c r="C3921" s="3">
-        <v>300075</v>
+        <v>300068</v>
       </c>
       <c r="D3921" s="4"/>
       <c r="E3921" s="1" t="s">
-        <v>7765</v>
+        <v>7763</v>
       </c>
       <c r="F3921" s="6" t="s">
-        <v>7766</v>
+        <v>7764</v>
       </c>
     </row>
     <row r="3922" spans="3:6">
       <c r="C3922" s="3">
-        <v>300076</v>
+        <v>300069</v>
       </c>
       <c r="D3922" s="4"/>
       <c r="E3922" s="1" t="s">
-        <v>7767</v>
+        <v>7765</v>
       </c>
       <c r="F3922" s="6" t="s">
-        <v>7768</v>
+        <v>7766</v>
       </c>
     </row>
     <row r="3923" spans="3:6">
       <c r="C3923" s="3">
-        <v>300077</v>
+        <v>300070</v>
       </c>
       <c r="D3923" s="4"/>
       <c r="E3923" s="1" t="s">
-        <v>7769</v>
+        <v>7767</v>
       </c>
       <c r="F3923" s="6" t="s">
-        <v>7770</v>
+        <v>7768</v>
       </c>
     </row>
     <row r="3924" spans="3:6">
       <c r="C3924" s="3">
-        <v>300078</v>
+        <v>300071</v>
       </c>
       <c r="D3924" s="4"/>
       <c r="E3924" s="1" t="s">
-        <v>7771</v>
+        <v>7769</v>
       </c>
       <c r="F3924" s="6" t="s">
-        <v>7772</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="3925" spans="3:6">
       <c r="C3925" s="3">
-        <v>300079</v>
+        <v>300072</v>
       </c>
       <c r="D3925" s="4"/>
       <c r="E3925" s="1" t="s">
-        <v>7773</v>
+        <v>7771</v>
       </c>
       <c r="F3925" s="6" t="s">
-        <v>7774</v>
+        <v>7772</v>
       </c>
     </row>
     <row r="3926" spans="3:6">
       <c r="C3926" s="3">
-        <v>300080</v>
+        <v>300073</v>
       </c>
       <c r="D3926" s="4"/>
       <c r="E3926" s="1" t="s">
-        <v>7775</v>
+        <v>7773</v>
       </c>
       <c r="F3926" s="6" t="s">
-        <v>7776</v>
+        <v>7774</v>
       </c>
     </row>
     <row r="3927" spans="3:6">
       <c r="C3927" s="3">
-        <v>300081</v>
+        <v>300074</v>
       </c>
       <c r="D3927" s="4"/>
       <c r="E3927" s="1" t="s">
-        <v>7777</v>
+        <v>7775</v>
       </c>
       <c r="F3927" s="6" t="s">
-        <v>7778</v>
+        <v>7776</v>
       </c>
     </row>
     <row r="3928" spans="3:6">
       <c r="C3928" s="3">
-        <v>300082</v>
+        <v>300075</v>
       </c>
       <c r="D3928" s="4"/>
       <c r="E3928" s="1" t="s">
-        <v>7779</v>
+        <v>7777</v>
       </c>
       <c r="F3928" s="6" t="s">
-        <v>7780</v>
+        <v>7778</v>
       </c>
     </row>
     <row r="3929" spans="3:6">
       <c r="C3929" s="3">
-        <v>300083</v>
+        <v>300076</v>
       </c>
       <c r="D3929" s="4"/>
       <c r="E3929" s="1" t="s">
-        <v>7781</v>
+        <v>7779</v>
       </c>
       <c r="F3929" s="6" t="s">
-        <v>7782</v>
+        <v>7780</v>
       </c>
     </row>
     <row r="3930" spans="3:6">
       <c r="C3930" s="3">
-        <v>300084</v>
+        <v>300077</v>
       </c>
       <c r="D3930" s="4"/>
       <c r="E3930" s="1" t="s">
-        <v>7783</v>
+        <v>7781</v>
       </c>
       <c r="F3930" s="6" t="s">
-        <v>7784</v>
+        <v>7782</v>
       </c>
     </row>
     <row r="3931" spans="3:6">
       <c r="C3931" s="3">
-        <v>300085</v>
+        <v>300078</v>
       </c>
       <c r="D3931" s="4"/>
       <c r="E3931" s="1" t="s">
-        <v>7785</v>
+        <v>7783</v>
       </c>
       <c r="F3931" s="6" t="s">
-        <v>7786</v>
+        <v>7784</v>
       </c>
     </row>
     <row r="3932" spans="3:6">
       <c r="C3932" s="3">
-        <v>300086</v>
+        <v>300079</v>
       </c>
       <c r="D3932" s="4"/>
       <c r="E3932" s="1" t="s">
-        <v>7787</v>
+        <v>7785</v>
       </c>
       <c r="F3932" s="6" t="s">
-        <v>7788</v>
+        <v>7786</v>
       </c>
     </row>
     <row r="3933" spans="3:6">
       <c r="C3933" s="3">
-        <v>300087</v>
+        <v>300080</v>
       </c>
       <c r="D3933" s="4"/>
       <c r="E3933" s="1" t="s">
-        <v>7789</v>
+        <v>7787</v>
       </c>
       <c r="F3933" s="6" t="s">
-        <v>7790</v>
+        <v>7788</v>
       </c>
     </row>
     <row r="3934" spans="3:6">
       <c r="C3934" s="3">
-        <v>300088</v>
+        <v>300081</v>
       </c>
       <c r="D3934" s="4"/>
       <c r="E3934" s="1" t="s">
-        <v>7791</v>
+        <v>7789</v>
       </c>
       <c r="F3934" s="6" t="s">
-        <v>7792</v>
+        <v>7790</v>
       </c>
     </row>
     <row r="3935" spans="3:6">
       <c r="C3935" s="3">
-        <v>300089</v>
+        <v>300082</v>
       </c>
       <c r="D3935" s="4"/>
       <c r="E3935" s="1" t="s">
-        <v>7793</v>
+        <v>7791</v>
       </c>
       <c r="F3935" s="6" t="s">
-        <v>7794</v>
+        <v>7792</v>
       </c>
     </row>
     <row r="3936" spans="3:6">
       <c r="C3936" s="3">
-        <v>300090</v>
+        <v>300083</v>
       </c>
       <c r="D3936" s="4"/>
       <c r="E3936" s="1" t="s">
-        <v>7795</v>
+        <v>7793</v>
       </c>
       <c r="F3936" s="6" t="s">
-        <v>7796</v>
+        <v>7794</v>
       </c>
     </row>
     <row r="3937" spans="3:6">
       <c r="C3937" s="3">
-        <v>300091</v>
+        <v>300084</v>
       </c>
       <c r="D3937" s="4"/>
       <c r="E3937" s="1" t="s">
-        <v>7797</v>
+        <v>7795</v>
       </c>
       <c r="F3937" s="6" t="s">
-        <v>7798</v>
+        <v>7796</v>
       </c>
     </row>
     <row r="3938" spans="3:6">
       <c r="C3938" s="3">
-        <v>300092</v>
+        <v>300085</v>
       </c>
       <c r="D3938" s="4"/>
       <c r="E3938" s="1" t="s">
-        <v>7799</v>
+        <v>7797</v>
       </c>
       <c r="F3938" s="6" t="s">
-        <v>7800</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="3939" spans="3:6">
       <c r="C3939" s="3">
-        <v>300093</v>
+        <v>300086</v>
       </c>
       <c r="D3939" s="4"/>
       <c r="E3939" s="1" t="s">
-        <v>7801</v>
+        <v>7799</v>
       </c>
       <c r="F3939" s="6" t="s">
-        <v>7802</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="3940" spans="3:6">
       <c r="C3940" s="3">
-        <v>300094</v>
+        <v>300087</v>
       </c>
       <c r="D3940" s="4"/>
       <c r="E3940" s="1" t="s">
-        <v>7803</v>
+        <v>7801</v>
       </c>
       <c r="F3940" s="6" t="s">
-        <v>7804</v>
+        <v>7802</v>
       </c>
     </row>
     <row r="3941" spans="3:6">
       <c r="C3941" s="3">
-        <v>300095</v>
+        <v>300088</v>
       </c>
       <c r="D3941" s="4"/>
       <c r="E3941" s="1" t="s">
-        <v>7805</v>
+        <v>7803</v>
       </c>
       <c r="F3941" s="6" t="s">
-        <v>7806</v>
+        <v>7804</v>
       </c>
     </row>
     <row r="3942" spans="3:6">
       <c r="C3942" s="3">
-        <v>300096</v>
+        <v>300089</v>
       </c>
       <c r="D3942" s="4"/>
       <c r="E3942" s="1" t="s">
-        <v>7807</v>
+        <v>7805</v>
       </c>
       <c r="F3942" s="6" t="s">
-        <v>7808</v>
+        <v>7806</v>
       </c>
     </row>
     <row r="3943" spans="3:6">
       <c r="C3943" s="3">
-        <v>300097</v>
+        <v>300090</v>
       </c>
       <c r="D3943" s="4"/>
       <c r="E3943" s="1" t="s">
-        <v>7809</v>
+        <v>7807</v>
       </c>
       <c r="F3943" s="6" t="s">
-        <v>7810</v>
+        <v>7808</v>
       </c>
     </row>
     <row r="3944" spans="3:6">
       <c r="C3944" s="3">
-        <v>300098</v>
+        <v>300091</v>
       </c>
       <c r="D3944" s="4"/>
       <c r="E3944" s="1" t="s">
-        <v>7811</v>
+        <v>7809</v>
       </c>
       <c r="F3944" s="6" t="s">
-        <v>7812</v>
+        <v>7810</v>
       </c>
     </row>
     <row r="3945" spans="3:6">
       <c r="C3945" s="3">
-        <v>300099</v>
+        <v>300092</v>
       </c>
       <c r="D3945" s="4"/>
       <c r="E3945" s="1" t="s">
-        <v>7813</v>
+        <v>7811</v>
       </c>
       <c r="F3945" s="6" t="s">
-        <v>7814</v>
+        <v>7812</v>
       </c>
     </row>
     <row r="3946" spans="3:6">
       <c r="C3946" s="3">
-        <v>300100</v>
+        <v>300093</v>
       </c>
       <c r="D3946" s="4"/>
       <c r="E3946" s="1" t="s">
-        <v>7815</v>
+        <v>7813</v>
       </c>
       <c r="F3946" s="6" t="s">
-        <v>7816</v>
+        <v>7814</v>
       </c>
     </row>
     <row r="3947" spans="3:6">
       <c r="C3947" s="3">
-        <v>300101</v>
+        <v>300094</v>
       </c>
       <c r="D3947" s="4"/>
       <c r="E3947" s="1" t="s">
-        <v>7817</v>
+        <v>7815</v>
       </c>
       <c r="F3947" s="6" t="s">
-        <v>7818</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="3948" spans="3:6">
       <c r="C3948" s="3">
-        <v>300102</v>
+        <v>300095</v>
       </c>
       <c r="D3948" s="4"/>
       <c r="E3948" s="1" t="s">
-        <v>7819</v>
+        <v>7817</v>
       </c>
       <c r="F3948" s="6" t="s">
-        <v>7820</v>
+        <v>7818</v>
       </c>
     </row>
     <row r="3949" spans="3:6">
       <c r="C3949" s="3">
-        <v>300103</v>
+        <v>300096</v>
       </c>
       <c r="D3949" s="4"/>
       <c r="E3949" s="1" t="s">
-        <v>7821</v>
+        <v>7819</v>
       </c>
       <c r="F3949" s="6" t="s">
-        <v>7822</v>
+        <v>7820</v>
       </c>
     </row>
     <row r="3950" spans="3:6">
       <c r="C3950" s="3">
-        <v>300104</v>
+        <v>300097</v>
       </c>
       <c r="D3950" s="4"/>
       <c r="E3950" s="1" t="s">
-        <v>7823</v>
+        <v>7821</v>
       </c>
       <c r="F3950" s="6" t="s">
-        <v>7824</v>
+        <v>7822</v>
       </c>
     </row>
     <row r="3951" spans="3:6">
       <c r="C3951" s="3">
-        <v>300105</v>
+        <v>300098</v>
       </c>
       <c r="D3951" s="4"/>
       <c r="E3951" s="1" t="s">
-        <v>7825</v>
+        <v>7823</v>
       </c>
       <c r="F3951" s="6" t="s">
-        <v>7826</v>
+        <v>7824</v>
       </c>
     </row>
     <row r="3952" spans="3:6">
       <c r="C3952" s="3">
-        <v>300106</v>
+        <v>300099</v>
       </c>
       <c r="D3952" s="4"/>
       <c r="E3952" s="1" t="s">
-        <v>7827</v>
+        <v>7825</v>
       </c>
       <c r="F3952" s="6" t="s">
-        <v>7828</v>
+        <v>7826</v>
       </c>
     </row>
     <row r="3953" spans="3:6">
       <c r="C3953" s="3">
-        <v>300107</v>
+        <v>300100</v>
       </c>
       <c r="D3953" s="4"/>
       <c r="E3953" s="1" t="s">
-        <v>7829</v>
+        <v>7827</v>
       </c>
       <c r="F3953" s="6" t="s">
-        <v>7830</v>
+        <v>7828</v>
       </c>
     </row>
     <row r="3954" spans="3:6">
       <c r="C3954" s="3">
-        <v>300108</v>
+        <v>300101</v>
       </c>
       <c r="D3954" s="4"/>
       <c r="E3954" s="1" t="s">
-        <v>7831</v>
+        <v>7829</v>
       </c>
       <c r="F3954" s="6" t="s">
-        <v>7832</v>
+        <v>7830</v>
       </c>
     </row>
     <row r="3955" spans="3:6">
       <c r="C3955" s="3">
-        <v>300109</v>
+        <v>300102</v>
       </c>
       <c r="D3955" s="4"/>
       <c r="E3955" s="1" t="s">
-        <v>7833</v>
+        <v>7831</v>
       </c>
       <c r="F3955" s="6" t="s">
-        <v>7834</v>
+        <v>7832</v>
       </c>
     </row>
     <row r="3956" spans="3:6">
       <c r="C3956" s="3">
-        <v>300110</v>
-      </c>
-      <c r="D3956"/>
+        <v>300103</v>
+      </c>
+      <c r="D3956" s="4"/>
       <c r="E3956" s="1" t="s">
-        <v>7835</v>
-      </c>
-      <c r="F3956" s="1" t="s">
-        <v>7836</v>
+        <v>7833</v>
+      </c>
+      <c r="F3956" s="6" t="s">
+        <v>7834</v>
       </c>
     </row>
     <row r="3957" spans="3:6">
       <c r="C3957" s="3">
-        <v>300111</v>
-      </c>
-      <c r="D3957"/>
+        <v>300104</v>
+      </c>
+      <c r="D3957" s="4"/>
       <c r="E3957" s="1" t="s">
-        <v>7837</v>
-      </c>
-      <c r="F3957" s="1" t="s">
-        <v>7838</v>
+        <v>7835</v>
+      </c>
+      <c r="F3957" s="6" t="s">
+        <v>7836</v>
       </c>
     </row>
     <row r="3958" spans="3:6">
       <c r="C3958" s="3">
-        <v>300112</v>
-      </c>
+        <v>300105</v>
+      </c>
+      <c r="D3958" s="4"/>
       <c r="E3958" s="1" t="s">
-        <v>7839</v>
-      </c>
-      <c r="F3958" s="1" t="s">
-        <v>7840</v>
+        <v>7837</v>
+      </c>
+      <c r="F3958" s="6" t="s">
+        <v>7838</v>
       </c>
     </row>
     <row r="3959" spans="3:6">
       <c r="C3959" s="3">
-        <v>300113</v>
-      </c>
+        <v>300106</v>
+      </c>
+      <c r="D3959" s="4"/>
       <c r="E3959" s="1" t="s">
-        <v>7841</v>
-      </c>
-      <c r="F3959" s="1" t="s">
-        <v>7842</v>
+        <v>7839</v>
+      </c>
+      <c r="F3959" s="6" t="s">
+        <v>7840</v>
       </c>
     </row>
     <row r="3960" spans="3:6">
       <c r="C3960" s="3">
-        <v>300114</v>
-      </c>
+        <v>300107</v>
+      </c>
+      <c r="D3960" s="4"/>
       <c r="E3960" s="1" t="s">
-        <v>7843</v>
-      </c>
-      <c r="F3960" s="1" t="s">
-        <v>7844</v>
+        <v>7841</v>
+      </c>
+      <c r="F3960" s="6" t="s">
+        <v>7842</v>
       </c>
     </row>
     <row r="3961" spans="3:6">
       <c r="C3961" s="3">
-        <v>300115</v>
-      </c>
+        <v>300108</v>
+      </c>
+      <c r="D3961" s="4"/>
       <c r="E3961" s="1" t="s">
-        <v>7845</v>
-      </c>
-      <c r="F3961" s="1" t="s">
-        <v>7846</v>
+        <v>7843</v>
+      </c>
+      <c r="F3961" s="6" t="s">
+        <v>7844</v>
       </c>
     </row>
     <row r="3962" spans="3:6">
       <c r="C3962" s="3">
-        <v>300116</v>
-      </c>
+        <v>300109</v>
+      </c>
+      <c r="D3962" s="4"/>
       <c r="E3962" s="1" t="s">
-        <v>7847</v>
-      </c>
-      <c r="F3962" s="1" t="s">
-        <v>1734</v>
+        <v>7845</v>
+      </c>
+      <c r="F3962" s="6" t="s">
+        <v>7846</v>
       </c>
     </row>
     <row r="3963" spans="3:6">
       <c r="C3963" s="3">
-        <v>300117</v>
-      </c>
+        <v>300110</v>
+      </c>
+      <c r="D3963"/>
       <c r="E3963" s="1" t="s">
-        <v>3182</v>
+        <v>7847</v>
       </c>
       <c r="F3963" s="1" t="s">
         <v>7848</v>
@@ -72823,8 +72865,9 @@
     </row>
     <row r="3964" spans="3:6">
       <c r="C3964" s="3">
-        <v>300118</v>
-      </c>
+        <v>300111</v>
+      </c>
+      <c r="D3964"/>
       <c r="E3964" s="1" t="s">
         <v>7849</v>
       </c>
@@ -72834,7 +72877,7 @@
     </row>
     <row r="3965" spans="3:6">
       <c r="C3965" s="3">
-        <v>300119</v>
+        <v>300112</v>
       </c>
       <c r="E3965" s="1" t="s">
         <v>7851</v>
@@ -72845,7 +72888,7 @@
     </row>
     <row r="3966" spans="3:6">
       <c r="C3966" s="3">
-        <v>300120</v>
+        <v>300113</v>
       </c>
       <c r="E3966" s="1" t="s">
         <v>7853</v>
@@ -72856,7 +72899,7 @@
     </row>
     <row r="3967" spans="3:6">
       <c r="C3967" s="3">
-        <v>300121</v>
+        <v>300114</v>
       </c>
       <c r="E3967" s="1" t="s">
         <v>7855</v>
@@ -72867,7 +72910,7 @@
     </row>
     <row r="3968" spans="3:6">
       <c r="C3968" s="3">
-        <v>300122</v>
+        <v>300115</v>
       </c>
       <c r="E3968" s="1" t="s">
         <v>7857</v>
@@ -72876,601 +72919,601 @@
         <v>7858</v>
       </c>
     </row>
-    <row r="3969" spans="2:6">
+    <row r="3969" spans="3:6">
       <c r="C3969" s="3">
-        <v>300123</v>
+        <v>300116</v>
       </c>
       <c r="E3969" s="1" t="s">
         <v>7859</v>
       </c>
       <c r="F3969" s="1" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="3970" spans="3:6">
+      <c r="C3970" s="3">
+        <v>300117</v>
+      </c>
+      <c r="E3970" s="1" t="s">
+        <v>3182</v>
+      </c>
+      <c r="F3970" s="1" t="s">
+        <v>7860</v>
+      </c>
+    </row>
+    <row r="3971" spans="3:6">
+      <c r="C3971" s="3">
+        <v>300118</v>
+      </c>
+      <c r="E3971" s="1" t="s">
+        <v>7861</v>
+      </c>
+      <c r="F3971" s="1" t="s">
+        <v>7862</v>
+      </c>
+    </row>
+    <row r="3972" spans="3:6">
+      <c r="C3972" s="3">
+        <v>300119</v>
+      </c>
+      <c r="E3972" s="1" t="s">
+        <v>7863</v>
+      </c>
+      <c r="F3972" s="1" t="s">
+        <v>7864</v>
+      </c>
+    </row>
+    <row r="3973" spans="3:6">
+      <c r="C3973" s="3">
+        <v>300120</v>
+      </c>
+      <c r="E3973" s="1" t="s">
+        <v>7865</v>
+      </c>
+      <c r="F3973" s="1" t="s">
+        <v>7866</v>
+      </c>
+    </row>
+    <row r="3974" spans="3:6">
+      <c r="C3974" s="3">
+        <v>300121</v>
+      </c>
+      <c r="E3974" s="1" t="s">
+        <v>7867</v>
+      </c>
+      <c r="F3974" s="1" t="s">
+        <v>7868</v>
+      </c>
+    </row>
+    <row r="3975" spans="3:6">
+      <c r="C3975" s="3">
+        <v>300122</v>
+      </c>
+      <c r="E3975" s="1" t="s">
+        <v>7869</v>
+      </c>
+      <c r="F3975" s="1" t="s">
+        <v>7870</v>
+      </c>
+    </row>
+    <row r="3976" spans="3:6">
+      <c r="C3976" s="3">
+        <v>300123</v>
+      </c>
+      <c r="E3976" s="1" t="s">
+        <v>7871</v>
+      </c>
+      <c r="F3976" s="1" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="3970" spans="2:6">
-      <c r="C3970" s="3">
+    <row r="3977" spans="3:6">
+      <c r="C3977" s="3">
         <v>300124</v>
       </c>
-      <c r="E3970" s="1" t="s">
-        <v>7860</v>
-      </c>
-      <c r="F3970" s="1" t="s">
-        <v>7861</v>
-      </c>
-    </row>
-    <row r="3971" spans="2:6">
-      <c r="C3971" s="3">
+      <c r="E3977" s="1" t="s">
+        <v>7872</v>
+      </c>
+      <c r="F3977" s="1" t="s">
+        <v>7873</v>
+      </c>
+    </row>
+    <row r="3978" spans="3:6">
+      <c r="C3978" s="3">
         <v>300125</v>
       </c>
-      <c r="E3971" s="1" t="s">
-        <v>7862</v>
-      </c>
-      <c r="F3971" s="1" t="s">
-        <v>7863</v>
-      </c>
-    </row>
-    <row r="3972" spans="2:6">
-      <c r="C3972" s="3">
+      <c r="E3978" s="1" t="s">
+        <v>7874</v>
+      </c>
+      <c r="F3978" s="1" t="s">
+        <v>7875</v>
+      </c>
+    </row>
+    <row r="3979" spans="3:6">
+      <c r="C3979" s="3">
         <v>300126</v>
       </c>
-      <c r="E3972" s="1" t="s">
-        <v>7864</v>
-      </c>
-      <c r="F3972" s="1" t="s">
-        <v>7865</v>
-      </c>
-    </row>
-    <row r="3973" spans="2:6">
-      <c r="C3973" s="3">
+      <c r="E3979" s="1" t="s">
+        <v>7876</v>
+      </c>
+      <c r="F3979" s="1" t="s">
+        <v>7877</v>
+      </c>
+    </row>
+    <row r="3980" spans="3:6">
+      <c r="C3980" s="3">
         <v>300127</v>
       </c>
-      <c r="E3973" s="1" t="s">
-        <v>7866</v>
-      </c>
-      <c r="F3973" s="1" t="s">
-        <v>7867</v>
-      </c>
-    </row>
-    <row r="3974" spans="2:6">
-      <c r="C3974" s="3">
+      <c r="E3980" s="1" t="s">
+        <v>7878</v>
+      </c>
+      <c r="F3980" s="1" t="s">
+        <v>7879</v>
+      </c>
+    </row>
+    <row r="3981" spans="3:6">
+      <c r="C3981" s="3">
         <v>300128</v>
       </c>
-      <c r="E3974" s="1" t="s">
-        <v>7868</v>
-      </c>
-      <c r="F3974" s="1" t="s">
-        <v>7869</v>
-      </c>
-    </row>
-    <row r="3975" spans="2:6">
-      <c r="C3975" s="3">
+      <c r="E3981" s="1" t="s">
+        <v>7880</v>
+      </c>
+      <c r="F3981" s="1" t="s">
+        <v>7881</v>
+      </c>
+    </row>
+    <row r="3982" spans="3:6">
+      <c r="C3982" s="3">
         <v>300129</v>
       </c>
-      <c r="E3975" s="1" t="s">
-        <v>7870</v>
-      </c>
-      <c r="F3975" s="1" t="s">
-        <v>7871</v>
-      </c>
-    </row>
-    <row r="3976" spans="2:6">
-      <c r="C3976" s="3">
+      <c r="E3982" s="1" t="s">
+        <v>7882</v>
+      </c>
+      <c r="F3982" s="1" t="s">
+        <v>7883</v>
+      </c>
+    </row>
+    <row r="3983" spans="3:6">
+      <c r="C3983" s="3">
         <v>300130</v>
       </c>
-      <c r="E3976" s="1" t="s">
-        <v>7872</v>
-      </c>
-      <c r="F3976" s="1" t="s">
-        <v>7873</v>
-      </c>
-    </row>
-    <row r="3977" spans="2:6">
-      <c r="C3977" s="3">
+      <c r="E3983" s="1" t="s">
+        <v>7884</v>
+      </c>
+      <c r="F3983" s="1" t="s">
+        <v>7885</v>
+      </c>
+    </row>
+    <row r="3984" spans="3:6">
+      <c r="C3984" s="3">
         <v>300131</v>
       </c>
-      <c r="E3977" s="1" t="s">
-        <v>7874</v>
-      </c>
-      <c r="F3977" s="1" t="s">
-        <v>7875</v>
-      </c>
-    </row>
-    <row r="3978" spans="2:6">
-      <c r="C3978" s="3">
+      <c r="E3984" s="1" t="s">
+        <v>7886</v>
+      </c>
+      <c r="F3984" s="1" t="s">
+        <v>7887</v>
+      </c>
+    </row>
+    <row r="3985" spans="2:6">
+      <c r="C3985" s="3">
         <v>300132</v>
       </c>
-      <c r="E3978" s="1" t="s">
-        <v>7876</v>
-      </c>
-      <c r="F3978" s="1" t="s">
-        <v>7877</v>
-      </c>
-    </row>
-    <row r="3979" spans="2:6">
-      <c r="C3979" s="3">
+      <c r="E3985" s="1" t="s">
+        <v>7888</v>
+      </c>
+      <c r="F3985" s="1" t="s">
+        <v>7889</v>
+      </c>
+    </row>
+    <row r="3986" spans="2:6">
+      <c r="C3986" s="3">
         <v>300133</v>
       </c>
-      <c r="E3979" s="1" t="s">
-        <v>7878</v>
-      </c>
-      <c r="F3979" s="1" t="s">
-        <v>7879</v>
-      </c>
-    </row>
-    <row r="3980" spans="2:6">
-      <c r="C3980" s="3">
+      <c r="E3986" s="1" t="s">
+        <v>7890</v>
+      </c>
+      <c r="F3986" s="1" t="s">
+        <v>7891</v>
+      </c>
+    </row>
+    <row r="3987" spans="2:6">
+      <c r="C3987" s="3">
         <v>300134</v>
       </c>
-      <c r="E3980" s="1" t="s">
-        <v>7880</v>
-      </c>
-      <c r="F3980" s="1" t="s">
-        <v>7881</v>
-      </c>
-    </row>
-    <row r="3981" spans="2:6">
-      <c r="C3981" s="3">
+      <c r="E3987" s="1" t="s">
+        <v>7892</v>
+      </c>
+      <c r="F3987" s="1" t="s">
+        <v>7893</v>
+      </c>
+    </row>
+    <row r="3988" spans="2:6">
+      <c r="C3988" s="3">
         <v>300135</v>
       </c>
-      <c r="E3981" s="1" t="s">
-        <v>7882</v>
-      </c>
-      <c r="F3981" s="1" t="s">
-        <v>7883</v>
-      </c>
-    </row>
-    <row r="3982" spans="2:6">
-      <c r="B3982" s="3"/>
-      <c r="C3982" s="3">
-        <v>300136</v>
-      </c>
-      <c r="E3982" s="1" t="s">
-        <v>7884</v>
-      </c>
-      <c r="F3982" s="1" t="s">
-        <v>7885</v>
-      </c>
-    </row>
-    <row r="3983" spans="2:6">
-      <c r="B3983" s="3"/>
-      <c r="C3983" s="3">
-        <v>300137</v>
-      </c>
-      <c r="E3983" s="1" t="s">
-        <v>7886</v>
-      </c>
-      <c r="F3983" s="1" t="s">
-        <v>7887</v>
-      </c>
-    </row>
-    <row r="3984" spans="2:6">
-      <c r="B3984" s="3"/>
-      <c r="C3984" s="3">
-        <v>300138</v>
-      </c>
-      <c r="E3984" s="1" t="s">
-        <v>7888</v>
-      </c>
-      <c r="F3984" s="1" t="s">
-        <v>7889</v>
-      </c>
-    </row>
-    <row r="3985" spans="2:6">
-      <c r="B3985" s="3"/>
-      <c r="C3985" s="3">
-        <v>300139</v>
-      </c>
-      <c r="E3985" s="1" t="s">
-        <v>7890</v>
-      </c>
-      <c r="F3985" s="1" t="s">
-        <v>7891</v>
-      </c>
-    </row>
-    <row r="3986" spans="2:6">
-      <c r="B3986" s="3"/>
-      <c r="C3986" s="3">
-        <v>300140</v>
-      </c>
-      <c r="E3986" s="1" t="s">
-        <v>7892</v>
-      </c>
-      <c r="F3986" s="1" t="s">
-        <v>7893</v>
-      </c>
-    </row>
-    <row r="3987" spans="2:6">
-      <c r="B3987" s="3"/>
-      <c r="C3987" s="3">
-        <v>300141</v>
-      </c>
-      <c r="E3987" s="1" t="s">
+      <c r="E3988" s="1" t="s">
         <v>7894</v>
       </c>
-      <c r="F3987" s="1" t="s">
+      <c r="F3988" s="1" t="s">
         <v>7895</v>
-      </c>
-    </row>
-    <row r="3988" spans="2:6">
-      <c r="B3988" s="3"/>
-      <c r="C3988" s="3">
-        <v>300142</v>
-      </c>
-      <c r="E3988" s="1" t="s">
-        <v>7896</v>
-      </c>
-      <c r="F3988" s="1" t="s">
-        <v>7897</v>
       </c>
     </row>
     <row r="3989" spans="2:6">
       <c r="B3989" s="3"/>
       <c r="C3989" s="3">
-        <v>300143</v>
+        <v>300136</v>
       </c>
       <c r="E3989" s="1" t="s">
-        <v>7898</v>
+        <v>7896</v>
       </c>
       <c r="F3989" s="1" t="s">
-        <v>7899</v>
+        <v>7897</v>
       </c>
     </row>
     <row r="3990" spans="2:6">
       <c r="B3990" s="3"/>
       <c r="C3990" s="3">
-        <v>300144</v>
+        <v>300137</v>
       </c>
       <c r="E3990" s="1" t="s">
-        <v>7900</v>
+        <v>7898</v>
       </c>
       <c r="F3990" s="1" t="s">
-        <v>7901</v>
+        <v>7899</v>
       </c>
     </row>
     <row r="3991" spans="2:6">
       <c r="B3991" s="3"/>
       <c r="C3991" s="3">
-        <v>300145</v>
+        <v>300138</v>
       </c>
       <c r="E3991" s="1" t="s">
-        <v>7902</v>
+        <v>7900</v>
       </c>
       <c r="F3991" s="1" t="s">
-        <v>7903</v>
+        <v>7901</v>
       </c>
     </row>
     <row r="3992" spans="2:6">
       <c r="B3992" s="3"/>
       <c r="C3992" s="3">
-        <v>300146</v>
+        <v>300139</v>
       </c>
       <c r="E3992" s="1" t="s">
-        <v>7904</v>
+        <v>7902</v>
       </c>
       <c r="F3992" s="1" t="s">
-        <v>7905</v>
+        <v>7903</v>
       </c>
     </row>
     <row r="3993" spans="2:6">
       <c r="B3993" s="3"/>
       <c r="C3993" s="3">
-        <v>300147</v>
+        <v>300140</v>
       </c>
       <c r="E3993" s="1" t="s">
-        <v>7906</v>
+        <v>7904</v>
       </c>
       <c r="F3993" s="1" t="s">
-        <v>7907</v>
+        <v>7905</v>
       </c>
     </row>
     <row r="3994" spans="2:6">
       <c r="B3994" s="3"/>
       <c r="C3994" s="3">
-        <v>300148</v>
+        <v>300141</v>
       </c>
       <c r="E3994" s="1" t="s">
-        <v>7908</v>
+        <v>7906</v>
       </c>
       <c r="F3994" s="1" t="s">
-        <v>7909</v>
+        <v>7907</v>
       </c>
     </row>
     <row r="3995" spans="2:6">
       <c r="B3995" s="3"/>
       <c r="C3995" s="3">
-        <v>300149</v>
+        <v>300142</v>
       </c>
       <c r="E3995" s="1" t="s">
-        <v>2906</v>
+        <v>7908</v>
       </c>
       <c r="F3995" s="1" t="s">
-        <v>7910</v>
+        <v>7909</v>
       </c>
     </row>
     <row r="3996" spans="2:6">
       <c r="B3996" s="3"/>
       <c r="C3996" s="3">
-        <v>300150</v>
+        <v>300143</v>
       </c>
       <c r="E3996" s="1" t="s">
+        <v>7910</v>
+      </c>
+      <c r="F3996" s="1" t="s">
         <v>7911</v>
-      </c>
-      <c r="F3996" s="1" t="s">
-        <v>7912</v>
       </c>
     </row>
     <row r="3997" spans="2:6">
       <c r="B3997" s="3"/>
       <c r="C3997" s="3">
-        <v>300151</v>
+        <v>300144</v>
       </c>
       <c r="E3997" s="1" t="s">
+        <v>7912</v>
+      </c>
+      <c r="F3997" s="1" t="s">
         <v>7913</v>
-      </c>
-      <c r="F3997" s="1" t="s">
-        <v>7914</v>
       </c>
     </row>
     <row r="3998" spans="2:6">
       <c r="B3998" s="3"/>
       <c r="C3998" s="3">
+        <v>300145</v>
+      </c>
+      <c r="E3998" s="1" t="s">
+        <v>7914</v>
+      </c>
+      <c r="F3998" s="1" t="s">
+        <v>7915</v>
+      </c>
+    </row>
+    <row r="3999" spans="2:6">
+      <c r="B3999" s="3"/>
+      <c r="C3999" s="3">
+        <v>300146</v>
+      </c>
+      <c r="E3999" s="1" t="s">
+        <v>7916</v>
+      </c>
+      <c r="F3999" s="1" t="s">
+        <v>7917</v>
+      </c>
+    </row>
+    <row r="4000" spans="2:6">
+      <c r="B4000" s="3"/>
+      <c r="C4000" s="3">
+        <v>300147</v>
+      </c>
+      <c r="E4000" s="1" t="s">
+        <v>7918</v>
+      </c>
+      <c r="F4000" s="1" t="s">
+        <v>7919</v>
+      </c>
+    </row>
+    <row r="4001" spans="2:6">
+      <c r="B4001" s="3"/>
+      <c r="C4001" s="3">
+        <v>300148</v>
+      </c>
+      <c r="E4001" s="1" t="s">
+        <v>7920</v>
+      </c>
+      <c r="F4001" s="1" t="s">
+        <v>7921</v>
+      </c>
+    </row>
+    <row r="4002" spans="2:6">
+      <c r="B4002" s="3"/>
+      <c r="C4002" s="3">
+        <v>300149</v>
+      </c>
+      <c r="E4002" s="1" t="s">
+        <v>2906</v>
+      </c>
+      <c r="F4002" s="1" t="s">
+        <v>7922</v>
+      </c>
+    </row>
+    <row r="4003" spans="2:6">
+      <c r="B4003" s="3"/>
+      <c r="C4003" s="3">
+        <v>300150</v>
+      </c>
+      <c r="E4003" s="1" t="s">
+        <v>7923</v>
+      </c>
+      <c r="F4003" s="1" t="s">
+        <v>7924</v>
+      </c>
+    </row>
+    <row r="4004" spans="2:6">
+      <c r="B4004" s="3"/>
+      <c r="C4004" s="3">
+        <v>300151</v>
+      </c>
+      <c r="E4004" s="1" t="s">
+        <v>7925</v>
+      </c>
+      <c r="F4004" s="1" t="s">
+        <v>7926</v>
+      </c>
+    </row>
+    <row r="4005" spans="2:6">
+      <c r="B4005" s="3"/>
+      <c r="C4005" s="3">
         <v>300152</v>
       </c>
-      <c r="E3998" s="1" t="s">
-        <v>7915</v>
-      </c>
-      <c r="F3998" s="1" t="s">
-        <v>7916</v>
-      </c>
-    </row>
-    <row r="3999" spans="2:6">
-      <c r="C3999" s="3">
+      <c r="E4005" s="1" t="s">
+        <v>7927</v>
+      </c>
+      <c r="F4005" s="1" t="s">
+        <v>7928</v>
+      </c>
+    </row>
+    <row r="4006" spans="2:6">
+      <c r="C4006" s="3">
         <v>300153</v>
       </c>
-      <c r="E3999" s="1" t="s">
-        <v>7917</v>
-      </c>
-      <c r="F3999" s="1" t="s">
-        <v>7918</v>
-      </c>
-    </row>
-    <row r="4000" spans="2:6">
-      <c r="C4000" s="3">
+      <c r="E4006" s="1" t="s">
+        <v>7929</v>
+      </c>
+      <c r="F4006" s="1" t="s">
+        <v>7930</v>
+      </c>
+    </row>
+    <row r="4007" spans="2:6">
+      <c r="C4007" s="3">
         <v>300154</v>
       </c>
-      <c r="E4000" s="1" t="s">
-        <v>7919</v>
-      </c>
-      <c r="F4000" s="1" t="s">
-        <v>7920</v>
-      </c>
-    </row>
-    <row r="4001" spans="3:6">
-      <c r="C4001" s="3">
+      <c r="E4007" s="1" t="s">
+        <v>7931</v>
+      </c>
+      <c r="F4007" s="1" t="s">
+        <v>7932</v>
+      </c>
+    </row>
+    <row r="4008" spans="2:6">
+      <c r="C4008" s="3">
         <v>300155</v>
       </c>
-      <c r="E4001" s="1" t="s">
-        <v>7921</v>
-      </c>
-      <c r="F4001" s="1" t="s">
-        <v>7922</v>
-      </c>
-    </row>
-    <row r="4002" spans="3:6">
-      <c r="C4002" s="3">
+      <c r="E4008" s="1" t="s">
+        <v>7933</v>
+      </c>
+      <c r="F4008" s="1" t="s">
+        <v>7934</v>
+      </c>
+    </row>
+    <row r="4009" spans="2:6">
+      <c r="C4009" s="3">
         <v>300156</v>
       </c>
-      <c r="E4002" s="1" t="s">
-        <v>7923</v>
-      </c>
-      <c r="F4002" s="1" t="s">
-        <v>7924</v>
-      </c>
-    </row>
-    <row r="4003" spans="3:6">
-      <c r="C4003" s="3">
+      <c r="E4009" s="1" t="s">
+        <v>7935</v>
+      </c>
+      <c r="F4009" s="1" t="s">
+        <v>7936</v>
+      </c>
+    </row>
+    <row r="4010" spans="2:6">
+      <c r="C4010" s="3">
         <v>300157</v>
       </c>
-      <c r="E4003" s="1" t="s">
-        <v>7925</v>
-      </c>
-      <c r="F4003" s="1" t="s">
-        <v>7926</v>
-      </c>
-    </row>
-    <row r="4004" spans="3:6">
-      <c r="C4004" s="3">
+      <c r="E4010" s="1" t="s">
+        <v>7937</v>
+      </c>
+      <c r="F4010" s="1" t="s">
+        <v>7938</v>
+      </c>
+    </row>
+    <row r="4011" spans="2:6">
+      <c r="C4011" s="3">
         <v>300158</v>
       </c>
-      <c r="E4004" s="1" t="s">
-        <v>7927</v>
-      </c>
-      <c r="F4004" s="1" t="s">
-        <v>7928</v>
-      </c>
-    </row>
-    <row r="4005" spans="3:6">
-      <c r="C4005" s="3">
+      <c r="E4011" s="1" t="s">
+        <v>7939</v>
+      </c>
+      <c r="F4011" s="1" t="s">
+        <v>7940</v>
+      </c>
+    </row>
+    <row r="4012" spans="2:6">
+      <c r="C4012" s="3">
         <v>300159</v>
       </c>
-      <c r="E4005" s="1" t="s">
-        <v>7929</v>
-      </c>
-      <c r="F4005" s="1" t="s">
-        <v>7930</v>
-      </c>
-    </row>
-    <row r="4006" spans="3:6">
-      <c r="C4006" s="3">
+      <c r="E4012" s="1" t="s">
+        <v>7941</v>
+      </c>
+      <c r="F4012" s="1" t="s">
+        <v>7942</v>
+      </c>
+    </row>
+    <row r="4013" spans="2:6">
+      <c r="C4013" s="3">
         <v>300160</v>
       </c>
-      <c r="E4006" s="1" t="s">
-        <v>7931</v>
-      </c>
-      <c r="F4006" s="1" t="s">
-        <v>7932</v>
-      </c>
-    </row>
-    <row r="4007" spans="3:6">
-      <c r="C4007" s="3">
-        <v>300161</v>
-      </c>
-      <c r="E4007" s="1" t="s">
-        <v>7933</v>
-      </c>
-      <c r="F4007" s="1" t="s">
-        <v>7934</v>
-      </c>
-    </row>
-    <row r="4008" spans="3:6">
-      <c r="C4008" s="3">
-        <v>300162</v>
-      </c>
-      <c r="E4008" s="1" t="s">
-        <v>7935</v>
-      </c>
-      <c r="F4008" s="1" t="s">
-        <v>7936</v>
-      </c>
-    </row>
-    <row r="4009" spans="3:6">
-      <c r="C4009" s="3">
-        <v>300163</v>
-      </c>
-      <c r="E4009" s="1" t="s">
-        <v>7937</v>
-      </c>
-      <c r="F4009" s="1" t="s">
-        <v>7938</v>
-      </c>
-    </row>
-    <row r="4010" spans="3:6">
-      <c r="C4010" s="3">
-        <v>300164</v>
-      </c>
-      <c r="E4010" s="1" t="s">
-        <v>7939</v>
-      </c>
-      <c r="F4010" s="1" t="s">
-        <v>7940</v>
-      </c>
-    </row>
-    <row r="4011" spans="3:6">
-      <c r="C4011" s="3">
-        <v>300165</v>
-      </c>
-      <c r="E4011" s="1" t="s">
-        <v>7941</v>
-      </c>
-      <c r="F4011" s="1" t="s">
-        <v>7942</v>
-      </c>
-    </row>
-    <row r="4012" spans="3:6">
-      <c r="C4012" s="3">
-        <v>300166</v>
-      </c>
-      <c r="E4012" s="1" t="s">
-        <v>1068</v>
-      </c>
-      <c r="F4012" s="1" t="s">
+      <c r="E4013" s="1" t="s">
         <v>7943</v>
-      </c>
-    </row>
-    <row r="4013" spans="3:6">
-      <c r="C4013" s="3">
-        <v>300167</v>
-      </c>
-      <c r="E4013" s="1" t="s">
-        <v>1070</v>
       </c>
       <c r="F4013" s="1" t="s">
         <v>7944</v>
       </c>
     </row>
-    <row r="4014" spans="3:6">
+    <row r="4014" spans="2:6">
       <c r="C4014" s="3">
-        <v>300168</v>
+        <v>300161</v>
       </c>
       <c r="E4014" s="1" t="s">
-        <v>1072</v>
+        <v>7945</v>
       </c>
       <c r="F4014" s="1" t="s">
-        <v>7945</v>
-      </c>
-    </row>
-    <row r="4015" spans="3:6">
+        <v>7946</v>
+      </c>
+    </row>
+    <row r="4015" spans="2:6">
       <c r="C4015" s="3">
-        <v>300169</v>
+        <v>300162</v>
       </c>
       <c r="E4015" s="1" t="s">
-        <v>1074</v>
+        <v>7947</v>
       </c>
       <c r="F4015" s="1" t="s">
-        <v>7946</v>
-      </c>
-    </row>
-    <row r="4016" spans="3:6">
+        <v>7948</v>
+      </c>
+    </row>
+    <row r="4016" spans="2:6">
       <c r="C4016" s="3">
-        <v>300170</v>
+        <v>300163</v>
       </c>
       <c r="E4016" s="1" t="s">
-        <v>7947</v>
+        <v>7949</v>
       </c>
       <c r="F4016" s="1" t="s">
-        <v>1254</v>
+        <v>7950</v>
       </c>
     </row>
     <row r="4017" spans="3:6">
       <c r="C4017" s="3">
-        <v>300171</v>
+        <v>300164</v>
       </c>
       <c r="E4017" s="1" t="s">
-        <v>7948</v>
+        <v>7951</v>
       </c>
       <c r="F4017" s="1" t="s">
-        <v>7949</v>
+        <v>7952</v>
       </c>
     </row>
     <row r="4018" spans="3:6">
       <c r="C4018" s="3">
-        <v>300172</v>
+        <v>300165</v>
       </c>
       <c r="E4018" s="1" t="s">
-        <v>7950</v>
+        <v>7953</v>
       </c>
       <c r="F4018" s="1" t="s">
-        <v>7951</v>
+        <v>7954</v>
       </c>
     </row>
     <row r="4019" spans="3:6">
       <c r="C4019" s="3">
-        <v>300173</v>
+        <v>300166</v>
       </c>
       <c r="E4019" s="1" t="s">
-        <v>7952</v>
+        <v>1068</v>
       </c>
       <c r="F4019" s="1" t="s">
-        <v>7953</v>
+        <v>7955</v>
       </c>
     </row>
     <row r="4020" spans="3:6">
       <c r="C4020" s="3">
-        <v>300174</v>
+        <v>300167</v>
       </c>
       <c r="E4020" s="1" t="s">
-        <v>7954</v>
+        <v>1070</v>
       </c>
       <c r="F4020" s="1" t="s">
-        <v>7955</v>
+        <v>7956</v>
       </c>
     </row>
     <row r="4021" spans="3:6">
       <c r="C4021" s="3">
-        <v>300175</v>
+        <v>300168</v>
       </c>
       <c r="E4021" s="1" t="s">
-        <v>7956</v>
+        <v>1072</v>
       </c>
       <c r="F4021" s="1" t="s">
         <v>7957</v>
@@ -73478,51 +73521,51 @@
     </row>
     <row r="4022" spans="3:6">
       <c r="C4022" s="3">
-        <v>300176</v>
+        <v>300169</v>
       </c>
       <c r="E4022" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F4022" s="1" t="s">
         <v>7958</v>
-      </c>
-      <c r="F4022" s="1" t="s">
-        <v>7959</v>
       </c>
     </row>
     <row r="4023" spans="3:6">
       <c r="C4023" s="3">
-        <v>300177</v>
+        <v>300170</v>
       </c>
       <c r="E4023" s="1" t="s">
-        <v>7960</v>
+        <v>7959</v>
       </c>
       <c r="F4023" s="1" t="s">
-        <v>2357</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="4024" spans="3:6">
       <c r="C4024" s="3">
-        <v>300178</v>
+        <v>300171</v>
       </c>
       <c r="E4024" s="1" t="s">
+        <v>7960</v>
+      </c>
+      <c r="F4024" s="1" t="s">
         <v>7961</v>
-      </c>
-      <c r="F4024" s="1" t="s">
-        <v>7962</v>
       </c>
     </row>
     <row r="4025" spans="3:6">
       <c r="C4025" s="3">
-        <v>300179</v>
+        <v>300172</v>
       </c>
       <c r="E4025" s="1" t="s">
+        <v>7962</v>
+      </c>
+      <c r="F4025" s="1" t="s">
         <v>7963</v>
-      </c>
-      <c r="F4025" s="1" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="4026" spans="3:6">
       <c r="C4026" s="3">
-        <v>300180</v>
+        <v>300173</v>
       </c>
       <c r="E4026" s="1" t="s">
         <v>7964</v>
@@ -73533,7 +73576,7 @@
     </row>
     <row r="4027" spans="3:6">
       <c r="C4027" s="3">
-        <v>300181</v>
+        <v>300174</v>
       </c>
       <c r="E4027" s="1" t="s">
         <v>7966</v>
@@ -73544,7 +73587,7 @@
     </row>
     <row r="4028" spans="3:6">
       <c r="C4028" s="3">
-        <v>300182</v>
+        <v>300175</v>
       </c>
       <c r="E4028" s="1" t="s">
         <v>7968</v>
@@ -73555,7 +73598,7 @@
     </row>
     <row r="4029" spans="3:6">
       <c r="C4029" s="3">
-        <v>300183</v>
+        <v>300176</v>
       </c>
       <c r="E4029" s="1" t="s">
         <v>7970</v>
@@ -73566,178 +73609,255 @@
     </row>
     <row r="4030" spans="3:6">
       <c r="C4030" s="3">
-        <v>300184</v>
+        <v>300177</v>
       </c>
       <c r="E4030" s="1" t="s">
-        <v>4328</v>
+        <v>7972</v>
       </c>
       <c r="F4030" s="1" t="s">
-        <v>718</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="4031" spans="3:6">
       <c r="C4031" s="3">
-        <v>300185</v>
+        <v>300178</v>
       </c>
       <c r="E4031" s="1" t="s">
-        <v>7972</v>
+        <v>7973</v>
       </c>
       <c r="F4031" s="1" t="s">
-        <v>7973</v>
+        <v>7974</v>
       </c>
     </row>
     <row r="4032" spans="3:6">
       <c r="C4032" s="3">
-        <v>300186</v>
+        <v>300179</v>
       </c>
       <c r="E4032" s="1" t="s">
-        <v>7974</v>
+        <v>7975</v>
       </c>
       <c r="F4032" s="1" t="s">
-        <v>718</v>
+        <v>678</v>
       </c>
     </row>
     <row r="4033" spans="3:6">
       <c r="C4033" s="3">
-        <v>300187</v>
+        <v>300180</v>
       </c>
       <c r="E4033" s="1" t="s">
-        <v>7975</v>
+        <v>7976</v>
       </c>
       <c r="F4033" s="1" t="s">
-        <v>7976</v>
+        <v>7977</v>
       </c>
     </row>
     <row r="4034" spans="3:6">
       <c r="C4034" s="3">
-        <v>300188</v>
+        <v>300181</v>
       </c>
       <c r="E4034" s="1" t="s">
-        <v>7977</v>
+        <v>7978</v>
       </c>
       <c r="F4034" s="1" t="s">
-        <v>7978</v>
+        <v>7979</v>
       </c>
     </row>
     <row r="4035" spans="3:6">
       <c r="C4035" s="3">
-        <v>300189</v>
+        <v>300182</v>
       </c>
       <c r="E4035" s="1" t="s">
-        <v>7979</v>
+        <v>7980</v>
       </c>
       <c r="F4035" s="1" t="s">
-        <v>7980</v>
+        <v>7981</v>
       </c>
     </row>
     <row r="4036" spans="3:6">
       <c r="C4036" s="3">
-        <v>300190</v>
+        <v>300183</v>
       </c>
       <c r="E4036" s="1" t="s">
-        <v>7981</v>
+        <v>7982</v>
       </c>
       <c r="F4036" s="1" t="s">
-        <v>7982</v>
+        <v>7983</v>
       </c>
     </row>
     <row r="4037" spans="3:6">
       <c r="C4037" s="3">
-        <v>300191</v>
+        <v>300184</v>
       </c>
       <c r="E4037" s="1" t="s">
-        <v>7983</v>
+        <v>4328</v>
       </c>
       <c r="F4037" s="1" t="s">
-        <v>7984</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4038" spans="3:6">
       <c r="C4038" s="3">
-        <v>300192</v>
+        <v>300185</v>
       </c>
       <c r="E4038" s="1" t="s">
+        <v>7984</v>
+      </c>
+      <c r="F4038" s="1" t="s">
         <v>7985</v>
-      </c>
-      <c r="F4038" s="1" t="s">
-        <v>7986</v>
       </c>
     </row>
     <row r="4039" spans="3:6">
       <c r="C4039" s="3">
-        <v>300193</v>
+        <v>300186</v>
       </c>
       <c r="E4039" s="1" t="s">
-        <v>7987</v>
+        <v>7986</v>
       </c>
       <c r="F4039" s="1" t="s">
-        <v>7988</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4040" spans="3:6">
       <c r="C4040" s="3">
-        <v>300194</v>
+        <v>300187</v>
       </c>
       <c r="E4040" s="1" t="s">
-        <v>7989</v>
+        <v>7987</v>
       </c>
       <c r="F4040" s="1" t="s">
-        <v>7990</v>
+        <v>7988</v>
       </c>
     </row>
     <row r="4041" spans="3:6">
       <c r="C4041" s="3">
-        <v>300195</v>
+        <v>300188</v>
       </c>
       <c r="E4041" s="1" t="s">
-        <v>7991</v>
+        <v>7989</v>
       </c>
       <c r="F4041" s="1" t="s">
-        <v>7992</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="4042" spans="3:6">
       <c r="C4042" s="3">
-        <v>300196</v>
+        <v>300189</v>
       </c>
       <c r="E4042" s="1" t="s">
-        <v>7993</v>
+        <v>7991</v>
       </c>
       <c r="F4042" s="1" t="s">
-        <v>7994</v>
+        <v>7992</v>
       </c>
     </row>
     <row r="4043" spans="3:6">
       <c r="C4043" s="3">
-        <v>300197</v>
+        <v>300190</v>
       </c>
       <c r="E4043" s="1" t="s">
-        <v>7995</v>
+        <v>7993</v>
       </c>
       <c r="F4043" s="1" t="s">
-        <v>7996</v>
+        <v>7994</v>
       </c>
     </row>
     <row r="4044" spans="3:6">
       <c r="C4044" s="3">
-        <v>300198</v>
+        <v>300191</v>
       </c>
       <c r="E4044" s="1" t="s">
-        <v>7997</v>
+        <v>7995</v>
       </c>
       <c r="F4044" s="1" t="s">
-        <v>7998</v>
+        <v>7996</v>
       </c>
     </row>
     <row r="4045" spans="3:6">
       <c r="C4045" s="3">
+        <v>300192</v>
+      </c>
+      <c r="E4045" s="1" t="s">
+        <v>7997</v>
+      </c>
+      <c r="F4045" s="1" t="s">
+        <v>7998</v>
+      </c>
+    </row>
+    <row r="4046" spans="3:6">
+      <c r="C4046" s="3">
+        <v>300193</v>
+      </c>
+      <c r="E4046" s="1" t="s">
+        <v>7999</v>
+      </c>
+      <c r="F4046" s="1" t="s">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="4047" spans="3:6">
+      <c r="C4047" s="3">
+        <v>300194</v>
+      </c>
+      <c r="E4047" s="1" t="s">
+        <v>8001</v>
+      </c>
+      <c r="F4047" s="1" t="s">
+        <v>8002</v>
+      </c>
+    </row>
+    <row r="4048" spans="3:6">
+      <c r="C4048" s="3">
+        <v>300195</v>
+      </c>
+      <c r="E4048" s="1" t="s">
+        <v>8003</v>
+      </c>
+      <c r="F4048" s="1" t="s">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="4049" spans="3:6">
+      <c r="C4049" s="3">
+        <v>300196</v>
+      </c>
+      <c r="E4049" s="1" t="s">
+        <v>8005</v>
+      </c>
+      <c r="F4049" s="1" t="s">
+        <v>8006</v>
+      </c>
+    </row>
+    <row r="4050" spans="3:6">
+      <c r="C4050" s="3">
+        <v>300197</v>
+      </c>
+      <c r="E4050" s="1" t="s">
+        <v>8007</v>
+      </c>
+      <c r="F4050" s="1" t="s">
+        <v>8008</v>
+      </c>
+    </row>
+    <row r="4051" spans="3:6">
+      <c r="C4051" s="3">
+        <v>300198</v>
+      </c>
+      <c r="E4051" s="1" t="s">
+        <v>8009</v>
+      </c>
+      <c r="F4051" s="1" t="s">
+        <v>8010</v>
+      </c>
+    </row>
+    <row r="4052" spans="3:6">
+      <c r="C4052" s="3">
         <v>300199</v>
       </c>
-      <c r="E4045" s="1" t="s">
-        <v>7999</v>
-      </c>
-      <c r="F4045" s="1" t="s">
-        <v>8000</v>
+      <c r="E4052" s="1" t="s">
+        <v>8011</v>
+      </c>
+      <c r="F4052" s="1" t="s">
+        <v>8012</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8222" uniqueCount="8013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8226" uniqueCount="8018">
   <si>
     <t>c</t>
   </si>
@@ -22925,13 +22925,28 @@
     <t>Click the button to enter the adventure</t>
   </si>
   <si>
-    <t>第一赛季</t>
-  </si>
-  <si>
-    <t>First season</t>
-  </si>
-  <si>
-    <t>Level rewards</t>
+    <t>2026第一赛季</t>
+  </si>
+  <si>
+    <t>2026 Season 1</t>
+  </si>
+  <si>
+    <t>2026第二赛季</t>
+  </si>
+  <si>
+    <t>2026 Season 2</t>
+  </si>
+  <si>
+    <t>2026第三赛季</t>
+  </si>
+  <si>
+    <t>2026 Season 3</t>
+  </si>
+  <si>
+    <t>2026第四赛季</t>
+  </si>
+  <si>
+    <t>2026 Season 4</t>
   </si>
   <si>
     <t>合区补偿</t>
@@ -25074,7 +25089,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4052"/>
+  <dimension ref="B2:F4054"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -71535,2183 +71550,2185 @@
       </c>
       <c r="D3853" s="4"/>
       <c r="E3853" s="1" t="s">
-        <v>2012</v>
+        <v>7634</v>
       </c>
       <c r="F3853" s="8" t="s">
-        <v>7634</v>
+        <v>7635</v>
       </c>
     </row>
     <row r="3854" spans="3:6">
       <c r="C3854" s="3">
-        <v>300001</v>
-      </c>
-      <c r="D3854" s="4" t="s">
-        <v>1961</v>
-      </c>
+        <v>203737</v>
+      </c>
+      <c r="D3854" s="4"/>
       <c r="E3854" s="1" t="s">
-        <v>7635</v>
+        <v>7636</v>
       </c>
       <c r="F3854" s="8" t="s">
-        <v>7636</v>
+        <v>7637</v>
       </c>
     </row>
     <row r="3855" spans="3:6">
       <c r="C3855" s="3">
-        <v>300002</v>
+        <v>203738</v>
       </c>
       <c r="D3855" s="4"/>
       <c r="E3855" s="1" t="s">
-        <v>7637</v>
+        <v>7638</v>
       </c>
       <c r="F3855" s="8" t="s">
-        <v>7638</v>
+        <v>7639</v>
       </c>
     </row>
     <row r="3856" spans="3:6">
       <c r="C3856" s="3">
-        <v>300003</v>
-      </c>
-      <c r="D3856" s="4"/>
+        <v>300001</v>
+      </c>
+      <c r="D3856" s="4" t="s">
+        <v>1961</v>
+      </c>
       <c r="E3856" s="1" t="s">
-        <v>7639</v>
+        <v>7640</v>
       </c>
       <c r="F3856" s="8" t="s">
-        <v>7640</v>
+        <v>7641</v>
       </c>
     </row>
     <row r="3857" spans="3:6">
       <c r="C3857" s="3">
-        <v>300004</v>
+        <v>300002</v>
       </c>
       <c r="D3857" s="4"/>
       <c r="E3857" s="1" t="s">
-        <v>7641</v>
+        <v>7642</v>
       </c>
       <c r="F3857" s="8" t="s">
-        <v>7642</v>
+        <v>7643</v>
       </c>
     </row>
     <row r="3858" spans="3:6">
       <c r="C3858" s="3">
-        <v>300005</v>
+        <v>300003</v>
       </c>
       <c r="D3858" s="4"/>
       <c r="E3858" s="1" t="s">
-        <v>7643</v>
+        <v>7644</v>
       </c>
       <c r="F3858" s="8" t="s">
-        <v>7644</v>
+        <v>7645</v>
       </c>
     </row>
     <row r="3859" spans="3:6">
       <c r="C3859" s="3">
-        <v>300006</v>
+        <v>300004</v>
       </c>
       <c r="D3859" s="4"/>
       <c r="E3859" s="1" t="s">
-        <v>7645</v>
+        <v>7646</v>
       </c>
       <c r="F3859" s="8" t="s">
-        <v>7646</v>
+        <v>7647</v>
       </c>
     </row>
     <row r="3860" spans="3:6">
       <c r="C3860" s="3">
-        <v>300007</v>
+        <v>300005</v>
       </c>
       <c r="D3860" s="4"/>
       <c r="E3860" s="1" t="s">
-        <v>7647</v>
+        <v>7648</v>
       </c>
       <c r="F3860" s="8" t="s">
-        <v>7648</v>
+        <v>7649</v>
       </c>
     </row>
     <row r="3861" spans="3:6">
       <c r="C3861" s="3">
-        <v>300008</v>
+        <v>300006</v>
       </c>
       <c r="D3861" s="4"/>
       <c r="E3861" s="1" t="s">
-        <v>7649</v>
+        <v>7650</v>
       </c>
       <c r="F3861" s="8" t="s">
-        <v>7650</v>
+        <v>7651</v>
       </c>
     </row>
     <row r="3862" spans="3:6">
       <c r="C3862" s="3">
-        <v>300009</v>
+        <v>300007</v>
       </c>
       <c r="D3862" s="4"/>
       <c r="E3862" s="1" t="s">
-        <v>7651</v>
+        <v>7652</v>
       </c>
       <c r="F3862" s="8" t="s">
-        <v>7652</v>
+        <v>7653</v>
       </c>
     </row>
     <row r="3863" spans="3:6">
       <c r="C3863" s="3">
-        <v>300010</v>
+        <v>300008</v>
       </c>
       <c r="D3863" s="4"/>
       <c r="E3863" s="1" t="s">
-        <v>7653</v>
+        <v>7654</v>
       </c>
       <c r="F3863" s="8" t="s">
-        <v>7654</v>
+        <v>7655</v>
       </c>
     </row>
     <row r="3864" spans="3:6">
       <c r="C3864" s="3">
-        <v>300011</v>
+        <v>300009</v>
       </c>
       <c r="D3864" s="4"/>
       <c r="E3864" s="1" t="s">
-        <v>7655</v>
+        <v>7656</v>
       </c>
       <c r="F3864" s="8" t="s">
-        <v>7656</v>
+        <v>7657</v>
       </c>
     </row>
     <row r="3865" spans="3:6">
       <c r="C3865" s="3">
-        <v>300012</v>
+        <v>300010</v>
       </c>
       <c r="D3865" s="4"/>
       <c r="E3865" s="1" t="s">
-        <v>7657</v>
+        <v>7658</v>
       </c>
       <c r="F3865" s="8" t="s">
-        <v>7658</v>
+        <v>7659</v>
       </c>
     </row>
     <row r="3866" spans="3:6">
       <c r="C3866" s="3">
-        <v>300013</v>
+        <v>300011</v>
       </c>
       <c r="D3866" s="4"/>
       <c r="E3866" s="1" t="s">
-        <v>7659</v>
+        <v>7660</v>
       </c>
       <c r="F3866" s="8" t="s">
-        <v>7660</v>
+        <v>7661</v>
       </c>
     </row>
     <row r="3867" spans="3:6">
       <c r="C3867" s="3">
-        <v>300014</v>
+        <v>300012</v>
       </c>
       <c r="D3867" s="4"/>
       <c r="E3867" s="1" t="s">
-        <v>7661</v>
+        <v>7662</v>
       </c>
       <c r="F3867" s="8" t="s">
-        <v>7662</v>
+        <v>7663</v>
       </c>
     </row>
     <row r="3868" spans="3:6">
       <c r="C3868" s="3">
-        <v>300015</v>
+        <v>300013</v>
       </c>
       <c r="D3868" s="4"/>
       <c r="E3868" s="1" t="s">
-        <v>7663</v>
+        <v>7664</v>
       </c>
       <c r="F3868" s="8" t="s">
-        <v>7664</v>
+        <v>7665</v>
       </c>
     </row>
     <row r="3869" spans="3:6">
       <c r="C3869" s="3">
-        <v>300016</v>
+        <v>300014</v>
       </c>
       <c r="D3869" s="4"/>
       <c r="E3869" s="1" t="s">
-        <v>7665</v>
+        <v>7666</v>
       </c>
       <c r="F3869" s="8" t="s">
-        <v>7666</v>
+        <v>7667</v>
       </c>
     </row>
     <row r="3870" spans="3:6">
       <c r="C3870" s="3">
-        <v>300017</v>
+        <v>300015</v>
       </c>
       <c r="D3870" s="4"/>
       <c r="E3870" s="1" t="s">
-        <v>7667</v>
+        <v>7668</v>
       </c>
       <c r="F3870" s="8" t="s">
-        <v>7668</v>
+        <v>7669</v>
       </c>
     </row>
     <row r="3871" spans="3:6">
       <c r="C3871" s="3">
-        <v>300018</v>
+        <v>300016</v>
       </c>
       <c r="D3871" s="4"/>
       <c r="E3871" s="1" t="s">
-        <v>7669</v>
+        <v>7670</v>
       </c>
       <c r="F3871" s="8" t="s">
-        <v>7670</v>
+        <v>7671</v>
       </c>
     </row>
     <row r="3872" spans="3:6">
       <c r="C3872" s="3">
-        <v>300019</v>
+        <v>300017</v>
       </c>
       <c r="D3872" s="4"/>
       <c r="E3872" s="1" t="s">
-        <v>7671</v>
+        <v>7672</v>
       </c>
       <c r="F3872" s="8" t="s">
-        <v>7672</v>
+        <v>7673</v>
       </c>
     </row>
     <row r="3873" spans="3:6">
       <c r="C3873" s="3">
-        <v>300020</v>
+        <v>300018</v>
       </c>
       <c r="D3873" s="4"/>
       <c r="E3873" s="1" t="s">
-        <v>7673</v>
+        <v>7674</v>
       </c>
       <c r="F3873" s="8" t="s">
-        <v>7674</v>
+        <v>7675</v>
       </c>
     </row>
     <row r="3874" spans="3:6">
       <c r="C3874" s="3">
-        <v>300021</v>
+        <v>300019</v>
       </c>
       <c r="D3874" s="4"/>
       <c r="E3874" s="1" t="s">
-        <v>7675</v>
+        <v>7676</v>
       </c>
       <c r="F3874" s="8" t="s">
-        <v>7676</v>
+        <v>7677</v>
       </c>
     </row>
     <row r="3875" spans="3:6">
       <c r="C3875" s="3">
-        <v>300022</v>
+        <v>300020</v>
       </c>
       <c r="D3875" s="4"/>
       <c r="E3875" s="1" t="s">
-        <v>4218</v>
+        <v>7678</v>
       </c>
       <c r="F3875" s="8" t="s">
-        <v>7677</v>
+        <v>7679</v>
       </c>
     </row>
     <row r="3876" spans="3:6">
       <c r="C3876" s="3">
-        <v>300023</v>
+        <v>300021</v>
       </c>
       <c r="D3876" s="4"/>
       <c r="E3876" s="1" t="s">
-        <v>7678</v>
+        <v>7680</v>
       </c>
       <c r="F3876" s="8" t="s">
-        <v>7679</v>
+        <v>7681</v>
       </c>
     </row>
     <row r="3877" spans="3:6">
       <c r="C3877" s="3">
-        <v>300024</v>
+        <v>300022</v>
       </c>
       <c r="D3877" s="4"/>
       <c r="E3877" s="1" t="s">
-        <v>7680</v>
+        <v>4218</v>
       </c>
       <c r="F3877" s="8" t="s">
-        <v>7681</v>
+        <v>7682</v>
       </c>
     </row>
     <row r="3878" spans="3:6">
       <c r="C3878" s="3">
-        <v>300025</v>
+        <v>300023</v>
       </c>
       <c r="D3878" s="4"/>
       <c r="E3878" s="1" t="s">
-        <v>7682</v>
+        <v>7683</v>
       </c>
       <c r="F3878" s="8" t="s">
-        <v>7683</v>
+        <v>7684</v>
       </c>
     </row>
     <row r="3879" spans="3:6">
       <c r="C3879" s="3">
-        <v>300026</v>
+        <v>300024</v>
       </c>
       <c r="D3879" s="4"/>
       <c r="E3879" s="1" t="s">
-        <v>7684</v>
+        <v>7685</v>
       </c>
       <c r="F3879" s="8" t="s">
-        <v>7685</v>
+        <v>7686</v>
       </c>
     </row>
     <row r="3880" spans="3:6">
       <c r="C3880" s="3">
-        <v>300027</v>
+        <v>300025</v>
       </c>
       <c r="D3880" s="4"/>
       <c r="E3880" s="1" t="s">
-        <v>7686</v>
+        <v>7687</v>
       </c>
       <c r="F3880" s="8" t="s">
-        <v>7687</v>
+        <v>7688</v>
       </c>
     </row>
     <row r="3881" spans="3:6">
       <c r="C3881" s="3">
-        <v>300028</v>
+        <v>300026</v>
       </c>
       <c r="D3881" s="4"/>
       <c r="E3881" s="1" t="s">
-        <v>7688</v>
+        <v>7689</v>
       </c>
       <c r="F3881" s="8" t="s">
-        <v>7689</v>
+        <v>7690</v>
       </c>
     </row>
     <row r="3882" spans="3:6">
       <c r="C3882" s="3">
-        <v>300029</v>
+        <v>300027</v>
       </c>
       <c r="D3882" s="4"/>
       <c r="E3882" s="1" t="s">
-        <v>7690</v>
+        <v>7691</v>
       </c>
       <c r="F3882" s="8" t="s">
-        <v>7691</v>
+        <v>7692</v>
       </c>
     </row>
     <row r="3883" spans="3:6">
       <c r="C3883" s="3">
-        <v>300030</v>
+        <v>300028</v>
       </c>
       <c r="D3883" s="4"/>
       <c r="E3883" s="1" t="s">
-        <v>7692</v>
+        <v>7693</v>
       </c>
       <c r="F3883" s="8" t="s">
-        <v>7693</v>
+        <v>7694</v>
       </c>
     </row>
     <row r="3884" spans="3:6">
       <c r="C3884" s="3">
-        <v>300031</v>
+        <v>300029</v>
       </c>
       <c r="D3884" s="4"/>
       <c r="E3884" s="1" t="s">
-        <v>7694</v>
+        <v>7695</v>
       </c>
       <c r="F3884" s="8" t="s">
-        <v>7695</v>
+        <v>7696</v>
       </c>
     </row>
     <row r="3885" spans="3:6">
       <c r="C3885" s="3">
-        <v>300032</v>
+        <v>300030</v>
       </c>
       <c r="D3885" s="4"/>
       <c r="E3885" s="1" t="s">
-        <v>7696</v>
+        <v>7697</v>
       </c>
       <c r="F3885" s="8" t="s">
-        <v>7697</v>
+        <v>7698</v>
       </c>
     </row>
     <row r="3886" spans="3:6">
       <c r="C3886" s="3">
-        <v>300033</v>
+        <v>300031</v>
       </c>
       <c r="D3886" s="4"/>
       <c r="E3886" s="1" t="s">
-        <v>7698</v>
+        <v>7699</v>
       </c>
       <c r="F3886" s="8" t="s">
-        <v>7699</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="3887" spans="3:6">
       <c r="C3887" s="3">
-        <v>300034</v>
+        <v>300032</v>
       </c>
       <c r="D3887" s="4"/>
       <c r="E3887" s="1" t="s">
-        <v>7700</v>
+        <v>7701</v>
       </c>
       <c r="F3887" s="8" t="s">
-        <v>7701</v>
+        <v>7702</v>
       </c>
     </row>
     <row r="3888" spans="3:6">
       <c r="C3888" s="3">
-        <v>300035</v>
+        <v>300033</v>
       </c>
       <c r="D3888" s="4"/>
       <c r="E3888" s="1" t="s">
-        <v>7702</v>
+        <v>7703</v>
       </c>
       <c r="F3888" s="8" t="s">
-        <v>7703</v>
+        <v>7704</v>
       </c>
     </row>
     <row r="3889" spans="3:6">
       <c r="C3889" s="3">
-        <v>300036</v>
+        <v>300034</v>
       </c>
       <c r="D3889" s="4"/>
       <c r="E3889" s="1" t="s">
-        <v>7704</v>
+        <v>7705</v>
       </c>
       <c r="F3889" s="8" t="s">
-        <v>7705</v>
+        <v>7706</v>
       </c>
     </row>
     <row r="3890" spans="3:6">
       <c r="C3890" s="3">
-        <v>300037</v>
+        <v>300035</v>
       </c>
       <c r="D3890" s="4"/>
       <c r="E3890" s="1" t="s">
-        <v>5913</v>
+        <v>7707</v>
       </c>
       <c r="F3890" s="8" t="s">
-        <v>7706</v>
+        <v>7708</v>
       </c>
     </row>
     <row r="3891" spans="3:6">
       <c r="C3891" s="3">
-        <v>300038</v>
+        <v>300036</v>
       </c>
       <c r="D3891" s="4"/>
       <c r="E3891" s="1" t="s">
-        <v>4274</v>
+        <v>7709</v>
       </c>
       <c r="F3891" s="8" t="s">
-        <v>7707</v>
+        <v>7710</v>
       </c>
     </row>
     <row r="3892" spans="3:6">
       <c r="C3892" s="3">
-        <v>300039</v>
+        <v>300037</v>
       </c>
       <c r="D3892" s="4"/>
       <c r="E3892" s="1" t="s">
-        <v>7708</v>
+        <v>5913</v>
       </c>
       <c r="F3892" s="8" t="s">
-        <v>7709</v>
+        <v>7711</v>
       </c>
     </row>
     <row r="3893" spans="3:6">
       <c r="C3893" s="3">
-        <v>300040</v>
+        <v>300038</v>
       </c>
       <c r="D3893" s="4"/>
       <c r="E3893" s="1" t="s">
-        <v>7710</v>
+        <v>4274</v>
       </c>
       <c r="F3893" s="8" t="s">
-        <v>7711</v>
+        <v>7712</v>
       </c>
     </row>
     <row r="3894" spans="3:6">
       <c r="C3894" s="3">
-        <v>300041</v>
+        <v>300039</v>
       </c>
       <c r="D3894" s="4"/>
       <c r="E3894" s="1" t="s">
-        <v>7712</v>
+        <v>7713</v>
       </c>
       <c r="F3894" s="8" t="s">
-        <v>7713</v>
+        <v>7714</v>
       </c>
     </row>
     <row r="3895" spans="3:6">
       <c r="C3895" s="3">
-        <v>300042</v>
+        <v>300040</v>
       </c>
       <c r="D3895" s="4"/>
       <c r="E3895" s="1" t="s">
-        <v>1222</v>
+        <v>7715</v>
       </c>
       <c r="F3895" s="8" t="s">
-        <v>1041</v>
+        <v>7716</v>
       </c>
     </row>
     <row r="3896" spans="3:6">
       <c r="C3896" s="3">
-        <v>300043</v>
+        <v>300041</v>
       </c>
       <c r="D3896" s="4"/>
       <c r="E3896" s="1" t="s">
-        <v>7714</v>
+        <v>7717</v>
       </c>
       <c r="F3896" s="8" t="s">
-        <v>7715</v>
+        <v>7718</v>
       </c>
     </row>
     <row r="3897" spans="3:6">
       <c r="C3897" s="3">
-        <v>300044</v>
+        <v>300042</v>
       </c>
       <c r="D3897" s="4"/>
       <c r="E3897" s="1" t="s">
-        <v>4721</v>
+        <v>1222</v>
       </c>
       <c r="F3897" s="8" t="s">
-        <v>7716</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="3898" spans="3:6">
       <c r="C3898" s="3">
-        <v>300045</v>
-      </c>
-      <c r="D3898"/>
+        <v>300043</v>
+      </c>
+      <c r="D3898" s="4"/>
       <c r="E3898" s="1" t="s">
-        <v>7717</v>
-      </c>
-      <c r="F3898" t="s">
-        <v>7718</v>
+        <v>7719</v>
+      </c>
+      <c r="F3898" s="8" t="s">
+        <v>7720</v>
       </c>
     </row>
     <row r="3899" spans="3:6">
       <c r="C3899" s="3">
-        <v>300046</v>
-      </c>
-      <c r="D3899"/>
-      <c r="E3899" t="s">
-        <v>7719</v>
-      </c>
-      <c r="F3899" t="s">
-        <v>7720</v>
+        <v>300044</v>
+      </c>
+      <c r="D3899" s="4"/>
+      <c r="E3899" s="1" t="s">
+        <v>4721</v>
+      </c>
+      <c r="F3899" s="8" t="s">
+        <v>7721</v>
       </c>
     </row>
     <row r="3900" spans="3:6">
       <c r="C3900" s="3">
-        <v>300047</v>
-      </c>
-      <c r="D3900" s="4"/>
+        <v>300045</v>
+      </c>
+      <c r="D3900"/>
       <c r="E3900" s="1" t="s">
-        <v>7721</v>
-      </c>
-      <c r="F3900" s="6" t="s">
         <v>7722</v>
+      </c>
+      <c r="F3900" t="s">
+        <v>7723</v>
       </c>
     </row>
     <row r="3901" spans="3:6">
       <c r="C3901" s="3">
-        <v>300048</v>
-      </c>
-      <c r="D3901" s="4"/>
-      <c r="E3901" s="1" t="s">
-        <v>7723</v>
-      </c>
-      <c r="F3901" s="6" t="s">
+        <v>300046</v>
+      </c>
+      <c r="D3901"/>
+      <c r="E3901" t="s">
         <v>7724</v>
+      </c>
+      <c r="F3901" t="s">
+        <v>7725</v>
       </c>
     </row>
     <row r="3902" spans="3:6">
       <c r="C3902" s="3">
-        <v>300049</v>
+        <v>300047</v>
       </c>
       <c r="D3902" s="4"/>
       <c r="E3902" s="1" t="s">
-        <v>7725</v>
+        <v>7726</v>
       </c>
       <c r="F3902" s="6" t="s">
-        <v>7726</v>
+        <v>7727</v>
       </c>
     </row>
     <row r="3903" spans="3:6">
       <c r="C3903" s="3">
-        <v>300050</v>
+        <v>300048</v>
       </c>
       <c r="D3903" s="4"/>
       <c r="E3903" s="1" t="s">
-        <v>7727</v>
+        <v>7728</v>
       </c>
       <c r="F3903" s="6" t="s">
-        <v>7728</v>
+        <v>7729</v>
       </c>
     </row>
     <row r="3904" spans="3:6">
       <c r="C3904" s="3">
-        <v>300051</v>
+        <v>300049</v>
       </c>
       <c r="D3904" s="4"/>
       <c r="E3904" s="1" t="s">
-        <v>7729</v>
+        <v>7730</v>
       </c>
       <c r="F3904" s="6" t="s">
-        <v>7730</v>
+        <v>7731</v>
       </c>
     </row>
     <row r="3905" spans="3:6">
       <c r="C3905" s="3">
-        <v>300052</v>
+        <v>300050</v>
       </c>
       <c r="D3905" s="4"/>
       <c r="E3905" s="1" t="s">
-        <v>7731</v>
+        <v>7732</v>
       </c>
       <c r="F3905" s="6" t="s">
-        <v>7732</v>
+        <v>7733</v>
       </c>
     </row>
     <row r="3906" spans="3:6">
       <c r="C3906" s="3">
-        <v>300053</v>
+        <v>300051</v>
       </c>
       <c r="D3906" s="4"/>
       <c r="E3906" s="1" t="s">
-        <v>7733</v>
+        <v>7734</v>
       </c>
       <c r="F3906" s="6" t="s">
-        <v>7734</v>
+        <v>7735</v>
       </c>
     </row>
     <row r="3907" spans="3:6">
       <c r="C3907" s="3">
-        <v>300054</v>
+        <v>300052</v>
       </c>
       <c r="D3907" s="4"/>
       <c r="E3907" s="1" t="s">
-        <v>7735</v>
+        <v>7736</v>
       </c>
       <c r="F3907" s="6" t="s">
-        <v>7736</v>
+        <v>7737</v>
       </c>
     </row>
     <row r="3908" spans="3:6">
       <c r="C3908" s="3">
-        <v>300055</v>
+        <v>300053</v>
       </c>
       <c r="D3908" s="4"/>
       <c r="E3908" s="1" t="s">
-        <v>7737</v>
+        <v>7738</v>
       </c>
       <c r="F3908" s="6" t="s">
-        <v>7738</v>
+        <v>7739</v>
       </c>
     </row>
     <row r="3909" spans="3:6">
       <c r="C3909" s="3">
-        <v>300056</v>
+        <v>300054</v>
       </c>
       <c r="D3909" s="4"/>
       <c r="E3909" s="1" t="s">
-        <v>7739</v>
+        <v>7740</v>
       </c>
       <c r="F3909" s="6" t="s">
-        <v>7740</v>
+        <v>7741</v>
       </c>
     </row>
     <row r="3910" spans="3:6">
       <c r="C3910" s="3">
-        <v>300057</v>
+        <v>300055</v>
       </c>
       <c r="D3910" s="4"/>
       <c r="E3910" s="1" t="s">
-        <v>7741</v>
+        <v>7742</v>
       </c>
       <c r="F3910" s="6" t="s">
-        <v>7742</v>
+        <v>7743</v>
       </c>
     </row>
     <row r="3911" spans="3:6">
       <c r="C3911" s="3">
-        <v>300058</v>
+        <v>300056</v>
       </c>
       <c r="D3911" s="4"/>
       <c r="E3911" s="1" t="s">
-        <v>7743</v>
+        <v>7744</v>
       </c>
       <c r="F3911" s="6" t="s">
-        <v>7744</v>
+        <v>7745</v>
       </c>
     </row>
     <row r="3912" spans="3:6">
       <c r="C3912" s="3">
-        <v>300059</v>
+        <v>300057</v>
       </c>
       <c r="D3912" s="4"/>
       <c r="E3912" s="1" t="s">
-        <v>7745</v>
+        <v>7746</v>
       </c>
       <c r="F3912" s="6" t="s">
-        <v>7746</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="3913" spans="3:6">
       <c r="C3913" s="3">
-        <v>300060</v>
+        <v>300058</v>
       </c>
       <c r="D3913" s="4"/>
       <c r="E3913" s="1" t="s">
-        <v>7747</v>
+        <v>7748</v>
       </c>
       <c r="F3913" s="6" t="s">
-        <v>7748</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="3914" spans="3:6">
       <c r="C3914" s="3">
-        <v>300061</v>
+        <v>300059</v>
       </c>
       <c r="D3914" s="4"/>
       <c r="E3914" s="1" t="s">
-        <v>7749</v>
+        <v>7750</v>
       </c>
       <c r="F3914" s="6" t="s">
-        <v>7750</v>
+        <v>7751</v>
       </c>
     </row>
     <row r="3915" spans="3:6">
       <c r="C3915" s="3">
-        <v>300062</v>
+        <v>300060</v>
       </c>
       <c r="D3915" s="4"/>
       <c r="E3915" s="1" t="s">
-        <v>7751</v>
+        <v>7752</v>
       </c>
       <c r="F3915" s="6" t="s">
-        <v>7752</v>
+        <v>7753</v>
       </c>
     </row>
     <row r="3916" spans="3:6">
       <c r="C3916" s="3">
-        <v>300063</v>
+        <v>300061</v>
       </c>
       <c r="D3916" s="4"/>
       <c r="E3916" s="1" t="s">
-        <v>7753</v>
+        <v>7754</v>
       </c>
       <c r="F3916" s="6" t="s">
-        <v>7754</v>
+        <v>7755</v>
       </c>
     </row>
     <row r="3917" spans="3:6">
       <c r="C3917" s="3">
-        <v>300064</v>
+        <v>300062</v>
       </c>
       <c r="D3917" s="4"/>
       <c r="E3917" s="1" t="s">
-        <v>7755</v>
+        <v>7756</v>
       </c>
       <c r="F3917" s="6" t="s">
-        <v>7756</v>
+        <v>7757</v>
       </c>
     </row>
     <row r="3918" spans="3:6">
       <c r="C3918" s="3">
-        <v>300065</v>
+        <v>300063</v>
       </c>
       <c r="D3918" s="4"/>
       <c r="E3918" s="1" t="s">
-        <v>7757</v>
+        <v>7758</v>
       </c>
       <c r="F3918" s="6" t="s">
-        <v>7758</v>
+        <v>7759</v>
       </c>
     </row>
     <row r="3919" spans="3:6">
       <c r="C3919" s="3">
-        <v>300066</v>
+        <v>300064</v>
       </c>
       <c r="D3919" s="4"/>
       <c r="E3919" s="1" t="s">
-        <v>7759</v>
+        <v>7760</v>
       </c>
       <c r="F3919" s="6" t="s">
-        <v>7760</v>
+        <v>7761</v>
       </c>
     </row>
     <row r="3920" spans="3:6">
       <c r="C3920" s="3">
-        <v>300067</v>
+        <v>300065</v>
       </c>
       <c r="D3920" s="4"/>
       <c r="E3920" s="1" t="s">
-        <v>7761</v>
+        <v>7762</v>
       </c>
       <c r="F3920" s="6" t="s">
-        <v>7762</v>
+        <v>7763</v>
       </c>
     </row>
     <row r="3921" spans="3:6">
       <c r="C3921" s="3">
-        <v>300068</v>
+        <v>300066</v>
       </c>
       <c r="D3921" s="4"/>
       <c r="E3921" s="1" t="s">
-        <v>7763</v>
+        <v>7764</v>
       </c>
       <c r="F3921" s="6" t="s">
-        <v>7764</v>
+        <v>7765</v>
       </c>
     </row>
     <row r="3922" spans="3:6">
       <c r="C3922" s="3">
-        <v>300069</v>
+        <v>300067</v>
       </c>
       <c r="D3922" s="4"/>
       <c r="E3922" s="1" t="s">
-        <v>7765</v>
+        <v>7766</v>
       </c>
       <c r="F3922" s="6" t="s">
-        <v>7766</v>
+        <v>7767</v>
       </c>
     </row>
     <row r="3923" spans="3:6">
       <c r="C3923" s="3">
-        <v>300070</v>
+        <v>300068</v>
       </c>
       <c r="D3923" s="4"/>
       <c r="E3923" s="1" t="s">
-        <v>7767</v>
+        <v>7768</v>
       </c>
       <c r="F3923" s="6" t="s">
-        <v>7768</v>
+        <v>7769</v>
       </c>
     </row>
     <row r="3924" spans="3:6">
       <c r="C3924" s="3">
-        <v>300071</v>
+        <v>300069</v>
       </c>
       <c r="D3924" s="4"/>
       <c r="E3924" s="1" t="s">
-        <v>7769</v>
+        <v>7770</v>
       </c>
       <c r="F3924" s="6" t="s">
-        <v>7770</v>
+        <v>7771</v>
       </c>
     </row>
     <row r="3925" spans="3:6">
       <c r="C3925" s="3">
-        <v>300072</v>
+        <v>300070</v>
       </c>
       <c r="D3925" s="4"/>
       <c r="E3925" s="1" t="s">
-        <v>7771</v>
+        <v>7772</v>
       </c>
       <c r="F3925" s="6" t="s">
-        <v>7772</v>
+        <v>7773</v>
       </c>
     </row>
     <row r="3926" spans="3:6">
       <c r="C3926" s="3">
-        <v>300073</v>
+        <v>300071</v>
       </c>
       <c r="D3926" s="4"/>
       <c r="E3926" s="1" t="s">
-        <v>7773</v>
+        <v>7774</v>
       </c>
       <c r="F3926" s="6" t="s">
-        <v>7774</v>
+        <v>7775</v>
       </c>
     </row>
     <row r="3927" spans="3:6">
       <c r="C3927" s="3">
-        <v>300074</v>
+        <v>300072</v>
       </c>
       <c r="D3927" s="4"/>
       <c r="E3927" s="1" t="s">
-        <v>7775</v>
+        <v>7776</v>
       </c>
       <c r="F3927" s="6" t="s">
-        <v>7776</v>
+        <v>7777</v>
       </c>
     </row>
     <row r="3928" spans="3:6">
       <c r="C3928" s="3">
-        <v>300075</v>
+        <v>300073</v>
       </c>
       <c r="D3928" s="4"/>
       <c r="E3928" s="1" t="s">
-        <v>7777</v>
+        <v>7778</v>
       </c>
       <c r="F3928" s="6" t="s">
-        <v>7778</v>
+        <v>7779</v>
       </c>
     </row>
     <row r="3929" spans="3:6">
       <c r="C3929" s="3">
-        <v>300076</v>
+        <v>300074</v>
       </c>
       <c r="D3929" s="4"/>
       <c r="E3929" s="1" t="s">
-        <v>7779</v>
+        <v>7780</v>
       </c>
       <c r="F3929" s="6" t="s">
-        <v>7780</v>
+        <v>7781</v>
       </c>
     </row>
     <row r="3930" spans="3:6">
       <c r="C3930" s="3">
-        <v>300077</v>
+        <v>300075</v>
       </c>
       <c r="D3930" s="4"/>
       <c r="E3930" s="1" t="s">
-        <v>7781</v>
+        <v>7782</v>
       </c>
       <c r="F3930" s="6" t="s">
-        <v>7782</v>
+        <v>7783</v>
       </c>
     </row>
     <row r="3931" spans="3:6">
       <c r="C3931" s="3">
-        <v>300078</v>
+        <v>300076</v>
       </c>
       <c r="D3931" s="4"/>
       <c r="E3931" s="1" t="s">
-        <v>7783</v>
+        <v>7784</v>
       </c>
       <c r="F3931" s="6" t="s">
-        <v>7784</v>
+        <v>7785</v>
       </c>
     </row>
     <row r="3932" spans="3:6">
       <c r="C3932" s="3">
-        <v>300079</v>
+        <v>300077</v>
       </c>
       <c r="D3932" s="4"/>
       <c r="E3932" s="1" t="s">
-        <v>7785</v>
+        <v>7786</v>
       </c>
       <c r="F3932" s="6" t="s">
-        <v>7786</v>
+        <v>7787</v>
       </c>
     </row>
     <row r="3933" spans="3:6">
       <c r="C3933" s="3">
-        <v>300080</v>
+        <v>300078</v>
       </c>
       <c r="D3933" s="4"/>
       <c r="E3933" s="1" t="s">
-        <v>7787</v>
+        <v>7788</v>
       </c>
       <c r="F3933" s="6" t="s">
-        <v>7788</v>
+        <v>7789</v>
       </c>
     </row>
     <row r="3934" spans="3:6">
       <c r="C3934" s="3">
-        <v>300081</v>
+        <v>300079</v>
       </c>
       <c r="D3934" s="4"/>
       <c r="E3934" s="1" t="s">
-        <v>7789</v>
+        <v>7790</v>
       </c>
       <c r="F3934" s="6" t="s">
-        <v>7790</v>
+        <v>7791</v>
       </c>
     </row>
     <row r="3935" spans="3:6">
       <c r="C3935" s="3">
-        <v>300082</v>
+        <v>300080</v>
       </c>
       <c r="D3935" s="4"/>
       <c r="E3935" s="1" t="s">
-        <v>7791</v>
+        <v>7792</v>
       </c>
       <c r="F3935" s="6" t="s">
-        <v>7792</v>
+        <v>7793</v>
       </c>
     </row>
     <row r="3936" spans="3:6">
       <c r="C3936" s="3">
-        <v>300083</v>
+        <v>300081</v>
       </c>
       <c r="D3936" s="4"/>
       <c r="E3936" s="1" t="s">
-        <v>7793</v>
+        <v>7794</v>
       </c>
       <c r="F3936" s="6" t="s">
-        <v>7794</v>
+        <v>7795</v>
       </c>
     </row>
     <row r="3937" spans="3:6">
       <c r="C3937" s="3">
-        <v>300084</v>
+        <v>300082</v>
       </c>
       <c r="D3937" s="4"/>
       <c r="E3937" s="1" t="s">
-        <v>7795</v>
+        <v>7796</v>
       </c>
       <c r="F3937" s="6" t="s">
-        <v>7796</v>
+        <v>7797</v>
       </c>
     </row>
     <row r="3938" spans="3:6">
       <c r="C3938" s="3">
-        <v>300085</v>
+        <v>300083</v>
       </c>
       <c r="D3938" s="4"/>
       <c r="E3938" s="1" t="s">
-        <v>7797</v>
+        <v>7798</v>
       </c>
       <c r="F3938" s="6" t="s">
-        <v>7798</v>
+        <v>7799</v>
       </c>
     </row>
     <row r="3939" spans="3:6">
       <c r="C3939" s="3">
-        <v>300086</v>
+        <v>300084</v>
       </c>
       <c r="D3939" s="4"/>
       <c r="E3939" s="1" t="s">
-        <v>7799</v>
+        <v>7800</v>
       </c>
       <c r="F3939" s="6" t="s">
-        <v>7800</v>
+        <v>7801</v>
       </c>
     </row>
     <row r="3940" spans="3:6">
       <c r="C3940" s="3">
-        <v>300087</v>
+        <v>300085</v>
       </c>
       <c r="D3940" s="4"/>
       <c r="E3940" s="1" t="s">
-        <v>7801</v>
+        <v>7802</v>
       </c>
       <c r="F3940" s="6" t="s">
-        <v>7802</v>
+        <v>7803</v>
       </c>
     </row>
     <row r="3941" spans="3:6">
       <c r="C3941" s="3">
-        <v>300088</v>
+        <v>300086</v>
       </c>
       <c r="D3941" s="4"/>
       <c r="E3941" s="1" t="s">
-        <v>7803</v>
+        <v>7804</v>
       </c>
       <c r="F3941" s="6" t="s">
-        <v>7804</v>
+        <v>7805</v>
       </c>
     </row>
     <row r="3942" spans="3:6">
       <c r="C3942" s="3">
-        <v>300089</v>
+        <v>300087</v>
       </c>
       <c r="D3942" s="4"/>
       <c r="E3942" s="1" t="s">
-        <v>7805</v>
+        <v>7806</v>
       </c>
       <c r="F3942" s="6" t="s">
-        <v>7806</v>
+        <v>7807</v>
       </c>
     </row>
     <row r="3943" spans="3:6">
       <c r="C3943" s="3">
-        <v>300090</v>
+        <v>300088</v>
       </c>
       <c r="D3943" s="4"/>
       <c r="E3943" s="1" t="s">
-        <v>7807</v>
+        <v>7808</v>
       </c>
       <c r="F3943" s="6" t="s">
-        <v>7808</v>
+        <v>7809</v>
       </c>
     </row>
     <row r="3944" spans="3:6">
       <c r="C3944" s="3">
-        <v>300091</v>
+        <v>300089</v>
       </c>
       <c r="D3944" s="4"/>
       <c r="E3944" s="1" t="s">
-        <v>7809</v>
+        <v>7810</v>
       </c>
       <c r="F3944" s="6" t="s">
-        <v>7810</v>
+        <v>7811</v>
       </c>
     </row>
     <row r="3945" spans="3:6">
       <c r="C3945" s="3">
-        <v>300092</v>
+        <v>300090</v>
       </c>
       <c r="D3945" s="4"/>
       <c r="E3945" s="1" t="s">
-        <v>7811</v>
+        <v>7812</v>
       </c>
       <c r="F3945" s="6" t="s">
-        <v>7812</v>
+        <v>7813</v>
       </c>
     </row>
     <row r="3946" spans="3:6">
       <c r="C3946" s="3">
-        <v>300093</v>
+        <v>300091</v>
       </c>
       <c r="D3946" s="4"/>
       <c r="E3946" s="1" t="s">
-        <v>7813</v>
+        <v>7814</v>
       </c>
       <c r="F3946" s="6" t="s">
-        <v>7814</v>
+        <v>7815</v>
       </c>
     </row>
     <row r="3947" spans="3:6">
       <c r="C3947" s="3">
-        <v>300094</v>
+        <v>300092</v>
       </c>
       <c r="D3947" s="4"/>
       <c r="E3947" s="1" t="s">
-        <v>7815</v>
+        <v>7816</v>
       </c>
       <c r="F3947" s="6" t="s">
-        <v>7816</v>
+        <v>7817</v>
       </c>
     </row>
     <row r="3948" spans="3:6">
       <c r="C3948" s="3">
-        <v>300095</v>
+        <v>300093</v>
       </c>
       <c r="D3948" s="4"/>
       <c r="E3948" s="1" t="s">
-        <v>7817</v>
+        <v>7818</v>
       </c>
       <c r="F3948" s="6" t="s">
-        <v>7818</v>
+        <v>7819</v>
       </c>
     </row>
     <row r="3949" spans="3:6">
       <c r="C3949" s="3">
-        <v>300096</v>
+        <v>300094</v>
       </c>
       <c r="D3949" s="4"/>
       <c r="E3949" s="1" t="s">
-        <v>7819</v>
+        <v>7820</v>
       </c>
       <c r="F3949" s="6" t="s">
-        <v>7820</v>
+        <v>7821</v>
       </c>
     </row>
     <row r="3950" spans="3:6">
       <c r="C3950" s="3">
-        <v>300097</v>
+        <v>300095</v>
       </c>
       <c r="D3950" s="4"/>
       <c r="E3950" s="1" t="s">
-        <v>7821</v>
+        <v>7822</v>
       </c>
       <c r="F3950" s="6" t="s">
-        <v>7822</v>
+        <v>7823</v>
       </c>
     </row>
     <row r="3951" spans="3:6">
       <c r="C3951" s="3">
-        <v>300098</v>
+        <v>300096</v>
       </c>
       <c r="D3951" s="4"/>
       <c r="E3951" s="1" t="s">
-        <v>7823</v>
+        <v>7824</v>
       </c>
       <c r="F3951" s="6" t="s">
-        <v>7824</v>
+        <v>7825</v>
       </c>
     </row>
     <row r="3952" spans="3:6">
       <c r="C3952" s="3">
-        <v>300099</v>
+        <v>300097</v>
       </c>
       <c r="D3952" s="4"/>
       <c r="E3952" s="1" t="s">
-        <v>7825</v>
+        <v>7826</v>
       </c>
       <c r="F3952" s="6" t="s">
-        <v>7826</v>
+        <v>7827</v>
       </c>
     </row>
     <row r="3953" spans="3:6">
       <c r="C3953" s="3">
-        <v>300100</v>
+        <v>300098</v>
       </c>
       <c r="D3953" s="4"/>
       <c r="E3953" s="1" t="s">
-        <v>7827</v>
+        <v>7828</v>
       </c>
       <c r="F3953" s="6" t="s">
-        <v>7828</v>
+        <v>7829</v>
       </c>
     </row>
     <row r="3954" spans="3:6">
       <c r="C3954" s="3">
-        <v>300101</v>
+        <v>300099</v>
       </c>
       <c r="D3954" s="4"/>
       <c r="E3954" s="1" t="s">
-        <v>7829</v>
+        <v>7830</v>
       </c>
       <c r="F3954" s="6" t="s">
-        <v>7830</v>
+        <v>7831</v>
       </c>
     </row>
     <row r="3955" spans="3:6">
       <c r="C3955" s="3">
-        <v>300102</v>
+        <v>300100</v>
       </c>
       <c r="D3955" s="4"/>
       <c r="E3955" s="1" t="s">
-        <v>7831</v>
+        <v>7832</v>
       </c>
       <c r="F3955" s="6" t="s">
-        <v>7832</v>
+        <v>7833</v>
       </c>
     </row>
     <row r="3956" spans="3:6">
       <c r="C3956" s="3">
-        <v>300103</v>
+        <v>300101</v>
       </c>
       <c r="D3956" s="4"/>
       <c r="E3956" s="1" t="s">
-        <v>7833</v>
+        <v>7834</v>
       </c>
       <c r="F3956" s="6" t="s">
-        <v>7834</v>
+        <v>7835</v>
       </c>
     </row>
     <row r="3957" spans="3:6">
       <c r="C3957" s="3">
-        <v>300104</v>
+        <v>300102</v>
       </c>
       <c r="D3957" s="4"/>
       <c r="E3957" s="1" t="s">
-        <v>7835</v>
+        <v>7836</v>
       </c>
       <c r="F3957" s="6" t="s">
-        <v>7836</v>
+        <v>7837</v>
       </c>
     </row>
     <row r="3958" spans="3:6">
       <c r="C3958" s="3">
-        <v>300105</v>
+        <v>300103</v>
       </c>
       <c r="D3958" s="4"/>
       <c r="E3958" s="1" t="s">
-        <v>7837</v>
+        <v>7838</v>
       </c>
       <c r="F3958" s="6" t="s">
-        <v>7838</v>
+        <v>7839</v>
       </c>
     </row>
     <row r="3959" spans="3:6">
       <c r="C3959" s="3">
-        <v>300106</v>
+        <v>300104</v>
       </c>
       <c r="D3959" s="4"/>
       <c r="E3959" s="1" t="s">
-        <v>7839</v>
+        <v>7840</v>
       </c>
       <c r="F3959" s="6" t="s">
-        <v>7840</v>
+        <v>7841</v>
       </c>
     </row>
     <row r="3960" spans="3:6">
       <c r="C3960" s="3">
-        <v>300107</v>
+        <v>300105</v>
       </c>
       <c r="D3960" s="4"/>
       <c r="E3960" s="1" t="s">
-        <v>7841</v>
+        <v>7842</v>
       </c>
       <c r="F3960" s="6" t="s">
-        <v>7842</v>
+        <v>7843</v>
       </c>
     </row>
     <row r="3961" spans="3:6">
       <c r="C3961" s="3">
-        <v>300108</v>
+        <v>300106</v>
       </c>
       <c r="D3961" s="4"/>
       <c r="E3961" s="1" t="s">
-        <v>7843</v>
+        <v>7844</v>
       </c>
       <c r="F3961" s="6" t="s">
-        <v>7844</v>
+        <v>7845</v>
       </c>
     </row>
     <row r="3962" spans="3:6">
       <c r="C3962" s="3">
-        <v>300109</v>
+        <v>300107</v>
       </c>
       <c r="D3962" s="4"/>
       <c r="E3962" s="1" t="s">
-        <v>7845</v>
+        <v>7846</v>
       </c>
       <c r="F3962" s="6" t="s">
-        <v>7846</v>
+        <v>7847</v>
       </c>
     </row>
     <row r="3963" spans="3:6">
       <c r="C3963" s="3">
-        <v>300110</v>
-      </c>
-      <c r="D3963"/>
+        <v>300108</v>
+      </c>
+      <c r="D3963" s="4"/>
       <c r="E3963" s="1" t="s">
-        <v>7847</v>
-      </c>
-      <c r="F3963" s="1" t="s">
         <v>7848</v>
+      </c>
+      <c r="F3963" s="6" t="s">
+        <v>7849</v>
       </c>
     </row>
     <row r="3964" spans="3:6">
       <c r="C3964" s="3">
-        <v>300111</v>
-      </c>
-      <c r="D3964"/>
+        <v>300109</v>
+      </c>
+      <c r="D3964" s="4"/>
       <c r="E3964" s="1" t="s">
-        <v>7849</v>
-      </c>
-      <c r="F3964" s="1" t="s">
         <v>7850</v>
+      </c>
+      <c r="F3964" s="6" t="s">
+        <v>7851</v>
       </c>
     </row>
     <row r="3965" spans="3:6">
       <c r="C3965" s="3">
-        <v>300112</v>
-      </c>
+        <v>300110</v>
+      </c>
+      <c r="D3965"/>
       <c r="E3965" s="1" t="s">
-        <v>7851</v>
+        <v>7852</v>
       </c>
       <c r="F3965" s="1" t="s">
-        <v>7852</v>
+        <v>7853</v>
       </c>
     </row>
     <row r="3966" spans="3:6">
       <c r="C3966" s="3">
-        <v>300113</v>
-      </c>
+        <v>300111</v>
+      </c>
+      <c r="D3966"/>
       <c r="E3966" s="1" t="s">
-        <v>7853</v>
+        <v>7854</v>
       </c>
       <c r="F3966" s="1" t="s">
-        <v>7854</v>
+        <v>7855</v>
       </c>
     </row>
     <row r="3967" spans="3:6">
       <c r="C3967" s="3">
-        <v>300114</v>
+        <v>300112</v>
       </c>
       <c r="E3967" s="1" t="s">
-        <v>7855</v>
+        <v>7856</v>
       </c>
       <c r="F3967" s="1" t="s">
-        <v>7856</v>
+        <v>7857</v>
       </c>
     </row>
     <row r="3968" spans="3:6">
       <c r="C3968" s="3">
-        <v>300115</v>
+        <v>300113</v>
       </c>
       <c r="E3968" s="1" t="s">
-        <v>7857</v>
+        <v>7858</v>
       </c>
       <c r="F3968" s="1" t="s">
-        <v>7858</v>
+        <v>7859</v>
       </c>
     </row>
     <row r="3969" spans="3:6">
       <c r="C3969" s="3">
-        <v>300116</v>
+        <v>300114</v>
       </c>
       <c r="E3969" s="1" t="s">
-        <v>7859</v>
+        <v>7860</v>
       </c>
       <c r="F3969" s="1" t="s">
-        <v>1734</v>
+        <v>7861</v>
       </c>
     </row>
     <row r="3970" spans="3:6">
       <c r="C3970" s="3">
-        <v>300117</v>
+        <v>300115</v>
       </c>
       <c r="E3970" s="1" t="s">
-        <v>3182</v>
+        <v>7862</v>
       </c>
       <c r="F3970" s="1" t="s">
-        <v>7860</v>
+        <v>7863</v>
       </c>
     </row>
     <row r="3971" spans="3:6">
       <c r="C3971" s="3">
-        <v>300118</v>
+        <v>300116</v>
       </c>
       <c r="E3971" s="1" t="s">
-        <v>7861</v>
+        <v>7864</v>
       </c>
       <c r="F3971" s="1" t="s">
-        <v>7862</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="3972" spans="3:6">
       <c r="C3972" s="3">
-        <v>300119</v>
+        <v>300117</v>
       </c>
       <c r="E3972" s="1" t="s">
-        <v>7863</v>
+        <v>3182</v>
       </c>
       <c r="F3972" s="1" t="s">
-        <v>7864</v>
+        <v>7865</v>
       </c>
     </row>
     <row r="3973" spans="3:6">
       <c r="C3973" s="3">
-        <v>300120</v>
+        <v>300118</v>
       </c>
       <c r="E3973" s="1" t="s">
-        <v>7865</v>
+        <v>7866</v>
       </c>
       <c r="F3973" s="1" t="s">
-        <v>7866</v>
+        <v>7867</v>
       </c>
     </row>
     <row r="3974" spans="3:6">
       <c r="C3974" s="3">
-        <v>300121</v>
+        <v>300119</v>
       </c>
       <c r="E3974" s="1" t="s">
-        <v>7867</v>
+        <v>7868</v>
       </c>
       <c r="F3974" s="1" t="s">
-        <v>7868</v>
+        <v>7869</v>
       </c>
     </row>
     <row r="3975" spans="3:6">
       <c r="C3975" s="3">
-        <v>300122</v>
+        <v>300120</v>
       </c>
       <c r="E3975" s="1" t="s">
-        <v>7869</v>
+        <v>7870</v>
       </c>
       <c r="F3975" s="1" t="s">
-        <v>7870</v>
+        <v>7871</v>
       </c>
     </row>
     <row r="3976" spans="3:6">
       <c r="C3976" s="3">
-        <v>300123</v>
+        <v>300121</v>
       </c>
       <c r="E3976" s="1" t="s">
-        <v>7871</v>
+        <v>7872</v>
       </c>
       <c r="F3976" s="1" t="s">
-        <v>343</v>
+        <v>7873</v>
       </c>
     </row>
     <row r="3977" spans="3:6">
       <c r="C3977" s="3">
-        <v>300124</v>
+        <v>300122</v>
       </c>
       <c r="E3977" s="1" t="s">
-        <v>7872</v>
+        <v>7874</v>
       </c>
       <c r="F3977" s="1" t="s">
-        <v>7873</v>
+        <v>7875</v>
       </c>
     </row>
     <row r="3978" spans="3:6">
       <c r="C3978" s="3">
-        <v>300125</v>
+        <v>300123</v>
       </c>
       <c r="E3978" s="1" t="s">
-        <v>7874</v>
+        <v>7876</v>
       </c>
       <c r="F3978" s="1" t="s">
-        <v>7875</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3979" spans="3:6">
       <c r="C3979" s="3">
-        <v>300126</v>
+        <v>300124</v>
       </c>
       <c r="E3979" s="1" t="s">
-        <v>7876</v>
+        <v>7877</v>
       </c>
       <c r="F3979" s="1" t="s">
-        <v>7877</v>
+        <v>7878</v>
       </c>
     </row>
     <row r="3980" spans="3:6">
       <c r="C3980" s="3">
-        <v>300127</v>
+        <v>300125</v>
       </c>
       <c r="E3980" s="1" t="s">
-        <v>7878</v>
+        <v>7879</v>
       </c>
       <c r="F3980" s="1" t="s">
-        <v>7879</v>
+        <v>7880</v>
       </c>
     </row>
     <row r="3981" spans="3:6">
       <c r="C3981" s="3">
-        <v>300128</v>
+        <v>300126</v>
       </c>
       <c r="E3981" s="1" t="s">
-        <v>7880</v>
+        <v>7881</v>
       </c>
       <c r="F3981" s="1" t="s">
-        <v>7881</v>
+        <v>7882</v>
       </c>
     </row>
     <row r="3982" spans="3:6">
       <c r="C3982" s="3">
-        <v>300129</v>
+        <v>300127</v>
       </c>
       <c r="E3982" s="1" t="s">
-        <v>7882</v>
+        <v>7883</v>
       </c>
       <c r="F3982" s="1" t="s">
-        <v>7883</v>
+        <v>7884</v>
       </c>
     </row>
     <row r="3983" spans="3:6">
       <c r="C3983" s="3">
-        <v>300130</v>
+        <v>300128</v>
       </c>
       <c r="E3983" s="1" t="s">
-        <v>7884</v>
+        <v>7885</v>
       </c>
       <c r="F3983" s="1" t="s">
-        <v>7885</v>
+        <v>7886</v>
       </c>
     </row>
     <row r="3984" spans="3:6">
       <c r="C3984" s="3">
-        <v>300131</v>
+        <v>300129</v>
       </c>
       <c r="E3984" s="1" t="s">
-        <v>7886</v>
+        <v>7887</v>
       </c>
       <c r="F3984" s="1" t="s">
-        <v>7887</v>
+        <v>7888</v>
       </c>
     </row>
     <row r="3985" spans="2:6">
       <c r="C3985" s="3">
-        <v>300132</v>
+        <v>300130</v>
       </c>
       <c r="E3985" s="1" t="s">
-        <v>7888</v>
+        <v>7889</v>
       </c>
       <c r="F3985" s="1" t="s">
-        <v>7889</v>
+        <v>7890</v>
       </c>
     </row>
     <row r="3986" spans="2:6">
       <c r="C3986" s="3">
-        <v>300133</v>
+        <v>300131</v>
       </c>
       <c r="E3986" s="1" t="s">
-        <v>7890</v>
+        <v>7891</v>
       </c>
       <c r="F3986" s="1" t="s">
-        <v>7891</v>
+        <v>7892</v>
       </c>
     </row>
     <row r="3987" spans="2:6">
       <c r="C3987" s="3">
-        <v>300134</v>
+        <v>300132</v>
       </c>
       <c r="E3987" s="1" t="s">
-        <v>7892</v>
+        <v>7893</v>
       </c>
       <c r="F3987" s="1" t="s">
-        <v>7893</v>
+        <v>7894</v>
       </c>
     </row>
     <row r="3988" spans="2:6">
       <c r="C3988" s="3">
+        <v>300133</v>
+      </c>
+      <c r="E3988" s="1" t="s">
+        <v>7895</v>
+      </c>
+      <c r="F3988" s="1" t="s">
+        <v>7896</v>
+      </c>
+    </row>
+    <row r="3989" spans="2:6">
+      <c r="C3989" s="3">
+        <v>300134</v>
+      </c>
+      <c r="E3989" s="1" t="s">
+        <v>7897</v>
+      </c>
+      <c r="F3989" s="1" t="s">
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="3990" spans="2:6">
+      <c r="C3990" s="3">
         <v>300135</v>
       </c>
-      <c r="E3988" s="1" t="s">
-        <v>7894</v>
-      </c>
-      <c r="F3988" s="1" t="s">
-        <v>7895</v>
-      </c>
-    </row>
-    <row r="3989" spans="2:6">
-      <c r="B3989" s="3"/>
-      <c r="C3989" s="3">
-        <v>300136</v>
-      </c>
-      <c r="E3989" s="1" t="s">
-        <v>7896</v>
-      </c>
-      <c r="F3989" s="1" t="s">
-        <v>7897</v>
-      </c>
-    </row>
-    <row r="3990" spans="2:6">
-      <c r="B3990" s="3"/>
-      <c r="C3990" s="3">
-        <v>300137</v>
-      </c>
       <c r="E3990" s="1" t="s">
-        <v>7898</v>
+        <v>7899</v>
       </c>
       <c r="F3990" s="1" t="s">
-        <v>7899</v>
+        <v>7900</v>
       </c>
     </row>
     <row r="3991" spans="2:6">
       <c r="B3991" s="3"/>
       <c r="C3991" s="3">
-        <v>300138</v>
+        <v>300136</v>
       </c>
       <c r="E3991" s="1" t="s">
-        <v>7900</v>
+        <v>7901</v>
       </c>
       <c r="F3991" s="1" t="s">
-        <v>7901</v>
+        <v>7902</v>
       </c>
     </row>
     <row r="3992" spans="2:6">
       <c r="B3992" s="3"/>
       <c r="C3992" s="3">
-        <v>300139</v>
+        <v>300137</v>
       </c>
       <c r="E3992" s="1" t="s">
-        <v>7902</v>
+        <v>7903</v>
       </c>
       <c r="F3992" s="1" t="s">
-        <v>7903</v>
+        <v>7904</v>
       </c>
     </row>
     <row r="3993" spans="2:6">
       <c r="B3993" s="3"/>
       <c r="C3993" s="3">
-        <v>300140</v>
+        <v>300138</v>
       </c>
       <c r="E3993" s="1" t="s">
-        <v>7904</v>
+        <v>7905</v>
       </c>
       <c r="F3993" s="1" t="s">
-        <v>7905</v>
+        <v>7906</v>
       </c>
     </row>
     <row r="3994" spans="2:6">
       <c r="B3994" s="3"/>
       <c r="C3994" s="3">
-        <v>300141</v>
+        <v>300139</v>
       </c>
       <c r="E3994" s="1" t="s">
-        <v>7906</v>
+        <v>7907</v>
       </c>
       <c r="F3994" s="1" t="s">
-        <v>7907</v>
+        <v>7908</v>
       </c>
     </row>
     <row r="3995" spans="2:6">
       <c r="B3995" s="3"/>
       <c r="C3995" s="3">
-        <v>300142</v>
+        <v>300140</v>
       </c>
       <c r="E3995" s="1" t="s">
-        <v>7908</v>
+        <v>7909</v>
       </c>
       <c r="F3995" s="1" t="s">
-        <v>7909</v>
+        <v>7910</v>
       </c>
     </row>
     <row r="3996" spans="2:6">
       <c r="B3996" s="3"/>
       <c r="C3996" s="3">
-        <v>300143</v>
+        <v>300141</v>
       </c>
       <c r="E3996" s="1" t="s">
-        <v>7910</v>
+        <v>7911</v>
       </c>
       <c r="F3996" s="1" t="s">
-        <v>7911</v>
+        <v>7912</v>
       </c>
     </row>
     <row r="3997" spans="2:6">
       <c r="B3997" s="3"/>
       <c r="C3997" s="3">
-        <v>300144</v>
+        <v>300142</v>
       </c>
       <c r="E3997" s="1" t="s">
-        <v>7912</v>
+        <v>7913</v>
       </c>
       <c r="F3997" s="1" t="s">
-        <v>7913</v>
+        <v>7914</v>
       </c>
     </row>
     <row r="3998" spans="2:6">
       <c r="B3998" s="3"/>
       <c r="C3998" s="3">
-        <v>300145</v>
+        <v>300143</v>
       </c>
       <c r="E3998" s="1" t="s">
-        <v>7914</v>
+        <v>7915</v>
       </c>
       <c r="F3998" s="1" t="s">
-        <v>7915</v>
+        <v>7916</v>
       </c>
     </row>
     <row r="3999" spans="2:6">
       <c r="B3999" s="3"/>
       <c r="C3999" s="3">
-        <v>300146</v>
+        <v>300144</v>
       </c>
       <c r="E3999" s="1" t="s">
-        <v>7916</v>
+        <v>7917</v>
       </c>
       <c r="F3999" s="1" t="s">
-        <v>7917</v>
+        <v>7918</v>
       </c>
     </row>
     <row r="4000" spans="2:6">
       <c r="B4000" s="3"/>
       <c r="C4000" s="3">
-        <v>300147</v>
+        <v>300145</v>
       </c>
       <c r="E4000" s="1" t="s">
-        <v>7918</v>
+        <v>7919</v>
       </c>
       <c r="F4000" s="1" t="s">
-        <v>7919</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="4001" spans="2:6">
       <c r="B4001" s="3"/>
       <c r="C4001" s="3">
-        <v>300148</v>
+        <v>300146</v>
       </c>
       <c r="E4001" s="1" t="s">
-        <v>7920</v>
+        <v>7921</v>
       </c>
       <c r="F4001" s="1" t="s">
-        <v>7921</v>
+        <v>7922</v>
       </c>
     </row>
     <row r="4002" spans="2:6">
       <c r="B4002" s="3"/>
       <c r="C4002" s="3">
-        <v>300149</v>
+        <v>300147</v>
       </c>
       <c r="E4002" s="1" t="s">
-        <v>2906</v>
+        <v>7923</v>
       </c>
       <c r="F4002" s="1" t="s">
-        <v>7922</v>
+        <v>7924</v>
       </c>
     </row>
     <row r="4003" spans="2:6">
       <c r="B4003" s="3"/>
       <c r="C4003" s="3">
-        <v>300150</v>
+        <v>300148</v>
       </c>
       <c r="E4003" s="1" t="s">
-        <v>7923</v>
+        <v>7925</v>
       </c>
       <c r="F4003" s="1" t="s">
-        <v>7924</v>
+        <v>7926</v>
       </c>
     </row>
     <row r="4004" spans="2:6">
       <c r="B4004" s="3"/>
       <c r="C4004" s="3">
-        <v>300151</v>
+        <v>300149</v>
       </c>
       <c r="E4004" s="1" t="s">
-        <v>7925</v>
+        <v>2906</v>
       </c>
       <c r="F4004" s="1" t="s">
-        <v>7926</v>
+        <v>7927</v>
       </c>
     </row>
     <row r="4005" spans="2:6">
       <c r="B4005" s="3"/>
       <c r="C4005" s="3">
+        <v>300150</v>
+      </c>
+      <c r="E4005" s="1" t="s">
+        <v>7928</v>
+      </c>
+      <c r="F4005" s="1" t="s">
+        <v>7929</v>
+      </c>
+    </row>
+    <row r="4006" spans="2:6">
+      <c r="B4006" s="3"/>
+      <c r="C4006" s="3">
+        <v>300151</v>
+      </c>
+      <c r="E4006" s="1" t="s">
+        <v>7930</v>
+      </c>
+      <c r="F4006" s="1" t="s">
+        <v>7931</v>
+      </c>
+    </row>
+    <row r="4007" spans="2:6">
+      <c r="B4007" s="3"/>
+      <c r="C4007" s="3">
         <v>300152</v>
       </c>
-      <c r="E4005" s="1" t="s">
-        <v>7927</v>
-      </c>
-      <c r="F4005" s="1" t="s">
-        <v>7928</v>
-      </c>
-    </row>
-    <row r="4006" spans="2:6">
-      <c r="C4006" s="3">
-        <v>300153</v>
-      </c>
-      <c r="E4006" s="1" t="s">
-        <v>7929</v>
-      </c>
-      <c r="F4006" s="1" t="s">
-        <v>7930</v>
-      </c>
-    </row>
-    <row r="4007" spans="2:6">
-      <c r="C4007" s="3">
-        <v>300154</v>
-      </c>
       <c r="E4007" s="1" t="s">
-        <v>7931</v>
+        <v>7932</v>
       </c>
       <c r="F4007" s="1" t="s">
-        <v>7932</v>
+        <v>7933</v>
       </c>
     </row>
     <row r="4008" spans="2:6">
       <c r="C4008" s="3">
-        <v>300155</v>
+        <v>300153</v>
       </c>
       <c r="E4008" s="1" t="s">
-        <v>7933</v>
+        <v>7934</v>
       </c>
       <c r="F4008" s="1" t="s">
-        <v>7934</v>
+        <v>7935</v>
       </c>
     </row>
     <row r="4009" spans="2:6">
       <c r="C4009" s="3">
-        <v>300156</v>
+        <v>300154</v>
       </c>
       <c r="E4009" s="1" t="s">
-        <v>7935</v>
+        <v>7936</v>
       </c>
       <c r="F4009" s="1" t="s">
-        <v>7936</v>
+        <v>7937</v>
       </c>
     </row>
     <row r="4010" spans="2:6">
       <c r="C4010" s="3">
-        <v>300157</v>
+        <v>300155</v>
       </c>
       <c r="E4010" s="1" t="s">
-        <v>7937</v>
+        <v>7938</v>
       </c>
       <c r="F4010" s="1" t="s">
-        <v>7938</v>
+        <v>7939</v>
       </c>
     </row>
     <row r="4011" spans="2:6">
       <c r="C4011" s="3">
-        <v>300158</v>
+        <v>300156</v>
       </c>
       <c r="E4011" s="1" t="s">
-        <v>7939</v>
+        <v>7940</v>
       </c>
       <c r="F4011" s="1" t="s">
-        <v>7940</v>
+        <v>7941</v>
       </c>
     </row>
     <row r="4012" spans="2:6">
       <c r="C4012" s="3">
-        <v>300159</v>
+        <v>300157</v>
       </c>
       <c r="E4012" s="1" t="s">
-        <v>7941</v>
+        <v>7942</v>
       </c>
       <c r="F4012" s="1" t="s">
-        <v>7942</v>
+        <v>7943</v>
       </c>
     </row>
     <row r="4013" spans="2:6">
       <c r="C4013" s="3">
-        <v>300160</v>
+        <v>300158</v>
       </c>
       <c r="E4013" s="1" t="s">
-        <v>7943</v>
+        <v>7944</v>
       </c>
       <c r="F4013" s="1" t="s">
-        <v>7944</v>
+        <v>7945</v>
       </c>
     </row>
     <row r="4014" spans="2:6">
       <c r="C4014" s="3">
-        <v>300161</v>
+        <v>300159</v>
       </c>
       <c r="E4014" s="1" t="s">
-        <v>7945</v>
+        <v>7946</v>
       </c>
       <c r="F4014" s="1" t="s">
-        <v>7946</v>
+        <v>7947</v>
       </c>
     </row>
     <row r="4015" spans="2:6">
       <c r="C4015" s="3">
-        <v>300162</v>
+        <v>300160</v>
       </c>
       <c r="E4015" s="1" t="s">
-        <v>7947</v>
+        <v>7948</v>
       </c>
       <c r="F4015" s="1" t="s">
-        <v>7948</v>
+        <v>7949</v>
       </c>
     </row>
     <row r="4016" spans="2:6">
       <c r="C4016" s="3">
-        <v>300163</v>
+        <v>300161</v>
       </c>
       <c r="E4016" s="1" t="s">
-        <v>7949</v>
+        <v>7950</v>
       </c>
       <c r="F4016" s="1" t="s">
-        <v>7950</v>
+        <v>7951</v>
       </c>
     </row>
     <row r="4017" spans="3:6">
       <c r="C4017" s="3">
-        <v>300164</v>
+        <v>300162</v>
       </c>
       <c r="E4017" s="1" t="s">
-        <v>7951</v>
+        <v>7952</v>
       </c>
       <c r="F4017" s="1" t="s">
-        <v>7952</v>
+        <v>7953</v>
       </c>
     </row>
     <row r="4018" spans="3:6">
       <c r="C4018" s="3">
-        <v>300165</v>
+        <v>300163</v>
       </c>
       <c r="E4018" s="1" t="s">
-        <v>7953</v>
+        <v>7954</v>
       </c>
       <c r="F4018" s="1" t="s">
-        <v>7954</v>
+        <v>7955</v>
       </c>
     </row>
     <row r="4019" spans="3:6">
       <c r="C4019" s="3">
-        <v>300166</v>
+        <v>300164</v>
       </c>
       <c r="E4019" s="1" t="s">
-        <v>1068</v>
+        <v>7956</v>
       </c>
       <c r="F4019" s="1" t="s">
-        <v>7955</v>
+        <v>7957</v>
       </c>
     </row>
     <row r="4020" spans="3:6">
       <c r="C4020" s="3">
-        <v>300167</v>
+        <v>300165</v>
       </c>
       <c r="E4020" s="1" t="s">
-        <v>1070</v>
+        <v>7958</v>
       </c>
       <c r="F4020" s="1" t="s">
-        <v>7956</v>
+        <v>7959</v>
       </c>
     </row>
     <row r="4021" spans="3:6">
       <c r="C4021" s="3">
-        <v>300168</v>
+        <v>300166</v>
       </c>
       <c r="E4021" s="1" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="F4021" s="1" t="s">
-        <v>7957</v>
+        <v>7960</v>
       </c>
     </row>
     <row r="4022" spans="3:6">
       <c r="C4022" s="3">
-        <v>300169</v>
+        <v>300167</v>
       </c>
       <c r="E4022" s="1" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="F4022" s="1" t="s">
-        <v>7958</v>
+        <v>7961</v>
       </c>
     </row>
     <row r="4023" spans="3:6">
       <c r="C4023" s="3">
-        <v>300170</v>
+        <v>300168</v>
       </c>
       <c r="E4023" s="1" t="s">
-        <v>7959</v>
+        <v>1072</v>
       </c>
       <c r="F4023" s="1" t="s">
-        <v>1254</v>
+        <v>7962</v>
       </c>
     </row>
     <row r="4024" spans="3:6">
       <c r="C4024" s="3">
-        <v>300171</v>
+        <v>300169</v>
       </c>
       <c r="E4024" s="1" t="s">
-        <v>7960</v>
+        <v>1074</v>
       </c>
       <c r="F4024" s="1" t="s">
-        <v>7961</v>
+        <v>7963</v>
       </c>
     </row>
     <row r="4025" spans="3:6">
       <c r="C4025" s="3">
-        <v>300172</v>
+        <v>300170</v>
       </c>
       <c r="E4025" s="1" t="s">
-        <v>7962</v>
+        <v>7964</v>
       </c>
       <c r="F4025" s="1" t="s">
-        <v>7963</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="4026" spans="3:6">
       <c r="C4026" s="3">
-        <v>300173</v>
+        <v>300171</v>
       </c>
       <c r="E4026" s="1" t="s">
-        <v>7964</v>
+        <v>7965</v>
       </c>
       <c r="F4026" s="1" t="s">
-        <v>7965</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="4027" spans="3:6">
       <c r="C4027" s="3">
-        <v>300174</v>
+        <v>300172</v>
       </c>
       <c r="E4027" s="1" t="s">
-        <v>7966</v>
+        <v>7967</v>
       </c>
       <c r="F4027" s="1" t="s">
-        <v>7967</v>
+        <v>7968</v>
       </c>
     </row>
     <row r="4028" spans="3:6">
       <c r="C4028" s="3">
-        <v>300175</v>
+        <v>300173</v>
       </c>
       <c r="E4028" s="1" t="s">
-        <v>7968</v>
+        <v>7969</v>
       </c>
       <c r="F4028" s="1" t="s">
-        <v>7969</v>
+        <v>7970</v>
       </c>
     </row>
     <row r="4029" spans="3:6">
       <c r="C4029" s="3">
-        <v>300176</v>
+        <v>300174</v>
       </c>
       <c r="E4029" s="1" t="s">
-        <v>7970</v>
+        <v>7971</v>
       </c>
       <c r="F4029" s="1" t="s">
-        <v>7971</v>
+        <v>7972</v>
       </c>
     </row>
     <row r="4030" spans="3:6">
       <c r="C4030" s="3">
-        <v>300177</v>
+        <v>300175</v>
       </c>
       <c r="E4030" s="1" t="s">
-        <v>7972</v>
+        <v>7973</v>
       </c>
       <c r="F4030" s="1" t="s">
-        <v>2357</v>
+        <v>7974</v>
       </c>
     </row>
     <row r="4031" spans="3:6">
       <c r="C4031" s="3">
-        <v>300178</v>
+        <v>300176</v>
       </c>
       <c r="E4031" s="1" t="s">
-        <v>7973</v>
+        <v>7975</v>
       </c>
       <c r="F4031" s="1" t="s">
-        <v>7974</v>
+        <v>7976</v>
       </c>
     </row>
     <row r="4032" spans="3:6">
       <c r="C4032" s="3">
-        <v>300179</v>
+        <v>300177</v>
       </c>
       <c r="E4032" s="1" t="s">
-        <v>7975</v>
+        <v>7977</v>
       </c>
       <c r="F4032" s="1" t="s">
-        <v>678</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="4033" spans="3:6">
       <c r="C4033" s="3">
-        <v>300180</v>
+        <v>300178</v>
       </c>
       <c r="E4033" s="1" t="s">
-        <v>7976</v>
+        <v>7978</v>
       </c>
       <c r="F4033" s="1" t="s">
-        <v>7977</v>
+        <v>7979</v>
       </c>
     </row>
     <row r="4034" spans="3:6">
       <c r="C4034" s="3">
-        <v>300181</v>
+        <v>300179</v>
       </c>
       <c r="E4034" s="1" t="s">
-        <v>7978</v>
+        <v>7980</v>
       </c>
       <c r="F4034" s="1" t="s">
-        <v>7979</v>
+        <v>678</v>
       </c>
     </row>
     <row r="4035" spans="3:6">
       <c r="C4035" s="3">
-        <v>300182</v>
+        <v>300180</v>
       </c>
       <c r="E4035" s="1" t="s">
-        <v>7980</v>
+        <v>7981</v>
       </c>
       <c r="F4035" s="1" t="s">
-        <v>7981</v>
+        <v>7982</v>
       </c>
     </row>
     <row r="4036" spans="3:6">
       <c r="C4036" s="3">
-        <v>300183</v>
+        <v>300181</v>
       </c>
       <c r="E4036" s="1" t="s">
-        <v>7982</v>
+        <v>7983</v>
       </c>
       <c r="F4036" s="1" t="s">
-        <v>7983</v>
+        <v>7984</v>
       </c>
     </row>
     <row r="4037" spans="3:6">
       <c r="C4037" s="3">
-        <v>300184</v>
+        <v>300182</v>
       </c>
       <c r="E4037" s="1" t="s">
-        <v>4328</v>
+        <v>7985</v>
       </c>
       <c r="F4037" s="1" t="s">
-        <v>718</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="4038" spans="3:6">
       <c r="C4038" s="3">
-        <v>300185</v>
+        <v>300183</v>
       </c>
       <c r="E4038" s="1" t="s">
-        <v>7984</v>
+        <v>7987</v>
       </c>
       <c r="F4038" s="1" t="s">
-        <v>7985</v>
+        <v>7988</v>
       </c>
     </row>
     <row r="4039" spans="3:6">
       <c r="C4039" s="3">
-        <v>300186</v>
+        <v>300184</v>
       </c>
       <c r="E4039" s="1" t="s">
-        <v>7986</v>
+        <v>4328</v>
       </c>
       <c r="F4039" s="1" t="s">
         <v>718</v>
@@ -73719,145 +73736,167 @@
     </row>
     <row r="4040" spans="3:6">
       <c r="C4040" s="3">
-        <v>300187</v>
+        <v>300185</v>
       </c>
       <c r="E4040" s="1" t="s">
-        <v>7987</v>
+        <v>7989</v>
       </c>
       <c r="F4040" s="1" t="s">
-        <v>7988</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="4041" spans="3:6">
       <c r="C4041" s="3">
-        <v>300188</v>
+        <v>300186</v>
       </c>
       <c r="E4041" s="1" t="s">
-        <v>7989</v>
+        <v>7991</v>
       </c>
       <c r="F4041" s="1" t="s">
-        <v>7990</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4042" spans="3:6">
       <c r="C4042" s="3">
-        <v>300189</v>
+        <v>300187</v>
       </c>
       <c r="E4042" s="1" t="s">
-        <v>7991</v>
+        <v>7992</v>
       </c>
       <c r="F4042" s="1" t="s">
-        <v>7992</v>
+        <v>7993</v>
       </c>
     </row>
     <row r="4043" spans="3:6">
       <c r="C4043" s="3">
-        <v>300190</v>
+        <v>300188</v>
       </c>
       <c r="E4043" s="1" t="s">
-        <v>7993</v>
+        <v>7994</v>
       </c>
       <c r="F4043" s="1" t="s">
-        <v>7994</v>
+        <v>7995</v>
       </c>
     </row>
     <row r="4044" spans="3:6">
       <c r="C4044" s="3">
-        <v>300191</v>
+        <v>300189</v>
       </c>
       <c r="E4044" s="1" t="s">
-        <v>7995</v>
+        <v>7996</v>
       </c>
       <c r="F4044" s="1" t="s">
-        <v>7996</v>
+        <v>7997</v>
       </c>
     </row>
     <row r="4045" spans="3:6">
       <c r="C4045" s="3">
-        <v>300192</v>
+        <v>300190</v>
       </c>
       <c r="E4045" s="1" t="s">
-        <v>7997</v>
+        <v>7998</v>
       </c>
       <c r="F4045" s="1" t="s">
-        <v>7998</v>
+        <v>7999</v>
       </c>
     </row>
     <row r="4046" spans="3:6">
       <c r="C4046" s="3">
-        <v>300193</v>
+        <v>300191</v>
       </c>
       <c r="E4046" s="1" t="s">
-        <v>7999</v>
+        <v>8000</v>
       </c>
       <c r="F4046" s="1" t="s">
-        <v>8000</v>
+        <v>8001</v>
       </c>
     </row>
     <row r="4047" spans="3:6">
       <c r="C4047" s="3">
-        <v>300194</v>
+        <v>300192</v>
       </c>
       <c r="E4047" s="1" t="s">
-        <v>8001</v>
+        <v>8002</v>
       </c>
       <c r="F4047" s="1" t="s">
-        <v>8002</v>
+        <v>8003</v>
       </c>
     </row>
     <row r="4048" spans="3:6">
       <c r="C4048" s="3">
-        <v>300195</v>
+        <v>300193</v>
       </c>
       <c r="E4048" s="1" t="s">
-        <v>8003</v>
+        <v>8004</v>
       </c>
       <c r="F4048" s="1" t="s">
-        <v>8004</v>
+        <v>8005</v>
       </c>
     </row>
     <row r="4049" spans="3:6">
       <c r="C4049" s="3">
-        <v>300196</v>
+        <v>300194</v>
       </c>
       <c r="E4049" s="1" t="s">
-        <v>8005</v>
+        <v>8006</v>
       </c>
       <c r="F4049" s="1" t="s">
-        <v>8006</v>
+        <v>8007</v>
       </c>
     </row>
     <row r="4050" spans="3:6">
       <c r="C4050" s="3">
-        <v>300197</v>
+        <v>300195</v>
       </c>
       <c r="E4050" s="1" t="s">
-        <v>8007</v>
+        <v>8008</v>
       </c>
       <c r="F4050" s="1" t="s">
-        <v>8008</v>
+        <v>8009</v>
       </c>
     </row>
     <row r="4051" spans="3:6">
       <c r="C4051" s="3">
-        <v>300198</v>
+        <v>300196</v>
       </c>
       <c r="E4051" s="1" t="s">
-        <v>8009</v>
+        <v>8010</v>
       </c>
       <c r="F4051" s="1" t="s">
-        <v>8010</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="4052" spans="3:6">
       <c r="C4052" s="3">
+        <v>300197</v>
+      </c>
+      <c r="E4052" s="1" t="s">
+        <v>8012</v>
+      </c>
+      <c r="F4052" s="1" t="s">
+        <v>8013</v>
+      </c>
+    </row>
+    <row r="4053" spans="3:6">
+      <c r="C4053" s="3">
+        <v>300198</v>
+      </c>
+      <c r="E4053" s="1" t="s">
+        <v>8014</v>
+      </c>
+      <c r="F4053" s="1" t="s">
+        <v>8015</v>
+      </c>
+    </row>
+    <row r="4054" spans="3:6">
+      <c r="C4054" s="3">
         <v>300199</v>
       </c>
-      <c r="E4052" s="1" t="s">
-        <v>8011</v>
-      </c>
-      <c r="F4052" s="1" t="s">
-        <v>8012</v>
+      <c r="E4054" s="1" t="s">
+        <v>8016</v>
+      </c>
+      <c r="F4054" s="1" t="s">
+        <v>8017</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MulLanguageConfig.xlsx
+++ b/Excel/MulLanguageConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8226" uniqueCount="8018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8266" uniqueCount="8057">
   <si>
     <t>c</t>
   </si>
@@ -22928,25 +22928,142 @@
     <t>2026第一赛季</t>
   </si>
   <si>
-    <t>2026 Season 1</t>
+    <t>The first season of 2026</t>
   </si>
   <si>
     <t>2026第二赛季</t>
   </si>
   <si>
-    <t>2026 Season 2</t>
+    <t>The second season of 2026</t>
   </si>
   <si>
     <t>2026第三赛季</t>
   </si>
   <si>
-    <t>2026 Season 3</t>
+    <t>The third season of 2026</t>
   </si>
   <si>
     <t>2026第四赛季</t>
   </si>
   <si>
-    <t>2026 Season 4</t>
+    <t>The fourth season of 2026</t>
+  </si>
+  <si>
+    <t>2027第一赛季</t>
+  </si>
+  <si>
+    <t>The first season of 2027</t>
+  </si>
+  <si>
+    <t>2027第二赛季</t>
+  </si>
+  <si>
+    <t>The second season of 2027</t>
+  </si>
+  <si>
+    <t>2027第三赛季</t>
+  </si>
+  <si>
+    <t>The third season of 2027</t>
+  </si>
+  <si>
+    <t>2027第四赛季</t>
+  </si>
+  <si>
+    <t>The fourth season of 2027</t>
+  </si>
+  <si>
+    <t>巨刃士</t>
+  </si>
+  <si>
+    <t>Greatsword Warrior</t>
+  </si>
+  <si>
+    <t>全区第一巨刃士</t>
+  </si>
+  <si>
+    <t>The first Greatsword Warrior in the region</t>
+  </si>
+  <si>
+    <t>全区第二巨刃士</t>
+  </si>
+  <si>
+    <t>The second Greatsword Warrior in the region</t>
+  </si>
+  <si>
+    <t>全区第三巨刃士</t>
+  </si>
+  <si>
+    <t>The third Greatsword Warrior in the region</t>
+  </si>
+  <si>
+    <t>隐私协议</t>
+  </si>
+  <si>
+    <t>Privacy Agreement</t>
+  </si>
+  <si>
+    <t>黄\n金</t>
+  </si>
+  <si>
+    <t>钻\n石</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+  <si>
+    <t>未领取</t>
+  </si>
+  <si>
+    <t>Unclaimed</t>
+  </si>
+  <si>
+    <t>1. 充值30元开启</t>
+  </si>
+  <si>
+    <t>1. Recharge 30 Yuan to Unlock</t>
+  </si>
+  <si>
+    <t>2. 每天可以领取一份超值的奖励</t>
+  </si>
+  <si>
+    <t>2. Claim one reward per day</t>
+  </si>
+  <si>
+    <t>3. 可以连续领取7天</t>
+  </si>
+  <si>
+    <t>3. Available for 7 days</t>
+  </si>
+  <si>
+    <t>4. 此活动正常累计对应的冒险家积分</t>
+  </si>
+  <si>
+    <t>4. Adventurer Points can be accumulated</t>
+  </si>
+  <si>
+    <t>次数：</t>
+  </si>
+  <si>
+    <t>Times：</t>
+  </si>
+  <si>
+    <t>开启黄金卡</t>
+  </si>
+  <si>
+    <t>Open Gold Card</t>
+  </si>
+  <si>
+    <t>开启钻石卡</t>
+  </si>
+  <si>
+    <t>Open Diamond Card</t>
+  </si>
+  <si>
+    <t>1. 充值98元开启</t>
+  </si>
+  <si>
+    <t>1. Recharge 98 Yuan to Unlock</t>
   </si>
   <si>
     <t>合区补偿</t>
@@ -25089,7 +25206,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:F4054"/>
+  <dimension ref="B2:F4074"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
@@ -71582,11 +71699,9 @@
     </row>
     <row r="3856" spans="3:6">
       <c r="C3856" s="3">
-        <v>300001</v>
-      </c>
-      <c r="D3856" s="4" t="s">
-        <v>1961</v>
-      </c>
+        <v>203739</v>
+      </c>
+      <c r="D3856" s="4"/>
       <c r="E3856" s="1" t="s">
         <v>7640</v>
       </c>
@@ -71596,7 +71711,7 @@
     </row>
     <row r="3857" spans="3:6">
       <c r="C3857" s="3">
-        <v>300002</v>
+        <v>203740</v>
       </c>
       <c r="D3857" s="4"/>
       <c r="E3857" s="1" t="s">
@@ -71608,7 +71723,7 @@
     </row>
     <row r="3858" spans="3:6">
       <c r="C3858" s="3">
-        <v>300003</v>
+        <v>203741</v>
       </c>
       <c r="D3858" s="4"/>
       <c r="E3858" s="1" t="s">
@@ -71620,7 +71735,7 @@
     </row>
     <row r="3859" spans="3:6">
       <c r="C3859" s="3">
-        <v>300004</v>
+        <v>203742</v>
       </c>
       <c r="D3859" s="4"/>
       <c r="E3859" s="1" t="s">
@@ -71632,7 +71747,7 @@
     </row>
     <row r="3860" spans="3:6">
       <c r="C3860" s="3">
-        <v>300005</v>
+        <v>203743</v>
       </c>
       <c r="D3860" s="4"/>
       <c r="E3860" s="1" t="s">
@@ -71644,43 +71759,43 @@
     </row>
     <row r="3861" spans="3:6">
       <c r="C3861" s="3">
-        <v>300006</v>
+        <v>203744</v>
       </c>
       <c r="D3861" s="4"/>
       <c r="E3861" s="1" t="s">
         <v>7650</v>
       </c>
-      <c r="F3861" s="8" t="s">
+      <c r="F3861" s="6" t="s">
         <v>7651</v>
       </c>
     </row>
     <row r="3862" spans="3:6">
       <c r="C3862" s="3">
-        <v>300007</v>
+        <v>203745</v>
       </c>
       <c r="D3862" s="4"/>
       <c r="E3862" s="1" t="s">
         <v>7652</v>
       </c>
-      <c r="F3862" s="8" t="s">
+      <c r="F3862" s="6" t="s">
         <v>7653</v>
       </c>
     </row>
     <row r="3863" spans="3:6">
       <c r="C3863" s="3">
-        <v>300008</v>
+        <v>203746</v>
       </c>
       <c r="D3863" s="4"/>
       <c r="E3863" s="1" t="s">
         <v>7654</v>
       </c>
-      <c r="F3863" s="8" t="s">
+      <c r="F3863" s="6" t="s">
         <v>7655</v>
       </c>
     </row>
     <row r="3864" spans="3:6">
       <c r="C3864" s="3">
-        <v>300009</v>
+        <v>203747</v>
       </c>
       <c r="D3864" s="4"/>
       <c r="E3864" s="1" t="s">
@@ -71692,155 +71807,157 @@
     </row>
     <row r="3865" spans="3:6">
       <c r="C3865" s="3">
-        <v>300010</v>
+        <v>203748</v>
       </c>
       <c r="D3865" s="4"/>
       <c r="E3865" s="1" t="s">
         <v>7658</v>
       </c>
       <c r="F3865" s="8" t="s">
-        <v>7659</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="3866" spans="3:6">
       <c r="C3866" s="3">
-        <v>300011</v>
+        <v>203749</v>
       </c>
       <c r="D3866" s="4"/>
       <c r="E3866" s="1" t="s">
+        <v>7659</v>
+      </c>
+      <c r="F3866" s="8" t="s">
         <v>7660</v>
-      </c>
-      <c r="F3866" s="8" t="s">
-        <v>7661</v>
       </c>
     </row>
     <row r="3867" spans="3:6">
       <c r="C3867" s="3">
-        <v>300012</v>
+        <v>203750</v>
       </c>
       <c r="D3867" s="4"/>
       <c r="E3867" s="1" t="s">
+        <v>7661</v>
+      </c>
+      <c r="F3867" s="8" t="s">
         <v>7662</v>
-      </c>
-      <c r="F3867" s="8" t="s">
-        <v>7663</v>
       </c>
     </row>
     <row r="3868" spans="3:6">
       <c r="C3868" s="3">
-        <v>300013</v>
+        <v>203751</v>
       </c>
       <c r="D3868" s="4"/>
       <c r="E3868" s="1" t="s">
+        <v>7663</v>
+      </c>
+      <c r="F3868" s="8" t="s">
         <v>7664</v>
-      </c>
-      <c r="F3868" s="8" t="s">
-        <v>7665</v>
       </c>
     </row>
     <row r="3869" spans="3:6">
       <c r="C3869" s="3">
-        <v>300014</v>
+        <v>203752</v>
       </c>
       <c r="D3869" s="4"/>
       <c r="E3869" s="1" t="s">
+        <v>7665</v>
+      </c>
+      <c r="F3869" s="8" t="s">
         <v>7666</v>
-      </c>
-      <c r="F3869" s="8" t="s">
-        <v>7667</v>
       </c>
     </row>
     <row r="3870" spans="3:6">
       <c r="C3870" s="3">
-        <v>300015</v>
+        <v>203753</v>
       </c>
       <c r="D3870" s="4"/>
       <c r="E3870" s="1" t="s">
+        <v>7667</v>
+      </c>
+      <c r="F3870" s="8" t="s">
         <v>7668</v>
-      </c>
-      <c r="F3870" s="8" t="s">
-        <v>7669</v>
       </c>
     </row>
     <row r="3871" spans="3:6">
       <c r="C3871" s="3">
-        <v>300016</v>
+        <v>203754</v>
       </c>
       <c r="D3871" s="4"/>
       <c r="E3871" s="1" t="s">
+        <v>7669</v>
+      </c>
+      <c r="F3871" s="8" t="s">
         <v>7670</v>
-      </c>
-      <c r="F3871" s="8" t="s">
-        <v>7671</v>
       </c>
     </row>
     <row r="3872" spans="3:6">
       <c r="C3872" s="3">
-        <v>300017</v>
+        <v>203755</v>
       </c>
       <c r="D3872" s="4"/>
       <c r="E3872" s="1" t="s">
+        <v>7671</v>
+      </c>
+      <c r="F3872" s="8" t="s">
         <v>7672</v>
-      </c>
-      <c r="F3872" s="8" t="s">
-        <v>7673</v>
       </c>
     </row>
     <row r="3873" spans="3:6">
       <c r="C3873" s="3">
-        <v>300018</v>
+        <v>203756</v>
       </c>
       <c r="D3873" s="4"/>
       <c r="E3873" s="1" t="s">
+        <v>7673</v>
+      </c>
+      <c r="F3873" s="8" t="s">
         <v>7674</v>
-      </c>
-      <c r="F3873" s="8" t="s">
-        <v>7675</v>
       </c>
     </row>
     <row r="3874" spans="3:6">
       <c r="C3874" s="3">
-        <v>300019</v>
+        <v>203757</v>
       </c>
       <c r="D3874" s="4"/>
       <c r="E3874" s="1" t="s">
+        <v>7675</v>
+      </c>
+      <c r="F3874" s="8" t="s">
         <v>7676</v>
-      </c>
-      <c r="F3874" s="8" t="s">
-        <v>7677</v>
       </c>
     </row>
     <row r="3875" spans="3:6">
       <c r="C3875" s="3">
-        <v>300020</v>
+        <v>203758</v>
       </c>
       <c r="D3875" s="4"/>
       <c r="E3875" s="1" t="s">
+        <v>7677</v>
+      </c>
+      <c r="F3875" s="8" t="s">
         <v>7678</v>
-      </c>
-      <c r="F3875" s="8" t="s">
-        <v>7679</v>
       </c>
     </row>
     <row r="3876" spans="3:6">
       <c r="C3876" s="3">
-        <v>300021</v>
-      </c>
-      <c r="D3876" s="4"/>
+        <v>300001</v>
+      </c>
+      <c r="D3876" s="4" t="s">
+        <v>1961</v>
+      </c>
       <c r="E3876" s="1" t="s">
+        <v>7679</v>
+      </c>
+      <c r="F3876" s="8" t="s">
         <v>7680</v>
-      </c>
-      <c r="F3876" s="8" t="s">
-        <v>7681</v>
       </c>
     </row>
     <row r="3877" spans="3:6">
       <c r="C3877" s="3">
-        <v>300022</v>
+        <v>300002</v>
       </c>
       <c r="D3877" s="4"/>
       <c r="E3877" s="1" t="s">
-        <v>4218</v>
+        <v>7681</v>
       </c>
       <c r="F3877" s="8" t="s">
         <v>7682</v>
@@ -71848,7 +71965,7 @@
     </row>
     <row r="3878" spans="3:6">
       <c r="C3878" s="3">
-        <v>300023</v>
+        <v>300003</v>
       </c>
       <c r="D3878" s="4"/>
       <c r="E3878" s="1" t="s">
@@ -71860,7 +71977,7 @@
     </row>
     <row r="3879" spans="3:6">
       <c r="C3879" s="3">
-        <v>300024</v>
+        <v>300004</v>
       </c>
       <c r="D3879" s="4"/>
       <c r="E3879" s="1" t="s">
@@ -71872,7 +71989,7 @@
     </row>
     <row r="3880" spans="3:6">
       <c r="C3880" s="3">
-        <v>300025</v>
+        <v>300005</v>
       </c>
       <c r="D3880" s="4"/>
       <c r="E3880" s="1" t="s">
@@ -71884,7 +72001,7 @@
     </row>
     <row r="3881" spans="3:6">
       <c r="C3881" s="3">
-        <v>300026</v>
+        <v>300006</v>
       </c>
       <c r="D3881" s="4"/>
       <c r="E3881" s="1" t="s">
@@ -71896,7 +72013,7 @@
     </row>
     <row r="3882" spans="3:6">
       <c r="C3882" s="3">
-        <v>300027</v>
+        <v>300007</v>
       </c>
       <c r="D3882" s="4"/>
       <c r="E3882" s="1" t="s">
@@ -71908,7 +72025,7 @@
     </row>
     <row r="3883" spans="3:6">
       <c r="C3883" s="3">
-        <v>300028</v>
+        <v>300008</v>
       </c>
       <c r="D3883" s="4"/>
       <c r="E3883" s="1" t="s">
@@ -71920,7 +72037,7 @@
     </row>
     <row r="3884" spans="3:6">
       <c r="C3884" s="3">
-        <v>300029</v>
+        <v>300009</v>
       </c>
       <c r="D3884" s="4"/>
       <c r="E3884" s="1" t="s">
@@ -71932,7 +72049,7 @@
     </row>
     <row r="3885" spans="3:6">
       <c r="C3885" s="3">
-        <v>300030</v>
+        <v>300010</v>
       </c>
       <c r="D3885" s="4"/>
       <c r="E3885" s="1" t="s">
@@ -71944,7 +72061,7 @@
     </row>
     <row r="3886" spans="3:6">
       <c r="C3886" s="3">
-        <v>300031</v>
+        <v>300011</v>
       </c>
       <c r="D3886" s="4"/>
       <c r="E3886" s="1" t="s">
@@ -71956,7 +72073,7 @@
     </row>
     <row r="3887" spans="3:6">
       <c r="C3887" s="3">
-        <v>300032</v>
+        <v>300012</v>
       </c>
       <c r="D3887" s="4"/>
       <c r="E3887" s="1" t="s">
@@ -71968,7 +72085,7 @@
     </row>
     <row r="3888" spans="3:6">
       <c r="C3888" s="3">
-        <v>300033</v>
+        <v>300013</v>
       </c>
       <c r="D3888" s="4"/>
       <c r="E3888" s="1" t="s">
@@ -71980,7 +72097,7 @@
     </row>
     <row r="3889" spans="3:6">
       <c r="C3889" s="3">
-        <v>300034</v>
+        <v>300014</v>
       </c>
       <c r="D3889" s="4"/>
       <c r="E3889" s="1" t="s">
@@ -71992,7 +72109,7 @@
     </row>
     <row r="3890" spans="3:6">
       <c r="C3890" s="3">
-        <v>300035</v>
+        <v>300015</v>
       </c>
       <c r="D3890" s="4"/>
       <c r="E3890" s="1" t="s">
@@ -72004,7 +72121,7 @@
     </row>
     <row r="3891" spans="3:6">
       <c r="C3891" s="3">
-        <v>300036</v>
+        <v>300016</v>
       </c>
       <c r="D3891" s="4"/>
       <c r="E3891" s="1" t="s">
@@ -72016,1196 +72133,1213 @@
     </row>
     <row r="3892" spans="3:6">
       <c r="C3892" s="3">
-        <v>300037</v>
+        <v>300017</v>
       </c>
       <c r="D3892" s="4"/>
       <c r="E3892" s="1" t="s">
-        <v>5913</v>
+        <v>7711</v>
       </c>
       <c r="F3892" s="8" t="s">
-        <v>7711</v>
+        <v>7712</v>
       </c>
     </row>
     <row r="3893" spans="3:6">
       <c r="C3893" s="3">
-        <v>300038</v>
+        <v>300018</v>
       </c>
       <c r="D3893" s="4"/>
       <c r="E3893" s="1" t="s">
-        <v>4274</v>
+        <v>7713</v>
       </c>
       <c r="F3893" s="8" t="s">
-        <v>7712</v>
+        <v>7714</v>
       </c>
     </row>
     <row r="3894" spans="3:6">
       <c r="C3894" s="3">
-        <v>300039</v>
+        <v>300019</v>
       </c>
       <c r="D3894" s="4"/>
       <c r="E3894" s="1" t="s">
-        <v>7713</v>
+        <v>7715</v>
       </c>
       <c r="F3894" s="8" t="s">
-        <v>7714</v>
+        <v>7716</v>
       </c>
     </row>
     <row r="3895" spans="3:6">
       <c r="C3895" s="3">
-        <v>300040</v>
+        <v>300020</v>
       </c>
       <c r="D3895" s="4"/>
       <c r="E3895" s="1" t="s">
-        <v>7715</v>
+        <v>7717</v>
       </c>
       <c r="F3895" s="8" t="s">
-        <v>7716</v>
+        <v>7718</v>
       </c>
     </row>
     <row r="3896" spans="3:6">
       <c r="C3896" s="3">
-        <v>300041</v>
+        <v>300021</v>
       </c>
       <c r="D3896" s="4"/>
       <c r="E3896" s="1" t="s">
-        <v>7717</v>
+        <v>7719</v>
       </c>
       <c r="F3896" s="8" t="s">
-        <v>7718</v>
+        <v>7720</v>
       </c>
     </row>
     <row r="3897" spans="3:6">
       <c r="C3897" s="3">
-        <v>300042</v>
+        <v>300022</v>
       </c>
       <c r="D3897" s="4"/>
       <c r="E3897" s="1" t="s">
-        <v>1222</v>
+        <v>4218</v>
       </c>
       <c r="F3897" s="8" t="s">
-        <v>1041</v>
+        <v>7721</v>
       </c>
     </row>
     <row r="3898" spans="3:6">
       <c r="C3898" s="3">
-        <v>300043</v>
+        <v>300023</v>
       </c>
       <c r="D3898" s="4"/>
       <c r="E3898" s="1" t="s">
-        <v>7719</v>
+        <v>7722</v>
       </c>
       <c r="F3898" s="8" t="s">
-        <v>7720</v>
+        <v>7723</v>
       </c>
     </row>
     <row r="3899" spans="3:6">
       <c r="C3899" s="3">
-        <v>300044</v>
+        <v>300024</v>
       </c>
       <c r="D3899" s="4"/>
       <c r="E3899" s="1" t="s">
-        <v>4721</v>
+        <v>7724</v>
       </c>
       <c r="F3899" s="8" t="s">
-        <v>7721</v>
+        <v>7725</v>
       </c>
     </row>
     <row r="3900" spans="3:6">
       <c r="C3900" s="3">
-        <v>300045</v>
-      </c>
-      <c r="D3900"/>
+        <v>300025</v>
+      </c>
+      <c r="D3900" s="4"/>
       <c r="E3900" s="1" t="s">
-        <v>7722</v>
-      </c>
-      <c r="F3900" t="s">
-        <v>7723</v>
+        <v>7726</v>
+      </c>
+      <c r="F3900" s="8" t="s">
+        <v>7727</v>
       </c>
     </row>
     <row r="3901" spans="3:6">
       <c r="C3901" s="3">
-        <v>300046</v>
-      </c>
-      <c r="D3901"/>
-      <c r="E3901" t="s">
-        <v>7724</v>
-      </c>
-      <c r="F3901" t="s">
-        <v>7725</v>
+        <v>300026</v>
+      </c>
+      <c r="D3901" s="4"/>
+      <c r="E3901" s="1" t="s">
+        <v>7728</v>
+      </c>
+      <c r="F3901" s="8" t="s">
+        <v>7729</v>
       </c>
     </row>
     <row r="3902" spans="3:6">
       <c r="C3902" s="3">
-        <v>300047</v>
+        <v>300027</v>
       </c>
       <c r="D3902" s="4"/>
       <c r="E3902" s="1" t="s">
-        <v>7726</v>
-      </c>
-      <c r="F3902" s="6" t="s">
-        <v>7727</v>
+        <v>7730</v>
+      </c>
+      <c r="F3902" s="8" t="s">
+        <v>7731</v>
       </c>
     </row>
     <row r="3903" spans="3:6">
       <c r="C3903" s="3">
-        <v>300048</v>
+        <v>300028</v>
       </c>
       <c r="D3903" s="4"/>
       <c r="E3903" s="1" t="s">
-        <v>7728</v>
-      </c>
-      <c r="F3903" s="6" t="s">
-        <v>7729</v>
+        <v>7732</v>
+      </c>
+      <c r="F3903" s="8" t="s">
+        <v>7733</v>
       </c>
     </row>
     <row r="3904" spans="3:6">
       <c r="C3904" s="3">
-        <v>300049</v>
+        <v>300029</v>
       </c>
       <c r="D3904" s="4"/>
       <c r="E3904" s="1" t="s">
-        <v>7730</v>
-      </c>
-      <c r="F3904" s="6" t="s">
-        <v>7731</v>
+        <v>7734</v>
+      </c>
+      <c r="F3904" s="8" t="s">
+        <v>7735</v>
       </c>
     </row>
     <row r="3905" spans="3:6">
       <c r="C3905" s="3">
-        <v>300050</v>
+        <v>300030</v>
       </c>
       <c r="D3905" s="4"/>
       <c r="E3905" s="1" t="s">
-        <v>7732</v>
-      </c>
-      <c r="F3905" s="6" t="s">
-        <v>7733</v>
+        <v>7736</v>
+      </c>
+      <c r="F3905" s="8" t="s">
+        <v>7737</v>
       </c>
     </row>
     <row r="3906" spans="3:6">
       <c r="C3906" s="3">
-        <v>300051</v>
+        <v>300031</v>
       </c>
       <c r="D3906" s="4"/>
       <c r="E3906" s="1" t="s">
-        <v>7734</v>
-      </c>
-      <c r="F3906" s="6" t="s">
-        <v>7735</v>
+        <v>7738</v>
+      </c>
+      <c r="F3906" s="8" t="s">
+        <v>7739</v>
       </c>
     </row>
     <row r="3907" spans="3:6">
       <c r="C3907" s="3">
-        <v>300052</v>
+        <v>300032</v>
       </c>
       <c r="D3907" s="4"/>
       <c r="E3907" s="1" t="s">
-        <v>7736</v>
-      </c>
-      <c r="F3907" s="6" t="s">
-        <v>7737</v>
+        <v>7740</v>
+      </c>
+      <c r="F3907" s="8" t="s">
+        <v>7741</v>
       </c>
     </row>
     <row r="3908" spans="3:6">
       <c r="C3908" s="3">
-        <v>300053</v>
+        <v>300033</v>
       </c>
       <c r="D3908" s="4"/>
       <c r="E3908" s="1" t="s">
-        <v>7738</v>
-      </c>
-      <c r="F3908" s="6" t="s">
-        <v>7739</v>
+        <v>7742</v>
+      </c>
+      <c r="F3908" s="8" t="s">
+        <v>7743</v>
       </c>
     </row>
     <row r="3909" spans="3:6">
       <c r="C3909" s="3">
-        <v>300054</v>
+        <v>300034</v>
       </c>
       <c r="D3909" s="4"/>
       <c r="E3909" s="1" t="s">
-        <v>7740</v>
-      </c>
-      <c r="F3909" s="6" t="s">
-        <v>7741</v>
+        <v>7744</v>
+      </c>
+      <c r="F3909" s="8" t="s">
+        <v>7745</v>
       </c>
     </row>
     <row r="3910" spans="3:6">
       <c r="C3910" s="3">
-        <v>300055</v>
+        <v>300035</v>
       </c>
       <c r="D3910" s="4"/>
       <c r="E3910" s="1" t="s">
-        <v>7742</v>
-      </c>
-      <c r="F3910" s="6" t="s">
-        <v>7743</v>
+        <v>7746</v>
+      </c>
+      <c r="F3910" s="8" t="s">
+        <v>7747</v>
       </c>
     </row>
     <row r="3911" spans="3:6">
       <c r="C3911" s="3">
-        <v>300056</v>
+        <v>300036</v>
       </c>
       <c r="D3911" s="4"/>
       <c r="E3911" s="1" t="s">
-        <v>7744</v>
-      </c>
-      <c r="F3911" s="6" t="s">
-        <v>7745</v>
+        <v>7748</v>
+      </c>
+      <c r="F3911" s="8" t="s">
+        <v>7749</v>
       </c>
     </row>
     <row r="3912" spans="3:6">
       <c r="C3912" s="3">
-        <v>300057</v>
+        <v>300037</v>
       </c>
       <c r="D3912" s="4"/>
       <c r="E3912" s="1" t="s">
-        <v>7746</v>
-      </c>
-      <c r="F3912" s="6" t="s">
-        <v>7747</v>
+        <v>5913</v>
+      </c>
+      <c r="F3912" s="8" t="s">
+        <v>7750</v>
       </c>
     </row>
     <row r="3913" spans="3:6">
       <c r="C3913" s="3">
-        <v>300058</v>
+        <v>300038</v>
       </c>
       <c r="D3913" s="4"/>
       <c r="E3913" s="1" t="s">
-        <v>7748</v>
-      </c>
-      <c r="F3913" s="6" t="s">
-        <v>7749</v>
+        <v>4274</v>
+      </c>
+      <c r="F3913" s="8" t="s">
+        <v>7751</v>
       </c>
     </row>
     <row r="3914" spans="3:6">
       <c r="C3914" s="3">
-        <v>300059</v>
+        <v>300039</v>
       </c>
       <c r="D3914" s="4"/>
       <c r="E3914" s="1" t="s">
-        <v>7750</v>
-      </c>
-      <c r="F3914" s="6" t="s">
-        <v>7751</v>
+        <v>7752</v>
+      </c>
+      <c r="F3914" s="8" t="s">
+        <v>7753</v>
       </c>
     </row>
     <row r="3915" spans="3:6">
       <c r="C3915" s="3">
-        <v>300060</v>
+        <v>300040</v>
       </c>
       <c r="D3915" s="4"/>
       <c r="E3915" s="1" t="s">
-        <v>7752</v>
-      </c>
-      <c r="F3915" s="6" t="s">
-        <v>7753</v>
+        <v>7754</v>
+      </c>
+      <c r="F3915" s="8" t="s">
+        <v>7755</v>
       </c>
     </row>
     <row r="3916" spans="3:6">
       <c r="C3916" s="3">
-        <v>300061</v>
+        <v>300041</v>
       </c>
       <c r="D3916" s="4"/>
       <c r="E3916" s="1" t="s">
-        <v>7754</v>
-      </c>
-      <c r="F3916" s="6" t="s">
-        <v>7755</v>
+        <v>7756</v>
+      </c>
+      <c r="F3916" s="8" t="s">
+        <v>7757</v>
       </c>
     </row>
     <row r="3917" spans="3:6">
       <c r="C3917" s="3">
-        <v>300062</v>
+        <v>300042</v>
       </c>
       <c r="D3917" s="4"/>
       <c r="E3917" s="1" t="s">
-        <v>7756</v>
-      </c>
-      <c r="F3917" s="6" t="s">
-        <v>7757</v>
+        <v>1222</v>
+      </c>
+      <c r="F3917" s="8" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="3918" spans="3:6">
       <c r="C3918" s="3">
-        <v>300063</v>
+        <v>300043</v>
       </c>
       <c r="D3918" s="4"/>
       <c r="E3918" s="1" t="s">
         <v>7758</v>
       </c>
-      <c r="F3918" s="6" t="s">
+      <c r="F3918" s="8" t="s">
         <v>7759</v>
       </c>
     </row>
     <row r="3919" spans="3:6">
       <c r="C3919" s="3">
-        <v>300064</v>
+        <v>300044</v>
       </c>
       <c r="D3919" s="4"/>
       <c r="E3919" s="1" t="s">
+        <v>4721</v>
+      </c>
+      <c r="F3919" s="8" t="s">
         <v>7760</v>
-      </c>
-      <c r="F3919" s="6" t="s">
-        <v>7761</v>
       </c>
     </row>
     <row r="3920" spans="3:6">
       <c r="C3920" s="3">
-        <v>300065</v>
-      </c>
-      <c r="D3920" s="4"/>
+        <v>300045</v>
+      </c>
+      <c r="D3920"/>
       <c r="E3920" s="1" t="s">
+        <v>7761</v>
+      </c>
+      <c r="F3920" t="s">
         <v>7762</v>
-      </c>
-      <c r="F3920" s="6" t="s">
-        <v>7763</v>
       </c>
     </row>
     <row r="3921" spans="3:6">
       <c r="C3921" s="3">
-        <v>300066</v>
-      </c>
-      <c r="D3921" s="4"/>
-      <c r="E3921" s="1" t="s">
+        <v>300046</v>
+      </c>
+      <c r="D3921"/>
+      <c r="E3921" t="s">
+        <v>7763</v>
+      </c>
+      <c r="F3921" t="s">
         <v>7764</v>
-      </c>
-      <c r="F3921" s="6" t="s">
-        <v>7765</v>
       </c>
     </row>
     <row r="3922" spans="3:6">
       <c r="C3922" s="3">
-        <v>300067</v>
+        <v>300047</v>
       </c>
       <c r="D3922" s="4"/>
       <c r="E3922" s="1" t="s">
+        <v>7765</v>
+      </c>
+      <c r="F3922" s="6" t="s">
         <v>7766</v>
-      </c>
-      <c r="F3922" s="6" t="s">
-        <v>7767</v>
       </c>
     </row>
     <row r="3923" spans="3:6">
       <c r="C3923" s="3">
-        <v>300068</v>
+        <v>300048</v>
       </c>
       <c r="D3923" s="4"/>
       <c r="E3923" s="1" t="s">
+        <v>7767</v>
+      </c>
+      <c r="F3923" s="6" t="s">
         <v>7768</v>
-      </c>
-      <c r="F3923" s="6" t="s">
-        <v>7769</v>
       </c>
     </row>
     <row r="3924" spans="3:6">
       <c r="C3924" s="3">
-        <v>300069</v>
+        <v>300049</v>
       </c>
       <c r="D3924" s="4"/>
       <c r="E3924" s="1" t="s">
+        <v>7769</v>
+      </c>
+      <c r="F3924" s="6" t="s">
         <v>7770</v>
-      </c>
-      <c r="F3924" s="6" t="s">
-        <v>7771</v>
       </c>
     </row>
     <row r="3925" spans="3:6">
       <c r="C3925" s="3">
-        <v>300070</v>
+        <v>300050</v>
       </c>
       <c r="D3925" s="4"/>
       <c r="E3925" s="1" t="s">
+        <v>7771</v>
+      </c>
+      <c r="F3925" s="6" t="s">
         <v>7772</v>
-      </c>
-      <c r="F3925" s="6" t="s">
-        <v>7773</v>
       </c>
     </row>
     <row r="3926" spans="3:6">
       <c r="C3926" s="3">
-        <v>300071</v>
+        <v>300051</v>
       </c>
       <c r="D3926" s="4"/>
       <c r="E3926" s="1" t="s">
+        <v>7773</v>
+      </c>
+      <c r="F3926" s="6" t="s">
         <v>7774</v>
-      </c>
-      <c r="F3926" s="6" t="s">
-        <v>7775</v>
       </c>
     </row>
     <row r="3927" spans="3:6">
       <c r="C3927" s="3">
-        <v>300072</v>
+        <v>300052</v>
       </c>
       <c r="D3927" s="4"/>
       <c r="E3927" s="1" t="s">
+        <v>7775</v>
+      </c>
+      <c r="F3927" s="6" t="s">
         <v>7776</v>
-      </c>
-      <c r="F3927" s="6" t="s">
-        <v>7777</v>
       </c>
     </row>
     <row r="3928" spans="3:6">
       <c r="C3928" s="3">
-        <v>300073</v>
+        <v>300053</v>
       </c>
       <c r="D3928" s="4"/>
       <c r="E3928" s="1" t="s">
+        <v>7777</v>
+      </c>
+      <c r="F3928" s="6" t="s">
         <v>7778</v>
-      </c>
-      <c r="F3928" s="6" t="s">
-        <v>7779</v>
       </c>
     </row>
     <row r="3929" spans="3:6">
       <c r="C3929" s="3">
-        <v>300074</v>
+        <v>300054</v>
       </c>
       <c r="D3929" s="4"/>
       <c r="E3929" s="1" t="s">
+        <v>7779</v>
+      </c>
+      <c r="F3929" s="6" t="s">
         <v>7780</v>
-      </c>
-      <c r="F3929" s="6" t="s">
-        <v>7781</v>
       </c>
     </row>
     <row r="3930" spans="3:6">
       <c r="C3930" s="3">
-        <v>300075</v>
+        <v>300055</v>
       </c>
       <c r="D3930" s="4"/>
       <c r="E3930" s="1" t="s">
+        <v>7781</v>
+      </c>
+      <c r="F3930" s="6" t="s">
         <v>7782</v>
-      </c>
-      <c r="F3930" s="6" t="s">
-        <v>7783</v>
       </c>
     </row>
     <row r="3931" spans="3:6">
       <c r="C3931" s="3">
-        <v>300076</v>
+        <v>300056</v>
       </c>
       <c r="D3931" s="4"/>
       <c r="E3931" s="1" t="s">
+        <v>7783</v>
+      </c>
+      <c r="F3931" s="6" t="s">
         <v>7784</v>
-      </c>
-      <c r="F3931" s="6" t="s">
-        <v>7785</v>
       </c>
     </row>
     <row r="3932" spans="3:6">
       <c r="C3932" s="3">
-        <v>300077</v>
+        <v>300057</v>
       </c>
       <c r="D3932" s="4"/>
       <c r="E3932" s="1" t="s">
+        <v>7785</v>
+      </c>
+      <c r="F3932" s="6" t="s">
         <v>7786</v>
-      </c>
-      <c r="F3932" s="6" t="s">
-        <v>7787</v>
       </c>
     </row>
     <row r="3933" spans="3:6">
       <c r="C3933" s="3">
-        <v>300078</v>
+        <v>300058</v>
       </c>
       <c r="D3933" s="4"/>
       <c r="E3933" s="1" t="s">
+        <v>7787</v>
+      </c>
+      <c r="F3933" s="6" t="s">
         <v>7788</v>
-      </c>
-      <c r="F3933" s="6" t="s">
-        <v>7789</v>
       </c>
     </row>
     <row r="3934" spans="3:6">
       <c r="C3934" s="3">
-        <v>300079</v>
+        <v>300059</v>
       </c>
       <c r="D3934" s="4"/>
       <c r="E3934" s="1" t="s">
+        <v>7789</v>
+      </c>
+      <c r="F3934" s="6" t="s">
         <v>7790</v>
-      </c>
-      <c r="F3934" s="6" t="s">
-        <v>7791</v>
       </c>
     </row>
     <row r="3935" spans="3:6">
       <c r="C3935" s="3">
-        <v>300080</v>
+        <v>300060</v>
       </c>
       <c r="D3935" s="4"/>
       <c r="E3935" s="1" t="s">
+        <v>7791</v>
+      </c>
+      <c r="F3935" s="6" t="s">
         <v>7792</v>
-      </c>
-      <c r="F3935" s="6" t="s">
-        <v>7793</v>
       </c>
     </row>
     <row r="3936" spans="3:6">
       <c r="C3936" s="3">
-        <v>300081</v>
+        <v>300061</v>
       </c>
       <c r="D3936" s="4"/>
       <c r="E3936" s="1" t="s">
+        <v>7793</v>
+      </c>
+      <c r="F3936" s="6" t="s">
         <v>7794</v>
-      </c>
-      <c r="F3936" s="6" t="s">
-        <v>7795</v>
       </c>
     </row>
     <row r="3937" spans="3:6">
       <c r="C3937" s="3">
-        <v>300082</v>
+        <v>300062</v>
       </c>
       <c r="D3937" s="4"/>
       <c r="E3937" s="1" t="s">
+        <v>7795</v>
+      </c>
+      <c r="F3937" s="6" t="s">
         <v>7796</v>
-      </c>
-      <c r="F3937" s="6" t="s">
-        <v>7797</v>
       </c>
     </row>
     <row r="3938" spans="3:6">
       <c r="C3938" s="3">
-        <v>300083</v>
+        <v>300063</v>
       </c>
       <c r="D3938" s="4"/>
       <c r="E3938" s="1" t="s">
+        <v>7797</v>
+      </c>
+      <c r="F3938" s="6" t="s">
         <v>7798</v>
-      </c>
-      <c r="F3938" s="6" t="s">
-        <v>7799</v>
       </c>
     </row>
     <row r="3939" spans="3:6">
       <c r="C3939" s="3">
-        <v>300084</v>
+        <v>300064</v>
       </c>
       <c r="D3939" s="4"/>
       <c r="E3939" s="1" t="s">
+        <v>7799</v>
+      </c>
+      <c r="F3939" s="6" t="s">
         <v>7800</v>
-      </c>
-      <c r="F3939" s="6" t="s">
-        <v>7801</v>
       </c>
     </row>
     <row r="3940" spans="3:6">
       <c r="C3940" s="3">
-        <v>300085</v>
+        <v>300065</v>
       </c>
       <c r="D3940" s="4"/>
       <c r="E3940" s="1" t="s">
+        <v>7801</v>
+      </c>
+      <c r="F3940" s="6" t="s">
         <v>7802</v>
-      </c>
-      <c r="F3940" s="6" t="s">
-        <v>7803</v>
       </c>
     </row>
     <row r="3941" spans="3:6">
       <c r="C3941" s="3">
-        <v>300086</v>
+        <v>300066</v>
       </c>
       <c r="D3941" s="4"/>
       <c r="E3941" s="1" t="s">
+        <v>7803</v>
+      </c>
+      <c r="F3941" s="6" t="s">
         <v>7804</v>
-      </c>
-      <c r="F3941" s="6" t="s">
-        <v>7805</v>
       </c>
     </row>
     <row r="3942" spans="3:6">
       <c r="C3942" s="3">
-        <v>300087</v>
+        <v>300067</v>
       </c>
       <c r="D3942" s="4"/>
       <c r="E3942" s="1" t="s">
+        <v>7805</v>
+      </c>
+      <c r="F3942" s="6" t="s">
         <v>7806</v>
-      </c>
-      <c r="F3942" s="6" t="s">
-        <v>7807</v>
       </c>
     </row>
     <row r="3943" spans="3:6">
       <c r="C3943" s="3">
-        <v>300088</v>
+        <v>300068</v>
       </c>
       <c r="D3943" s="4"/>
       <c r="E3943" s="1" t="s">
+        <v>7807</v>
+      </c>
+      <c r="F3943" s="6" t="s">
         <v>7808</v>
-      </c>
-      <c r="F3943" s="6" t="s">
-        <v>7809</v>
       </c>
     </row>
     <row r="3944" spans="3:6">
       <c r="C3944" s="3">
-        <v>300089</v>
+        <v>300069</v>
       </c>
       <c r="D3944" s="4"/>
       <c r="E3944" s="1" t="s">
+        <v>7809</v>
+      </c>
+      <c r="F3944" s="6" t="s">
         <v>7810</v>
-      </c>
-      <c r="F3944" s="6" t="s">
-        <v>7811</v>
       </c>
     </row>
     <row r="3945" spans="3:6">
       <c r="C3945" s="3">
-        <v>300090</v>
+        <v>300070</v>
       </c>
       <c r="D3945" s="4"/>
       <c r="E3945" s="1" t="s">
+        <v>7811</v>
+      </c>
+      <c r="F3945" s="6" t="s">
         <v>7812</v>
-      </c>
-      <c r="F3945" s="6" t="s">
-        <v>7813</v>
       </c>
     </row>
     <row r="3946" spans="3:6">
       <c r="C3946" s="3">
-        <v>300091</v>
+        <v>300071</v>
       </c>
       <c r="D3946" s="4"/>
       <c r="E3946" s="1" t="s">
+        <v>7813</v>
+      </c>
+      <c r="F3946" s="6" t="s">
         <v>7814</v>
-      </c>
-      <c r="F3946" s="6" t="s">
-        <v>7815</v>
       </c>
     </row>
     <row r="3947" spans="3:6">
       <c r="C3947" s="3">
-        <v>300092</v>
+        <v>300072</v>
       </c>
       <c r="D3947" s="4"/>
       <c r="E3947" s="1" t="s">
+        <v>7815</v>
+      </c>
+      <c r="F3947" s="6" t="s">
         <v>7816</v>
-      </c>
-      <c r="F3947" s="6" t="s">
-        <v>7817</v>
       </c>
     </row>
     <row r="3948" spans="3:6">
       <c r="C3948" s="3">
-        <v>300093</v>
+        <v>300073</v>
       </c>
       <c r="D3948" s="4"/>
       <c r="E3948" s="1" t="s">
+        <v>7817</v>
+      </c>
+      <c r="F3948" s="6" t="s">
         <v>7818</v>
-      </c>
-      <c r="F3948" s="6" t="s">
-        <v>7819</v>
       </c>
     </row>
     <row r="3949" spans="3:6">
       <c r="C3949" s="3">
-        <v>300094</v>
+        <v>300074</v>
       </c>
       <c r="D3949" s="4"/>
       <c r="E3949" s="1" t="s">
+        <v>7819</v>
+      </c>
+      <c r="F3949" s="6" t="s">
         <v>7820</v>
-      </c>
-      <c r="F3949" s="6" t="s">
-        <v>7821</v>
       </c>
     </row>
     <row r="3950" spans="3:6">
       <c r="C3950" s="3">
-        <v>300095</v>
+        <v>300075</v>
       </c>
       <c r="D3950" s="4"/>
       <c r="E3950" s="1" t="s">
+        <v>7821</v>
+      </c>
+      <c r="F3950" s="6" t="s">
         <v>7822</v>
-      </c>
-      <c r="F3950" s="6" t="s">
-        <v>7823</v>
       </c>
     </row>
     <row r="3951" spans="3:6">
       <c r="C3951" s="3">
-        <v>300096</v>
+        <v>300076</v>
       </c>
       <c r="D3951" s="4"/>
       <c r="E3951" s="1" t="s">
+        <v>7823</v>
+      </c>
+      <c r="F3951" s="6" t="s">
         <v>7824</v>
-      </c>
-      <c r="F3951" s="6" t="s">
-        <v>7825</v>
       </c>
     </row>
     <row r="3952" spans="3:6">
       <c r="C3952" s="3">
-        <v>300097</v>
+        <v>300077</v>
       </c>
       <c r="D3952" s="4"/>
       <c r="E3952" s="1" t="s">
+        <v>7825</v>
+      </c>
+      <c r="F3952" s="6" t="s">
         <v>7826</v>
-      </c>
-      <c r="F3952" s="6" t="s">
-        <v>7827</v>
       </c>
     </row>
     <row r="3953" spans="3:6">
       <c r="C3953" s="3">
-        <v>300098</v>
+        <v>300078</v>
       </c>
       <c r="D3953" s="4"/>
       <c r="E3953" s="1" t="s">
+        <v>7827</v>
+      </c>
+      <c r="F3953" s="6" t="s">
         <v>7828</v>
-      </c>
-      <c r="F3953" s="6" t="s">
-        <v>7829</v>
       </c>
     </row>
     <row r="3954" spans="3:6">
       <c r="C3954" s="3">
-        <v>300099</v>
+        <v>300079</v>
       </c>
       <c r="D3954" s="4"/>
       <c r="E3954" s="1" t="s">
+        <v>7829</v>
+      </c>
+      <c r="F3954" s="6" t="s">
         <v>7830</v>
-      </c>
-      <c r="F3954" s="6" t="s">
-        <v>7831</v>
       </c>
     </row>
     <row r="3955" spans="3:6">
       <c r="C3955" s="3">
-        <v>300100</v>
+        <v>300080</v>
       </c>
       <c r="D3955" s="4"/>
       <c r="E3955" s="1" t="s">
+        <v>7831</v>
+      </c>
+      <c r="F3955" s="6" t="s">
         <v>7832</v>
-      </c>
-      <c r="F3955" s="6" t="s">
-        <v>7833</v>
       </c>
     </row>
     <row r="3956" spans="3:6">
       <c r="C3956" s="3">
-        <v>300101</v>
+        <v>300081</v>
       </c>
       <c r="D3956" s="4"/>
       <c r="E3956" s="1" t="s">
+        <v>7833</v>
+      </c>
+      <c r="F3956" s="6" t="s">
         <v>7834</v>
-      </c>
-      <c r="F3956" s="6" t="s">
-        <v>7835</v>
       </c>
     </row>
     <row r="3957" spans="3:6">
       <c r="C3957" s="3">
-        <v>300102</v>
+        <v>300082</v>
       </c>
       <c r="D3957" s="4"/>
       <c r="E3957" s="1" t="s">
+        <v>7835</v>
+      </c>
+      <c r="F3957" s="6" t="s">
         <v>7836</v>
-      </c>
-      <c r="F3957" s="6" t="s">
-        <v>7837</v>
       </c>
     </row>
     <row r="3958" spans="3:6">
       <c r="C3958" s="3">
-        <v>300103</v>
+        <v>300083</v>
       </c>
       <c r="D3958" s="4"/>
       <c r="E3958" s="1" t="s">
+        <v>7837</v>
+      </c>
+      <c r="F3958" s="6" t="s">
         <v>7838</v>
-      </c>
-      <c r="F3958" s="6" t="s">
-        <v>7839</v>
       </c>
     </row>
     <row r="3959" spans="3:6">
       <c r="C3959" s="3">
-        <v>300104</v>
+        <v>300084</v>
       </c>
       <c r="D3959" s="4"/>
       <c r="E3959" s="1" t="s">
+        <v>7839</v>
+      </c>
+      <c r="F3959" s="6" t="s">
         <v>7840</v>
-      </c>
-      <c r="F3959" s="6" t="s">
-        <v>7841</v>
       </c>
     </row>
     <row r="3960" spans="3:6">
       <c r="C3960" s="3">
-        <v>300105</v>
+        <v>300085</v>
       </c>
       <c r="D3960" s="4"/>
       <c r="E3960" s="1" t="s">
+        <v>7841</v>
+      </c>
+      <c r="F3960" s="6" t="s">
         <v>7842</v>
-      </c>
-      <c r="F3960" s="6" t="s">
-        <v>7843</v>
       </c>
     </row>
     <row r="3961" spans="3:6">
       <c r="C3961" s="3">
-        <v>300106</v>
+        <v>300086</v>
       </c>
       <c r="D3961" s="4"/>
       <c r="E3961" s="1" t="s">
+        <v>7843</v>
+      </c>
+      <c r="F3961" s="6" t="s">
         <v>7844</v>
-      </c>
-      <c r="F3961" s="6" t="s">
-        <v>7845</v>
       </c>
     </row>
     <row r="3962" spans="3:6">
       <c r="C3962" s="3">
-        <v>300107</v>
+        <v>300087</v>
       </c>
       <c r="D3962" s="4"/>
       <c r="E3962" s="1" t="s">
+        <v>7845</v>
+      </c>
+      <c r="F3962" s="6" t="s">
         <v>7846</v>
-      </c>
-      <c r="F3962" s="6" t="s">
-        <v>7847</v>
       </c>
     </row>
     <row r="3963" spans="3:6">
       <c r="C3963" s="3">
-        <v>300108</v>
+        <v>300088</v>
       </c>
       <c r="D3963" s="4"/>
       <c r="E3963" s="1" t="s">
+        <v>7847</v>
+      </c>
+      <c r="F3963" s="6" t="s">
         <v>7848</v>
-      </c>
-      <c r="F3963" s="6" t="s">
-        <v>7849</v>
       </c>
     </row>
     <row r="3964" spans="3:6">
       <c r="C3964" s="3">
-        <v>300109</v>
+        <v>300089</v>
       </c>
       <c r="D3964" s="4"/>
       <c r="E3964" s="1" t="s">
+        <v>7849</v>
+      </c>
+      <c r="F3964" s="6" t="s">
         <v>7850</v>
-      </c>
-      <c r="F3964" s="6" t="s">
-        <v>7851</v>
       </c>
     </row>
     <row r="3965" spans="3:6">
       <c r="C3965" s="3">
-        <v>300110</v>
-      </c>
-      <c r="D3965"/>
+        <v>300090</v>
+      </c>
+      <c r="D3965" s="4"/>
       <c r="E3965" s="1" t="s">
+        <v>7851</v>
+      </c>
+      <c r="F3965" s="6" t="s">
         <v>7852</v>
-      </c>
-      <c r="F3965" s="1" t="s">
-        <v>7853</v>
       </c>
     </row>
     <row r="3966" spans="3:6">
       <c r="C3966" s="3">
-        <v>300111</v>
-      </c>
-      <c r="D3966"/>
+        <v>300091</v>
+      </c>
+      <c r="D3966" s="4"/>
       <c r="E3966" s="1" t="s">
+        <v>7853</v>
+      </c>
+      <c r="F3966" s="6" t="s">
         <v>7854</v>
-      </c>
-      <c r="F3966" s="1" t="s">
-        <v>7855</v>
       </c>
     </row>
     <row r="3967" spans="3:6">
       <c r="C3967" s="3">
-        <v>300112</v>
-      </c>
+        <v>300092</v>
+      </c>
+      <c r="D3967" s="4"/>
       <c r="E3967" s="1" t="s">
+        <v>7855</v>
+      </c>
+      <c r="F3967" s="6" t="s">
         <v>7856</v>
-      </c>
-      <c r="F3967" s="1" t="s">
-        <v>7857</v>
       </c>
     </row>
     <row r="3968" spans="3:6">
       <c r="C3968" s="3">
-        <v>300113</v>
-      </c>
+        <v>300093</v>
+      </c>
+      <c r="D3968" s="4"/>
       <c r="E3968" s="1" t="s">
+        <v>7857</v>
+      </c>
+      <c r="F3968" s="6" t="s">
         <v>7858</v>
-      </c>
-      <c r="F3968" s="1" t="s">
-        <v>7859</v>
       </c>
     </row>
     <row r="3969" spans="3:6">
       <c r="C3969" s="3">
-        <v>300114</v>
-      </c>
+        <v>300094</v>
+      </c>
+      <c r="D3969" s="4"/>
       <c r="E3969" s="1" t="s">
+        <v>7859</v>
+      </c>
+      <c r="F3969" s="6" t="s">
         <v>7860</v>
-      </c>
-      <c r="F3969" s="1" t="s">
-        <v>7861</v>
       </c>
     </row>
     <row r="3970" spans="3:6">
       <c r="C3970" s="3">
-        <v>300115</v>
-      </c>
+        <v>300095</v>
+      </c>
+      <c r="D3970" s="4"/>
       <c r="E3970" s="1" t="s">
+        <v>7861</v>
+      </c>
+      <c r="F3970" s="6" t="s">
         <v>7862</v>
-      </c>
-      <c r="F3970" s="1" t="s">
-        <v>7863</v>
       </c>
     </row>
     <row r="3971" spans="3:6">
       <c r="C3971" s="3">
-        <v>300116</v>
-      </c>
+        <v>300096</v>
+      </c>
+      <c r="D3971" s="4"/>
       <c r="E3971" s="1" t="s">
+        <v>7863</v>
+      </c>
+      <c r="F3971" s="6" t="s">
         <v>7864</v>
-      </c>
-      <c r="F3971" s="1" t="s">
-        <v>1734</v>
       </c>
     </row>
     <row r="3972" spans="3:6">
       <c r="C3972" s="3">
-        <v>300117</v>
-      </c>
+        <v>300097</v>
+      </c>
+      <c r="D3972" s="4"/>
       <c r="E3972" s="1" t="s">
-        <v>3182</v>
-      </c>
-      <c r="F3972" s="1" t="s">
         <v>7865</v>
+      </c>
+      <c r="F3972" s="6" t="s">
+        <v>7866</v>
       </c>
     </row>
     <row r="3973" spans="3:6">
       <c r="C3973" s="3">
-        <v>300118</v>
-      </c>
+        <v>300098</v>
+      </c>
+      <c r="D3973" s="4"/>
       <c r="E3973" s="1" t="s">
-        <v>7866</v>
-      </c>
-      <c r="F3973" s="1" t="s">
         <v>7867</v>
+      </c>
+      <c r="F3973" s="6" t="s">
+        <v>7868</v>
       </c>
     </row>
     <row r="3974" spans="3:6">
       <c r="C3974" s="3">
-        <v>300119</v>
-      </c>
+        <v>300099</v>
+      </c>
+      <c r="D3974" s="4"/>
       <c r="E3974" s="1" t="s">
-        <v>7868</v>
-      </c>
-      <c r="F3974" s="1" t="s">
         <v>7869</v>
+      </c>
+      <c r="F3974" s="6" t="s">
+        <v>7870</v>
       </c>
     </row>
     <row r="3975" spans="3:6">
       <c r="C3975" s="3">
-        <v>300120</v>
-      </c>
+        <v>300100</v>
+      </c>
+      <c r="D3975" s="4"/>
       <c r="E3975" s="1" t="s">
-        <v>7870</v>
-      </c>
-      <c r="F3975" s="1" t="s">
         <v>7871</v>
+      </c>
+      <c r="F3975" s="6" t="s">
+        <v>7872</v>
       </c>
     </row>
     <row r="3976" spans="3:6">
       <c r="C3976" s="3">
-        <v>300121</v>
-      </c>
+        <v>300101</v>
+      </c>
+      <c r="D3976" s="4"/>
       <c r="E3976" s="1" t="s">
-        <v>7872</v>
-      </c>
-      <c r="F3976" s="1" t="s">
         <v>7873</v>
+      </c>
+      <c r="F3976" s="6" t="s">
+        <v>7874</v>
       </c>
     </row>
     <row r="3977" spans="3:6">
       <c r="C3977" s="3">
-        <v>300122</v>
-      </c>
+        <v>300102</v>
+      </c>
+      <c r="D3977" s="4"/>
       <c r="E3977" s="1" t="s">
-        <v>7874</v>
-      </c>
-      <c r="F3977" s="1" t="s">
         <v>7875</v>
+      </c>
+      <c r="F3977" s="6" t="s">
+        <v>7876</v>
       </c>
     </row>
     <row r="3978" spans="3:6">
       <c r="C3978" s="3">
-        <v>300123</v>
-      </c>
+        <v>300103</v>
+      </c>
+      <c r="D3978" s="4"/>
       <c r="E3978" s="1" t="s">
-        <v>7876</v>
-      </c>
-      <c r="F3978" s="1" t="s">
-        <v>343</v>
+        <v>7877</v>
+      </c>
+      <c r="F3978" s="6" t="s">
+        <v>7878</v>
       </c>
     </row>
     <row r="3979" spans="3:6">
       <c r="C3979" s="3">
-        <v>300124</v>
-      </c>
+        <v>300104</v>
+      </c>
+      <c r="D3979" s="4"/>
       <c r="E3979" s="1" t="s">
-        <v>7877</v>
-      </c>
-      <c r="F3979" s="1" t="s">
-        <v>7878</v>
+        <v>7879</v>
+      </c>
+      <c r="F3979" s="6" t="s">
+        <v>7880</v>
       </c>
     </row>
     <row r="3980" spans="3:6">
       <c r="C3980" s="3">
-        <v>300125</v>
-      </c>
+        <v>300105</v>
+      </c>
+      <c r="D3980" s="4"/>
       <c r="E3980" s="1" t="s">
-        <v>7879</v>
-      </c>
-      <c r="F3980" s="1" t="s">
-        <v>7880</v>
+        <v>7881</v>
+      </c>
+      <c r="F3980" s="6" t="s">
+        <v>7882</v>
       </c>
     </row>
     <row r="3981" spans="3:6">
       <c r="C3981" s="3">
-        <v>300126</v>
-      </c>
+        <v>300106</v>
+      </c>
+      <c r="D3981" s="4"/>
       <c r="E3981" s="1" t="s">
-        <v>7881</v>
-      </c>
-      <c r="F3981" s="1" t="s">
-        <v>7882</v>
+        <v>7883</v>
+      </c>
+      <c r="F3981" s="6" t="s">
+        <v>7884</v>
       </c>
     </row>
     <row r="3982" spans="3:6">
       <c r="C3982" s="3">
-        <v>300127</v>
-      </c>
+        <v>300107</v>
+      </c>
+      <c r="D3982" s="4"/>
       <c r="E3982" s="1" t="s">
-        <v>7883</v>
-      </c>
-      <c r="F3982" s="1" t="s">
-        <v>7884</v>
+        <v>7885</v>
+      </c>
+      <c r="F3982" s="6" t="s">
+        <v>7886</v>
       </c>
     </row>
     <row r="3983" spans="3:6">
       <c r="C3983" s="3">
-        <v>300128</v>
-      </c>
+        <v>300108</v>
+      </c>
+      <c r="D3983" s="4"/>
       <c r="E3983" s="1" t="s">
-        <v>7885</v>
-      </c>
-      <c r="F3983" s="1" t="s">
-        <v>7886</v>
+        <v>7887</v>
+      </c>
+      <c r="F3983" s="6" t="s">
+        <v>7888</v>
       </c>
     </row>
     <row r="3984" spans="3:6">
       <c r="C3984" s="3">
-        <v>300129</v>
-      </c>
+        <v>300109</v>
+      </c>
+      <c r="D3984" s="4"/>
       <c r="E3984" s="1" t="s">
-        <v>7887</v>
-      </c>
-      <c r="F3984" s="1" t="s">
-        <v>7888</v>
-      </c>
-    </row>
-    <row r="3985" spans="2:6">
+        <v>7889</v>
+      </c>
+      <c r="F3984" s="6" t="s">
+        <v>7890</v>
+      </c>
+    </row>
+    <row r="3985" spans="3:6">
       <c r="C3985" s="3">
-        <v>300130</v>
-      </c>
+        <v>300110</v>
+      </c>
+      <c r="D3985"/>
       <c r="E3985" s="1" t="s">
-        <v>7889</v>
+        <v>7891</v>
       </c>
       <c r="F3985" s="1" t="s">
-        <v>7890</v>
-      </c>
-    </row>
-    <row r="3986" spans="2:6">
+        <v>7892</v>
+      </c>
+    </row>
+    <row r="3986" spans="3:6">
       <c r="C3986" s="3">
-        <v>300131</v>
-      </c>
+        <v>300111</v>
+      </c>
+      <c r="D3986"/>
       <c r="E3986" s="1" t="s">
-        <v>7891</v>
+        <v>7893</v>
       </c>
       <c r="F3986" s="1" t="s">
-        <v>7892</v>
-      </c>
-    </row>
-    <row r="3987" spans="2:6">
+        <v>7894</v>
+      </c>
+    </row>
+    <row r="3987" spans="3:6">
       <c r="C3987" s="3">
-        <v>300132</v>
+        <v>300112</v>
       </c>
       <c r="E3987" s="1" t="s">
-        <v>7893</v>
+        <v>7895</v>
       </c>
       <c r="F3987" s="1" t="s">
-        <v>7894</v>
-      </c>
-    </row>
-    <row r="3988" spans="2:6">
+        <v>7896</v>
+      </c>
+    </row>
+    <row r="3988" spans="3:6">
       <c r="C3988" s="3">
-        <v>300133</v>
+        <v>300113</v>
       </c>
       <c r="E3988" s="1" t="s">
-        <v>7895</v>
+        <v>7897</v>
       </c>
       <c r="F3988" s="1" t="s">
-        <v>7896</v>
-      </c>
-    </row>
-    <row r="3989" spans="2:6">
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="3989" spans="3:6">
       <c r="C3989" s="3">
-        <v>300134</v>
+        <v>300114</v>
       </c>
       <c r="E3989" s="1" t="s">
-        <v>7897</v>
+        <v>7899</v>
       </c>
       <c r="F3989" s="1" t="s">
-        <v>7898</v>
-      </c>
-    </row>
-    <row r="3990" spans="2:6">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="3990" spans="3:6">
       <c r="C3990" s="3">
-        <v>300135</v>
+        <v>300115</v>
       </c>
       <c r="E3990" s="1" t="s">
-        <v>7899</v>
+        <v>7901</v>
       </c>
       <c r="F3990" s="1" t="s">
-        <v>7900</v>
-      </c>
-    </row>
-    <row r="3991" spans="2:6">
-      <c r="B3991" s="3"/>
+        <v>7902</v>
+      </c>
+    </row>
+    <row r="3991" spans="3:6">
       <c r="C3991" s="3">
-        <v>300136</v>
+        <v>300116</v>
       </c>
       <c r="E3991" s="1" t="s">
-        <v>7901</v>
+        <v>7903</v>
       </c>
       <c r="F3991" s="1" t="s">
-        <v>7902</v>
-      </c>
-    </row>
-    <row r="3992" spans="2:6">
-      <c r="B3992" s="3"/>
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="3992" spans="3:6">
       <c r="C3992" s="3">
-        <v>300137</v>
+        <v>300117</v>
       </c>
       <c r="E3992" s="1" t="s">
-        <v>7903</v>
+        <v>3182</v>
       </c>
       <c r="F3992" s="1" t="s">
         <v>7904</v>
       </c>
     </row>
-    <row r="3993" spans="2:6">
-      <c r="B3993" s="3"/>
+    <row r="3993" spans="3:6">
       <c r="C3993" s="3">
-        <v>300138</v>
+        <v>300118</v>
       </c>
       <c r="E3993" s="1" t="s">
         <v>7905</v>
@@ -73214,10 +73348,9 @@
         <v>7906</v>
       </c>
     </row>
-    <row r="3994" spans="2:6">
-      <c r="B3994" s="3"/>
+    <row r="3994" spans="3:6">
       <c r="C3994" s="3">
-        <v>300139</v>
+        <v>300119</v>
       </c>
       <c r="E3994" s="1" t="s">
         <v>7907</v>
@@ -73226,10 +73359,9 @@
         <v>7908</v>
       </c>
     </row>
-    <row r="3995" spans="2:6">
-      <c r="B3995" s="3"/>
+    <row r="3995" spans="3:6">
       <c r="C3995" s="3">
-        <v>300140</v>
+        <v>300120</v>
       </c>
       <c r="E3995" s="1" t="s">
         <v>7909</v>
@@ -73238,10 +73370,9 @@
         <v>7910</v>
       </c>
     </row>
-    <row r="3996" spans="2:6">
-      <c r="B3996" s="3"/>
+    <row r="3996" spans="3:6">
       <c r="C3996" s="3">
-        <v>300141</v>
+        <v>300121</v>
       </c>
       <c r="E3996" s="1" t="s">
         <v>7911</v>
@@ -73250,10 +73381,9 @@
         <v>7912</v>
       </c>
     </row>
-    <row r="3997" spans="2:6">
-      <c r="B3997" s="3"/>
+    <row r="3997" spans="3:6">
       <c r="C3997" s="3">
-        <v>300142</v>
+        <v>300122</v>
       </c>
       <c r="E3997" s="1" t="s">
         <v>7913</v>
@@ -73262,94 +73392,86 @@
         <v>7914</v>
       </c>
     </row>
-    <row r="3998" spans="2:6">
-      <c r="B3998" s="3"/>
+    <row r="3998" spans="3:6">
       <c r="C3998" s="3">
-        <v>300143</v>
+        <v>300123</v>
       </c>
       <c r="E3998" s="1" t="s">
         <v>7915</v>
       </c>
       <c r="F3998" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3999" spans="3:6">
+      <c r="C3999" s="3">
+        <v>300124</v>
+      </c>
+      <c r="E3999" s="1" t="s">
         <v>7916</v>
       </c>
-    </row>
-    <row r="3999" spans="2:6">
-      <c r="B3999" s="3"/>
-      <c r="C3999" s="3">
-        <v>300144</v>
-      </c>
-      <c r="E3999" s="1" t="s">
+      <c r="F3999" s="1" t="s">
         <v>7917</v>
       </c>
-      <c r="F3999" s="1" t="s">
+    </row>
+    <row r="4000" spans="3:6">
+      <c r="C4000" s="3">
+        <v>300125</v>
+      </c>
+      <c r="E4000" s="1" t="s">
         <v>7918</v>
       </c>
-    </row>
-    <row r="4000" spans="2:6">
-      <c r="B4000" s="3"/>
-      <c r="C4000" s="3">
-        <v>300145</v>
-      </c>
-      <c r="E4000" s="1" t="s">
+      <c r="F4000" s="1" t="s">
         <v>7919</v>
       </c>
-      <c r="F4000" s="1" t="s">
+    </row>
+    <row r="4001" spans="2:6">
+      <c r="C4001" s="3">
+        <v>300126</v>
+      </c>
+      <c r="E4001" s="1" t="s">
         <v>7920</v>
       </c>
-    </row>
-    <row r="4001" spans="2:6">
-      <c r="B4001" s="3"/>
-      <c r="C4001" s="3">
-        <v>300146</v>
-      </c>
-      <c r="E4001" s="1" t="s">
+      <c r="F4001" s="1" t="s">
         <v>7921</v>
       </c>
-      <c r="F4001" s="1" t="s">
+    </row>
+    <row r="4002" spans="2:6">
+      <c r="C4002" s="3">
+        <v>300127</v>
+      </c>
+      <c r="E4002" s="1" t="s">
         <v>7922</v>
       </c>
-    </row>
-    <row r="4002" spans="2:6">
-      <c r="B4002" s="3"/>
-      <c r="C4002" s="3">
-        <v>300147</v>
-      </c>
-      <c r="E4002" s="1" t="s">
+      <c r="F4002" s="1" t="s">
         <v>7923</v>
       </c>
-      <c r="F4002" s="1" t="s">
+    </row>
+    <row r="4003" spans="2:6">
+      <c r="C4003" s="3">
+        <v>300128</v>
+      </c>
+      <c r="E4003" s="1" t="s">
         <v>7924</v>
       </c>
-    </row>
-    <row r="4003" spans="2:6">
-      <c r="B4003" s="3"/>
-      <c r="C4003" s="3">
-        <v>300148</v>
-      </c>
-      <c r="E4003" s="1" t="s">
+      <c r="F4003" s="1" t="s">
         <v>7925</v>
       </c>
-      <c r="F4003" s="1" t="s">
+    </row>
+    <row r="4004" spans="2:6">
+      <c r="C4004" s="3">
+        <v>300129</v>
+      </c>
+      <c r="E4004" s="1" t="s">
         <v>7926</v>
-      </c>
-    </row>
-    <row r="4004" spans="2:6">
-      <c r="B4004" s="3"/>
-      <c r="C4004" s="3">
-        <v>300149</v>
-      </c>
-      <c r="E4004" s="1" t="s">
-        <v>2906</v>
       </c>
       <c r="F4004" s="1" t="s">
         <v>7927</v>
       </c>
     </row>
     <row r="4005" spans="2:6">
-      <c r="B4005" s="3"/>
       <c r="C4005" s="3">
-        <v>300150</v>
+        <v>300130</v>
       </c>
       <c r="E4005" s="1" t="s">
         <v>7928</v>
@@ -73359,9 +73481,8 @@
       </c>
     </row>
     <row r="4006" spans="2:6">
-      <c r="B4006" s="3"/>
       <c r="C4006" s="3">
-        <v>300151</v>
+        <v>300131</v>
       </c>
       <c r="E4006" s="1" t="s">
         <v>7930</v>
@@ -73371,9 +73492,8 @@
       </c>
     </row>
     <row r="4007" spans="2:6">
-      <c r="B4007" s="3"/>
       <c r="C4007" s="3">
-        <v>300152</v>
+        <v>300132</v>
       </c>
       <c r="E4007" s="1" t="s">
         <v>7932</v>
@@ -73384,7 +73504,7 @@
     </row>
     <row r="4008" spans="2:6">
       <c r="C4008" s="3">
-        <v>300153</v>
+        <v>300133</v>
       </c>
       <c r="E4008" s="1" t="s">
         <v>7934</v>
@@ -73395,7 +73515,7 @@
     </row>
     <row r="4009" spans="2:6">
       <c r="C4009" s="3">
-        <v>300154</v>
+        <v>300134</v>
       </c>
       <c r="E4009" s="1" t="s">
         <v>7936</v>
@@ -73406,7 +73526,7 @@
     </row>
     <row r="4010" spans="2:6">
       <c r="C4010" s="3">
-        <v>300155</v>
+        <v>300135</v>
       </c>
       <c r="E4010" s="1" t="s">
         <v>7938</v>
@@ -73416,8 +73536,9 @@
       </c>
     </row>
     <row r="4011" spans="2:6">
+      <c r="B4011" s="3"/>
       <c r="C4011" s="3">
-        <v>300156</v>
+        <v>300136</v>
       </c>
       <c r="E4011" s="1" t="s">
         <v>7940</v>
@@ -73427,8 +73548,9 @@
       </c>
     </row>
     <row r="4012" spans="2:6">
+      <c r="B4012" s="3"/>
       <c r="C4012" s="3">
-        <v>300157</v>
+        <v>300137</v>
       </c>
       <c r="E4012" s="1" t="s">
         <v>7942</v>
@@ -73438,8 +73560,9 @@
       </c>
     </row>
     <row r="4013" spans="2:6">
+      <c r="B4013" s="3"/>
       <c r="C4013" s="3">
-        <v>300158</v>
+        <v>300138</v>
       </c>
       <c r="E4013" s="1" t="s">
         <v>7944</v>
@@ -73449,8 +73572,9 @@
       </c>
     </row>
     <row r="4014" spans="2:6">
+      <c r="B4014" s="3"/>
       <c r="C4014" s="3">
-        <v>300159</v>
+        <v>300139</v>
       </c>
       <c r="E4014" s="1" t="s">
         <v>7946</v>
@@ -73460,8 +73584,9 @@
       </c>
     </row>
     <row r="4015" spans="2:6">
+      <c r="B4015" s="3"/>
       <c r="C4015" s="3">
-        <v>300160</v>
+        <v>300140</v>
       </c>
       <c r="E4015" s="1" t="s">
         <v>7948</v>
@@ -73471,8 +73596,9 @@
       </c>
     </row>
     <row r="4016" spans="2:6">
+      <c r="B4016" s="3"/>
       <c r="C4016" s="3">
-        <v>300161</v>
+        <v>300141</v>
       </c>
       <c r="E4016" s="1" t="s">
         <v>7950</v>
@@ -73481,9 +73607,10 @@
         <v>7951</v>
       </c>
     </row>
-    <row r="4017" spans="3:6">
+    <row r="4017" spans="2:6">
+      <c r="B4017" s="3"/>
       <c r="C4017" s="3">
-        <v>300162</v>
+        <v>300142</v>
       </c>
       <c r="E4017" s="1" t="s">
         <v>7952</v>
@@ -73492,9 +73619,10 @@
         <v>7953</v>
       </c>
     </row>
-    <row r="4018" spans="3:6">
+    <row r="4018" spans="2:6">
+      <c r="B4018" s="3"/>
       <c r="C4018" s="3">
-        <v>300163</v>
+        <v>300143</v>
       </c>
       <c r="E4018" s="1" t="s">
         <v>7954</v>
@@ -73503,9 +73631,10 @@
         <v>7955</v>
       </c>
     </row>
-    <row r="4019" spans="3:6">
+    <row r="4019" spans="2:6">
+      <c r="B4019" s="3"/>
       <c r="C4019" s="3">
-        <v>300164</v>
+        <v>300144</v>
       </c>
       <c r="E4019" s="1" t="s">
         <v>7956</v>
@@ -73514,9 +73643,10 @@
         <v>7957</v>
       </c>
     </row>
-    <row r="4020" spans="3:6">
+    <row r="4020" spans="2:6">
+      <c r="B4020" s="3"/>
       <c r="C4020" s="3">
-        <v>300165</v>
+        <v>300145</v>
       </c>
       <c r="E4020" s="1" t="s">
         <v>7958</v>
@@ -73525,378 +73655,605 @@
         <v>7959</v>
       </c>
     </row>
-    <row r="4021" spans="3:6">
+    <row r="4021" spans="2:6">
+      <c r="B4021" s="3"/>
       <c r="C4021" s="3">
-        <v>300166</v>
+        <v>300146</v>
       </c>
       <c r="E4021" s="1" t="s">
-        <v>1068</v>
+        <v>7960</v>
       </c>
       <c r="F4021" s="1" t="s">
-        <v>7960</v>
-      </c>
-    </row>
-    <row r="4022" spans="3:6">
+        <v>7961</v>
+      </c>
+    </row>
+    <row r="4022" spans="2:6">
+      <c r="B4022" s="3"/>
       <c r="C4022" s="3">
-        <v>300167</v>
+        <v>300147</v>
       </c>
       <c r="E4022" s="1" t="s">
-        <v>1070</v>
+        <v>7962</v>
       </c>
       <c r="F4022" s="1" t="s">
-        <v>7961</v>
-      </c>
-    </row>
-    <row r="4023" spans="3:6">
+        <v>7963</v>
+      </c>
+    </row>
+    <row r="4023" spans="2:6">
+      <c r="B4023" s="3"/>
       <c r="C4023" s="3">
-        <v>300168</v>
+        <v>300148</v>
       </c>
       <c r="E4023" s="1" t="s">
-        <v>1072</v>
+        <v>7964</v>
       </c>
       <c r="F4023" s="1" t="s">
-        <v>7962</v>
-      </c>
-    </row>
-    <row r="4024" spans="3:6">
+        <v>7965</v>
+      </c>
+    </row>
+    <row r="4024" spans="2:6">
+      <c r="B4024" s="3"/>
       <c r="C4024" s="3">
-        <v>300169</v>
+        <v>300149</v>
       </c>
       <c r="E4024" s="1" t="s">
-        <v>1074</v>
+        <v>2906</v>
       </c>
       <c r="F4024" s="1" t="s">
-        <v>7963</v>
-      </c>
-    </row>
-    <row r="4025" spans="3:6">
+        <v>7966</v>
+      </c>
+    </row>
+    <row r="4025" spans="2:6">
+      <c r="B4025" s="3"/>
       <c r="C4025" s="3">
-        <v>300170</v>
+        <v>300150</v>
       </c>
       <c r="E4025" s="1" t="s">
-        <v>7964</v>
+        <v>7967</v>
       </c>
       <c r="F4025" s="1" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="4026" spans="3:6">
+        <v>7968</v>
+      </c>
+    </row>
+    <row r="4026" spans="2:6">
+      <c r="B4026" s="3"/>
       <c r="C4026" s="3">
-        <v>300171</v>
+        <v>300151</v>
       </c>
       <c r="E4026" s="1" t="s">
-        <v>7965</v>
+        <v>7969</v>
       </c>
       <c r="F4026" s="1" t="s">
-        <v>7966</v>
-      </c>
-    </row>
-    <row r="4027" spans="3:6">
+        <v>7970</v>
+      </c>
+    </row>
+    <row r="4027" spans="2:6">
+      <c r="B4027" s="3"/>
       <c r="C4027" s="3">
-        <v>300172</v>
+        <v>300152</v>
       </c>
       <c r="E4027" s="1" t="s">
-        <v>7967</v>
+        <v>7971</v>
       </c>
       <c r="F4027" s="1" t="s">
-        <v>7968</v>
-      </c>
-    </row>
-    <row r="4028" spans="3:6">
+        <v>7972</v>
+      </c>
+    </row>
+    <row r="4028" spans="2:6">
       <c r="C4028" s="3">
-        <v>300173</v>
+        <v>300153</v>
       </c>
       <c r="E4028" s="1" t="s">
-        <v>7969</v>
+        <v>7973</v>
       </c>
       <c r="F4028" s="1" t="s">
-        <v>7970</v>
-      </c>
-    </row>
-    <row r="4029" spans="3:6">
+        <v>7974</v>
+      </c>
+    </row>
+    <row r="4029" spans="2:6">
       <c r="C4029" s="3">
-        <v>300174</v>
+        <v>300154</v>
       </c>
       <c r="E4029" s="1" t="s">
-        <v>7971</v>
+        <v>7975</v>
       </c>
       <c r="F4029" s="1" t="s">
-        <v>7972</v>
-      </c>
-    </row>
-    <row r="4030" spans="3:6">
+        <v>7976</v>
+      </c>
+    </row>
+    <row r="4030" spans="2:6">
       <c r="C4030" s="3">
-        <v>300175</v>
+        <v>300155</v>
       </c>
       <c r="E4030" s="1" t="s">
-        <v>7973</v>
+        <v>7977</v>
       </c>
       <c r="F4030" s="1" t="s">
-        <v>7974</v>
-      </c>
-    </row>
-    <row r="4031" spans="3:6">
+        <v>7978</v>
+      </c>
+    </row>
+    <row r="4031" spans="2:6">
       <c r="C4031" s="3">
-        <v>300176</v>
+        <v>300156</v>
       </c>
       <c r="E4031" s="1" t="s">
-        <v>7975</v>
+        <v>7979</v>
       </c>
       <c r="F4031" s="1" t="s">
-        <v>7976</v>
-      </c>
-    </row>
-    <row r="4032" spans="3:6">
+        <v>7980</v>
+      </c>
+    </row>
+    <row r="4032" spans="2:6">
       <c r="C4032" s="3">
-        <v>300177</v>
+        <v>300157</v>
       </c>
       <c r="E4032" s="1" t="s">
-        <v>7977</v>
+        <v>7981</v>
       </c>
       <c r="F4032" s="1" t="s">
-        <v>2357</v>
+        <v>7982</v>
       </c>
     </row>
     <row r="4033" spans="3:6">
       <c r="C4033" s="3">
-        <v>300178</v>
+        <v>300158</v>
       </c>
       <c r="E4033" s="1" t="s">
-        <v>7978</v>
+        <v>7983</v>
       </c>
       <c r="F4033" s="1" t="s">
-        <v>7979</v>
+        <v>7984</v>
       </c>
     </row>
     <row r="4034" spans="3:6">
       <c r="C4034" s="3">
-        <v>300179</v>
+        <v>300159</v>
       </c>
       <c r="E4034" s="1" t="s">
-        <v>7980</v>
+        <v>7985</v>
       </c>
       <c r="F4034" s="1" t="s">
-        <v>678</v>
+        <v>7986</v>
       </c>
     </row>
     <row r="4035" spans="3:6">
       <c r="C4035" s="3">
-        <v>300180</v>
+        <v>300160</v>
       </c>
       <c r="E4035" s="1" t="s">
-        <v>7981</v>
+        <v>7987</v>
       </c>
       <c r="F4035" s="1" t="s">
-        <v>7982</v>
+        <v>7988</v>
       </c>
     </row>
     <row r="4036" spans="3:6">
       <c r="C4036" s="3">
-        <v>300181</v>
+        <v>300161</v>
       </c>
       <c r="E4036" s="1" t="s">
-        <v>7983</v>
+        <v>7989</v>
       </c>
       <c r="F4036" s="1" t="s">
-        <v>7984</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="4037" spans="3:6">
       <c r="C4037" s="3">
-        <v>300182</v>
+        <v>300162</v>
       </c>
       <c r="E4037" s="1" t="s">
-        <v>7985</v>
+        <v>7991</v>
       </c>
       <c r="F4037" s="1" t="s">
-        <v>7986</v>
+        <v>7992</v>
       </c>
     </row>
     <row r="4038" spans="3:6">
       <c r="C4038" s="3">
-        <v>300183</v>
+        <v>300163</v>
       </c>
       <c r="E4038" s="1" t="s">
-        <v>7987</v>
+        <v>7993</v>
       </c>
       <c r="F4038" s="1" t="s">
-        <v>7988</v>
+        <v>7994</v>
       </c>
     </row>
     <row r="4039" spans="3:6">
       <c r="C4039" s="3">
-        <v>300184</v>
+        <v>300164</v>
       </c>
       <c r="E4039" s="1" t="s">
-        <v>4328</v>
+        <v>7995</v>
       </c>
       <c r="F4039" s="1" t="s">
-        <v>718</v>
+        <v>7996</v>
       </c>
     </row>
     <row r="4040" spans="3:6">
       <c r="C4040" s="3">
-        <v>300185</v>
+        <v>300165</v>
       </c>
       <c r="E4040" s="1" t="s">
-        <v>7989</v>
+        <v>7997</v>
       </c>
       <c r="F4040" s="1" t="s">
-        <v>7990</v>
+        <v>7998</v>
       </c>
     </row>
     <row r="4041" spans="3:6">
       <c r="C4041" s="3">
-        <v>300186</v>
+        <v>300166</v>
       </c>
       <c r="E4041" s="1" t="s">
-        <v>7991</v>
+        <v>1068</v>
       </c>
       <c r="F4041" s="1" t="s">
-        <v>718</v>
+        <v>7999</v>
       </c>
     </row>
     <row r="4042" spans="3:6">
       <c r="C4042" s="3">
-        <v>300187</v>
+        <v>300167</v>
       </c>
       <c r="E4042" s="1" t="s">
-        <v>7992</v>
+        <v>1070</v>
       </c>
       <c r="F4042" s="1" t="s">
-        <v>7993</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="4043" spans="3:6">
       <c r="C4043" s="3">
-        <v>300188</v>
+        <v>300168</v>
       </c>
       <c r="E4043" s="1" t="s">
-        <v>7994</v>
+        <v>1072</v>
       </c>
       <c r="F4043" s="1" t="s">
-        <v>7995</v>
+        <v>8001</v>
       </c>
     </row>
     <row r="4044" spans="3:6">
       <c r="C4044" s="3">
-        <v>300189</v>
+        <v>300169</v>
       </c>
       <c r="E4044" s="1" t="s">
-        <v>7996</v>
+        <v>1074</v>
       </c>
       <c r="F4044" s="1" t="s">
-        <v>7997</v>
+        <v>8002</v>
       </c>
     </row>
     <row r="4045" spans="3:6">
       <c r="C4045" s="3">
-        <v>300190</v>
+        <v>300170</v>
       </c>
       <c r="E4045" s="1" t="s">
-        <v>7998</v>
+        <v>8003</v>
       </c>
       <c r="F4045" s="1" t="s">
-        <v>7999</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="4046" spans="3:6">
       <c r="C4046" s="3">
-        <v>300191</v>
+        <v>300171</v>
       </c>
       <c r="E4046" s="1" t="s">
-        <v>8000</v>
+        <v>8004</v>
       </c>
       <c r="F4046" s="1" t="s">
-        <v>8001</v>
+        <v>8005</v>
       </c>
     </row>
     <row r="4047" spans="3:6">
       <c r="C4047" s="3">
-        <v>300192</v>
+        <v>300172</v>
       </c>
       <c r="E4047" s="1" t="s">
-        <v>8002</v>
+        <v>8006</v>
       </c>
       <c r="F4047" s="1" t="s">
-        <v>8003</v>
+        <v>8007</v>
       </c>
     </row>
     <row r="4048" spans="3:6">
       <c r="C4048" s="3">
-        <v>300193</v>
+        <v>300173</v>
       </c>
       <c r="E4048" s="1" t="s">
-        <v>8004</v>
+        <v>8008</v>
       </c>
       <c r="F4048" s="1" t="s">
-        <v>8005</v>
+        <v>8009</v>
       </c>
     </row>
     <row r="4049" spans="3:6">
       <c r="C4049" s="3">
-        <v>300194</v>
+        <v>300174</v>
       </c>
       <c r="E4049" s="1" t="s">
-        <v>8006</v>
+        <v>8010</v>
       </c>
       <c r="F4049" s="1" t="s">
-        <v>8007</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="4050" spans="3:6">
       <c r="C4050" s="3">
-        <v>300195</v>
+        <v>300175</v>
       </c>
       <c r="E4050" s="1" t="s">
-        <v>8008</v>
+        <v>8012</v>
       </c>
       <c r="F4050" s="1" t="s">
-        <v>8009</v>
+        <v>8013</v>
       </c>
     </row>
     <row r="4051" spans="3:6">
       <c r="C4051" s="3">
-        <v>300196</v>
+        <v>300176</v>
       </c>
       <c r="E4051" s="1" t="s">
-        <v>8010</v>
+        <v>8014</v>
       </c>
       <c r="F4051" s="1" t="s">
-        <v>8011</v>
+        <v>8015</v>
       </c>
     </row>
     <row r="4052" spans="3:6">
       <c r="C4052" s="3">
-        <v>300197</v>
+        <v>300177</v>
       </c>
       <c r="E4052" s="1" t="s">
-        <v>8012</v>
+        <v>8016</v>
       </c>
       <c r="F4052" s="1" t="s">
-        <v>8013</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="4053" spans="3:6">
       <c r="C4053" s="3">
-        <v>300198</v>
+        <v>300178</v>
       </c>
       <c r="E4053" s="1" t="s">
-        <v>8014</v>
+        <v>8017</v>
       </c>
       <c r="F4053" s="1" t="s">
-        <v>8015</v>
+        <v>8018</v>
       </c>
     </row>
     <row r="4054" spans="3:6">
       <c r="C4054" s="3">
+        <v>300179</v>
+      </c>
+      <c r="E4054" s="1" t="s">
+        <v>8019</v>
+      </c>
+      <c r="F4054" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="4055" spans="3:6">
+      <c r="C4055" s="3">
+        <v>300180</v>
+      </c>
+      <c r="E4055" s="1" t="s">
+        <v>8020</v>
+      </c>
+      <c r="F4055" s="1" t="s">
+        <v>8021</v>
+      </c>
+    </row>
+    <row r="4056" spans="3:6">
+      <c r="C4056" s="3">
+        <v>300181</v>
+      </c>
+      <c r="E4056" s="1" t="s">
+        <v>8022</v>
+      </c>
+      <c r="F4056" s="1" t="s">
+        <v>8023</v>
+      </c>
+    </row>
+    <row r="4057" spans="3:6">
+      <c r="C4057" s="3">
+        <v>300182</v>
+      </c>
+      <c r="E4057" s="1" t="s">
+        <v>8024</v>
+      </c>
+      <c r="F4057" s="1" t="s">
+        <v>8025</v>
+      </c>
+    </row>
+    <row r="4058" spans="3:6">
+      <c r="C4058" s="3">
+        <v>300183</v>
+      </c>
+      <c r="E4058" s="1" t="s">
+        <v>8026</v>
+      </c>
+      <c r="F4058" s="1" t="s">
+        <v>8027</v>
+      </c>
+    </row>
+    <row r="4059" spans="3:6">
+      <c r="C4059" s="3">
+        <v>300184</v>
+      </c>
+      <c r="E4059" s="1" t="s">
+        <v>4328</v>
+      </c>
+      <c r="F4059" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="4060" spans="3:6">
+      <c r="C4060" s="3">
+        <v>300185</v>
+      </c>
+      <c r="E4060" s="1" t="s">
+        <v>8028</v>
+      </c>
+      <c r="F4060" s="1" t="s">
+        <v>8029</v>
+      </c>
+    </row>
+    <row r="4061" spans="3:6">
+      <c r="C4061" s="3">
+        <v>300186</v>
+      </c>
+      <c r="E4061" s="1" t="s">
+        <v>8030</v>
+      </c>
+      <c r="F4061" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="4062" spans="3:6">
+      <c r="C4062" s="3">
+        <v>300187</v>
+      </c>
+      <c r="E4062" s="1" t="s">
+        <v>8031</v>
+      </c>
+      <c r="F4062" s="1" t="s">
+        <v>8032</v>
+      </c>
+    </row>
+    <row r="4063" spans="3:6">
+      <c r="C4063" s="3">
+        <v>300188</v>
+      </c>
+      <c r="E4063" s="1" t="s">
+        <v>8033</v>
+      </c>
+      <c r="F4063" s="1" t="s">
+        <v>8034</v>
+      </c>
+    </row>
+    <row r="4064" spans="3:6">
+      <c r="C4064" s="3">
+        <v>300189</v>
+      </c>
+      <c r="E4064" s="1" t="s">
+        <v>8035</v>
+      </c>
+      <c r="F4064" s="1" t="s">
+        <v>8036</v>
+      </c>
+    </row>
+    <row r="4065" spans="3:6">
+      <c r="C4065" s="3">
+        <v>300190</v>
+      </c>
+      <c r="E4065" s="1" t="s">
+        <v>8037</v>
+      </c>
+      <c r="F4065" s="1" t="s">
+        <v>8038</v>
+      </c>
+    </row>
+    <row r="4066" spans="3:6">
+      <c r="C4066" s="3">
+        <v>300191</v>
+      </c>
+      <c r="E4066" s="1" t="s">
+        <v>8039</v>
+      </c>
+      <c r="F4066" s="1" t="s">
+        <v>8040</v>
+      </c>
+    </row>
+    <row r="4067" spans="3:6">
+      <c r="C4067" s="3">
+        <v>300192</v>
+      </c>
+      <c r="E4067" s="1" t="s">
+        <v>8041</v>
+      </c>
+      <c r="F4067" s="1" t="s">
+        <v>8042</v>
+      </c>
+    </row>
+    <row r="4068" spans="3:6">
+      <c r="C4068" s="3">
+        <v>300193</v>
+      </c>
+      <c r="E4068" s="1" t="s">
+        <v>8043</v>
+      </c>
+      <c r="F4068" s="1" t="s">
+        <v>8044</v>
+      </c>
+    </row>
+    <row r="4069" spans="3:6">
+      <c r="C4069" s="3">
+        <v>300194</v>
+      </c>
+      <c r="E4069" s="1" t="s">
+        <v>8045</v>
+      </c>
+      <c r="F4069" s="1" t="s">
+        <v>8046</v>
+      </c>
+    </row>
+    <row r="4070" spans="3:6">
+      <c r="C4070" s="3">
+        <v>300195</v>
+      </c>
+      <c r="E4070" s="1" t="s">
+        <v>8047</v>
+      </c>
+      <c r="F4070" s="1" t="s">
+        <v>8048</v>
+      </c>
+    </row>
+    <row r="4071" spans="3:6">
+      <c r="C4071" s="3">
+        <v>300196</v>
+      </c>
+      <c r="E4071" s="1" t="s">
+        <v>8049</v>
+      </c>
+      <c r="F4071" s="1" t="s">
+        <v>8050</v>
+      </c>
+    </row>
+    <row r="4072" spans="3:6">
+      <c r="C4072" s="3">
+        <v>300197</v>
+      </c>
+      <c r="E4072" s="1" t="s">
+        <v>8051</v>
+      </c>
+      <c r="F4072" s="1" t="s">
+        <v>8052</v>
+      </c>
+    </row>
+    <row r="4073" spans="3:6">
+      <c r="C4073" s="3">
+        <v>300198</v>
+      </c>
+      <c r="E4073" s="1" t="s">
+        <v>8053</v>
+      </c>
+      <c r="F4073" s="1" t="s">
+        <v>8054</v>
+      </c>
+    </row>
+    <row r="4074" spans="3:6">
+      <c r="C4074" s="3">
         <v>300199</v>
       </c>
-      <c r="E4054" s="1" t="s">
-        <v>8016</v>
-      </c>
-      <c r="F4054" s="1" t="s">
-        <v>8017</v>
+      <c r="E4074" s="1" t="s">
+        <v>8055</v>
+      </c>
+      <c r="F4074" s="1" t="s">
+        <v>8056</v>
       </c>
     </row>
   </sheetData>
